--- a/DF_RankScoreFM.xlsx
+++ b/DF_RankScoreFM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="248">
   <si>
     <t>FM_Bancos</t>
   </si>
@@ -67,163 +67,166 @@
     <t>AMER3</t>
   </si>
   <si>
-    <t>LIGT3</t>
-  </si>
-  <si>
     <t>PRIO3</t>
   </si>
   <si>
     <t>VBBR3</t>
   </si>
   <si>
+    <t>BBSE3</t>
+  </si>
+  <si>
+    <t>VULC3</t>
+  </si>
+  <si>
     <t>MRFG3</t>
   </si>
   <si>
-    <t>BBSE3</t>
-  </si>
-  <si>
     <t>CMIG4</t>
   </si>
   <si>
+    <t>TAEE11</t>
+  </si>
+  <si>
+    <t>JHSF3</t>
+  </si>
+  <si>
+    <t>SAPR11</t>
+  </si>
+  <si>
+    <t>SBSP3</t>
+  </si>
+  <si>
+    <t>PETR4</t>
+  </si>
+  <si>
+    <t>PETR3</t>
+  </si>
+  <si>
     <t>TEND3</t>
   </si>
   <si>
-    <t>VULC3</t>
+    <t>TTEN3</t>
+  </si>
+  <si>
+    <t>CPFE3</t>
+  </si>
+  <si>
+    <t>POMO4</t>
+  </si>
+  <si>
+    <t>MDNE3</t>
   </si>
   <si>
     <t>PLPL3</t>
   </si>
   <si>
-    <t>SAPR11</t>
-  </si>
-  <si>
-    <t>JHSF3</t>
-  </si>
-  <si>
-    <t>SBSP3</t>
-  </si>
-  <si>
-    <t>TAEE11</t>
-  </si>
-  <si>
-    <t>PETR4</t>
-  </si>
-  <si>
-    <t>PETR3</t>
-  </si>
-  <si>
-    <t>GRND3</t>
-  </si>
-  <si>
-    <t>POMO4</t>
-  </si>
-  <si>
-    <t>TTEN3</t>
-  </si>
-  <si>
-    <t>CPFE3</t>
-  </si>
-  <si>
-    <t>MDNE3</t>
+    <t>ENGI11</t>
   </si>
   <si>
     <t>ISAE4</t>
   </si>
   <si>
-    <t>ENGI11</t>
+    <t>CXSE3</t>
+  </si>
+  <si>
+    <t>ECOR3</t>
+  </si>
+  <si>
+    <t>RECV3</t>
+  </si>
+  <si>
+    <t>ITUB3</t>
+  </si>
+  <si>
+    <t>CYRE3</t>
   </si>
   <si>
     <t>UNIP6</t>
   </si>
   <si>
-    <t>ECOR3</t>
-  </si>
-  <si>
-    <t>CXSE3</t>
-  </si>
-  <si>
-    <t>CYRE3</t>
-  </si>
-  <si>
-    <t>RECV3</t>
-  </si>
-  <si>
-    <t>ITUB3</t>
-  </si>
-  <si>
     <t>UGPA3</t>
   </si>
   <si>
     <t>VIVA3</t>
   </si>
   <si>
+    <t>BRAV3</t>
+  </si>
+  <si>
+    <t>CURY3</t>
+  </si>
+  <si>
+    <t>ITSA4</t>
+  </si>
+  <si>
+    <t>ITUB4</t>
+  </si>
+  <si>
+    <t>SUZB3</t>
+  </si>
+  <si>
+    <t>DIRR3</t>
+  </si>
+  <si>
+    <t>BRFS3</t>
+  </si>
+  <si>
+    <t>EGIE3</t>
+  </si>
+  <si>
     <t>ODPV3</t>
   </si>
   <si>
-    <t>EGIE3</t>
-  </si>
-  <si>
-    <t>CURY3</t>
-  </si>
-  <si>
-    <t>BRAV3</t>
-  </si>
-  <si>
-    <t>DIRR3</t>
-  </si>
-  <si>
-    <t>BRFS3</t>
-  </si>
-  <si>
     <t>BRAP4</t>
   </si>
   <si>
-    <t>ITSA4</t>
-  </si>
-  <si>
-    <t>ITUB4</t>
+    <t>PORT3</t>
+  </si>
+  <si>
+    <t>PSSA3</t>
   </si>
   <si>
     <t>STBP3</t>
   </si>
   <si>
-    <t>PORT3</t>
-  </si>
-  <si>
-    <t>SUZB3</t>
+    <t>IRBR3</t>
+  </si>
+  <si>
+    <t>MULT3</t>
   </si>
   <si>
     <t>SBFG3</t>
   </si>
   <si>
-    <t>PSSA3</t>
-  </si>
-  <si>
-    <t>MULT3</t>
+    <t>KLBN11</t>
+  </si>
+  <si>
+    <t>BBDC3</t>
   </si>
   <si>
     <t>CSMG3</t>
   </si>
   <si>
-    <t>IRBR3</t>
-  </si>
-  <si>
-    <t>KLBN11</t>
-  </si>
-  <si>
-    <t>BBDC3</t>
-  </si>
-  <si>
     <t>COGN3</t>
   </si>
   <si>
+    <t>CMIN3</t>
+  </si>
+  <si>
+    <t>BRSR6</t>
+  </si>
+  <si>
     <t>BBAS3</t>
   </si>
   <si>
-    <t>BRSR6</t>
-  </si>
-  <si>
-    <t>CMIN3</t>
+    <t>VALE3</t>
+  </si>
+  <si>
+    <t>INTB3</t>
+  </si>
+  <si>
+    <t>B3SA3</t>
   </si>
   <si>
     <t>NEOE3</t>
@@ -232,15 +235,6 @@
     <t>EZTC3</t>
   </si>
   <si>
-    <t>INTB3</t>
-  </si>
-  <si>
-    <t>B3SA3</t>
-  </si>
-  <si>
-    <t>VALE3</t>
-  </si>
-  <si>
     <t>BBDC4</t>
   </si>
   <si>
@@ -250,51 +244,45 @@
     <t>CEAB3</t>
   </si>
   <si>
+    <t>ALUP11</t>
+  </si>
+  <si>
     <t>BPAC11</t>
   </si>
   <si>
-    <t>ALUP11</t>
+    <t>GMAT3</t>
+  </si>
+  <si>
+    <t>AZZA3</t>
+  </si>
+  <si>
+    <t>SLCE3</t>
+  </si>
+  <si>
+    <t>SANB11</t>
+  </si>
+  <si>
+    <t>ABEV3</t>
+  </si>
+  <si>
+    <t>LREN3</t>
+  </si>
+  <si>
+    <t>ASAI3</t>
   </si>
   <si>
     <t>MOVI3</t>
   </si>
   <si>
-    <t>GMAT3</t>
-  </si>
-  <si>
-    <t>MYPK3</t>
-  </si>
-  <si>
-    <t>SANB11</t>
-  </si>
-  <si>
-    <t>TFCO4</t>
-  </si>
-  <si>
-    <t>SLCE3</t>
-  </si>
-  <si>
-    <t>ABEV3</t>
-  </si>
-  <si>
-    <t>AZZA3</t>
-  </si>
-  <si>
-    <t>ASAI3</t>
+    <t>GOAU4</t>
+  </si>
+  <si>
+    <t>EQTL3</t>
   </si>
   <si>
     <t>CPLE3</t>
   </si>
   <si>
-    <t>EQTL3</t>
-  </si>
-  <si>
-    <t>LREN3</t>
-  </si>
-  <si>
-    <t>GOAU4</t>
-  </si>
-  <si>
     <t>MOTV3</t>
   </si>
   <si>
@@ -307,25 +295,22 @@
     <t>RADL3</t>
   </si>
   <si>
-    <t>CASH3</t>
+    <t>GGBR4</t>
   </si>
   <si>
     <t>RDOR3</t>
   </si>
   <si>
+    <t>TOTS3</t>
+  </si>
+  <si>
+    <t>YDUQ3</t>
+  </si>
+  <si>
     <t>ANIM3</t>
   </si>
   <si>
-    <t>TOTS3</t>
-  </si>
-  <si>
-    <t>FRAS3</t>
-  </si>
-  <si>
-    <t>GGBR4</t>
-  </si>
-  <si>
-    <t>YDUQ3</t>
+    <t>SMTO3</t>
   </si>
   <si>
     <t>IGTI11</t>
@@ -337,60 +322,54 @@
     <t>RAPT4</t>
   </si>
   <si>
-    <t>SMTO3</t>
-  </si>
-  <si>
     <t>VAMO3</t>
   </si>
   <si>
+    <t>EMBR3</t>
+  </si>
+  <si>
     <t>RENT3</t>
   </si>
   <si>
+    <t>MDIA3</t>
+  </si>
+  <si>
     <t>CBAV3</t>
   </si>
   <si>
-    <t>EMBR3</t>
-  </si>
-  <si>
-    <t>MDIA3</t>
-  </si>
-  <si>
     <t>TIMS3</t>
   </si>
   <si>
     <t>VIVT3</t>
   </si>
   <si>
+    <t>NATU3</t>
+  </si>
+  <si>
     <t>ELET3</t>
   </si>
   <si>
-    <t>NATU3</t>
+    <t>SMFT3</t>
   </si>
   <si>
     <t>ELET6</t>
   </si>
   <si>
-    <t>SMFT3</t>
-  </si>
-  <si>
     <t>USIM5</t>
   </si>
   <si>
+    <t>HYPE3</t>
+  </si>
+  <si>
+    <t>ALOS3</t>
+  </si>
+  <si>
+    <t>ALPA4</t>
+  </si>
+  <si>
     <t>MGLU3</t>
   </si>
   <si>
-    <t>HYPE3</t>
-  </si>
-  <si>
-    <t>ALOS3</t>
-  </si>
-  <si>
-    <t>ALPA4</t>
-  </si>
-  <si>
-    <t>BPAN4</t>
-  </si>
-  <si>
     <t>RAIL3</t>
   </si>
   <si>
@@ -400,12 +379,12 @@
     <t>LWSA3</t>
   </si>
   <si>
+    <t>ORVR3</t>
+  </si>
+  <si>
     <t>SRNA3</t>
   </si>
   <si>
-    <t>ORVR3</t>
-  </si>
-  <si>
     <t>AURA33</t>
   </si>
   <si>
@@ -424,9 +403,6 @@
     <t>CSNA3</t>
   </si>
   <si>
-    <t>NTCO3</t>
-  </si>
-  <si>
     <t>ENEV3</t>
   </si>
   <si>
@@ -448,157 +424,160 @@
     <t>Americanas S.A. operates in the e-commerce business in Brazil. It offers e-commerce digital platform for various digital solutions. The company operates Americanas.com, an online store with various products; Submarino, a digital brand in books, games, technology, and entertainment; Shoptime, an online brand in books, games, technology, and entertainment; Ame, a platform for financial and non-financial products and services; and Puket, an online clothing platform; MinD, an online design and home decoration platform. In addition, it provides imaginarium, a multi-brand e-commerce channels; Lovebrands, an online platform that offers various products and services; Skoob, a virtual library platform, as well as operates a retail chain of fruits and vegetables under Hortifruti Natural da Terra brand. Americanas S.A. was founded in 1999 and is headquartered in Rio de Janeiro, Brazil.</t>
   </si>
   <si>
-    <t>Light S.A., together with its subsidiaries, engages in the generation, transmission, distribution, and sale of electric power in Brazil. The company distributes electricity in the state of Rio de Janeiro. It also engages in the research, planning, building, operation, and exploration of generation and transmission systems; purchase, sale, import, and export of electric and thermal power, and gas and industrial utilities; provision of consulting services in the energy sector; lease of real estate and personal properties; acquisition and sale of goods related to the studies and projects; implementation, operation, and maintenance of construction works and facilities; and hydropower generation activities. In addition, the company provides services to low voltage clients, including the assembly, renovation, and maintenance of facilities. Further, it offers technology solutions and systems for the operating management of utility concessionaires; and builds, installs, operates, and explores electric power plants. The company primarily serves residential, commercial, and industrial customers. Light S.A. was founded in 1899 and is headquartered in Rio De Janeiro, Brazil.</t>
-  </si>
-  <si>
     <t>Prio S.A., together with its subsidiaries, engages in the exploration, development, and production of oil and natural gas properties in Brazil and internationally. It holds a 100% interest in the Polvo Field covering an area of approximately 134 square kilometers located in the southern portion of the Campos Basin, Rio de Janeiro; and the Frade Field that consists of approximately 154 square kilometers located in the northern region of the Campos Basin, Rio de Janeiro. The company also holds interest in the Albacora leste Field and the Wahoo and Itaipu Field located in the Camumu Basin, State of Bahia. In addition, it imports, exports, refines, sells, and distributes oil, natural gas, fuels, and oil by-products; and engages in the generation, sale, and distribution of electric power, as well as holds interests in other companies. The company was formerly known as Petro Rio S.A. and changed its name to Prio S.A. in May 2023. Prio S.A. was incorporated in 2009 and is headquartered in Rio de Janeiro, Brazil.</t>
   </si>
   <si>
     <t>Vibra Energia S.A. manufactures, processes, distributes, trades in, transports, imports, and exports oil-based products, lubricants, and other fuels. The company also produces, distributes, trades in, and transports various energy forms and chemical products. It operates in Retail and B2B segments. The company markets its oil products, lubricants, compressed natural gas, biofuels, and convenience store products. It also markets oil-based fuels and lubricants and provides associated services to its consumer's market, as well as markets aviation products and services at Brazil's airport facilities. The company was incorporated in 1971 and is based in Rio de Janeiro, Brazil.</t>
   </si>
   <si>
+    <t>BB Seguridade Participações S.A., through its subsidiaries operates in the insurance, pension plans, and bonds, businesses in Brazil. The company operates through two segments Security and Brokerage. The Security segment offers life, rural, special risks and financial, transport, hulls, and housing people insurance products. It also offers pension plans, dental, and capitalization plans. The Brokerage segment engages in the brokerage, management, and promotion of pension plans, capitalization, capitalization, and dental plans. BB Seguridade Participações S.A. was incorporated in 2012 and is headquartered in Brasília, Brazil. BB Seguridade Participações S.A. is a subsidiary of Banco do Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Vulcabras S.A., through its subsidiaries, operates as a footwear company in Brazil and internationally. The company offers sports-oriented clothing, footwear, and accessories; and safety boots for hospital workers, mining companies, steelmakers, agribusiness, civil construction, and other sectors. It offers its products through e-commerce and brand-owned stores. The company markets its products under the Mizuno, Olympikus, UNDER ARMOUR, and Botas Vulcabras brand names. The company was founded in 1952 and is headquartered in Jundiaí, Brazil. Vulcabras S.A. operates as a subsidiary of Gianpega Negócios e Participações S.A.</t>
+  </si>
+  <si>
     <t>Marfrig Global Foods S.A., through its subsidiaries, operates in the food industry in Brazil and internationally. It operates through Beef  North America; Beef  South America; and Poultry, Pork and Processed Products  BRF segments. The company produces, processes, distributes, and sells animal-based proteins, such as beef, pork, lamb, fish, and poultry; pastas, margarine, pet food, and plant-based proteins; hamburgers; and various ready-to-eat products, including frozen vegetables, lamb, fish, and sauces. It also engages in leather processing; processing and marketing of beef and lamb; trading activities; transportation; transportation leasing; energy generation, trading, and related services; processing and sale of milk derivatives; processing, sale, distribution, and retail of animal feed and nutrition products; road freight; asset management; veterinary services; and real estate activities; as well as produces canned meat and other processed products. In addition, the company provides administrative and marketing services; logistics services; consulting services. It imports, sells, and exports its products to restaurant and supermarket chains, and homes. The company was formerly known as Marfrig Alimentos S.A. and changed its name to Marfrig Global Foods S.A. in January 2014. Marfrig Global Foods S.A. was founded in 1986 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
-    <t>BB Seguridade Participações S.A., through its subsidiaries operates in the insurance, pension plans, and bonds, businesses in Brazil. The company operates through two segments Security and Brokerage. The Security segment offers life, rural, special risks and financial, transport, hulls, and housing people insurance products. It also offers pension plans, dental, and capitalization plans. The Brokerage segment engages in the brokerage, management, and promotion of pension plans, capitalization, capitalization, and dental plans. BB Seguridade Participações S.A. was incorporated in 2012 and is headquartered in Brasília, Brazil. BB Seguridade Participações S.A. is a subsidiary of Banco do Brasil S.A.</t>
-  </si>
-  <si>
     <t>Companhia Energética de Minas Gerais - CEMIG, through its subsidiaries, engages in the generation, transmission, distribution, and sale of energy in Brazil. As of December 31, 2024, the company operated 36 hydro plants with a total capacity of 4,449.0 MW, 2 wind farms with a total capacity of 70.8 MW, and 10 photovoltaic power stations with a total capacity of 158.99 MW; 357,044 miles of distribution lines; and 4,754 miles of transmission lines. It is also involved in the acquisition, transportation, and distribution of gas and its sub products and derivatives; sale and trading of energy; construction, implementation, operation and maintenance of electricity transmission; marketing and intermediation of energy-related business; installation, operation, maintenance and rental of solar plants; and distributed generation, account services, cogeneration, energy efficiency, and supply and storage management activities. The company was incorporated in 1952 and is headquartered in Belo Horizonte, Brazil.</t>
   </si>
   <si>
+    <t>Transmissora Aliança de Energia Elétrica S.A., together with its subsidiaries, engages in the implementation, operation, and maintenance of electric power transmission lines in Brazil. It operates approximately a total length of 15,1550 kilometers (km) of transmission lines, which include 14,420 km of transmission lines in operation and 735 km of lines under construction; 110 substations with voltage between 69 and 525kV; and one system operation center located in Rio de Janeiro. The company was founded in 2000 is headquartered in Rio de Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>JHSF Participações S.A., through its subsidiaries, engages in the real estate development business. The company operates through Recurring Income, Real Estate Business, Airport, and Hotels and Restaurants segments. It also engages in construction and operation of shopping malls; purchase and sale of residential and commercial properties, as well as goods; leasing of commercial real estate; operation of hotel, gastronomy, and tourism activities; rental of houses and club; and operation and management of the airfield, as well as rendering of administration services. The company operates through JHSF, Fazenda Boa Vista, Cidade Jardim Mall, Catarina Fashion Outlet, and Fasano brands. The company was founded in 1972 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Companhia de Saneamento do Paraná - SANEPAR provides sanitation services in Brazil. The company engages in water distribution; collection and treatment of sewage and solid waste; study, project, and construction work of facilities; expansion of water distribution; and collection and treatment of sewage networks. It also offers advisory and technical assistance services in its areas of activity. It serves federal, state, municipal agencies, and other entities. The company was founded in 1963 and is headquartered in Curitiba, Brazil.</t>
+  </si>
+  <si>
+    <t>Companhia de Saneamento Básico do Estado de São Paulo - SABESP provides basic and environmental sanitation services in the São Paulo State, Brazil. The company supplies treated water and sewage services on a wholesale basis. As of December 31, 2024, it provided water services through 9.5 million water connections; and sewage services through 8.2 million sewage connections in 375 municipalities of the São Paulo State. The company was founded in 1954 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Petróleo Brasileiro S.A. - Petrobras explores, produces, and sells oil and gas in Brazil and internationally. It operates through three segments: Exploration and Production; Refining, Transportation &amp; Marketing; and Gas &amp; Low Carbon Energies. The Exploration and Production segment explores, develops, and produces crude oil, natural gas liquids, and natural gas primarily for supplies to the domestic refineries. The Refining, Transportation and Marketing segment engages in the refining, logistics, transport, acquisition, and export of crude oil; trading of oil products; and production of fertilizers, as well as holding interests in petrochemical companies. The Gas and Low Carbon Energies segment is involved in the logistic and trading of natural gas and electricity; transportation and trading of liquefied natural gas; generation of electricity through thermoelectric power plants; renewable energy business; low carbon business; and natural gas processing business, as well as production of biodiesel and its co-products. The company also engages in prospecting, drilling, refining, processing, trading, and transporting crude oil from producing onshore and offshore oil fields, and shale or other rocks, as well as oil products, natural gas, and other liquid hydrocarbons. In addition, it engages in the research, development, production, transportation, distribution, and trading of energy. The company was incorporated in 1953 and is headquartered in Rio de Janeiro, Brazil.</t>
+  </si>
+  <si>
     <t>Construtora Tenda S.A. operates as a construction company in Brazil. The company engages in the construction works, real estate development, real estate purchase and sale, the provision of general construction management services, and the intermediation of the sale of consortium shares. It also holds interests in other companies. Construtora Tenda S.A. was founded in 1969 is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
-    <t>Vulcabras S.A., through its subsidiaries, operates as a footwear company in Brazil and internationally. The company offers sports-oriented clothing, footwear, and accessories; and safety boots for hospital workers, mining companies, steelmakers, agribusiness, civil construction, and other sectors. It offers its products through e-commerce and brand-owned stores. The company markets its products under the Mizuno, Olympikus, UNDER ARMOUR, and Botas Vulcabras brand names. The company was founded in 1952 and is headquartered in Jundiaí, Brazil. Vulcabras S.A. operates as a subsidiary of Gianpega Negócios e Participações S.A.</t>
+    <t>Três Tentos Agroindustrial S/A, together with its subsidiaries, operates in the agribusiness sector in Brazil. It operates in three segments: Agricultural Inputs; Soybean, Corn and Wheat Grains; and Industry. The company markets foliar fertilizers, plant-protection products, and seeds for soybean, corn, and wheat; and processes soybean to produce meal for animal feed and biodiesel. It is also involved in the receipt, standardization, and trading of grain from third parties. In addition, the company provides technical assistance, such as consulting services in administration, crop management, and crop technology; and digital solutions. Further, it is involved in sales promotion; insurance brokerage, supplementary pension plans, and health plans; credit services, such as credit card and financing services to rural producers; and trading of agricultural commodities. The company exports to Saudi Arabia, Australia, Bangladesh, Chile, China, Colombia, South Korea, Denmark, Spain, Guatemala, Netherlands, Virgin Islands, Indonesia, Italy, Japan, Morocco, Singapore, Switzerland, Thailand, Uruguay, Venezuela, and Vietnam. Três Tentos Agroindustrial S/A was founded in 1954 and is headquartered in Santa Bárbara do Sul, Brazil.</t>
+  </si>
+  <si>
+    <t>CPFL Energia S.A., through its subsidiaries, engages in the electric power business in Brazil. It operates through Generation, Distribution, Transmission, Commercialization, and Services segments. The company generates electricity through hydro, wind, biomass, and solar sources; and distributes its products to residential, industrial, and commercial customers under the  CPFL Paulista, CPFL Piratininga, CPFL Santa Cruz, and RGE brands. It also engages in the marketing business; and provides various services, including energy management and consultancy, purchase and trade of electricity, energy infrastructure and services, decarbonization, distributed generation, energy efficiency, maintenance of electrical installations, and renovation of transformer and electrical equipment. The company was founded in 1912 and is headquartered in Campinas, Brazil. CPFL Energia S.A. operates as a subsidiary of State Grid Brazil Power Participações S.A.</t>
+  </si>
+  <si>
+    <t>Marcopolo S.A. engages in manufacture and sale of bus bodies in Brazil, Africa, Argentina, Australia, China, the United Arab Emirates, and Mexico. It operates through Industrial and Financial segments. The company offers buses and micro buses; multiple units with different propulsion, passenger cars, and boxes for people movers, TRAMs, and EMUs; and parts and components. It also provides mobility systems and services; credit solutions for purchase of buses and minibuses; and advance payment services. In addition, the company is involved in wholesale trade of motor vehicle parts and accessories; assembling, import, export, and sale of refrigeration and air conditioning equipment; and the provision of technical services regarding foreign trade, as well as banking activities. The company was founded in 1949 and is headquartered in Caxias Do Sul, Brazil.</t>
+  </si>
+  <si>
+    <t>Moura Dubeux Engenharia S.A. provides real estate development services in Brazil. It engages in the purchase and sale of properties; rental and split of land allotment; real estate construction of properties; and management and administration of own or third parties real properties. The company develops flats, hotels, resorts, and residential buildings; and offers technical construction management and advisory services to the condominiums, as well as engineering services. Moura Dubeux Engenharia S.A. was founded in 1983 and is based in Recife, Brazil.</t>
   </si>
   <si>
     <t>Plano &amp; Plano Desenvolvimento Imobiliário S.A., through its subsidiaries develops, constructs, and sells real estate projects in the São Paulo Metropolitan Region. The company was founded in 1997 and is based in São Paulo, Brazil.</t>
   </si>
   <si>
-    <t>Companhia de Saneamento do Paraná - SANEPAR provides sanitation services in Brazil. The company engages in water distribution; collection and treatment of sewage and solid waste; study, project, and construction work of facilities; expansion of water distribution; and collection and treatment of sewage networks. It also offers advisory and technical assistance services in its areas of activity. It serves federal, state, municipal agencies, and other entities. The company was founded in 1963 and is headquartered in Curitiba, Brazil.</t>
-  </si>
-  <si>
-    <t>JHSF Participações S.A., through its subsidiaries, engages in the real estate development business. The company operates through Recurring Income, Real Estate Business, Airport, and Hotels and Restaurants segments. It also engages in construction and operation of shopping malls; purchase and sale of residential and commercial properties, as well as goods; leasing of commercial real estate; operation of hotel, gastronomy, and tourism activities; rental of houses and club; and operation and management of the airfield, as well as rendering of administration services. The company operates through JHSF, Fazenda Boa Vista, Cidade Jardim Mall, Catarina Fashion Outlet, and Fasano brands. The company was founded in 1972 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Companhia de Saneamento Básico do Estado de São Paulo - SABESP provides basic and environmental sanitation services in the São Paulo State, Brazil. The company supplies treated water and sewage services on a wholesale basis. As of December 31, 2024, it provided water services through 9.5 million water connections; and sewage services through 8.2 million sewage connections in 375 municipalities of the São Paulo State. The company was founded in 1954 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Transmissora Aliança de Energia Elétrica S.A., together with its subsidiaries, engages in the implementation, operation, and maintenance of electric power transmission lines in Brazil. It operates approximately a total length of 15,1550 kilometers (km) of transmission lines, which include 14,420 km of transmission lines in operation and 735 km of lines under construction; 110 substations with voltage between 69 and 525kV; and one system operation center located in Rio de Janeiro. The company was founded in 2000 is headquartered in Rio de Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Petróleo Brasileiro S.A. - Petrobras explores, produces, and sells oil and gas in Brazil and internationally. It operates through three segments: Exploration and Production; Refining, Transportation &amp; Marketing; and Gas &amp; Low Carbon Energies. The Exploration and Production segment explores, develops, and produces crude oil, natural gas liquids, and natural gas primarily for supplies to the domestic refineries. The Refining, Transportation and Marketing segment engages in the refining, logistics, transport, acquisition, and export of crude oil; trading of oil products; and production of fertilizers, as well as holding interests in petrochemical companies. The Gas and Low Carbon Energies segment is involved in the logistic and trading of natural gas and electricity; transportation and trading of liquefied natural gas; generation of electricity through thermoelectric power plants; renewable energy business; low carbon business; and natural gas processing business, as well as production of biodiesel and its co-products. The company also engages in prospecting, drilling, refining, processing, trading, and transporting crude oil from producing onshore and offshore oil fields, and shale or other rocks, as well as oil products, natural gas, and other liquid hydrocarbons. In addition, it engages in the research, development, production, transportation, distribution, and trading of energy. The company was incorporated in 1953 and is headquartered in Rio de Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Grendene S.A., together with its subsidiaries, engages in the development, production, distribution, and sale of footwear for women, men, and children in Brazil and internationally. The company sells its products through its stores, franchised stores, and web commerce channels, as well as through commercial representatives and distributors under the Melissa, Grendha, Rider, Cartago, Ipanema, Zaxy, Pega Forte, Grendene Kids, Nuar, Lump and Stably, Lello, and Zizou brand names. It also licenses the use of celebrity personalities and characters in the children's media. The company also exports its products in North America, Asia and Oceania, Europe, Central and South America, the Middle East, and Africa. Grendene S.A. was founded in 1971 and is headquartered in Sobral, Brazil.</t>
-  </si>
-  <si>
-    <t>Marcopolo S.A. engages in manufacture and sale of bus bodies in Brazil, Africa, Argentina, Australia, China, the United Arab Emirates, and Mexico. It operates through Industrial and Financial segments. The company offers buses and micro buses; multiple units with different propulsion, passenger cars, and boxes for people movers, TRAMs, and EMUs; and parts and components. It also provides mobility systems and services; credit solutions for purchase of buses and minibuses; and advance payment services. In addition, the company is involved in wholesale trade of motor vehicle parts and accessories; assembling, import, export, and sale of refrigeration and air conditioning equipment; and the provision of technical services regarding foreign trade, as well as banking activities. The company was founded in 1949 and is headquartered in Caxias Do Sul, Brazil.</t>
-  </si>
-  <si>
-    <t>Três Tentos Agroindustrial S/A, together with its subsidiaries, operates in the agribusiness sector in Brazil. It operates in three segments: Agricultural Inputs; Soybean, Corn and Wheat Grains; and Industry. The company markets foliar fertilizers, plant-protection products, and seeds for soybean, corn, and wheat; and processes soybean to produce meal for animal feed and biodiesel. It is also involved in the receipt, standardization, and trading of grain from third parties. In addition, the company provides technical assistance, such as consulting services in administration, crop management, and crop technology; and digital solutions. Further, it is involved in sales promotion; insurance brokerage, supplementary pension plans, and health plans; credit services, such as credit card and financing services to rural producers; and trading of agricultural commodities. The company exports to Saudi Arabia, Australia, Bangladesh, Chile, China, Colombia, South Korea, Denmark, Spain, Guatemala, Netherlands, Virgin Islands, Indonesia, Italy, Japan, Morocco, Singapore, Switzerland, Thailand, Uruguay, Venezuela, and Vietnam. Três Tentos Agroindustrial S/A was founded in 1954 and is headquartered in Santa Bárbara do Sul, Brazil.</t>
-  </si>
-  <si>
-    <t>CPFL Energia S.A., through its subsidiaries, engages in the electric power business in Brazil. It operates through Generation, Distribution, Transmission, Commercialization, and Services segments. The company generates electricity through hydro, wind, biomass, and solar sources; and distributes its products to residential, industrial, and commercial customers under the  CPFL Paulista, CPFL Piratininga, CPFL Santa Cruz, and RGE brands. It also engages in the marketing business; and provides various services, including energy management and consultancy, purchase and trade of electricity, energy infrastructure and services, decarbonization, distributed generation, energy efficiency, maintenance of electrical installations, and renovation of transformer and electrical equipment. The company was founded in 1912 and is headquartered in Campinas, Brazil. CPFL Energia S.A. operates as a subsidiary of State Grid Brazil Power Participações S.A.</t>
-  </si>
-  <si>
-    <t>Moura Dubeux Engenharia S.A. provides real estate development services in Brazil. It engages in the purchase and sale of properties; rental and split of land allotment; real estate construction of properties; and management and administration of own or third parties real properties. The company develops flats, hotels, resorts, and residential buildings; and offers technical construction management and advisory services to the condominiums, as well as engineering services. Moura Dubeux Engenharia S.A. was founded in 1983 and is based in Recife, Brazil.</t>
+    <t>Energisa S.A., through its subsidiaries, engages in the distribution, transmission, and generation of electricity in Brazil. The company generates electricity through hydraulic, solar, and wind projects. It also provides operating and maintenance services related to electricity distribution, generation, transmission, commission, preparation, and remote and local operations; and offers electrical and mechanical maintenance of plants, substations, transmission lines, and facilities. In addition, the company provides construction, operation, maintenance, and services related to electricity generation, transmission, and distribution; tele-services and personal services for electricity consumers; and aerial surveying services for supporting companies operating high-voltage lines, oil pipelines, and reforestation engineering works. Further, it is involved in the production, marketing, and distribution of natural gas; treatment of industrial organic waste for the production of biofertilizer; development of computer systems and programs, licensing of non-customizable software, intermediation and brokerage of services and business, and business management consulting and provision of insurance brokerage, payment systems optimization, securitization of credits, and financial products and services. The company serves customers in residential, industrial, and commercial markets. It serves approximately 20 million consumers in the Brazilian states. The company was founded in 1905 and is headquartered in Cataguases, Brazil. Energisa S.A. operates as a subsidiary of Gipar S.A.</t>
   </si>
   <si>
     <t>ISA Energía Brasil S.A engages in the electric transmission business in Brazil. As of December 31, 2023, it had a total installed transformation capacity of 85,000 MVA together with transmission lines of 23, 0000 kilometers; 32, 0000 kilometers of circuits; and 137 substations. It operates in the states of Alagoas, Bahia, Espírito Santo, Goiás, Maranhão, Mato Grosso, Mato Grosso do Sul, Minas Gerais, Paraíba, Paraná, Pernambuco, Piauí, Rio Grande do Sul, Rondônia, Santa Catarina, São Paulo, and Tocantins. ISA Energía Brasil S.A was founded in 1999 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
-    <t>Energisa S.A., through its subsidiaries, engages in the distribution, transmission, and generation of electricity in Brazil. The company generates electricity through hydraulic, solar, and wind projects. It also provides operating and maintenance services related to electricity distribution, generation, transmission, commission, preparation, and remote and local operations; and offers electrical and mechanical maintenance of plants, substations, transmission lines, and facilities. In addition, the company provides construction, operation, maintenance, and services related to electricity generation, transmission, and distribution; tele-services and personal services for electricity consumers; and aerial surveying services for supporting companies operating high-voltage lines, oil pipelines, and reforestation engineering works. Further, it is involved in the production, marketing, and distribution of natural gas; treatment of industrial organic waste for the production of biofertilizer; development of computer systems and programs, licensing of non-customizable software, intermediation and brokerage of services and business, and business management consulting and provision of insurance brokerage, payment systems optimization, securitization of credits, and financial products and services. The company serves customers in residential, industrial, and commercial markets. It serves approximately 20 million consumers in the Brazilian states. The company was founded in 1905 and is headquartered in Cataguases, Brazil. Energisa S.A. operates as a subsidiary of Gipar S.A.</t>
+    <t>Caixa Seguridade Participações S.A. provides various life and non-life insurance products in Brazil. It offers health plans and insurance; dental and assistance insurance; open private pension, premium bonds, and credit letters; capitalization products; and Consortia, basic and life, housing and residential, auto, credit life, and personal and damage insurance products. The company also engages in insurance brokerage business; and provision of intermediation services for assistance services, technical advice in general, and advisory and consultancy services in the insurance field, as well as holds equity interests. The company was incorporated in 2015 and is based in Brasília, Brazil. Caixa Seguridade Participações S.A. is a subsidiary of Caixa Econômica Federal.</t>
+  </si>
+  <si>
+    <t>EcoRodovias Infraestrutura e Logística S.A. operates as an infrastructure company that operates highway concessions in Brazil. It operates Ecopátio Logística Cubatão, an intermodal logistics platform, which is the regulating site for trucks at the Port of Santos. The company is also involved in the port operations and handling and storage of import and export cargo at the Port of Santos. In addition, it offers empty container storage, special export customs clearance, and general warehousing services. The company was founded in 1997 and is based in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Petroreconcavo S.A. engages in the exploration and production of oil and natural gas in Brazil. The company was founded in 1999 and is headquartered in Mata De Sao Joao, Brazil.</t>
+  </si>
+  <si>
+    <t>Itaú Unibanco Holding S.A. provides various financial products and services to personal and corporate customers in Brazil and internationally. It operates through three segments: Retail Banking, Wholesale Banking, and Activities with the Market + Corporation. The company offers current account; loans; credit and debit cards; investment and commercial banking services; real estate lending and financing services; economic, financial and brokerage advisory; and leasing and foreign exchange services. The company also provides non-life insurance products covering loss, damage, or liability for objects or people, as well as life insurance products covering death and personal accidents. It serves retail customers, account and non-account holders, individuals and legal entities, high income clients, microenterprises, and small companies, as well as middle-market companies and high net worth institutional clients. The company was formerly known as Itaú Unibanco Banco Múltiplo S.A. and changed its name to Itaú Unibanco Holding S.A. in April 2009. The company was incorporated in 1924 and is headquartered in São Paulo, Brazil. Itaú Unibanco Holding S.A. is a subsidiary of IUPAR - Itaú Unibanco Participações S.A.</t>
+  </si>
+  <si>
+    <t>Cyrela Brazil Realty S.A. Empreendimentos e Participações develops and constructs residential properties in Brazil. It also provides real estate services, such as construction management and technical consultancy services. The company was founded in 1962 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
     <t>Unipar Carbocloro S.A. produces and sells chlorine and caustic soda in South America. The company offers liquid caustic soda, sodium hypochlorite, dicloroetano, hydrochloric acid, and polyvinyl chloride. Its products are used in textile, pulp and paper, food, beverage, medicine, and construction industries. Unipar Carbocloro S.A. was incorporated in 1969 and is based in São Paulo, Brazil. Unipar Carbocloro S.A. operates as a subsidiary of Vila Velha S.A. Administração e Participações.</t>
   </si>
   <si>
-    <t>EcoRodovias Infraestrutura e Logística S.A. operates as an infrastructure company that operates highway concessions in Brazil. It operates Ecopátio Logística Cubatão, an intermodal logistics platform, which is the regulating site for trucks at the Port of Santos. The company is also involved in the port operations and handling and storage of import and export cargo at the Port of Santos. In addition, it offers empty container storage, special export customs clearance, and general warehousing services. The company was founded in 1997 and is based in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Caixa Seguridade Participações S.A. provides various life and non-life insurance products in Brazil. It offers health plans and insurance; dental and assistance insurance; open private pension, premium bonds, and credit letters; capitalization products; and Consortia, basic and life, housing and residential, auto, credit life, and personal and damage insurance products. The company also engages in insurance brokerage business; and provision of intermediation services for assistance services, technical advice in general, and advisory and consultancy services in the insurance field, as well as holds equity interests. The company was incorporated in 2015 and is based in Brasília, Brazil. Caixa Seguridade Participações S.A. is a subsidiary of Caixa Econômica Federal.</t>
-  </si>
-  <si>
-    <t>Cyrela Brazil Realty S.A. Empreendimentos e Participações develops and constructs residential properties in Brazil. It also provides real estate services, such as construction management and technical consultancy services. The company was founded in 1962 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Petroreconcavo S.A. engages in the exploration and production of oil and natural gas in Brazil. The company was founded in 1999 and is headquartered in Mata De Sao Joao, Brazil.</t>
-  </si>
-  <si>
-    <t>Itaú Unibanco Holding S.A. provides various financial products and services to personal and corporate customers in Brazil and internationally. It operates through three segments: Retail Banking, Wholesale Banking, and Activities with the Market + Corporation. The company offers current account; loans; credit and debit cards; investment and commercial banking services; real estate lending and financing services; economic, financial and brokerage advisory; and leasing and foreign exchange services. The company also provides non-life insurance products covering loss, damage, or liability for objects or people, as well as life insurance products covering death and personal accidents. It serves retail customers, account and non-account holders, individuals and legal entities, high income clients, microenterprises, and small companies, as well as middle-market companies and high net worth institutional clients. The company was formerly known as Itaú Unibanco Banco Múltiplo S.A. and changed its name to Itaú Unibanco Holding S.A. in April 2009. The company was incorporated in 1924 and is headquartered in São Paulo, Brazil. Itaú Unibanco Holding S.A. is a subsidiary of IUPAR - Itaú Unibanco Participações S.A.</t>
-  </si>
-  <si>
     <t>Ultrapar Participações S.A., through its subsidiaries, operates in the energy and infrastructure business in Brazil. The company distributes liquefied petroleum gas to residential, commercial, and industrial consumers. In addition, the company is involved in the distribution and marketing of gasoline, ethanol, diesel, fuel oil, kerosene, natural gas for vehicles, and lubricants; and holds AmPm convenience stores and provides Jet Oil lubricant services. Further, it operates liquid bulk storage terminals. Additionally, the company offers digital payments services, combining the abastece aí app and the loyalty program Km de Vantagens. It also exports its products and services to customers in Europe, the United States, Canada, other Latin American countries, Asia, and internationally. The company was founded in 1937 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
     <t>Vivara Participações S.A. engages in the manufacture and sale of jewelry and other articles in Latin America. It offers jewelry products, including rings, necklaces, alliances and solitaires, earrings, chains, pendants, and bracelets. The company provides various accessories, such as cufflinks, pens, sunglasses, watch and passport holders, notebooks, wallets, bags and backpacks, perfumes, and jewelry cases, pocket knives, travel items, keychains, and watch bands, as well as clocks, gifts, and gift cards. It offers its products through stores and kiosks, as well as through online. Vivara Participações S.A. was founded in 1962 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
+    <t>Brava Energia S.A. engages in the exploration and production of oil and natural gas in Brazil. The company was formerly known as 3R Petroleum Óleo e Gás S.A. and changed its name to Brava Energia S.A. in September 2024. The company was founded in 2010 and is headquartered in Rio De Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>Cury Construtora e Incorporadora S.A. operates in real estate businesses. The company provides real estate agency and brokerage services. It also offers financing services. In addition, the company is involved in credit analysis and online brokerage activities. Cury Construtora e Incorporadora S.A. was founded in 1963 and is based in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Itaúsa S.A., through its subsidiaries, operates in the financial and industrial markets in Brazil and internationally. The company offers credit products and other financial services to individuals and corporate clients. It also engages in the operation of highway concessions, urban mobility, and airports, as well as the transportation of gas through gas pipelines to distribution companies. In addition, it manufactures and sells bathroom fixtures, fittings, and showers; ceramic tiles, including floor and wall coatings under the Ceusa, Portinari, and Castelatto brands; pine and eucalyptus wood panels primarily used in the manufacture of medium- and high-density wood panels under the Duratex and Durafloor brand; and footwear, apparel, textiles, and related components, as well as leather, resin, and natural and artificial rubber. Further, it provides sanitation services. The company was formerly known as Itaúsa - Investimentos Itaú SA. Itaúsa S.A. was incorporated in 1966 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Suzano S.A. manufactures and sells pulp and paper products in Brazil and internationally. It operates in two segments, Pulp, and Paper and Consumer Goods. The company offers coated and uncoated printing and writing papers, paperboards, tissue papers, and market and fluff pulps. It also engages in the research, development, and production of biofuel; operation of port terminals; biotechnology and nanocrystalline pulps research and development activities; power generation and distribution business; road freight transport activities; commercialization of equipment and parts; research and development of lignin; industrialization and commercialization of cellulose, microfiber cellulose, paper, and paperboard products; industrialization, commercialization, and exporting of pulp products; and commercialization of paper and computer materials. In addition, the company is involved in the business office, corporate venture capital, and financial fundraising activities; production of consumer goods through cellulose-based liquids; development and production of cellulose-based fibers, yarns, and textile filaments; restoration, conservation, and preservation of forests; and research of raw materials for the textile industry. The company was formerly known as Suzano Papel e Celulose S.A. and changed its name to Suzano S.A. in April 2019. The company was founded in 1924 and is headquartered in Salvador, Brazil.</t>
+  </si>
+  <si>
+    <t>Direcional Engenharia S.A. engages in the development and construction of real estate properties in Brazil. It primarily develops and builds projects for low-income and middle-income families. The company was incorporated in 1981 and is based in Belo Horizonte, Brazil.</t>
+  </si>
+  <si>
+    <t>BRF S.A. raises, produces, and slaughters poultry and pork for processing, production, and sale of fresh meat, processed products, pasta, margarine, pet food, and other products. The company offers frozen whole and cut chicken, frozen pork, and turkey, and halal products for Islamic markets; processed foods, such as marinated, frozen, seasoned whole, and cut chicken, roosters, sausages, ham products, bologna, frankfurters, salamis, bacons, cold meats, and other smoked products; hamburgers, steaks, breaded meat products, kibbeh, and meatballs; and chicken sausages, hot dogs, and chicken bologna. It produces and sells lasagna, macaroni and cheese, pies, ready-to-eat meals, pizzas, and other frozen foods; nuggets, pies, vegetables, and burgers; frozen desserts and cheese bread; margarine, butter, cream cheese, sweet specialties, sandwiches, and pate, as well as soy meal, refined soy flour, animal feed, pet food and hatcheries. The company sells its products under the Sadia, Perdigão, Qualy, Sadia Halal, Chester, BRF Ingredients, Kidelli, Perdix, Borella, Hilal, Balance, Onefoods, Banvit, Deline, Sadia Bio, Sadia Salamitos, Sadia Veg&amp;Tal, Sadia Livre&amp;Lev, Confidence and Hilal, Sadia Hot Pocket, Perdigão Ouro, Chester Perdigão, Perdigão NaBrasa, Claybom, Biofresh, Three Dogs, Three Cats, Guabi Natural, Giran Plus, Balance, PrimoCão, PrimoGato, Faro, Bônos, Apolo, Átila, and Giran Plus brands. It serves supermarkets, wholesalers, retail and wholesale stores, restaurants, and other institutional buyers. The company offers consultancy, administrative, marketing, road freight, and logistics services; generates and commercializes electric energy; distributes nutrients for animals; and veterinary activities, as well as real estate. The company was formerly known as BRF-Brasil Foods S.A. and changed its name to BRF S.A. in April 2013. BRF S.A. was founded in 1934 and is headquartered in São Paulo, Brazil. BRF S.A. is a subsidiary of Marfrig Global Foods S.A.</t>
+  </si>
+  <si>
+    <t>Engie Brasil Energia S.A., together with its subsidiaries, generates, sells, and trades in electrical energy in Brazil. The company operates various plants, including hydroelectric power plants, wind farms, biomass plants, photovoltaic solar plants, and small hydroelectric power plants. It also engages in transportation of natural gas business. Engie Brasil Energia S.A. was founded in 2005 and is headquartered in Florianópolis, Brazil. The company operates as a subsidiary of ENGIE Brasil Participações Ltda.</t>
+  </si>
+  <si>
     <t>Odontoprev S.A. provides private dental plans in Brazil. It operates through Corporate, Small and Medium-Sized Enterprise (SME), Individual, and Other segments. The company manages and sells dental care plans to corporations and/or individuals. It is also involved in commercial advisory, consulting, and business management services; develops and licenses software programs; retails and wholesales sanitizers, drugs, medicines, pharmaceutical inputs, and related items; provision of warehousing, storage, loading, organization, custody of goods, technical, and administrative programming services, as well as general management of goods and business. In addition, the company engages in collecting, sending, or delivering mail, documents, and objects or goods; integrating technologies to develop dental solutions; and provision of specialized services related to accidents and diseases, besides actuarial, financial, administrative, and commercial and risk management services. Odontoprev S.A. was founded in 1987 and is headquartered in Barueri, Brazil. Odontoprev S.A. is a subsidiary of Bradesco Saúde S.A.</t>
   </si>
   <si>
-    <t>Engie Brasil Energia S.A., together with its subsidiaries, generates, sells, and trades in electrical energy in Brazil. The company operates various plants, including hydroelectric power plants, wind farms, biomass plants, photovoltaic solar plants, and small hydroelectric power plants. It also engages in transportation of natural gas business. Engie Brasil Energia S.A. was founded in 2005 and is headquartered in Florianópolis, Brazil. The company operates as a subsidiary of ENGIE Brasil Participações Ltda.</t>
-  </si>
-  <si>
-    <t>Cury Construtora e Incorporadora S.A. operates in real estate businesses. The company provides real estate agency and brokerage services. It also offers financing services. In addition, the company is involved in credit analysis and online brokerage activities. Cury Construtora e Incorporadora S.A. was founded in 1963 and is based in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Brava Energia S.A. engages in the exploration and production of oil and natural gas in Brazil. The company was formerly known as 3R Petroleum Óleo e Gás S.A. and changed its name to Brava Energia S.A. in September 2024. The company was founded in 2010 and is headquartered in Rio De Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Direcional Engenharia S.A. engages in the development and construction of real estate properties in Brazil. It primarily develops and builds projects for low-income and middle-income families. The company was incorporated in 1981 and is based in Belo Horizonte, Brazil.</t>
-  </si>
-  <si>
-    <t>BRF S.A. raises, produces, and slaughters poultry and pork for processing, production, and sale of fresh meat, processed products, pasta, margarine, pet food, and other products. The company provides frozen whole and cut chicken, frozen pork, and turkey, and halal products for Islamic markets; processed foods, such as marinated, frozen, seasoned whole, and cut chicken, roosters, sausages, ham products, bologna, frankfurters, salamis, bacons, cold meats, and other smoked products; and hamburgers, steaks, breaded meat products, kibbeh, and meatballs, as well as chicken sausages, hot dogs, and chicken bologna. It produces and sells lasagna, macaroni and cheese, pies, ready-to-eat meals, pizzas, and other frozen foods; plant-based products, such as nuggets, pies, vegetables, and burgers; frozen desserts and cheese bread; margarine, butter, cream cheese, sweet specialties, sandwiches, and pate, as well as soy meal, refined soy flour, animal feed, pet food and hatcheries. The company sells its products under the Sadia, Perdigão, Qualy, Sadia Halal, Chester, BRF Ingredients, Kidelli, Perdix, Borella, Hilal, Balance, Onefoods, Banvit, Deline, Sadia Bio, Sadia Salamitos, Sadia Veg&amp;Tal, Sadia Livre&amp;Lev, Confidence and Hilal, Sadia Hot Pocket, Perdigão Ouro, Chester Perdigão, Perdigão NaBrasa, Claybom, Biofresh, Three Dogs, Three Cats, Guabi Natural, Giran Plus, Balance, PrimoCão, PrimoGato, Faro, Bônos, Apolo, Átila, and Giran Plus brands. It serves supermarkets, wholesalers, retail and wholesale stores, restaurants, and other institutional buyers. The company provides consultancy, administrative, marketing, and logistics services; generates and commercializes electric energy; distributes nutrients for animals; veterinary activities; road freight; and imports, exports, industrializes, and commercializes of products, as well as real estate. The company was formerly known as BRF-Brasil Foods S.A. and changed its name to BRF S.A. in April 2013. BRF S.A. was founded in 1934 and is headquartered in São Paulo, Brazil. BRF S.A. operates as a subsidiary of Marfrig Global Foods S.A.</t>
-  </si>
-  <si>
     <t>Bradespar S.A., through its interest in VALE, operates as a mining company in the production of iron ore and pellets, and nickel in Brazil. The company also produces copper, thermal and metallurgical coal, manganese, platinum group metals, gold, silver, and cobalt, as well as raw materials for the steel industry with applications in the stainless-steel industry, and metal alloys used in the production of various products. In addition, it operates logistics systems, including railways, ports, and terminals, as well as engages in energy generation business. Bradespar S.A. was founded in 1942 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
-    <t>Itaúsa S.A., through its subsidiaries, operates in the financial and industrial markets in Brazil and internationally. The company offers credit products and other financial services to individuals and corporate clients. It also engages in the operation of highway concessions, urban mobility, and airports, as well as the transportation of gas through gas pipelines to distribution companies. In addition, it manufactures and sells bathroom fixtures, fittings, and showers; ceramic tiles, including floor and wall coatings under the Ceusa, Portinari, and Castelatto brands; pine and eucalyptus wood panels primarily used in the manufacture of medium- and high-density wood panels under the Duratex and Durafloor brand; and footwear, apparel, textiles, and related components, as well as leather, resin, and natural and artificial rubber. Further, it provides sanitation services. The company was formerly known as Itaúsa - Investimentos Itaú SA. Itaúsa S.A. was incorporated in 1966 and is headquartered in São Paulo, Brazil.</t>
+    <t>Wilson Sons S.A., through its subsidiaries, provides port and maritime logistics and supply chain solutions primarily in Brazil. The company manages two container terminals, such as Rio Grande and Salvador container terminals. It provides general and bonded warehousing, inventory management, distribution, transport management, and foreign trade solutions. The company also operates 82 tugboats; and offers firefighting and others, as well as offshore maritime support and ocean towage services. In addition, it is involved in the construction, conversion, maintenance, and repair of vessels, marine and offshore structures, as well as shipping agency activities. Further, the company provides logistics services, such as wharf for mooring, cargo handling, storage, water storage/supply, procurement, material inventory management, office, fluid plant, and road scale services; and environmental services, waste management, tank cleaning, and containment barriers to prevent oil spills during docking. It serves shipping owners, importers, exporters, and oil and gas industries, as well as other participants in various sectors. Wilson Sons S.A. was founded in 1837 and is headquartered in Rio De Janeiro, Brazil. As of June 4, 2025, Wilson Sons S.A. operates as a subsidiary of SAS Shipping Agencies Services SÀRL.</t>
+  </si>
+  <si>
+    <t>Porto Seguro S.A. provides a range of insurance products and services in Brazil and Uruguay. It offers auto, health and dental, damage and personal, health, casualty, financial risk, and life insurance; and reinsurance products. The company also provides services related to insurance, protection, and electronic monitoring; telemarketing and call center, telecommunications, and technical insurance brokerage services; vehicle subscription models, cargo management for companies, and other vehicle rental modalities; administrative advisory services to physicians and health care providers; consulting and advisory services in occupational health, labor security, ergonomics, and outpatient medical services; services to obtain credits and financing; assistance, maintenance, repairs, and individualization of consumption measurement; vehicle maintenance, assistance, and repair services; service platform that offers solutions to end consumers through retailers, telecom, utilities and insurers; and assistance services to consumers in the auto, travel, health, concierge and home lines. In addition, the company trades and distributes in auto parts; manages securities portfolios, investment funds, special savings bonds, and other third party funds; retail trades in live animals and pet articles and food; operates oncology, hematology, and radiotherapy centers; grants loans and financing; acquires chattels and properties; distributes investment fund quotas; operates credit cards, electronic payment for opening of toll gates and parking lots, and rental property listing platform; develops technological solutions for the real estate industry; and installs heating, natural gas, and liquefied petroleum gas systems technical. The company was founded in 1945 and is based in São Paulo, Brazil.</t>
   </si>
   <si>
     <t>Santos Brasil Participações S.A. provides port container handling and logistics services in Brazil. It offers loading and unloading containers, vehicles and general cargo on and off ships to handling, warehousing, transporting and distributing containers, as well as connects engages in connecting supply chain, integrated, and customized logistics solutions. The company serves shipowners, and import and export clients in various segments, such as chemical, industrial supplies, automotive components, pharmaceutical, food, petrochemicals, agribusiness, auto parts and consumer goods. Santos Brasil Participações S.A. was founded in 1997 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
-    <t>Wilson Sons S.A., through its subsidiaries, provides port and maritime logistics and supply chain solutions primarily in Brazil. The company manages two container terminals, such as Rio Grande and Salvador container terminals. It provides general and bonded warehousing, inventory management, distribution, transport management, and foreign trade solutions. The company also operates 82 tugboats; and offers firefighting and others, as well as offshore maritime support and ocean towage services. In addition, it is involved in the construction, conversion, maintenance, and repair of vessels, marine and offshore structures, as well as shipping agency activities. Further, the company provides logistics services, such as wharf for mooring, cargo handling, storage, water storage/supply, procurement, material inventory management, office, fluid plant, and road scale services; and environmental services, waste management, tank cleaning, and containment barriers to prevent oil spills during docking. It serves shipping owners, importers, exporters, and oil and gas industries, as well as other participants in various sectors. Wilson Sons S.A. was founded in 1837 and is headquartered in Rio De Janeiro, Brazil. As of June 4, 2025, Wilson Sons S.A. operates as a subsidiary of SAS Shipping Agencies Services SÀRL.</t>
-  </si>
-  <si>
-    <t>Suzano S.A. manufactures and sells pulp and paper products in Brazil and internationally. It operates in two segments, Pulp, and Paper and Consumer Goods. The company offers coated and uncoated printing and writing papers, paperboards, tissue papers, and market and fluff pulps. It also engages in the research, development, and production of biofuel; operation of port terminals; biotechnology and nanocrystalline pulps research and development activities; power generation and distribution business; road freight transport activities; commercialization of equipment and parts; research and development of lignin; industrialization and commercialization of cellulose, microfiber cellulose, paper, and paperboard products; industrialization, commercialization, and exporting of pulp products; and commercialization of paper and computer materials. In addition, the company is involved in the business office, corporate venture capital, and financial fundraising activities; production of consumer goods through cellulose-based liquids; development and production of cellulose-based fibers, yarns, and textile filaments; restoration, conservation, and preservation of forests; and research of raw materials for the textile industry. The company was formerly known as Suzano Papel e Celulose S.A. and changed its name to Suzano S.A. in April 2019. The company was founded in 1924 and is headquartered in Salvador, Brazil.</t>
+    <t>IRB-Brasil Resseguros S.A. engages in the provision of reinsurance solutions in Brazil and internationally. It offers reinsurance solutions for life and pension, agricultural risks, cargo and marine, casualty, property, oil and gas, financial lines, surety, and housing. The company was incorporated in 1939 and is headquartered in Rio de Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>Multiplan Empreendimentos Imobiliários S.A. engages in the planning, development, construction, and sale of real estate projects in Brazil. The company develops residential or commercial properties, including urban shopping malls. It is also involved in the purchase and sale of real estate properties, as well as acquisition and disposal of real estate rights, and its operation through leasing. In addition, the company provides management and administrative services for own or third party shopping malls; consultancy and technical advisory and support services concerning real estate matters; and civil construction, construction works execution, and engineering and related services. Further, it engages in the planning, development, management, promotion, and intermediation of real estate projects; import and export of goods and services related to its activities; generation and sale of electric power; storage of vehicles; and parking, as well as operates theaters; and involved in advertising, agency, and amusement services. Additionally, the company engages in artistic, cultural events, exhibitions, auctions, music festivals, cinematographic, social and promotional events; and charities; and leases sound and light equipment. Multiplan Empreendimentos Imobiliários S.A. was founded in 1974 and is based in Rio de Janeiro, Brazil.</t>
   </si>
   <si>
     <t>Grupo SBF S.A. engages in the retail and wholesale of sports and leisure products in Brazil. The company offers footwear, clothing, equipment, and accessories. It also provides logistics services; and organizing races and sporting events under the Xterra and Uphill brands. In addition, the company engages in the advertising films and audiovisual production businesses. Further, it operates dance platform and sports channel network. The company sells its sports and leisure products through physical stores and e-commerce channels. Grupo SBF S.A. was founded in 1981 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
-    <t>Porto Seguro S.A. provides a range of insurance products and services in Brazil and Uruguay. The company operates through Auto Insurance, Health Plans and Insurance, Personal Insurance and Supplementary Pension, Insurance - Other Lines, Financial Entities and Consortia, and Other segments. It offers auto, health and dental, damage and personal, health, casualty, financial risk, and life insurance; and reinsurance products. The company also provides services related to insurance, protection, and electronic monitoring; telemarketing and call center, telecommunications, and technical insurance brokerage services; vehicle subscription models, cargo management for companies, and other vehicle rental modalities; administrative advisory services to physicians and health care providers; consulting and advisory services in occupational health, labor security, ergonomics, and outpatient medical services; services to obtain credits and financing; assistance, maintenance, repairs, and individualization of consumption measurement; vehicle maintenance, assistance, and repair services; service platform that offers solutions to end consumers through retailers, telecom, utilities and insurers; and assistance services to consumers in the auto, travel, health, concierge and home lines. In addition, the company trades and distributes in auto parts; manages securities portfolios, investment funds, special savings bonds, and other third party funds; retail trades in live animals and pet articles and food; operates oncology, hematology, and radiotherapy centers; grants loans and financing; acquires chattels and properties; distributes investment fund quotas; operates credit cards, electronic payment for opening of toll gates and parking lots, and rental property listing platform; develops technological solutions for the real estate industry; and installs heating, natural gas, and liquefied petroleum gas systems technical. The company was founded in 1945 and is based in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Multiplan Empreendimentos Imobiliários S.A. engages in the planning, development, construction, and sale of real estate projects in Brazil. The company develops residential or commercial properties, including urban shopping malls. It is also involved in the purchase and sale of real estate properties, as well as acquisition and disposal of real estate rights, and its operation through leasing. In addition, the company provides management and administrative services for own or third party shopping malls; consultancy and technical advisory and support services concerning real estate matters; and civil construction, construction works execution, and engineering and related services. Further, it engages in the planning, development, management, promotion, and intermediation of real estate projects; import and export of goods and services related to its activities; generation and sale of electric power; storage of vehicles; and parking, as well as operates theaters; and involved in advertising, agency, and amusement services. Additionally, the company engages in artistic, cultural events, exhibitions, auctions, music festivals, cinematographic, social and promotional events; and charities; and leases sound and light equipment. Multiplan Empreendimentos Imobiliários S.A. was founded in 1974 and is based in Rio de Janeiro, Brazil.</t>
+    <t>Klabin S.A., together with its subsidiaries, produces and exports packaging paper and sustainable paper packaging solutions in Brazil and internationally. The company engages in the planting of pine and eucalyptus; and forestry management business. It also produces and sells hardwood (eucalyptus), softwood (pine), and fluffed pulp; and paperboard, sackraft, Kraftliner paper, and recycled paper. In addition, the company offers industrial bags, corrugated boxes, and other packaging products. Klabin S.A. was founded in 1899 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Banco Bradesco S.A., together with its subsidiaries, provides various banking products and services to individuals, corporates, and businesses in Brazil and internationally. The company operates through two segments, Banking and Insurance. It provides current, savings, click, and salary accounts; real estate credit, vehicle financing, payroll loans, mortgage loans, microcredit, leasing, and personal and installment credit; overdraft and agribusiness loans; debit and business cards; financial and security services; consortium products; car, personal accident, dental, travel, and life insurance; investment products; pension products; foreign currency exchange services; capitalization bonds; and internet banking services. The company was founded in 1943 and is headquartered in Osasco, Brazil.</t>
   </si>
   <si>
     <t>Companhia de Saneamento de Minas Gerais plans, designs, performs, expands, remodels, manages, and provides water supply and sewage treatment services in Brazil and internationally. It engages in the collection, recycling, treatment, and final disposal of sanitary sewage; drainage and management of urban rainwater; supply of drinking water; and collection, transport, transfer, treatment, and destination of urban, domestic, and industrial waste. The company was formerly known as Companhia Mineira de Água e Esgotos and changed its name to Companhia de Saneamento de Minas Gerais in November 1974. The company was founded in 1963 and is headquartered in Belo Horizonte, Brazil.</t>
   </si>
   <si>
-    <t>IRB-Brasil Resseguros S.A. engages in the provision of reinsurance solutions in Brazil and internationally. It offers reinsurance solutions for life and pension, agricultural risks, cargo and marine, casualty, property, oil and gas, financial lines, surety, and housing. The company was incorporated in 1939 and is headquartered in Rio de Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Klabin S.A., together with its subsidiaries, produces and exports packaging paper and sustainable paper packaging solutions in Brazil and internationally. The company engages in the planting of pine and eucalyptus; and forestry management business. It also produces and sells hardwood (eucalyptus), softwood (pine), and fluffed pulp; and paperboard, sackraft, Kraftliner paper, and recycled paper. In addition, the company offers industrial bags, corrugated boxes, and other packaging products. Klabin S.A. was founded in 1899 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Banco Bradesco S.A., together with its subsidiaries, provides various banking products and services to individuals, corporates, and businesses in Brazil and internationally. The company operates through two segments, Banking and Insurance. It provides current, savings, click, and salary accounts; real estate credit, vehicle financing, payroll loans, mortgage loans, microcredit, leasing, and personal and installment credit; overdraft and agribusiness loans; debit and business cards; financial and security services; consortium products; car, personal accident, dental, travel, and life insurance; investment products; pension products; foreign currency exchange services; capitalization bonds; and internet banking services. The company was founded in 1943 and is headquartered in Osasco, Brazil.</t>
-  </si>
-  <si>
     <t>Cogna Educação S.A. operates as a private educational organization in Brazil and internationally. It operates through three segments: Kroton, Vasta, and Saber. The company provides on campus and distance-learning higher education, and undergraduate and graduate courses; and editing, marketing, and distribution of teaching books, educational materials, and workbooks. It offers basic education, pre-university preparatory courses, and language courses; educational solutions for technical and higher education; and complementary activities, such as education technology development for services to complement management and training. In addition, the company offers administration of kindergarten, elementary and high school activities; advises on and/or enables direct and indirect financing for students; and develops software for adaptive teaching and academic management optimization. The company was incorporated in 2001 and is headquartered in Belo Horizonte, Brazil.</t>
   </si>
   <si>
+    <t>CSN Mineração S.A. engages in the iron ore mining business in Brazil. The company operates Casa de Pedra and Engenho mines. It also operates a hydroelectric power plant. The company was founded in 1913 and is based in São Paulo, Brazil. CSN Mineração S.A. operates as a subsidiary of Companhia Siderúrgica Nacional.</t>
+  </si>
+  <si>
+    <t>Banco do Estado do Rio Grande do Sul S.A., a multiple-service bank, provides a range of banking products and services primarily in Brazil. The company engages in the retail banking, lending, financing and investment, mortgage loan, development, lease portfolio, and foreign exchange activities. It also provides securities brokerage, payment industry solutions, insurance, and pension plan and saving bonds products, as well as manages sales poll groups. The company was incorporated in 1928 and is headquartered in Porto Alegre, Brazil.</t>
+  </si>
+  <si>
     <t>Banco do Brasil S.A., together with its subsidiaries, provides banking products and services for individuals, companies, and public sectors in Brazil and internationally. The company's Banking segment offers various products and services, including deposits, loans, and other services to retail, wholesale, and public sectors. This segment also engages in the business with micro-entrepreneurs and low-income population undertaken through banking correspondents. Its Investments segment engages in the domestic capital markets; intermediation and distribution of debts in the primary and secondary markets; and provision of equity investments and financial services. The company's Fund Management segment is involved in the purchase, sale, and custody of securities and portfolio management; and management of investment funds and clubs. Its Insurance, Pension and Capitalization segment provides life, property, and automobile insurance products, as well as private pension and capitalization plans. The company's Payments Method segment provides funding, transmission, processing, and settlement services for electronic transactions. Its Other segment engages in the provision of credit recovery and consortium management services. This segment is also involved in developing, manufacturing, selling, leasing, and integrating of digital electronic equipment and systems, peripherals, programs, inputs, and computing supplies. The company was incorporated in 1808 and is headquartered in Brasília, Brazil.</t>
   </si>
   <si>
-    <t>Banco do Estado do Rio Grande do Sul S.A., a multiple-service bank, provides a range of banking products and services primarily in Brazil. It engages in the commercial, credit, financing and investment, real estate credit, development, leasing and foreign exchange portfolios. The company also offers securities brokerage, consortium management, payment methods, insurance and pension plans. Banco do Estado do Rio Grande do Sul S.A. was incorporated in 1928 and is headquartered in Porto Alegre, Brazil.</t>
-  </si>
-  <si>
-    <t>CSN Mineração S.A. engages in the iron ore mining business in Brazil. The company operates Casa de Pedra and Engenho mines. It also operates a hydroelectric power plant. The company was founded in 1913 and is based in São Paulo, Brazil. CSN Mineração S.A. operates as a subsidiary of Companhia Siderúrgica Nacional.</t>
+    <t>Vale S.A., together with its subsidiaries, produces iron ore and nickel in Asia, the Americas, Europe, and internationally. It operates through Iron Solutions and Energy Transition Materials segments. The company  extracts, produces, and distributes iron ore, iron ore pellets, briquettes, and other ferrous products; and operates mining complexes, railways, maritime terminals, and ports for the transportation of its products. It also produces nickel, copper, cobalt, and by-products, such as gold, silver, cobalt, platinum group metals, and other precious metals. In addition, the company engages in greenfield mineral exploration; invests in energy businesses through renewable sources; research; trading; and pelletizing plant. It exports its products. The company was formerly known as Companhia Vale do Rio Doce and changed its name to Vale S.A. in May 2009. Vale S.A. was founded in 1942 and is headquartered in Rio De Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>Intelbras S.A. - Indústria de Telecomunicação Eletrônica Brasileira engages in the manufacturing, developing, and sale of electronic security equipment and electronic surveillance and monitoring services in Brazil. The company operates through Security, Communication, and Energy segments. It offers electronic safety products and solutions, including automation devices, alarms, storage, cameras, condominium communication, corporate access control, locks, digital video recorders, fire and intercom products, vehicle monitoring, sensors, emergency signaling, video walls, software and application products, and accessories; and networks products and solutions comprise racks, routers, 5G and corporate Wi-Fi products, outdoor radios, optical fiber and passive products, switches, PoE injectors, signal repeaters, USB adapters, software and apps, and cables. The company also provides communication related products and solutions, such as webcams, projectors, wireless mouse and keyboards, cloud solutions, antennas and converters, phone centrals, appliance and conference products, gateways, headsets, radio communicators, smart boxes and controls, smart speakers, software and applications, and phones; and energy related products and solutions that includes electric vehicle chargers, fonts, batteries, UPS, electronic protectors, surge protectors, USB accessories, and illumination presence sensors. In addition, it offers on grid solutions, which includes attachment structures, on grid generators and inverters, solar panels, and string box; and off grid solutions, such as illumination products, mounting structures, outdoor cabinets, solar drive and panels, solar bomb, and off grid generators and inverters. The company was incorporated in 1974 and is headquartered in São José, Brazil.</t>
+  </si>
+  <si>
+    <t>B3 S.A. - Brasil, Bolsa, Balcão, a financial market infrastructure company, provides trading services in an exchange and OTC environment. The company engages in the administration of organized securities and bond markets; operation and maintenance of environments or systems for conducting business, including purchases and sales, auctions, and registration of transactions involving securities, bonds, rights, and financial assets; and creation of databases and related activities, including data processing and intelligence. It also provides registration, clearing and settlement services; registrar and central depository; safekeeping services; services for the registration of liens and encumbrances on securities, bonds, financial assets, other types of assets, and other financial instruments, including the registration of instruments constituting collateral; and services associated with the insurance, reinsurance, pension, and capitalization bonds market. In addition, the company offers services related to processed data, including standardization, classification, analysis, quotations, statistics, professional training, conducting studies, publications, information, provision of information. Further, it provides services related to transactions registered and deposited in the markets and systems, and support for credit, financing, and leasing transactions, or transactions registered and deposited in the managed systems. The company was formerly known as BM&amp;FBOVESPA S.A. - Bolsa de Valores, Mercadorias e Futuros and changed its name to B3 S.A. - Brasil, Bolsa, Balcão in June 2017. B3 S.A. - Brasil, Bolsa, Balcão was incorporated in 2007 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
     <t>Neoenergia S.A. generates, transmits, distributes, trades in, and commercializes electric energy in Brazil. It operates through Networks, Renewables, Liberalized, and Others. The company provides free energy markets solutions, such as free energy market, power management, management and billing system, renewable energy certificates, and long term contracts; green hydrogen, that includes green ammonia, steel, and methanol; industrial gas solutions; local and remote solar power plant; engineering; and electrified fleet solutions for businesses. It also offers solar electric charge, insurance, and services for residential customers. The company was founded in 1997 and is based in Rio De Janeiro, Brazil. Neoenergia S.A. operates as a subsidiary of Iberdrola Energía, S.A.U.</t>
@@ -607,67 +586,52 @@
     <t>EZTEC Empreendimentos e Participações S.A. engages in the engineering, construction, and real estate development activities in Brazil and internationally. The company develops and sells of real estate properties; manages and leases properties; construction of condominiums; and subdivision of land. It also engages in the provision of services related to construction, supervision, studies, and projects; and execution of civil engineering works and services. EZTEC Empreendimentos e Participações S.A. was founded in 1979 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
-    <t>Intelbras S.A. - Indústria de Telecomunicação Eletrônica Brasileira engages in the manufacturing, developing, and sale of electronic security equipment and electronic surveillance and monitoring services in Brazil. The company operates through Security, Communication, and Energy segments. It offers electronic safety products and solutions, including automation devices, alarms, storage, cameras, condominium communication, corporate access control, locks, digital video recorders, fire and intercom products, vehicle monitoring, sensors, emergency signaling, video walls, software and application products, and accessories; and networks products and solutions comprise racks, routers, 5G and corporate Wi-Fi products, outdoor radios, optical fiber and passive products, switches, PoE injectors, signal repeaters, USB adapters, software and apps, and cables. The company also provides communication related products and solutions, such as webcams, projectors, wireless mouse and keyboards, cloud solutions, antennas and converters, phone centrals, appliance and conference products, gateways, headsets, radio communicators, smart boxes and controls, smart speakers, software and applications, and phones; and energy related products and solutions that includes electric vehicle chargers, fonts, batteries, UPS, electronic protectors, surge protectors, USB accessories, and illumination presence sensors. In addition, it offers on grid solutions, which includes attachment structures, on grid generators and inverters, solar panels, and string box; and off grid solutions, such as illumination products, mounting structures, outdoor cabinets, solar drive and panels, solar bomb, and off grid generators and inverters. The company was incorporated in 1974 and is headquartered in São José, Brazil.</t>
-  </si>
-  <si>
-    <t>B3 S.A. - Brasil, Bolsa, Balcão, a financial market infrastructure company, provides trading services in an exchange and OTC environment. The company engages in the administration of organized securities and bond markets; operation and maintenance of environments or systems for conducting business, including purchases and sales, auctions, and registration of transactions involving securities, bonds, rights, and financial assets; and creation of databases and related activities, including data processing and intelligence. It also provides registration, clearing and settlement services; registrar and central depository; safekeeping services; services for the registration of liens and encumbrances on securities, bonds, financial assets, other types of assets, and other financial instruments, including the registration of instruments constituting collateral; and services associated with the insurance, reinsurance, pension, and capitalization bonds market. In addition, the company offers services related to processed data, including standardization, classification, analysis, quotations, statistics, professional training, conducting studies, publications, information, provision of information. Further, it provides services related to transactions registered and deposited in the markets and systems, and support for credit, financing, and leasing transactions, or transactions registered and deposited in the managed systems. The company was formerly known as BM&amp;FBOVESPA S.A. - Bolsa de Valores, Mercadorias e Futuros and changed its name to B3 S.A. - Brasil, Bolsa, Balcão in June 2017. B3 S.A. - Brasil, Bolsa, Balcão was incorporated in 2007 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Vale S.A., together with its subsidiaries, produces iron ore and nickel in Asia, the Americas, Europe, and internationally. It operates through Iron Solutions and Energy Transition Materials segments. The company  extracts, produces, and distributes iron ore, iron ore pellets, briquettes, and other ferrous products; and operates mining complexes, railways, maritime terminals, and ports for the transportation of its products. It also produces nickel, copper, cobalt, and by-products, such as gold, silver, cobalt, platinum group metals, and other precious metals. In addition, the company engages in greenfield mineral exploration; invests in energy businesses through renewable sources; research; trading; and pelletizing plant. It exports its products. The company was formerly known as Companhia Vale do Rio Doce and changed its name to Vale S.A. in May 2009. Vale S.A. was founded in 1942 and is headquartered in Rio De Janeiro, Brazil.</t>
-  </si>
-  <si>
     <t>WEG S.A. engages in the production and sale of capital goods in Brazil and internationally. The company offers electric motors, generators, and transformers; gear units and geared motors; hydraulic and steam turbines; frequency converters; motor starters and maneuver devices; control and protection of electric circuits for industrial automation; power sockets and switches; and electric traction solutions for heavy vehicles, SUV, locomotives, and sea transportation capital goods. It provides solutions for the generation of renewable and distributed energy through hydro, thermal, biomass, wind, and solar energy power plants; solutions for industry; uninterruptible power supplies and alternators for groups of generators; conventional and movable electric substations; industrial electrical and electronic systems; industrial paint and varnish; and paints for automotive repainting. WEG S.A. was founded in 1961 and is headquartered in Jaraguá do Sul, Brazil. WEG S.A. operates as a subsidiary of WEG Participações e Serviços S.A.</t>
   </si>
   <si>
     <t>C&amp;A Modas S.A. operates as a fashion retailer for women, men, and children in Brazil and internationally. It offers blouses, pants, dresses, skirts, coats, beach and intimate fashion products, T-shirts, Shirts, pants, jackets and coats, shorts, footwear, sandals, perfumes, makeup and skincare products, body and bath products, and accessories, as well as cell phones, smartphones, watches, decoration, pets, jewellery, and other products. The company sells its products through stores, as well as online. The company was founded in 1841 and is based in Barueri, Brazil. C&amp;A Modas S.A. operates as a subsidiary of C&amp;A AG.</t>
   </si>
   <si>
+    <t>Alupar Investimento S.A., through its subsidiaries, engages in the transmission, generation, and development of electricity business in Brazil, Colombia, and Peru. The company operates through Transmission and Generation segments. It operates hydroelectric and wind power plant. In addition, the company holds transmission assets. Further, it is involved in solar photovoltaic related business. Alupar Investimento S.A. was founded in 2007 and is headquartered in São Paulo, Brazil. Alupar Investimento S.A. operates as a subsidiary of Guarupart Participações Ltda.</t>
+  </si>
+  <si>
     <t>Banco BTG Pactual S.A. provides financial products and services related to trading and investment portfolios, credit, financing, leasing, insurance, and foreign exchange in Brazil and internationally. The company also offers personal investment services for a customized investment portfolio; international banking account services, including debit card, transfer, payment and receipt, and customer support services. It also provides wealth management services, such as educational resources, analytics, relationship management, technical advisory, brokerage, marketable securities placement, and research-related services. Banco BTG Pactual S.A. was founded in 1983 and is headquartered in Rio de Janeiro, Brazil. Banco BTG Pactual S.A. operates as a subsidiary of BTG Pactual Holding Financeira Ltda.</t>
   </si>
   <si>
-    <t>Alupar Investimento S.A., through its subsidiaries, engages in the transmission, generation, and development of electricity business in Brazil, Colombia, and Peru. The company operates through Transmission and Generation segments. It operates hydroelectric and wind power plant. In addition, the company holds transmission assets. Further, it is involved in solar photovoltaic related business. Alupar Investimento S.A. was founded in 2007 and is headquartered in São Paulo, Brazil. Alupar Investimento S.A. operates as a subsidiary of Guarupart Participações Ltda.</t>
+    <t>Grupo Mateus S.A. operates a supermarket chain in Brazil. The company operates cash and carry, wholesale, furniture, and appliance stores; and slicing and portioning centers, as well as in e-commerce and bakery industry. Grupo Mateus S.A. was founded in 1986 and is headquartered in São Luís, Brazil.</t>
+  </si>
+  <si>
+    <t>Azzas 2154 S.A. designs, develops, manufactures, markets, and sells shoes, handbags, clothing, and accessories for women and men. The company offers its products through franchise stores, company-operated store, and an e-commerce channel under the Arezzo, Schutz, Anacapri, Alexandre Birman, Alme, Vans, AR&amp;CO, TROC, ZZ mall, Baw clothing, Carol Bassi, and Vicenza brands. The company was formerly known as Arezzo Indústria e Comércio S.A. and changed its name to Azzas 2154 S.A. in July 2024. Azzas 2154 S.A. was founded in 1972 and is headquartered in Belo Horizonte, Brazil.</t>
+  </si>
+  <si>
+    <t>SLC Agrícola S.A. produces and sells agricultural products in Brazil and internationally. The company offers soybean, corn, cotton, wheat, seed corn, popcorn, mung bean, and brachiaria crops. In addition, it is involved in the cattle raising and livestock business. The company was founded in 1977 and is headquartered in Porto Alegre, Brazil.</t>
+  </si>
+  <si>
+    <t>Banco Santander (Brasil) S.A., together with its subsidiaries, provides various banking products and services to individuals, small and medium enterprises, and corporate customers in Brazil and internationally. It operates in Commercial Banking and Global Wholesale Banking segments. The company offers payroll and real estate loans; home equity financing solutions; a microfinance program; consortiums; agribusiness portfolio, including credit, securities, and other products; and insurance products, such as life and personal accident, vehicle and property coverage, and credit insurance, as well as insurance for travel and banking transactions. It also provides local transaction banking products, which include local loans, commercial financing options, development bank funds, and cash management services; fund and financial advisory services for infrastructure projects, origination, and distribution of fixed income instruments in capital markets; financing for acquisitions; syndicated loans in local and foreign currency; and advisory services for mergers and acquisitions and equity transactions in capital markets; research and brokerage services for corporate, institutional, and individual investors in stocks and listed derivatives; and foreign exchange products, derivatives, and investments to institutional investors, corporate customers, and individuals. In addition, the company offers cash management for corporate customers and SMEs; advance programs for entrepreneurs; and deposits and other bank funding instruments. It provides financial products and services to its customers through multichannel distribution network comprising branches, mini-branches, ATMs, call centers, Internet banking, and mobile banking. The company was incorporated in 1985 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Ambev S.A., through its subsidiaries, engages in the production, distribution, and sale of beer, draft beer, carbonated soft drinks, malt and food, other alcoholic beverages, and non-alcoholic and non-carbonated products in Brazil, Central America and Caribbean, Latin America South, and Canada. It also provides carbonated soft drinks, bottled water, isotonic beverages, energy drinks, coconut water, powdered and natural juices, and ready-to-drink teas. The company offers its products under its own main brands, such as Brahma, SkoL, Antarctica, Original, Quilmes, Andes Origen, Patricia, Paceña, Huari, Pilsen, Presidente, Balboa, Guaraná Antarctica, and e Beats; and licensed brands, including Budweiser, Corona, Spaten, Stella Artois, Beck's, Modelo, Bud Light, Busch, and e Michelob Ultra, as well as under the Pepsi, H2OH! , Lipton IceTea, and Red Bull. It offers its products through a network of third-party distributors and a direct distribution system. The company was founded in 1885 and is headquartered in São Paulo, Brazil. Ambev S.A. operates as a subsidiary of Interbrew International B.V</t>
+  </si>
+  <si>
+    <t>Lojas Renner S.A., together with its subsidiaries, operates as a fashion and lifestyle company in Brazil, Argentina, and Uruguay. It operates through Retail and Financial Products segments. The company trades clothes and sports products, shoes, accessories, perfumery, domestic appliances, towels and linen, furniture, and decoration articles, as well as cosmetics. It also involved in the granting of loans to individuals and legal entities, financing of purchases, insurance, and credit and debit transaction services to credit, financing, and investment companies, as well as provides personal loans. It offers its products through stores, as well as digital channels under Renner, Youcom, Camicado, realize, Ashua, Uello, and repasse brand names. Lojas Renner S.A. was incorporated in 1965 and is headquartered in Porto Alegre, Brazil.</t>
+  </si>
+  <si>
+    <t>Sendas Distribuidora S.A. engages in the retail and wholesale sale of food products, bazaar items, and other products in Brazil. The company offers grocery, food, perishable, beverage, wrapping, and hygiene products; and parking, air-conditioned, well-lit environments, and butcher services. It serves restaurants, pizzerias, snack bars, schools, small businesses, religious institutions, hospitals, hotels, grocery stores, neighborhood supermarkets, and individuals. The company sells its products through brick-and-mortar stores, as well as telesales. The company was founded in 1974 and is headquartered in Rio De Janeiro, Brazil.</t>
   </si>
   <si>
     <t>Movida Participações S.A., through its subsidiaries, provides car rental services in Brazil. It operates in two segments, Rent-a-Car, and Fleet Management and Outsourcing (GTF). The company also offers light vehicle fleet management and outsourcing services; fleet sizing study, including acquisition, customization, and standardization of the customer's fleet, as well as rental, maintenance management, provision of temporary vehicles, replacement vehicles, documentation management, and asset retirement services; and added services, such as corrective and preventive maintenance, insurance, tire replacement, replacement vehicles for maintenance periods, as well as a wide range of vehicle makes and models. In addition, it sells pre-owned cars. The company was formerly known as H.L.C.S.P.E Empreendimentos e Participações S.A. and changed its name to Movida Participações S.A. in December 2014. The company was founded in 2006 and is based in São Paulo, Brazil. Movida Participações S.A. is a subsidiary of Simpar S.A.</t>
   </si>
   <si>
-    <t>Grupo Mateus S.A. operates a supermarket chain in Brazil. The company operates cash and carry, wholesale, furniture, and appliance stores; and slicing and portioning centers, as well as in e-commerce and bakery industry. Grupo Mateus S.A. was founded in 1986 and is headquartered in São Luís, Brazil.</t>
-  </si>
-  <si>
-    <t>Iochpe-Maxion S.A. produces and sells automotive wheels and structural components for commercial and light vehicles in North America, South America, Europe, Asia, and internationally. It operates in two divisions, Maxion Wheels and Maxion Structural Components. The company offers steel and aluminum wheels; wheels for agricultural machinery; side rails and chassis for commercial vehicles; and railway freight cars, wheels, and castings, as well as industrial castings. It also provides structural components, such as frames, sidebars, crossbars, metal stampings, hand brake levers, pedal and welded assemblies, structural pieces, and other automotive components. The company was founded in 1918 and is headquartered in Cruzeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Banco Santander (Brasil) S.A., together with its subsidiaries, provides various banking products and services to individuals, small and medium enterprises, and corporate customers in Brazil and internationally. It operates in Commercial Banking and Global Wholesale Banking segments. The company offers payroll and real estate loans; home equity financing solutions; a microfinance program; consortiums; agribusiness portfolio, including credit, securities, and other products; and insurance products, such as life and personal accident, vehicle and property coverage, and credit insurance, as well as insurance for travel and banking transactions. It also provides local transaction banking products, which include local loans, commercial financing options, development bank funds, and cash management services; fund and financial advisory services for infrastructure projects, origination, and distribution of fixed income instruments in capital markets; financing for acquisitions; syndicated loans in local and foreign currency; and advisory services for mergers and acquisitions and equity transactions in capital markets; research and brokerage services for corporate, institutional, and individual investors in stocks and listed derivatives; and foreign exchange products, derivatives, and investments to institutional investors, corporate customers, and individuals. In addition, the company offers cash management for corporate customers and SMEs; advance programs for entrepreneurs; and deposits and other bank funding instruments. It provides financial products and services to its customers through multichannel distribution network comprising branches, mini-branches, ATMs, call centers, Internet banking, and mobile banking. The company was incorporated in 1985 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Track &amp; Field Co S.A. engages in the development and sale of sports and leisure products in Brazil. It offers athletic wear, lifestyle products, beachwear, footwear, and accessories. The company sells its products through physical stores, franchise stores, and e-commerce. Track &amp; Field Co S.A. was founded in 1988 and is based in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>SLC Agrícola S.A. produces and sells agricultural products in Brazil and internationally. The company offers soybean, corn, cotton, wheat, seed corn, popcorn, mung bean, and brachiaria crops. In addition, it is involved in the cattle raising and livestock business. The company was founded in 1977 and is headquartered in Porto Alegre, Brazil.</t>
-  </si>
-  <si>
-    <t>Ambev S.A., through its subsidiaries, engages in the production, distribution, and sale of beer, draft beer, carbonated soft drinks, malt and food, other alcoholic beverages, and non-alcoholic and non-carbonated products in Brazil, Central America and Caribbean, Latin America South, and Canada. It also provides carbonated soft drinks, bottled water, isotonic beverages, energy drinks, coconut water, powdered and natural juices, and ready-to-drink teas. The company offers its products under its own main brands, such as Brahma, SkoL, Antarctica, Original, Quilmes, Andes Origen, Patricia, Paceña, Huari, Pilsen, Presidente, Balboa, Guaraná Antarctica, and e Beats; and licensed brands, including Budweiser, Corona, Spaten, Stella Artois, Beck's, Modelo, Bud Light, Busch, and e Michelob Ultra, as well as under the Pepsi, H2OH! , Lipton IceTea, and Red Bull. It offers its products through a network of third-party distributors and a direct distribution system. The company was founded in 1885 and is headquartered in São Paulo, Brazil. Ambev S.A. operates as a subsidiary of Interbrew International B.V</t>
-  </si>
-  <si>
-    <t>Azzas 2154 S.A. designs, develops, manufactures, markets, and sells shoes, handbags, clothing, and accessories for women and men. The company offers its products through franchise stores, company-operated store, and an e-commerce channel under the Arezzo, Schutz, Anacapri, Alexandre Birman, Alme, Vans, AR&amp;CO, TROC, ZZ mall, Baw clothing, Carol Bassi, and Vicenza brands. The company was formerly known as Arezzo Indústria e Comércio S.A. and changed its name to Azzas 2154 S.A. in July 2024. Azzas 2154 S.A. was founded in 1972 and is headquartered in Belo Horizonte, Brazil.</t>
-  </si>
-  <si>
-    <t>Sendas Distribuidora S.A. engages in the retail and wholesale sale of food products, bazaar items, and other products in Brazil. The company offers grocery, food, perishable, beverage, wrapping, and hygiene products; and parking, air-conditioned, well-lit environments, and butcher services. It serves restaurants, pizzerias, snack bars, schools, small businesses, religious institutions, hospitals, hotels, grocery stores, neighborhood supermarkets, and individuals. The company sells its products through brick-and-mortar stores, as well as telesales. The company was founded in 1974 and is headquartered in Rio De Janeiro, Brazil.</t>
+    <t>Metalurgica Gerdau S.A., together with its subsidiaries, produces and supplies long and special steel products in Brazil, Latin America, and North America. The company offers rebars, bars, profiles and drawn products, billets, blocks, plates, wire rod, structural profiles, iron ore, heavy and light structural profiles, stainless steel, as well as square, round, and flat bars. The company was formerly known as METALÚRGICA HUGO GERDAU S.A and changed its name to Metalurgica Gerdau S.A. in June 1965. Metalurgica Gerdau S.A. was founded in 1976 and is headquartered in São Paulo, Brazil. Metalurgica Gerdau S.A. operates as a subsidiary of Indac - Indústria, Administração e Comércio S.A.</t>
+  </si>
+  <si>
+    <t>Equatorial S.A., through its subsidiaries, engages in the electricity generation, distribution, and transmission operations in Brazil. The company generates energy from wind and biomass. It also distributes electric energy in the municipalities of Maranhão and Pará State. In addition, the company distributes electric energy in municipalities of Piauí and Alagoas State. Further, it is involved in telecom related business. Equatorial S.A. was formerly known as Equatorial Energia S.A. and changed its name to Equatorial S.A. in August 2024. Equatorial S.A. was founded in 1958 and is based in Brasília, Brazil.</t>
   </si>
   <si>
     <t>Companhia Paranaense de Energia - COPEL engages in the generation, transformation, distribution, and sale of electricity to industrial, residential, commercial, rural, and other customers in Brazil. The company operates through Power Generation and Transmission, Power Distribution, GAS, Power Sale, and Holding and Services segments. It is also involved in the piped natural gas distribution. The company operates hydroelectric, wind, and thermoelectric plants; and owns and operates transmission and distribution lines. It holds concessions to distribute electricity in municipalities in the State of Paraná and in the municipality of Porto União in the State of Santa Catarina. Companhia Paranaense de Energia  COPEL was founded in 1954 and is headquartered in Curitiba, Brazil.</t>
   </si>
   <si>
-    <t>Equatorial S.A., through its subsidiaries, engages in the electricity generation, distribution, and transmission operations in Brazil. The company generates energy from wind and biomass. It also distributes electric energy in the municipalities of Maranhão and Pará State. In addition, the company distributes electric energy in municipalities of Piauí and Alagoas State. Further, it is involved in telecom related business. Equatorial S.A. was formerly known as Equatorial Energia S.A. and changed its name to Equatorial S.A. in August 2024. Equatorial S.A. was founded in 1958 and is based in Brasília, Brazil.</t>
-  </si>
-  <si>
-    <t>Lojas Renner S.A., together with its subsidiaries, operates as a fashion and lifestyle company in Brazil, Argentina, and Uruguay. It operates through Retail and Financial Products segments. The company trades clothes and sports products, shoes, accessories, perfumery, domestic appliances, towels and linen, furniture, and decoration articles, as well as cosmetics. It also involved in the granting of loans to individuals and legal entities, financing of purchases, insurance, and credit and debit transaction services to credit, financing, and investment companies, as well as provides personal loans. It offers its products through stores, as well as digital channels under Renner, Youcom, Camicado, realize, Ashua, Uello, and repasse brand names. Lojas Renner S.A. was incorporated in 1965 and is headquartered in Porto Alegre, Brazil.</t>
-  </si>
-  <si>
-    <t>Metalurgica Gerdau S.A., together with its subsidiaries, produces and supplies long and special steel products in Brazil, Latin America, and North America. The company offers rebars, bars, profiles and drawn products, billets, blocks, plates, wire rod, structural profiles, iron ore, heavy and light structural profiles, stainless steel, as well as square, round, and flat bars. The company was formerly known as METALÚRGICA HUGO GERDAU S.A and changed its name to Metalurgica Gerdau S.A. in June 1965. Metalurgica Gerdau S.A. was founded in 1976 and is headquartered in São Paulo, Brazil. Metalurgica Gerdau S.A. operates as a subsidiary of Indac - Indústria, Administração e Comércio S.A.</t>
-  </si>
-  <si>
-    <t>Motiva Infraestrutura de Mobilidade S.A. provides infrastructure services for highway, rail, and airport concessions in Brazil. It manages and maintains 36 concessions?on highways, airports, and rails. The company was formerly known as CCR S.A. and changed its name to Motiva Infraestrutura de Mobilidade S.A. in April 2025. Motiva Infraestrutura de Mobilidade S.A. was incorporated in 1998 and is based in São Paulo, Brazil.</t>
+    <t>Motiva Infraestrutura de Mobilidade S.A. provides infrastructure services for highway, rail, and airport concessions in Brazil. It manages and maintains 36 concessions on highways, airports, and rails. The company was formerly known as CCR S.A. and changed its name to Motiva Infraestrutura de Mobilidade S.A. in April 2025. Motiva Infraestrutura de Mobilidade S.A. was incorporated in 1998 and is based in São Paulo, Brazil.</t>
   </si>
   <si>
     <t>GPS Participações e Empreendimentos S.A., together its subsidiaries, engages in the provision of facilities, security, logistics, utility engineering, industrial service, catering, and infrastructure services in Brazil. It offers security services in the areas of property, firefighting and prevention, personal, monitoring center operations, armed escort, event security, integrated security solution, and civil aviation security (APAC). The company also provides facilities services, including cleaning and conservation, technical and industrial cleaning, cleaning at heights, hospital cleaning and sanitizing, administrative support, specialized services, operational support, caterers and servers, reception desk and gatehouse, building maintenance, firefighters, landscaping and plant maintenance, and indoor waste management services. In addition, it provides electromechanical maintenance, conveyor belts, industrial automation, overhead cranes, electromechanical assembly and shutdowns, scaffolding and lift platforms, industrial cleaning, metallic structures and tubing, building, and refractory industrial maintenance services; industrial refrigeration, compressed air and gases, refrigeration systems automation, steam generation systems, fire suppression systems maintenance, and water and wastewater treatment services; and logistics services. Further, the company operates restaurants under LC Cores and LC Essência brand names; and provides infrastructure services, such as highway maintenance and conservation, and airport and port infrastructure maintenance and conservation, as well as mining, gas pipelines and distribution, railroad, sanitation, and energy project infrastructure and maintenance. Additionally, it engages in installation, operation, and maintenance of utility systems. The company was founded in 1962 and is headquartered in São Paulo, Brazil.</t>
@@ -676,25 +640,22 @@
     <t>Raia Drogasil S.A. engages in the retail sale of medicines, perfumery, personal care and beauty products, cosmetics, dermocosmetics, and specialty medicines in Brazil. It sells its products through stores, telesales, and call centers in the states of São Paulo, Tocantins, Pernambuco, ParanÃ¡, Rio de Janeiro and Bahia. The company was founded in 1905 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
-    <t>Méliuz S.A., together with its subsidiaries, operate a virtual portal for the placement and dissemination of brands, products, services, and other advertising and publicity materials. It offers leasing of virtual advertising space for the insertion of texts, drawings, and other materials, as well as rental of space. The company was incorporated in 2011 and is based in São Bernardo do Campo, Brazil.</t>
+    <t>Gerdau S.A., together with its subsidiaries, operates as a steel producer company. The company operates through Brazil Business, North America Business, South America Business, and Special Steel Business segments. It provides semi-finished products, including billets, blooms, and slabs; common long-rolled products, such as rebars, wire rods, merchant bars, light shapes, and profiles to the construction and manufacturing industries; drawn products, including barbed and barbless fence wires, galvanized wires, fences, concrete reinforcing wire mesh, nails, and clamps for manufacturing, construction, and agricultural industries; and special steel products used in auto parts, light and heavy vehicles, and agricultural machinery, as well as in the oil and gas, wind energy, machinery and equipment, mining and rail, and other markets. The company also offers flat products, such as hot-rolled steel coils and heavy plates; and resells flat steel products. In addition, it operates mines that produce iron ore located in the Brazilian state of Minas Gerais. The company sells its products through independent distributors, direct sales from the mills, and its retail network. Gerdau S.A. was founded in 1901 and is based in São Paulo, Brazil.</t>
   </si>
   <si>
     <t>Rede D'Or São Luiz S.A. operates a network of hospitals in Brazil. The company provides services in the medical areas; and diagnosis and treatment on cancer. It operates own hospitals, 75 hospitals, and 61 oncology and radiotherapy treatment clinics, and 11laboratories, having a total of 9,857 operational beds and provides other services, such as blood bank, dialysis, and outpatient clinics of various specialties in the states of Rio de Janeiro, São Paulo, Pernambuco, Maranhão, Bahia, Sergipe, Paraná, Ceará, Minas Gerais, Mato Grosso do Sul, Paraíba and in the Federal District. In addition, it offers health and dental insurance; health and dental plans, and health and wellness solutions; and life insurance, private pension, and asset management solutions. The company was formerly known as Hospital Maternidade São Luiz S.A. Rede D'Or São Luiz S.A. is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
+    <t>TOTVS S.A. develops and sells management software, and productivity and collaboration platforms in Brazil and internationally. It offers an ERP platform, which integrates software management, social networks, real-time reporting, and other applications; business intelligence solutions; Fluig platform; and HR solutions, such as recruitment and selection, positions and salaries, electronic point, medicine and work safety, sheet, performance evaluation, and training and development solutions. The company also provides B2B credit, prepayment of receivables, payments via PIX, credit cards, and digital wallets and payment solutions; digital marketing, data intelligence and sales /digital commerce, and customer experience solutions; cloud, CRM, analytics, IPAAS, and electronic signature; and consulting and related services, as well as operates as an investment and equity investment fund. It serves services, manufacturing, agribusiness, logistics, education, construction, healthcare, financial services, retail, legal, distribution, and hospitality industries. TOTVS S.A. was founded in 1983 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Yduqs Participações S.A. provides higher education services in Brazil. The company offers face-to-face, semi-face-to-face, and distance education; and masters and doctorate courses. It also operate in two edtechs to prepare the candidates for exams and competitions named HardWork Medicina and Grupo Q, which offers Qconcursos solutions. It serves under stácio, Ibmec, IDOMED, Wyden, and Damásio brand names. The company was formerly known as Estácio Participações S.A. Yduqs Participações S.A. was founded in 1970 and is headquartered in Rio De Janeiro, Brazil.</t>
+  </si>
+  <si>
     <t>Ânima Holding S.A. operates as an education organization in Brazil. It operates in two segments, Inspirali Medical Education and Ânima Core. The company provides undergraduate courses in medicine; educational services in higher education and professional development courses; professional development services in postgraduate courses; and publishes books and magazine. It also offers consultancy services in technological innovation, technical support, and maintenance; and develops computer programs. The company was founded in 2003 and is based in São Paulo, Brazil.</t>
   </si>
   <si>
-    <t>TOTVS S.A. develops and sells management software, and productivity and collaboration platforms in Brazil and internationally. It offers an ERP platform, which integrates software management, social networks, real-time reporting, and other applications; business intelligence solutions; Fluig platform; and HR solutions, such as recruitment and selection, positions and salaries, electronic point, medicine and work safety, sheet, performance evaluation, and training and development solutions. The company also provides B2B credit, prepayment of receivables, payments via PIX, credit cards, and digital wallets and payment solutions; digital marketing, data intelligence and sales /digital commerce, and customer experience solutions; cloud, CRM, analytics, IPAAS, and electronic signature; and consulting and related services, as well as operates as an investment and equity investment fund. It serves services, manufacturing, agribusiness, logistics, education, construction, healthcare, financial services, retail, legal, distribution, and hospitality industries. TOTVS S.A. was founded in 1983 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Fras-le S.A. provides friction materials for braking systems and other products in Brazil, England, Argentina, the United States, China, India, Uruguay, the Netherlands, and internationally. It operates through Automakers and Replacement segments. The company offers brake linings and pads, railway and brake shoes, clutch facings, universal sheets, and industrial products; brake discs and drums, and master and wheel cylinders; and shock absorbers and kits, suspension brushings, pivots, suspension trays, ball joints, homokinetic joints, linkage bars, and wheel hubs. It also provides engine components comprising pistons, valves, water and oil pumps, fuel pumps, hoses, air filters, and gaskets; packed liquids consisting of brake fluids, coolants, anticorrosive, antifreezes, concentrated additives, and lubricators; and servo brakes, repair kits, actuators, polymer materials, bearings, crosspieces, shafts, crowns, pinions, flanges, tie rod ends, steering and connection bars, CV joints, braking plates, riveting machines, dies, and iron and steel scrap and composite materials. The company sells its products under the FRAS-LE, Controil, FREMAX, and NAKATA brands. It also exports its products. The company serves OEMs and aftermarkets. Fras-le S.A. was founded in 1954 and is based in Caxias Do Sul, Brazil. Fras-le S.A. operates as a subsidiary of Randon S.A. Implementos e Participações.</t>
-  </si>
-  <si>
-    <t>Gerdau S.A., together with its subsidiaries, operates as a steel producer company. The company operates through Brazil Business, North America Business, South America Business, and Special Steel Business segments. It provides semi-finished products, including billets, blooms, and slabs; common long-rolled products, such as rebars, wire rods, merchant bars, light shapes, and profiles to the construction and manufacturing industries; drawn products, including barbed and barbless fence wires, galvanized wires, fences, concrete reinforcing wire mesh, nails, and clamps for manufacturing, construction, and agricultural industries; and special steel products used in auto parts, light and heavy vehicles, and agricultural machinery, as well as in the oil and gas, wind energy, machinery and equipment, mining and rail, and other markets. The company also offers flat products, such as hot-rolled steel coils and heavy plates; and resells flat steel products. In addition, it operates mines that produce iron ore located in the Brazilian state of Minas Gerais. The company sells its products through independent distributors, direct sales from the mills, and its retail network. Gerdau S.A. was founded in 1901 and is based in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Yduqs Participações S.A. provides higher education services in Brazil. The company offers face-to-face, semi-face-to-face, and distance education; and masters and doctorate courses. It also operate in two edtechs to prepare the candidates for exams and competitions named HardWork Medicina and Grupo Q, which offers Qconcursos solutions. It serves under stácio, Ibmec, IDOMED, Wyden, and Damásio brand names. The company was formerly known as Estácio Participações S.A. Yduqs Participações S.A. was founded in 1970 and is headquartered in Rio De Janeiro, Brazil.</t>
+    <t>São Martinho S.A., together with its subsidiaries, engages in the production and sale of sugar, ethanol, and other sugarcane byproducts in Brazil. The company operates through Sugar, Ethanol, Electric Power, Real Estate Business, Yeast, and Other Products segment. It offers a range of raw sugar; hydrous ethanol, which is used direct fuel; anhydrous ethanol that is used as a gasoline additive in gasoline-powered vehicles; and industrial ethanol, which is primarily used in the production of paints, cosmetics, and alcoholic beverages. The company also generates electricity from sugarcane bagasse; provides byproducts, including yeast used in animal feed; and SMartLiO, a substitute for soybean oil used in the production of animal nutrition, biofuels, paint manufacturing, and chemical industries, as well as Dried Distillers Grains with Solubles, an animal nutrition for ruminants, pigs, horses, birds, fish, and pets. In addition, it is involved in the cultivation of sugarcane; development of real estate properties; import and export of goods, products, and raw materials; agricultural productions; and investment in other companies. The company was founded in 1914 and is based in São Paulo, Brazil. São Martinho S.A. is a subsidiary of LJN Participações S.A.</t>
   </si>
   <si>
     <t>Iguatemi S.A., together with its subsidiaries, operates shopping centers in Brazil. It also operates commercial towers. The company was formerly known as Jereissati Participações S.A. and changed its name to Iguatemi S.A. in November 2021. The company was founded in 1946 and is headquartered in São Paulo, Brazil.</t>
@@ -706,67 +667,61 @@
     <t>Randoncorp S.A. manufactures and sells trailers and semi-trailers in Latin America and internationally. The company offers trailers and semi-trailers, such as Bulk Trailer, dumper, tank, dry van, sider, refrigerated van, container chassis, sugarcane trailer, logging trailer, low bed semi-trailer, and silo; truck body, including general cargo truck body, beverages distribution, and dry-cargo body. It also provides rail wagons comprising hopper, gondola, flat, sider, tank, and telescopic; and genuine spare parts, such as Tarpaulin Bow, Tarpaulin, Fire Extinguisher Box, G-bracket and Hinge, fender, rear led light, Led light, grease, water reservoir, and red reflective sticker. In addition, the company offers salck and manual adjustor, landing gear, flat and locking and smooth washer, equalizer, locking bar, suspension bushings, brake chamber, hub, friction disc, camshaft, towing hitch, twist lock, roller fastener, locking grip, hubodometer, brake linings, anchor / return spring, brake shoes, rocker and king pin, fifth wheel, turntable, hub sealing, bearings, brake drum, spring brake, pneumatic spring, spring seat support, and aluminum wheel. Randoncorp S.A. was founded in 1949 and is headquartered in Caxias Do Sul, Brazil.</t>
   </si>
   <si>
-    <t>São Martinho S.A., together with its subsidiaries, engages in the production and sale of sugar, ethanol, and other sugarcane byproducts in Brazil. The company operates through Sugar, Ethanol, Electric Power, Real Estate Business, Yeast, and Other Products segment. It offers a range of raw sugar; hydrous ethanol, which is used direct fuel; anhydrous ethanol that is used as a gasoline additive in gasoline-powered vehicles; and industrial ethanol, which is primarily used in the production of paints, cosmetics, and alcoholic beverages. The company also generates electricity from sugarcane bagasse; provides byproducts, including yeast used in animal feed; and SMartLiO, a substitute for soybean oil used in the production of animal nutrition, biofuels, paint manufacturing, and chemical industries, as well as Dried Distillers Grains with Solubles, an animal nutrition for ruminants, pigs, horses, birds, fish, and pets. In addition, it is involved in the cultivation of sugarcane; development of real estate properties; import and export of goods, products, and raw materials; agricultural productions; and investment in other companies. The company was founded in 1914 and is based in São Paulo, Brazil. São Martinho S.A. is a subsidiary of LJN Participações S.A.</t>
-  </si>
-  <si>
     <t>Vamos Locação de Caminhões, Máquinas e Equipamentos S.A., together with its subsidiaries engages in the leasing, reselling, and selling of trucks, machinery, and equipment in Brazil. The company leases tractors, forklift trucks, agricultural machinery and implements, buses, and other vehicles; sells automobile parts and accessories; sells new and used tractors, machines, tires, air tubes, implements, motor vehicles, buses, and micro buses; and provides automobile maintenance and repair, and technical assistance and related services, as well as engages in the logistics and road transportation of cargos. It also offers parts, accessories, lubricants; and fleet management and rendering services, as well as act as a motor vehicle agency. In addition, the company sells fertilizers, herbicides, and seeds; and provides engineering services related to customization of trucks and buses, as well as provision of agricultural activities. Further, the company manufactures and sells truck trailers, truck bodies, wagons, road implements, truck cabs, and industrial machinery and equipment; and provides installation, renovation, repair, and maintenance of equipment and vehicles; information technology services; technical analyses on motor vehicles; forklift operator services; and outsourcing and managing of human resources. Vamos Locação de Caminhões, Máquinas e Equipamentos S.A. was incorporated in 2015 and is headquartered in São Paulo, Brazil. Vamos Locação de Caminhões, Máquinas e Equipamentos S.A. is a subsidiary of SIMPAR S.A.</t>
   </si>
   <si>
+    <t>Embraer S.A., together with its subsidiaries, designs, develops, manufactures, and sells aircraft and systems in North America, Latin America, the Asia Pacific, Brazil, Europe, and internationally. It operates through Commercial Aviation; Defense &amp; Security; Executive Aviation; Services &amp; Support; and Other segments. The Commercial Aviation segment develops, produces, and sells commercial jets. Its Defense &amp; Security segment develops and produces military aircraft and radars; and is involved in research and development of software and integrated information systems, communications, border monitoring and surveillance, space systems/satellites, and aircraft modernization services and services support, as well as command, control, communications, computer, intelligence, surveillance, and reconnaissance systems. The Executive Aviation segment develops, produces, and sells executive jets. Its Service &amp; Support segment provides field and technical support, flight operations solutions, aircraft modification, materials management, maintenance solutions, and training programs. The Other segment engages in the supply of structural parts and hydraulic systems; production of agricultural crop-spraying aircraft; development and certification of eVTOLs; creation of a maintenance and service network, and air traffic control system for eVTOLs; development and manufacture of electrical propulsion systems; cybersecurity; and software and technical products. It is also involved in leasing used aircraft; pilot, mechanic, and crew training; engineering services; retail trade, maintenance, and repair of computer products; information technology consulting, data processing, application service providers, and internet hosting; and fabrication of aircraft interiors. The company was formerly known as Embraer-Empresa Brasileira de Aeronáutica S.A. and changed its name to Embraer S.A. in November 2010. Embraer S.A. was incorporated in 1969 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
     <t>Localiza Rent a Car S.A. engages in car and fleet rental business in Brazil and internationally. The company is also involved in granting franchises; sale of cars; and provision of insurance solution. It serves individuals and legal entities. Localiza Rent a Car S.A. was founded in 1973 and is headquartered in Belo Horizonte, Brazil.</t>
   </si>
   <si>
+    <t>M. Dias Branco S.A. Indústria e Comércio de Alimentos engages in the manufacture, distribution, and sale of food products in Brazil. Its products include wheat and rice crackers and cookies, wheat and corn pasta, wheat flour and bran products, cake mixes, margarines and vegetable shortenings, cakes, corn and wheat snacks, toasts, chocolate-iced cookies, peanut butter, cereal bits, spices, and chocolates, as well as healthy foods, seasonings, sauces, and condiments. In addition, the company engages in the wheat milling activities. It offers its products under various brand names, such as Adria, Adorita, Basilar, Bonsabor, Estrela, Delicitos, Isabela, Finna, Fortaleza, Jasmine, Las Acacias, Medalha de Ouro, Pelaggio, Pilar, Piraquê, Predilleto, Puro Sabor, Richester, Salsitos, Vitarella, Zabet, Fit Food, Frontera, Smart, Taste&amp;Co, Jasmine, and Las Acacias brands. The company also exports its products. M. Dias Branco S.A. Indústria e Comércio de Alimentos was founded in 1936 and is headquartered in Eusébio, Brazil.</t>
+  </si>
+  <si>
     <t>Companhia Brasileira de Alumínio produces and sells aluminum products. The company provides bauxite, hydrate, alumina, molten aluminum, ingots, secondary ingots, slabs, billets, rod, caster rolls, caster sheet and coils, hot-rolled sheet and coils, roofing and siding, foil, coated foil, extruded profiles, surface treatment lines, custom parts, and components and services. It also owns and operates hydroelectric power plants. The company serves e automotive, building and construction, energy, agribusiness, consumer goods, packaging, transportation, and other industries. It operates in Brazil, South America, North America, and Europe. Companhia Brasileira de Alumínio was incorporated in 1941 and is headquartered in São Paulo, Brazil. Companhia Brasileira de Alumínio operates as a subsidiary of Votorantim S.A.</t>
   </si>
   <si>
-    <t>Embraer S.A., together with its subsidiaries, designs, develops, manufactures, and sells aircraft and systems in North America, Latin America, the Asia Pacific, Brazil, Europe, and internationally. It operates through Commercial Aviation; Defense &amp; Security; Executive Aviation; Services &amp; Support; and Other segments. The Commercial Aviation segment develops, produces, and sells commercial jets. Its Defense &amp; Security segment develops and produces military aircraft and radars; and is involved in research and development of software and integrated information systems, communications, border monitoring and surveillance, space systems/satellites, and aircraft modernization services and services support, as well as command, control, communications, computer, intelligence, surveillance, and reconnaissance systems. The Executive Aviation segment develops, produces, and sells executive jets. Its Service &amp; Support segment provides field and technical support, flight operations solutions, aircraft modification, materials management, maintenance solutions, and training programs. The Other segment engages in the supply of structural parts and hydraulic systems; production of agricultural crop-spraying aircraft; development and certification of eVTOLs; creation of a maintenance and service network, and air traffic control system for eVTOLs; development and manufacture of electrical propulsion systems; cybersecurity; and software and technical products. It is also involved in leasing used aircraft; pilot, mechanic, and crew training; engineering services; retail trade, maintenance, and repair of computer products; information technology consulting, data processing, application service providers, and internet hosting; and fabrication of aircraft interiors. The company was formerly known as Embraer-Empresa Brasileira de Aeronáutica S.A. and changed its name to Embraer S.A. in November 2010. Embraer S.A. was incorporated in 1969 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>M. Dias Branco S.A. Indústria e Comércio de Alimentos engages in the manufacture, distribution, and sale of food products in Brazil. Its products include wheat and rice crackers and cookies, wheat and corn pasta, wheat flour and bran products, cake mixes, margarines and vegetable shortenings, cakes, corn and wheat snacks, toasts, chocolate-iced cookies, peanut butter, cereal bits, spices, and chocolates, as well as healthy foods, seasonings, sauces, and condiments. In addition, the company engages in the wheat milling activities. It offers its products under various brand names, such as Adria, Adorita, Basilar, Bonsabor, Estrela, Delicitos, Isabela, Finna, Fortaleza, Jasmine, Las Acacias, Medalha de Ouro, Pelaggio, Pilar, Piraquê, Predilleto, Puro Sabor, Richester, Salsitos, Vitarella, Zabet, Fit Food, Frontera, Smart, Taste&amp;Co, Jasmine, and Las Acacias brands. The company also exports its products. M. Dias Branco S.A. Indústria e Comércio de Alimentos was founded in 1936 and is headquartered in Eusébio, Brazil.</t>
-  </si>
-  <si>
     <t>TIM S.A., a telecommunications company, provides mobile, fixed, long-distance, data transmission, and broadband services in Brazil. The company offers landline switched telephone services in local, national, and international long-distance modes, as well as personal mobile, multimedia communication, and digital content services. It serves individuals and corporates, as well as small, medium, and large enterprises. The company is based in Rio de Janeiro, Brazil. TIM S.A. is a subsidiary of TIM Brasil Serviços e Participações S.A.</t>
   </si>
   <si>
     <t>Telefônica Brasil S.A., together with its subsidiaries, operates as a mobile telecommunications company in Brazil. Its fixed line voice services portfolio includes local, domestic long-distance, and international long-distance calls; and mobile portfolio comprises voice and broadband internet access through 3G, 4G, 4.5G, and 5G, as well as value-added, prepaid plans with data sharing features, family plans, voice mail, caller identification, voice minutes in unlimited bundles to mobile and fixed-line phones, and digital services and wireless roaming services. The company also offers data services, including broadband and mobile data services. In addition, it provides pay TV services through IPTV technologies; network services, such as rental of facilities; other services; wholesale services, including interconnection services to users of other network providers; and digital services, such as entertainment, cloud, and security and financial services. Further, the company offers multimedia communication services, which include audio, data, voice and other sounds, images, texts, and other information, as well as sells devices and accessories, such as smartphones, broadband USB modems, and other devices. Additionally, it provides telecommunications solutions and IT support to various industries, such as retail, distribution and digital channel, manufacturing, services, financial institutions, government, etc. It markets and sells its solutions through own stores, dealers, retail and distribution channels, door-to-door sales, and outbound tele sales. The company was formerly known as Telecomunicações de São Paulo S.A. - TELESP and changed its name to Telefônica Brasil S.A. in October 2011. Telefônica Brasil S.A. was incorporated in 1998 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
+    <t>Natura Cosméticos S.A. engages in the development, manufacture, distribution, and marketing of cosmetics, fragrances, and personal hygiene products in Brazil, Peru, Colombia, Chile, Argentina, Uruguay, and Ecuador. It offers its products through retail markets, e-commerce, business-to business, and franchise channels under the Avon and Natura brands. Natura Cosméticos S.A. was founded in 1969 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
     <t>Centrais Elétricas Brasileiras S.A. - Eletrobrás, through its subsidiaries, engages in the generation, transmission, and commercialization of electricity in Brazil. The company generates electricity through hydroelectric, thermoelectric, nuclear, wind, and solar plants. It also owns and operates 44 hydroelectric plants with a total capacity of 42,293.5 megawatt (MW); and 66,539.17 kilometers of transmission lines. Centrais Elétricas Brasileiras S.A.  Eletrobrás was incorporated in 1962 and is headquartered in Rio de Janeiro, Brazil.</t>
   </si>
   <si>
-    <t>Natura Cosméticos S.A. engages in the development, manufacture, distribution, and marketing of cosmetics, fragrances, and personal hygiene products in Brazil, Peru, Colombia, Chile, Argentina, Uruguay, and Ecuador. It offers its products through retail markets, e-commerce, business-to business, and franchise channels under the Avon and Natura brands. Natura Cosméticos S.A. was founded in 1969 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
     <t>Smartfit Escola de Ginástica e Dança S.A. operates a network of Smart Fit gyms in Latin America. It offers digital fitness services under the Queima Diária brand. The company operates through owned and franchised units in Brazil, Mexico, Colombia, Chile, Peru, Argentina, Paraguay, Uruguay, Panama, Costa Rica, Dominican Republic, Ecuador, Guatemala, El Salvador and Honduras under the Smart Fit and Bio Ritmo brands. Smartfit Escola de Ginástica e Dança S.A. was founded in 1996 and is based in São Paulo, Brazil.</t>
   </si>
   <si>
     <t>Usinas Siderúrgicas de Minas Gerais S.A. processes, manufactures, and markets flat steel products in Brazil and internationally. It operates in two segments, Mining and Logistics, and Steelmaking. The company extracts and process iron ore, such as pellet and sinter feed, and granulated iron ore; provides storage and handling of iron ore and steel products; and road cargo transportation services; and operates highway and railway cargo terminals. It also manufactures and sells steel products; manufactures and installs equipment for various industries; and transforms cold-rolled coils into hot-dip galvanized coils. In addition, the company provides technology transfer services for steel industry; project management and services for civil construction and capital goods industry; road transportation of flat steel; rectification of cylinders and rolling mill rolls; hot-dip galvanizing services; texturing and chrome plating of cylinders; and steel transformation solutions, as well as operates as a distribution center. Further, it offers thick plates, hot strips, cold rolled, electrogalvanized, hot dip galvanized, and synchron. The company serves automotive, construction, distribution, energy, white line, oil and gas, and machines and equipment markets. Usinas Siderúrgicas de Minas Gerais S.A. was founded in 1956 and is headquartered in Belo Horizonte, Brazil.</t>
   </si>
   <si>
+    <t>Hypera S.A. operates as a pharmaceutical company in Brazil. It offers prescription products under the Adacne, Addera, apri, AmpliumG, pleased, Celestamine, Celestone, Celestone Soluspan, Cizax, deciprax, Derive C Micro, Micro Drift, Dermotil Fusid, Digedrat, diprogent, Diprosalic, Diprosone, diprospan, Emprol XR, Flow, Garasone, Halobex, Lipanon, Luna, moon, Lydian, macrodantin, MaxSulid, Milgamma, Mioflex  A, Nesina, Novotram, oximax, peridal, Peridal Suspension, PredSim, Pressaliv, Quadriderm, Rizi, Rizi M, Softalm, Tacroz, Tinodin, Umma, and velunid brands. The company also provides sun protection and moisturizing skin care products under the Mantecorp Skincare brands; similar products under the Doralgina, Dropy D, Equilibrisse, balance, Flavonid, Histamin, neofresh, neolefrin, neoquimica Vitamins, Neosorum, and Torsilax brands; and over-the-counter drugs under the Apracur, Benegrip, Buscopan, Coristina D Pro, Engov, Epocler, Estomazil, and Neosaldina brands, as well as similar and generic drugs under the Neo Química brand. In addition, it offers nutritional and vitamin supplement products under the Tamarine, Biotônico Fontoura, and Zero-Cal brands; and generic medicines under the Hydroxyzine, Sodium Diclofenac, Dipyron, Ibuprofen, Losartan Potassium, Mal Dexchlorpheniramine, Naproxene, Paracetamol, Simethicon, Loratadine, Omeprazole, Tadalaphyl, and Desogestrel brands. The company was formerly known as Hypermarcas S.A. and changed its name to Hypera S.A. in February 2018. Hypera S.A. was founded in 1999 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Allos S.A. provides planning, development, administration, and sales services to third-party shopping centers in Brazil. It provides administration services, including financial, legal, commercial, and operational management; brokerage and advisory services; and operation of parking lots in shopping centers; as well as engages in management of shopping malls and condominiums. The company was formerly known as Aliansce Shopping Centers S.A. and changed its name to Allos S.A. in October 2023. Allos S.A. is headquartered in Rio De Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>Alpargatas S.A. manufactures and sells footwear and accessories in Brazil and internationally. The company offers its products under the Havaianas, ioasys, and Rothys brands. The company was formerly known as São Paulo Alpargatas S.A. and changed its name to Alpargatas S.A. in 2010. The company was incorporated in 1907 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
     <t>Magazine Luiza S.A. engages in the retail sale of consumer goods. It operates through Retail, Financial Operations, Insurance Operations, and Other Services segments. The company also grants credit and provides extended warranties for its products. In addition, it is involved in the provision of consortium and management services; and e-commerce of perfumes, cosmetics, sports, and fashion products, as well as product delivery management and software development services. Further, the company provides integration, logistics, and technological solutions, as well as resale goods and provision of services in the stores, electronic and food delivery management platform. It serves through physical stores, e-commerce platform, and SuperApp. The company was founded in 1957 and is headquartered in Franca, Brazil. Magazine Luiza S.A. operates as a subsidiary of LTD Administração e Participação S.A.</t>
   </si>
   <si>
-    <t>Hypera S.A. operates as a pharmaceutical company in Brazil. It offers prescription products under the Adacne, Addera, apri, AmpliumG, pleased, Celestamine, Celestone, Celestone Soluspan, Cizax, deciprax, Derive C Micro, Micro Drift, Dermotil Fusid, Digedrat, diprogent, Diprosalic, Diprosone, diprospan, Emprol XR, Flow, Garasone, Halobex, Lipanon, Luna, moon, Lydian, macrodantin, MaxSulid, Milgamma, Mioflex  A, Nesina, Novotram, oximax, peridal, Peridal Suspension, PredSim, Pressaliv, Quadriderm, Rizi, Rizi M, Softalm, Tacroz, Tinodin, Umma, and velunid brands. The company also provides sun protection and moisturizing skin care products under the Mantecorp Skincare brands; similar products under the Doralgina, Dropy D, Equilibrisse, balance, Flavonid, Histamin, neofresh, neolefrin, neoquimica Vitamins, Neosorum, and Torsilax brands; and over-the-counter drugs under the Apracur, Benegrip, Buscopan, Coristina D Pro, Engov, Epocler, Estomazil, and Neosaldina brands, as well as similar and generic drugs under the Neo Química brand. In addition, it offers nutritional and vitamin supplement products under the Tamarine, Biotônico Fontoura, and Zero-Cal brands; and generic medicines under the Hydroxyzine, Sodium Diclofenac, Dipyron, Ibuprofen, Losartan Potassium, Mal Dexchlorpheniramine, Naproxene, Paracetamol, Simethicon, Loratadine, Omeprazole, Tadalaphyl, and Desogestrel brands. The company was formerly known as Hypermarcas S.A. and changed its name to Hypera S.A. in February 2018. Hypera S.A. was founded in 1999 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Allos S.A. provides planning, development, administration, and sales services to third-party shopping centers in Brazil. It provides administration services, including financial, legal, commercial, and operational management; brokerage and advisory services; and operation of parking lots in shopping centers; as well as engages in management of shopping malls and condominiums. The company was formerly known as Aliansce Shopping Centers S.A. and changed its name to Allos S.A. in October 2023. Allos S.A. is headquartered in Rio De Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Alpargatas S.A. manufactures and sells footwear and accessories in Brazil and internationally. The company offers its products under the Havaianas, ioasys, and Rothys brands. The company was formerly known as São Paulo Alpargatas S.A. and changed its name to Alpargatas S.A. in 2010. The company was incorporated in 1907 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Banco Pan S.A., together with its subsidiaries, operate as a multiple solutions bank in Brazil. It operates through Financial and Other segments. The company offers current accounts; payroll-deductible credit; debit and credit cards; vehicle financing for pre-owned cars and new motorcycles; personal loans; emergency advances and overdraft facilities; car equity, buy now pay later, auto loans, FGTS loans, and payroll loans; investments; Mosaico and Mobiauto marketplaces; PAN health services; emergency limits and salary portability; prepaid cell phone top-ups, authorized direct debit, and loyalty programs; and insurance services. It also provides corporate loans; construction financing for developers and construction firms; real estate financing; and acquisition services for real estate receivables. The company was formerly known as Banco Panamericano S.A. and changed its name to Banco Pan S.A. in August 2014. The company was incorporated in 1964 and is headquartered in São Paulo, Brazil. Banco Pan S.A. operates as a subsidiary of Banco BTG Pactual S.A.</t>
-  </si>
-  <si>
     <t>Rumo S.A., through its subsidiaries, provides rail transportation services. The company operates through North Operations, South Operations, and Container Operations segments. The North Operations segment engages in the railway, highway, and transshipment operations. The South Operations segment comprises of rail and transhipment operations in the area of, Rumo Malha Sul and Rumo Malha Oeste concessions. The Container Operations segment is involved in the container logistics and operations. Rumo S.A. offers logistics services primarily for exporting commodities, including integrated solution for transportation, movement, storage, and shipping from the production centers to the main ports in the south and southeast of Brazil. The company was founded in 2008 and is based in Curitiba, Brazil.</t>
   </si>
   <si>
     <t>Locaweb Serviços de Internet S.A. offers hosting, software licensing, and technical support services in Brazil. It operates through two segments, Be Online and Software as a Service &amp; Solutions (Be Online &amp; SaaS), and Commerce. The Be Online and Software as a Service &amp; Solutions (Be Online &amp; SaaS) segment provides hosting and cloud services; and SaaS solutions, including email and marketing intelligence software and site builder under the Locaweb, Allin, Nextios, Kinghost, Delivery Diretso, Etus, Social Mine, and Connectplug brands. Its Commerce segment offers e-commerce solutions, platform, marketplace integration, and sub-acquiring business services under the Tray, Tray Corp, Yapay, Melhor Envio, Ideris, Samurai, Credisfera, Vindi, Bagy Sul, Bling, PagCerto, Bagy, Octadesk, Squid, and Sintese names. The company provides data center, telecommunications, and intermediation and collection services. Locaweb Serviços de Internet S.A. was founded in 1998 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
+    <t>Orizon Valorização de Resíduos S.A. operates as a waste recovery process company. It engages in disposal of solid waste treatment business; energy, biogas, and carbon credits units business captures and treats gases from the decomposition of waste for the sale or reutilization of methane gas. The company also produces energy from biogas-fueled power plant; and trades in carbon credit. The company's Waste Processing and Industrialization business develops plants for processing materials from the industrial sector, recycling solid urban waste, and the direct burning of waste for energy generation. The company's Environmental Engineering business offers services in the areas of recovery of degraded areas, remediation of contaminated areas, environmental diagnosis and monitoring, waste management, and the cleaning of oil industry tanks. The company was formerly known as Haztec Investimentos e Participações S.A. and changed its name to Orizon Valorização de Resíduos S.A. in August 2020. Orizon Valorização de Resíduos S.A. was founded in 1999 and is based in São Paulo, Brazil. Orizon Valorização de Resíduos S.A. subsidiary of Inovatec Participações S.A.</t>
+  </si>
+  <si>
     <t>Serena Energia S.A. generates and sells renewable energy. It generates through electricity through wind, water, and solar sources. The company was formerly known as Omega Energia S.A. and changed its name to Serena Energia S.A. in December 2023. The company was founded in 2008 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Orizon Valorização de Resíduos S.A. operates as a waste recovery process company. It engages in disposal of solid waste treatment business; energy, biogas, and carbon credits units business captures and treats gases from the decomposition of waste for the sale or reutilization of methane gas. The company also produces energy from biogas-fueled power plant; and trades in carbon credit. The company's Waste Processing and Industrialization business develops plants for processing materials from the industrial sector, recycling solid urban waste, and the direct burning of waste for energy generation. The company's Environmental Engineering business offers services in the areas of recovery of degraded areas, remediation of contaminated areas, environmental diagnosis and monitoring, waste management, and the cleaning of oil industry tanks. The company was formerly known as Haztec Investimentos e Participações S.A. and changed its name to Orizon Valorização de Resíduos S.A. in August 2020. Orizon Valorização de Resíduos S.A. was founded in 1999 and is based in São Paulo, Brazil. Orizon Valorização de Resíduos S.A. subsidiary of Inovatec Participações S.A.</t>
   </si>
   <si>
     <t>Aura Minerals Inc., a gold and copper production company, focuses on the development and operation of gold and base metal projects in the Americas. It operates through Minosa Mine, Apoena Mine, the Aranzazu Mine, Corporate, Almas Mine, and Borborema Projects segments. The company primarily explores gold, copper, and silver deposits. The company was formerly known as Aura Gold Inc. and changed its name to Aura Minerals Inc. in July 2007. The company was incorporated in 1946 and is headquartered in Coconut Grove, Florida.</t>
@@ -1160,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P128"/>
+  <dimension ref="A1:P120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1221,7 +1176,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1233,13 +1188,13 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="I2">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="J2">
         <v>21.85</v>
@@ -1248,19 +1203,19 @@
         <v>45.44</v>
       </c>
       <c r="L2">
-        <v>6.519999980926514</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="M2">
         <v>149.4638417812148</v>
       </c>
       <c r="N2">
-        <v>235.1227003668648</v>
+        <v>219.9121558429518</v>
       </c>
       <c r="O2">
-        <v>2192.39</v>
+        <v>2088.34</v>
       </c>
       <c r="P2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1271,46 +1226,46 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="I3">
-        <v>0.85</v>
+        <v>3.24</v>
       </c>
       <c r="J3">
-        <v>15</v>
+        <v>29.21</v>
       </c>
       <c r="K3">
-        <v>6.5</v>
+        <v>11.81</v>
       </c>
       <c r="L3">
-        <v>5.460000038146973</v>
+        <v>38.27000045776367</v>
       </c>
       <c r="M3">
-        <v>46.83748498798798</v>
+        <v>88.10123296526559</v>
       </c>
       <c r="N3">
-        <v>174.7252728058723</v>
+        <v>-23.67389691505925</v>
       </c>
       <c r="O3">
-        <v>757.83</v>
+        <v>130.21</v>
       </c>
       <c r="P3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1321,7 +1276,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -1333,34 +1288,34 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="I4">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="J4">
-        <v>29.21</v>
+        <v>18.63</v>
       </c>
       <c r="K4">
-        <v>11.81</v>
+        <v>5.03</v>
       </c>
       <c r="L4">
-        <v>37.93999862670898</v>
+        <v>24.56999969482422</v>
       </c>
       <c r="M4">
-        <v>88.10123296526559</v>
+        <v>45.91786417071248</v>
       </c>
       <c r="N4">
-        <v>-23.01001302768431</v>
+        <v>-24.17582323403735</v>
       </c>
       <c r="O4">
-        <v>132.21</v>
+        <v>86.89</v>
       </c>
       <c r="P4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1371,7 +1326,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1383,34 +1338,34 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="I5">
-        <v>4.77</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
-        <v>18.63</v>
+        <v>5.25</v>
       </c>
       <c r="K5">
-        <v>5.03</v>
+        <v>4.46</v>
       </c>
       <c r="L5">
-        <v>24.01000022888184</v>
+        <v>32.04000091552734</v>
       </c>
       <c r="M5">
-        <v>45.91786417071248</v>
+        <v>22.95294098803027</v>
       </c>
       <c r="N5">
-        <v>-22.40733101872355</v>
+        <v>-83.61423267795311</v>
       </c>
       <c r="O5">
-        <v>91.23999999999999</v>
+        <v>-28.36</v>
       </c>
       <c r="P5" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1418,49 +1373,49 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="I6">
-        <v>7.32</v>
+        <v>6.99</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="K6">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="L6">
-        <v>23.90999984741211</v>
+        <v>20.20000076293945</v>
       </c>
       <c r="M6">
-        <v>15.65327441783348</v>
+        <v>23.66033072465387</v>
       </c>
       <c r="N6">
-        <v>-86.19824332471849</v>
+        <v>-57.67326892538283</v>
       </c>
       <c r="O6">
-        <v>-34.53</v>
+        <v>17.13</v>
       </c>
       <c r="P6" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1471,46 +1426,46 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I7">
-        <v>7.33</v>
+        <v>7.58</v>
       </c>
       <c r="J7">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="K7">
-        <v>4.46</v>
+        <v>3.39</v>
       </c>
       <c r="L7">
-        <v>32.18999862670898</v>
+        <v>25.95999908447266</v>
       </c>
       <c r="M7">
-        <v>22.95294098803027</v>
+        <v>16.10388151968338</v>
       </c>
       <c r="N7">
-        <v>-83.69058644307017</v>
+        <v>-86.90292711900122</v>
       </c>
       <c r="O7">
-        <v>-28.7</v>
+        <v>-37.97</v>
       </c>
       <c r="P7" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1518,7 +1473,7 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1533,13 +1488,13 @@
         <v>10</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="J8">
         <v>9.949999999999999</v>
@@ -1548,19 +1503,19 @@
         <v>2.27</v>
       </c>
       <c r="L8">
-        <v>10.90999984741211</v>
+        <v>11.02999973297119</v>
       </c>
       <c r="M8">
         <v>22.54320851165601</v>
       </c>
       <c r="N8">
-        <v>-8.79926545223395</v>
+        <v>-9.791475603964217</v>
       </c>
       <c r="O8">
-        <v>106.63</v>
+        <v>104.38</v>
       </c>
       <c r="P8" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1571,46 +1526,46 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H9">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I9">
-        <v>7.37</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
-        <v>9.619999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="K9">
-        <v>3.16</v>
+        <v>5.2</v>
       </c>
       <c r="L9">
-        <v>22.81999969482422</v>
+        <v>34.97000122070312</v>
       </c>
       <c r="M9">
-        <v>26.15304953537924</v>
+        <v>50.84977876058066</v>
       </c>
       <c r="N9">
-        <v>-57.84399593054377</v>
+        <v>-36.80297618372331</v>
       </c>
       <c r="O9">
-        <v>14.61</v>
+        <v>45.41</v>
       </c>
       <c r="P9" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1618,10 +1573,10 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -1633,34 +1588,34 @@
         <v>10</v>
       </c>
       <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10">
         <v>7</v>
       </c>
-      <c r="H10">
-        <v>25</v>
-      </c>
       <c r="I10">
-        <v>7.55</v>
+        <v>3.28</v>
       </c>
       <c r="J10">
-        <v>8.550000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K10">
-        <v>2.91</v>
+        <v>1.68</v>
       </c>
       <c r="L10">
-        <v>21.65999984741211</v>
+        <v>5.510000228881836</v>
       </c>
       <c r="M10">
-        <v>23.66033072465387</v>
+        <v>18.22805529945528</v>
       </c>
       <c r="N10">
-        <v>-60.52631551139398</v>
+        <v>59.52812404481125</v>
       </c>
       <c r="O10">
-        <v>9.24</v>
+        <v>230.82</v>
       </c>
       <c r="P10" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1668,10 +1623,10 @@
         <v>25</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -1686,31 +1641,31 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>7.93</v>
+        <v>4.89</v>
       </c>
       <c r="J11">
-        <v>4.47</v>
+        <v>38.99</v>
       </c>
       <c r="K11">
-        <v>1.75</v>
+        <v>7.48</v>
       </c>
       <c r="L11">
-        <v>13.89999961853027</v>
+        <v>37.02000045776367</v>
       </c>
       <c r="M11">
-        <v>13.26673471506836</v>
+        <v>81.00627753452198</v>
       </c>
       <c r="N11">
-        <v>-67.8417257361577</v>
+        <v>5.321446563686338</v>
       </c>
       <c r="O11">
-        <v>-4.56</v>
+        <v>118.82</v>
       </c>
       <c r="P11" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1721,7 +1676,7 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -1733,34 +1688,34 @@
         <v>10</v>
       </c>
       <c r="G12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H12">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="I12">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>38.99</v>
+        <v>59.17</v>
       </c>
       <c r="K12">
-        <v>7.48</v>
+        <v>16.33</v>
       </c>
       <c r="L12">
-        <v>34.4900016784668</v>
+        <v>127.3000030517578</v>
       </c>
       <c r="M12">
-        <v>81.00627753452198</v>
+        <v>147.4467268202316</v>
       </c>
       <c r="N12">
-        <v>13.04725457390365</v>
+        <v>-53.51924699016497</v>
       </c>
       <c r="O12">
-        <v>134.87</v>
+        <v>15.83</v>
       </c>
       <c r="P12" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1768,49 +1723,49 @@
         <v>27</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13">
+        <v>42</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13">
         <v>9</v>
       </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <v>8</v>
-      </c>
-      <c r="F13">
-        <v>10</v>
-      </c>
       <c r="G13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H13">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="I13">
-        <v>3.34</v>
+        <v>5.2</v>
       </c>
       <c r="J13">
-        <v>8.789999999999999</v>
+        <v>30.97</v>
       </c>
       <c r="K13">
-        <v>1.68</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>5.519999980926514</v>
+        <v>31.3700008392334</v>
       </c>
       <c r="M13">
-        <v>18.22805529945528</v>
+        <v>64.66026600625766</v>
       </c>
       <c r="N13">
-        <v>59.23913098500822</v>
+        <v>-1.275106243328916</v>
       </c>
       <c r="O13">
-        <v>230.22</v>
+        <v>106.12</v>
       </c>
       <c r="P13" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1821,46 +1776,46 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>8</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H14">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I14">
-        <v>7.44</v>
+        <v>5.62</v>
       </c>
       <c r="J14">
-        <v>59.17</v>
+        <v>30.97</v>
       </c>
       <c r="K14">
-        <v>16.33</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>120.4100036621094</v>
+        <v>33.9900016784668</v>
       </c>
       <c r="M14">
-        <v>147.4467268202316</v>
+        <v>64.66026600625766</v>
       </c>
       <c r="N14">
-        <v>-50.85956465374677</v>
+        <v>-8.884970665888547</v>
       </c>
       <c r="O14">
-        <v>22.45</v>
+        <v>90.23</v>
       </c>
       <c r="P14" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1868,49 +1823,49 @@
         <v>29</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H15">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="I15">
-        <v>6.62</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
-        <v>22.1</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K15">
-        <v>5.2</v>
+        <v>3.16</v>
       </c>
       <c r="L15">
-        <v>34.36000061035156</v>
+        <v>26.6299991607666</v>
       </c>
       <c r="M15">
-        <v>50.84977876058066</v>
+        <v>26.15304953537924</v>
       </c>
       <c r="N15">
-        <v>-35.68102558955722</v>
+        <v>-63.87532743833903</v>
       </c>
       <c r="O15">
-        <v>47.99</v>
+        <v>-1.79</v>
       </c>
       <c r="P15" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1918,49 +1873,49 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16">
         <v>8</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>14</v>
       </c>
       <c r="H16">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="I16">
-        <v>5.19</v>
+        <v>7.35</v>
       </c>
       <c r="J16">
-        <v>30.97</v>
+        <v>8.98</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>1.96</v>
       </c>
       <c r="L16">
-        <v>31.20999908447266</v>
+        <v>14.56999969482422</v>
       </c>
       <c r="M16">
-        <v>64.66026600625766</v>
+        <v>19.90020100400999</v>
       </c>
       <c r="N16">
-        <v>-0.7689813890191965</v>
+        <v>-38.36650522930336</v>
       </c>
       <c r="O16">
-        <v>107.18</v>
+        <v>36.58</v>
       </c>
       <c r="P16" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1968,49 +1923,49 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>8</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H17">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>5.59</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="J17">
-        <v>30.97</v>
+        <v>18.64</v>
       </c>
       <c r="K17">
-        <v>6</v>
+        <v>4.69</v>
       </c>
       <c r="L17">
-        <v>33.65000152587891</v>
+        <v>38.11999893188477</v>
       </c>
       <c r="M17">
-        <v>64.66026600625766</v>
+        <v>44.3507158905017</v>
       </c>
       <c r="N17">
-        <v>-7.96434295498567</v>
+        <v>-51.10178247038482</v>
       </c>
       <c r="O17">
-        <v>92.16</v>
+        <v>16.35</v>
       </c>
       <c r="P17" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2018,49 +1973,49 @@
         <v>32</v>
       </c>
       <c r="B18">
+        <v>18</v>
+      </c>
+      <c r="C18">
+        <v>37</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="G18">
         <v>17</v>
       </c>
-      <c r="C18">
-        <v>39</v>
-      </c>
-      <c r="D18">
-        <v>4</v>
-      </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-      <c r="F18">
-        <v>10</v>
-      </c>
-      <c r="G18">
-        <v>16</v>
-      </c>
       <c r="H18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>8.94</v>
       </c>
       <c r="J18">
-        <v>4.46</v>
+        <v>3.67</v>
       </c>
       <c r="K18">
-        <v>0.9</v>
+        <v>1.06</v>
       </c>
       <c r="L18">
-        <v>5.380000114440918</v>
+        <v>9.609999656677246</v>
       </c>
       <c r="M18">
-        <v>9.503420436874293</v>
+        <v>9.355720175379338</v>
       </c>
       <c r="N18">
-        <v>-17.10037351061512</v>
+        <v>-61.8106125794708</v>
       </c>
       <c r="O18">
-        <v>76.64</v>
+        <v>-2.65</v>
       </c>
       <c r="P18" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2071,7 +2026,7 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D19">
         <v>4</v>
@@ -2083,34 +2038,34 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H19">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I19">
-        <v>8.67</v>
+        <v>6.81</v>
       </c>
       <c r="J19">
-        <v>3.67</v>
+        <v>19.91</v>
       </c>
       <c r="K19">
-        <v>1.06</v>
+        <v>3.83</v>
       </c>
       <c r="L19">
-        <v>9.090000152587891</v>
+        <v>26.36000061035156</v>
       </c>
       <c r="M19">
-        <v>9.355720175379338</v>
+        <v>41.42154330780059</v>
       </c>
       <c r="N19">
-        <v>-59.6259632739922</v>
+        <v>-24.46889400988348</v>
       </c>
       <c r="O19">
-        <v>2.92</v>
+        <v>57.14</v>
       </c>
       <c r="P19" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2121,7 +2076,7 @@
         <v>18</v>
       </c>
       <c r="C20">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -2133,34 +2088,34 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H20">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>7.35</v>
+        <v>9.51</v>
       </c>
       <c r="J20">
-        <v>8.98</v>
+        <v>4.47</v>
       </c>
       <c r="K20">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="L20">
-        <v>14.22999954223633</v>
+        <v>17.43000030517578</v>
       </c>
       <c r="M20">
-        <v>19.90020100400999</v>
+        <v>13.26673471506836</v>
       </c>
       <c r="N20">
-        <v>-36.8938841259531</v>
+        <v>-74.35456155056607</v>
       </c>
       <c r="O20">
-        <v>39.85</v>
+        <v>-23.89</v>
       </c>
       <c r="P20" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2171,7 +2126,7 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -2186,31 +2141,31 @@
         <v>20</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="I21">
-        <v>8.24</v>
+        <v>6.67</v>
       </c>
       <c r="J21">
-        <v>18.64</v>
+        <v>39.81</v>
       </c>
       <c r="K21">
-        <v>4.69</v>
+        <v>7.46</v>
       </c>
       <c r="L21">
-        <v>38.29000091552734</v>
+        <v>49.75</v>
       </c>
       <c r="M21">
-        <v>44.3507158905017</v>
+        <v>81.74416492936973</v>
       </c>
       <c r="N21">
-        <v>-51.31888337866005</v>
+        <v>-19.97989949748743</v>
       </c>
       <c r="O21">
-        <v>15.83</v>
+        <v>64.31</v>
       </c>
       <c r="P21" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2218,11 +2173,11 @@
         <v>36</v>
       </c>
       <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22">
         <v>21</v>
       </c>
-      <c r="C22">
-        <v>19</v>
-      </c>
       <c r="D22">
         <v>4</v>
       </c>
@@ -2233,34 +2188,34 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I22">
-        <v>6.56</v>
+        <v>4.72</v>
       </c>
       <c r="J22">
-        <v>19.91</v>
+        <v>31.27</v>
       </c>
       <c r="K22">
-        <v>3.83</v>
+        <v>4.93</v>
       </c>
       <c r="L22">
-        <v>24.8799991607666</v>
+        <v>23.30999946594238</v>
       </c>
       <c r="M22">
-        <v>41.42154330780059</v>
+        <v>58.89503162406825</v>
       </c>
       <c r="N22">
-        <v>-19.97588154505977</v>
+        <v>34.14843722192169</v>
       </c>
       <c r="O22">
-        <v>66.48999999999999</v>
+        <v>152.66</v>
       </c>
       <c r="P22" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2268,10 +2223,10 @@
         <v>37</v>
       </c>
       <c r="B23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D23">
         <v>4</v>
@@ -2283,34 +2238,34 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H23">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I23">
-        <v>4.67</v>
+        <v>9.65</v>
       </c>
       <c r="J23">
-        <v>31.27</v>
+        <v>4.44</v>
       </c>
       <c r="K23">
-        <v>4.93</v>
+        <v>1.44</v>
       </c>
       <c r="L23">
-        <v>22.95999908447266</v>
+        <v>13.92000007629395</v>
       </c>
       <c r="M23">
-        <v>58.89503162406825</v>
+        <v>11.99399849924953</v>
       </c>
       <c r="N23">
-        <v>36.19338522163624</v>
+        <v>-68.10344845068346</v>
       </c>
       <c r="O23">
-        <v>156.51</v>
+        <v>-13.84</v>
       </c>
       <c r="P23" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2318,10 +2273,10 @@
         <v>38</v>
       </c>
       <c r="B24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D24">
         <v>4</v>
@@ -2333,34 +2288,34 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H24">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I24">
-        <v>6.52</v>
+        <v>7.43</v>
       </c>
       <c r="J24">
-        <v>39.81</v>
+        <v>5.43</v>
       </c>
       <c r="K24">
-        <v>7.46</v>
+        <v>1.08</v>
       </c>
       <c r="L24">
-        <v>48.09999847412109</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="M24">
-        <v>81.74416492936973</v>
+        <v>11.48690558853863</v>
       </c>
       <c r="N24">
-        <v>-17.23492460936626</v>
+        <v>-32.6302764602309</v>
       </c>
       <c r="O24">
-        <v>69.95</v>
+        <v>42.52</v>
       </c>
       <c r="P24" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2371,7 +2326,7 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D25">
         <v>4</v>
@@ -2386,31 +2341,31 @@
         <v>24</v>
       </c>
       <c r="H25">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>9.31</v>
+        <v>5.77</v>
       </c>
       <c r="J25">
-        <v>24.83</v>
+        <v>15.12</v>
       </c>
       <c r="K25">
-        <v>7.03</v>
+        <v>2.24</v>
       </c>
       <c r="L25">
-        <v>64.77999877929688</v>
+        <v>12.97999954223633</v>
       </c>
       <c r="M25">
-        <v>62.66965174627988</v>
+        <v>27.60521689826037</v>
       </c>
       <c r="N25">
-        <v>-61.67026787914133</v>
+        <v>16.48690703570679</v>
       </c>
       <c r="O25">
-        <v>-3.26</v>
+        <v>112.68</v>
       </c>
       <c r="P25" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2421,7 +2376,7 @@
         <v>25</v>
       </c>
       <c r="C26">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -2436,31 +2391,31 @@
         <v>25</v>
       </c>
       <c r="H26">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="I26">
-        <v>7.47</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="J26">
-        <v>5.43</v>
+        <v>19.34</v>
       </c>
       <c r="K26">
-        <v>1.08</v>
+        <v>3.97</v>
       </c>
       <c r="L26">
-        <v>7.96999979019165</v>
+        <v>33.65000152587891</v>
       </c>
       <c r="M26">
-        <v>11.48690558853863</v>
+        <v>41.56375223677477</v>
       </c>
       <c r="N26">
-        <v>-31.86950887147479</v>
+        <v>-42.52600557796006</v>
       </c>
       <c r="O26">
-        <v>44.13</v>
+        <v>23.52</v>
       </c>
       <c r="P26" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2471,7 +2426,7 @@
         <v>25</v>
       </c>
       <c r="C27">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="D27">
         <v>4</v>
@@ -2486,31 +2441,31 @@
         <v>25</v>
       </c>
       <c r="H27">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I27">
-        <v>9.869999999999999</v>
+        <v>6.94</v>
       </c>
       <c r="J27">
-        <v>4.44</v>
+        <v>25.48</v>
       </c>
       <c r="K27">
-        <v>1.44</v>
+        <v>4.39</v>
       </c>
       <c r="L27">
-        <v>14.21000003814697</v>
+        <v>30.84000015258789</v>
       </c>
       <c r="M27">
-        <v>11.99399849924953</v>
+        <v>50.16758913880554</v>
       </c>
       <c r="N27">
-        <v>-68.75439839492788</v>
+        <v>-17.38002634911827</v>
       </c>
       <c r="O27">
-        <v>-15.59</v>
+        <v>62.67</v>
       </c>
       <c r="P27" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2521,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="C28">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -2536,31 +2491,31 @@
         <v>27</v>
       </c>
       <c r="H28">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I28">
-        <v>6.32</v>
+        <v>10.27</v>
       </c>
       <c r="J28">
-        <v>25.48</v>
+        <v>24.83</v>
       </c>
       <c r="K28">
-        <v>4.39</v>
+        <v>7.03</v>
       </c>
       <c r="L28">
-        <v>27.59000015258789</v>
+        <v>70.66999816894531</v>
       </c>
       <c r="M28">
-        <v>50.16758913880554</v>
+        <v>62.66965174627988</v>
       </c>
       <c r="N28">
-        <v>-7.64769895222337</v>
+        <v>-64.86486395451598</v>
       </c>
       <c r="O28">
-        <v>81.83</v>
+        <v>-11.32</v>
       </c>
       <c r="P28" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2568,10 +2523,10 @@
         <v>43</v>
       </c>
       <c r="B29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -2586,31 +2541,31 @@
         <v>28</v>
       </c>
       <c r="H29">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="I29">
-        <v>5.85</v>
+        <v>7.97</v>
       </c>
       <c r="J29">
-        <v>15.12</v>
+        <v>14.4</v>
       </c>
       <c r="K29">
-        <v>2.24</v>
+        <v>2.61</v>
       </c>
       <c r="L29">
-        <v>13.27999973297119</v>
+        <v>20.98999977111816</v>
       </c>
       <c r="M29">
-        <v>27.60521689826037</v>
+        <v>29.07988995852632</v>
       </c>
       <c r="N29">
-        <v>13.85542397610529</v>
+        <v>-31.39590206278076</v>
       </c>
       <c r="O29">
-        <v>107.87</v>
+        <v>38.54</v>
       </c>
       <c r="P29" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2621,7 +2576,7 @@
         <v>29</v>
       </c>
       <c r="C30">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -2633,34 +2588,34 @@
         <v>10</v>
       </c>
       <c r="G30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H30">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="I30">
-        <v>8.710000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="J30">
-        <v>19.34</v>
+        <v>11.7</v>
       </c>
       <c r="K30">
-        <v>3.97</v>
+        <v>2.85</v>
       </c>
       <c r="L30">
-        <v>34</v>
+        <v>28.86000061035156</v>
       </c>
       <c r="M30">
-        <v>41.56375223677477</v>
+        <v>27.39092002835976</v>
       </c>
       <c r="N30">
-        <v>-43.11764705882353</v>
+        <v>-59.45946031683928</v>
       </c>
       <c r="O30">
-        <v>22.25</v>
+        <v>-5.09</v>
       </c>
       <c r="P30" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2668,49 +2623,49 @@
         <v>45</v>
       </c>
       <c r="B31">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H31">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="I31">
-        <v>7.57</v>
+        <v>5.36</v>
       </c>
       <c r="J31">
-        <v>14.4</v>
+        <v>26.39</v>
       </c>
       <c r="K31">
-        <v>2.61</v>
+        <v>3.38</v>
       </c>
       <c r="L31">
-        <v>19.6299991607666</v>
+        <v>18.39999961853027</v>
       </c>
       <c r="M31">
-        <v>29.07988995852632</v>
+        <v>44.799101553491</v>
       </c>
       <c r="N31">
-        <v>-26.6428903941041</v>
+        <v>43.4239160169501</v>
       </c>
       <c r="O31">
-        <v>48.14</v>
+        <v>143.47</v>
       </c>
       <c r="P31" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2721,7 +2676,7 @@
         <v>31</v>
       </c>
       <c r="C32">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -2733,34 +2688,34 @@
         <v>10</v>
       </c>
       <c r="G32">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H32">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="I32">
-        <v>10.17</v>
+        <v>12.45</v>
       </c>
       <c r="J32">
-        <v>11.7</v>
+        <v>4.56</v>
       </c>
       <c r="K32">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="L32">
-        <v>28.45000076293945</v>
+        <v>33.52999877929688</v>
       </c>
       <c r="M32">
-        <v>27.39092002835976</v>
+        <v>16.6130671460751</v>
       </c>
       <c r="N32">
-        <v>-58.87522078649268</v>
+        <v>-86.40023809718843</v>
       </c>
       <c r="O32">
-        <v>-3.72</v>
+        <v>-50.45</v>
       </c>
       <c r="P32" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2768,10 +2723,10 @@
         <v>47</v>
       </c>
       <c r="B33">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C33">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -2786,31 +2741,31 @@
         <v>31</v>
       </c>
       <c r="H33">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I33">
-        <v>12.25</v>
+        <v>7.78</v>
       </c>
       <c r="J33">
-        <v>2.37</v>
+        <v>8.15</v>
       </c>
       <c r="K33">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="L33">
-        <v>12.9399995803833</v>
+        <v>11.14999961853027</v>
       </c>
       <c r="M33">
-        <v>7.518277728309855</v>
+        <v>16.0797621251062</v>
       </c>
       <c r="N33">
-        <v>-81.68469801503812</v>
+        <v>-26.90582709567586</v>
       </c>
       <c r="O33">
-        <v>-41.9</v>
+        <v>44.21</v>
       </c>
       <c r="P33" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2818,10 +2773,10 @@
         <v>48</v>
       </c>
       <c r="B34">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C34">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -2833,34 +2788,34 @@
         <v>10</v>
       </c>
       <c r="G34">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H34">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="I34">
-        <v>10.61</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="J34">
-        <v>15.09</v>
+        <v>19.34</v>
       </c>
       <c r="K34">
-        <v>3.69</v>
+        <v>3.97</v>
       </c>
       <c r="L34">
-        <v>38.88999938964844</v>
+        <v>37.93999862670898</v>
       </c>
       <c r="M34">
-        <v>35.39558235147432</v>
+        <v>41.56375223677477</v>
       </c>
       <c r="N34">
-        <v>-61.19825086956266</v>
+        <v>-49.02477411692621</v>
       </c>
       <c r="O34">
-        <v>-8.99</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="P34" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2871,46 +2826,46 @@
         <v>34</v>
       </c>
       <c r="C35">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G35">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H35">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="I35">
-        <v>12.5</v>
+        <v>8.15</v>
       </c>
       <c r="J35">
-        <v>4.56</v>
+        <v>34.12</v>
       </c>
       <c r="K35">
-        <v>2.69</v>
+        <v>6.19</v>
       </c>
       <c r="L35">
-        <v>33.36999893188477</v>
+        <v>50.54000091552734</v>
       </c>
       <c r="M35">
-        <v>16.6130671460751</v>
+        <v>68.93520871078871</v>
       </c>
       <c r="N35">
-        <v>-86.33503102799635</v>
+        <v>-32.48911875362204</v>
       </c>
       <c r="O35">
-        <v>-50.22</v>
+        <v>36.4</v>
       </c>
       <c r="P35" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2921,46 +2876,46 @@
         <v>34</v>
       </c>
       <c r="C36">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H36">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="I36">
-        <v>5.95</v>
+        <v>11.73</v>
       </c>
       <c r="J36">
-        <v>26.39</v>
+        <v>4.23</v>
       </c>
       <c r="K36">
-        <v>3.38</v>
+        <v>1.33</v>
       </c>
       <c r="L36">
-        <v>20.23999977111816</v>
+        <v>15.48999977111816</v>
       </c>
       <c r="M36">
-        <v>44.799101553491</v>
+        <v>11.25089996400288</v>
       </c>
       <c r="N36">
-        <v>30.38537696852</v>
+        <v>-72.69205898965193</v>
       </c>
       <c r="O36">
-        <v>121.34</v>
+        <v>-27.37</v>
       </c>
       <c r="P36" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2971,46 +2926,46 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H37">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>11.45</v>
+        <v>9.85</v>
       </c>
       <c r="J37">
-        <v>4.23</v>
+        <v>10.01</v>
       </c>
       <c r="K37">
-        <v>1.33</v>
+        <v>2.13</v>
       </c>
       <c r="L37">
-        <v>15.06999969482422</v>
+        <v>21.06999969482422</v>
       </c>
       <c r="M37">
-        <v>11.25089996400288</v>
+        <v>21.9027224335241</v>
       </c>
       <c r="N37">
-        <v>-71.93098815089697</v>
+        <v>-52.49169366405388</v>
       </c>
       <c r="O37">
-        <v>-25.34</v>
+        <v>3.95</v>
       </c>
       <c r="P37" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3018,49 +2973,49 @@
         <v>52</v>
       </c>
       <c r="B38">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D38">
         <v>4</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G38">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H38">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="I38">
-        <v>9.41</v>
+        <v>11.03</v>
       </c>
       <c r="J38">
-        <v>10.01</v>
+        <v>15.09</v>
       </c>
       <c r="K38">
-        <v>2.13</v>
+        <v>3.69</v>
       </c>
       <c r="L38">
-        <v>19.86000061035156</v>
+        <v>40.90999984741211</v>
       </c>
       <c r="M38">
-        <v>21.9027224335241</v>
+        <v>35.39558235147432</v>
       </c>
       <c r="N38">
-        <v>-49.59718181084788</v>
+        <v>-63.11415288124338</v>
       </c>
       <c r="O38">
-        <v>10.29</v>
+        <v>-13.48</v>
       </c>
       <c r="P38" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3071,46 +3026,46 @@
         <v>38</v>
       </c>
       <c r="C39">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39">
         <v>8</v>
       </c>
       <c r="F39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G39">
         <v>36</v>
       </c>
       <c r="H39">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="I39">
-        <v>5.98</v>
+        <v>12.69</v>
       </c>
       <c r="J39">
-        <v>22.31</v>
+        <v>2.37</v>
       </c>
       <c r="K39">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="L39">
-        <v>16.32999992370605</v>
+        <v>13.32999992370605</v>
       </c>
       <c r="M39">
-        <v>37.15415521849474</v>
+        <v>7.518277728309855</v>
       </c>
       <c r="N39">
-        <v>36.61971894814802</v>
+        <v>-82.22055503702445</v>
       </c>
       <c r="O39">
-        <v>127.52</v>
+        <v>-43.6</v>
       </c>
       <c r="P39" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3121,46 +3076,46 @@
         <v>39</v>
       </c>
       <c r="C40">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40">
         <v>8</v>
       </c>
       <c r="F40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G40">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H40">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I40">
-        <v>7.96</v>
+        <v>6.14</v>
       </c>
       <c r="J40">
-        <v>8.15</v>
+        <v>22.31</v>
       </c>
       <c r="K40">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="L40">
-        <v>11.07999992370605</v>
+        <v>16.89999961853027</v>
       </c>
       <c r="M40">
-        <v>16.0797621251062</v>
+        <v>37.15415521849474</v>
       </c>
       <c r="N40">
-        <v>-26.4440428148128</v>
+        <v>32.01183729932067</v>
       </c>
       <c r="O40">
-        <v>45.12</v>
+        <v>119.85</v>
       </c>
       <c r="P40" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3168,10 +3123,10 @@
         <v>55</v>
       </c>
       <c r="B41">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C41">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -3183,34 +3138,34 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H41">
-        <v>118</v>
+        <v>47</v>
       </c>
       <c r="I41">
-        <v>9.77</v>
+        <v>11.59</v>
       </c>
       <c r="J41">
-        <v>19.34</v>
+        <v>5.87</v>
       </c>
       <c r="K41">
-        <v>3.97</v>
+        <v>1.57</v>
       </c>
       <c r="L41">
-        <v>38.11000061035156</v>
+        <v>18.14999961853027</v>
       </c>
       <c r="M41">
-        <v>41.56375223677477</v>
+        <v>14.39992187478807</v>
       </c>
       <c r="N41">
-        <v>-49.25216559889846</v>
+        <v>-67.65840152411346</v>
       </c>
       <c r="O41">
-        <v>9.06</v>
+        <v>-20.66</v>
       </c>
       <c r="P41" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3218,10 +3173,10 @@
         <v>56</v>
       </c>
       <c r="B42">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C42">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -3233,34 +3188,34 @@
         <v>10</v>
       </c>
       <c r="G42">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H42">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I42">
-        <v>15.09</v>
+        <v>10.36</v>
       </c>
       <c r="J42">
-        <v>0.93</v>
+        <v>22.4</v>
       </c>
       <c r="K42">
-        <v>0.9399999999999999</v>
+        <v>4.83</v>
       </c>
       <c r="L42">
-        <v>14.23999977111816</v>
+        <v>50.22000122070312</v>
       </c>
       <c r="M42">
-        <v>4.435031003273822</v>
+        <v>49.33882852277706</v>
       </c>
       <c r="N42">
-        <v>-93.46910101862331</v>
+        <v>-55.39625755571343</v>
       </c>
       <c r="O42">
-        <v>-68.86</v>
+        <v>-1.75</v>
       </c>
       <c r="P42" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3268,10 +3223,10 @@
         <v>57</v>
       </c>
       <c r="B43">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C43">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -3283,34 +3238,34 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H43">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="I43">
-        <v>11.44</v>
+        <v>15.23</v>
       </c>
       <c r="J43">
-        <v>5.87</v>
+        <v>0.93</v>
       </c>
       <c r="K43">
-        <v>1.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L43">
-        <v>17.97999954223633</v>
+        <v>14.36999988555908</v>
       </c>
       <c r="M43">
-        <v>14.39992187478807</v>
+        <v>4.435031003273822</v>
       </c>
       <c r="N43">
-        <v>-67.35261318438333</v>
+        <v>-93.52818366453441</v>
       </c>
       <c r="O43">
-        <v>-19.91</v>
+        <v>-69.14</v>
       </c>
       <c r="P43" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3321,46 +3276,46 @@
         <v>43</v>
       </c>
       <c r="C44">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44">
         <v>3</v>
       </c>
-      <c r="E44">
-        <v>6</v>
-      </c>
-      <c r="F44">
-        <v>6</v>
-      </c>
       <c r="G44">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H44">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="I44">
-        <v>8.5</v>
+        <v>6.13</v>
       </c>
       <c r="J44">
-        <v>34.12</v>
+        <v>63.63</v>
       </c>
       <c r="K44">
-        <v>6.19</v>
+        <v>7.52</v>
       </c>
       <c r="L44">
-        <v>52.68999862670898</v>
+        <v>46.38999938964844</v>
       </c>
       <c r="M44">
-        <v>68.93520871078871</v>
+        <v>103.7602814182768</v>
       </c>
       <c r="N44">
-        <v>-35.2438776062061</v>
+        <v>37.16318352484939</v>
       </c>
       <c r="O44">
-        <v>30.83</v>
+        <v>123.67</v>
       </c>
       <c r="P44" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3371,7 +3326,7 @@
         <v>44</v>
       </c>
       <c r="C45">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -3386,31 +3341,31 @@
         <v>43</v>
       </c>
       <c r="H45">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I45">
-        <v>7.27</v>
+        <v>11.29</v>
       </c>
       <c r="J45">
-        <v>11.9</v>
+        <v>11.51</v>
       </c>
       <c r="K45">
-        <v>1.57</v>
+        <v>2.51</v>
       </c>
       <c r="L45">
-        <v>11.17000007629395</v>
+        <v>28.68000030517578</v>
       </c>
       <c r="M45">
-        <v>20.50286565336661</v>
+        <v>25.4956319788312</v>
       </c>
       <c r="N45">
-        <v>6.535361850671162</v>
+        <v>-59.8675039137889</v>
       </c>
       <c r="O45">
-        <v>83.55</v>
+        <v>-11.1</v>
       </c>
       <c r="P45" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3421,7 +3376,7 @@
         <v>45</v>
       </c>
       <c r="C46">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -3436,31 +3391,31 @@
         <v>44</v>
       </c>
       <c r="H46">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="I46">
-        <v>10.74</v>
+        <v>7.71</v>
       </c>
       <c r="J46">
-        <v>22.4</v>
+        <v>11.9</v>
       </c>
       <c r="K46">
-        <v>4.83</v>
+        <v>1.57</v>
       </c>
       <c r="L46">
-        <v>51.02000045776367</v>
+        <v>12.48999977111816</v>
       </c>
       <c r="M46">
-        <v>49.33882852277706</v>
+        <v>20.50286565336661</v>
       </c>
       <c r="N46">
-        <v>-56.09564915911049</v>
+        <v>-4.723777277262064</v>
       </c>
       <c r="O46">
-        <v>-3.3</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="P46" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3468,10 +3423,10 @@
         <v>61</v>
       </c>
       <c r="B47">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -3483,34 +3438,34 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H47">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="I47">
-        <v>11.04</v>
+        <v>11</v>
       </c>
       <c r="J47">
-        <v>11.51</v>
+        <v>8.25</v>
       </c>
       <c r="K47">
-        <v>2.51</v>
+        <v>1.69</v>
       </c>
       <c r="L47">
-        <v>27.39999961853027</v>
+        <v>18.54999923706055</v>
       </c>
       <c r="M47">
-        <v>25.4956319788312</v>
+        <v>17.71175457147033</v>
       </c>
       <c r="N47">
-        <v>-57.99270014509076</v>
+        <v>-55.52560463982368</v>
       </c>
       <c r="O47">
-        <v>-6.95</v>
+        <v>-4.52</v>
       </c>
       <c r="P47" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3518,49 +3473,49 @@
         <v>62</v>
       </c>
       <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48">
+        <v>115</v>
+      </c>
+      <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="E48">
+        <v>8</v>
+      </c>
+      <c r="F48">
+        <v>10</v>
+      </c>
+      <c r="G48">
         <v>46</v>
       </c>
-      <c r="C48">
-        <v>82</v>
-      </c>
-      <c r="D48">
-        <v>4</v>
-      </c>
-      <c r="E48">
-        <v>8</v>
-      </c>
-      <c r="F48">
-        <v>10</v>
-      </c>
-      <c r="G48">
-        <v>45</v>
-      </c>
       <c r="H48">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="I48">
-        <v>8.26</v>
+        <v>7.27</v>
       </c>
       <c r="J48">
-        <v>22.15</v>
+        <v>16.43</v>
       </c>
       <c r="K48">
-        <v>3.57</v>
+        <v>1.98</v>
       </c>
       <c r="L48">
-        <v>29.1200008392334</v>
+        <v>14.68000030517578</v>
       </c>
       <c r="M48">
-        <v>42.1805494274316</v>
+        <v>27.05469460186161</v>
       </c>
       <c r="N48">
-        <v>-23.93544175260707</v>
+        <v>11.92097859975667</v>
       </c>
       <c r="O48">
-        <v>44.85</v>
+        <v>84.3</v>
       </c>
       <c r="P48" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3568,49 +3523,49 @@
         <v>63</v>
       </c>
       <c r="B49">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C49">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="D49">
         <v>4</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G49">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H49">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="I49">
-        <v>6.24</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="J49">
-        <v>63.63</v>
+        <v>22.15</v>
       </c>
       <c r="K49">
-        <v>7.52</v>
+        <v>3.57</v>
       </c>
       <c r="L49">
-        <v>46.34999847412109</v>
+        <v>32.65999984741211</v>
       </c>
       <c r="M49">
-        <v>103.7602814182768</v>
+        <v>42.1805494274316</v>
       </c>
       <c r="N49">
-        <v>37.28155791747645</v>
+        <v>-32.18003642533665</v>
       </c>
       <c r="O49">
-        <v>123.86</v>
+        <v>29.15</v>
       </c>
       <c r="P49" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3621,46 +3576,46 @@
         <v>49</v>
       </c>
       <c r="C50">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F50">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H50">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="I50">
-        <v>10.88</v>
+        <v>4.92</v>
       </c>
       <c r="J50">
-        <v>8.25</v>
+        <v>6.7</v>
       </c>
       <c r="K50">
-        <v>1.69</v>
+        <v>0.59</v>
       </c>
       <c r="L50">
-        <v>18.32999992370605</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="M50">
-        <v>17.71175457147033</v>
+        <v>9.430933145770888</v>
       </c>
       <c r="N50">
-        <v>-54.99181650660928</v>
+        <v>120.3947396076948</v>
       </c>
       <c r="O50">
-        <v>-3.37</v>
+        <v>210.23</v>
       </c>
       <c r="P50" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3671,46 +3626,46 @@
         <v>50</v>
       </c>
       <c r="C51">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E51">
         <v>8</v>
       </c>
       <c r="F51">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G51">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H51">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>7.23</v>
+        <v>12.62</v>
       </c>
       <c r="J51">
-        <v>16.43</v>
+        <v>1.68</v>
       </c>
       <c r="K51">
-        <v>1.98</v>
+        <v>0.4</v>
       </c>
       <c r="L51">
-        <v>14.05000019073486</v>
+        <v>5.110000133514404</v>
       </c>
       <c r="M51">
-        <v>27.05469460186161</v>
+        <v>3.888444419044716</v>
       </c>
       <c r="N51">
-        <v>16.93950019185484</v>
+        <v>-67.12328853023767</v>
       </c>
       <c r="O51">
-        <v>92.56</v>
+        <v>-23.91</v>
       </c>
       <c r="P51" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3718,49 +3673,49 @@
         <v>66</v>
       </c>
       <c r="B52">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C52">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G52">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H52">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="I52">
-        <v>4.92</v>
+        <v>5.19</v>
       </c>
       <c r="J52">
-        <v>6.7</v>
+        <v>26.49</v>
       </c>
       <c r="K52">
-        <v>0.59</v>
+        <v>2.27</v>
       </c>
       <c r="L52">
-        <v>2.869999885559082</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="M52">
-        <v>9.430933145770888</v>
+        <v>36.78283227267851</v>
       </c>
       <c r="N52">
-        <v>133.4494866606877</v>
+        <v>128.9541979145442</v>
       </c>
       <c r="O52">
-        <v>228.6</v>
+        <v>217.92</v>
       </c>
       <c r="P52" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3771,7 +3726,7 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D53">
         <v>4</v>
@@ -3783,13 +3738,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H53">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="I53">
-        <v>6.43</v>
+        <v>6.82</v>
       </c>
       <c r="J53">
         <v>31.76</v>
@@ -3798,19 +3753,19 @@
         <v>3.27</v>
       </c>
       <c r="L53">
-        <v>20.32999992370605</v>
+        <v>22.09000015258789</v>
       </c>
       <c r="M53">
         <v>48.33985932954295</v>
       </c>
       <c r="N53">
-        <v>56.22233211602647</v>
+        <v>43.77546301772772</v>
       </c>
       <c r="O53">
-        <v>137.78</v>
+        <v>118.83</v>
       </c>
       <c r="P53" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3818,49 +3773,49 @@
         <v>68</v>
       </c>
       <c r="B54">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C54">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="D54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E54">
         <v>8</v>
       </c>
       <c r="F54">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G54">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H54">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="I54">
-        <v>5.05</v>
+        <v>8.93</v>
       </c>
       <c r="J54">
-        <v>26.49</v>
+        <v>47.19</v>
       </c>
       <c r="K54">
-        <v>2.27</v>
+        <v>6.38</v>
       </c>
       <c r="L54">
-        <v>11.43000030517578</v>
+        <v>57.29999923706055</v>
       </c>
       <c r="M54">
-        <v>36.78283227267851</v>
+        <v>82.30506971019464</v>
       </c>
       <c r="N54">
-        <v>131.7585239958802</v>
+        <v>-17.64397796103563</v>
       </c>
       <c r="O54">
-        <v>221.81</v>
+        <v>43.64</v>
       </c>
       <c r="P54" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3871,46 +3826,46 @@
         <v>54</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E55">
         <v>8</v>
       </c>
       <c r="F55">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G55">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="I55">
-        <v>12.82</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="J55">
-        <v>1.68</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="K55">
-        <v>0.4</v>
+        <v>1.39</v>
       </c>
       <c r="L55">
-        <v>5.190000057220459</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="M55">
-        <v>3.888444419044716</v>
+        <v>17.13686815027764</v>
       </c>
       <c r="N55">
-        <v>-67.63005816035124</v>
+        <v>-28.32061277431421</v>
       </c>
       <c r="O55">
-        <v>-25.08</v>
+        <v>30.82</v>
       </c>
       <c r="P55" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3918,10 +3873,10 @@
         <v>70</v>
       </c>
       <c r="B56">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C56">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -3933,34 +3888,34 @@
         <v>10</v>
       </c>
       <c r="G56">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H56">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="I56">
-        <v>7.65</v>
+        <v>14.22</v>
       </c>
       <c r="J56">
-        <v>29.02</v>
+        <v>3.75</v>
       </c>
       <c r="K56">
-        <v>3.56</v>
+        <v>0.91</v>
       </c>
       <c r="L56">
-        <v>27</v>
+        <v>13.42000007629395</v>
       </c>
       <c r="M56">
-        <v>48.21308950897048</v>
+        <v>8.762491084160942</v>
       </c>
       <c r="N56">
-        <v>7.481481481481489</v>
+        <v>-72.0566320515581</v>
       </c>
       <c r="O56">
-        <v>78.56999999999999</v>
+        <v>-34.71</v>
       </c>
       <c r="P56" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3971,7 +3926,7 @@
         <v>56</v>
       </c>
       <c r="C57">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -3986,31 +3941,31 @@
         <v>55</v>
       </c>
       <c r="H57">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I57">
-        <v>6.56</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="J57">
-        <v>22.7</v>
+        <v>29.02</v>
       </c>
       <c r="K57">
-        <v>2.23</v>
+        <v>3.56</v>
       </c>
       <c r="L57">
-        <v>14.51000022888184</v>
+        <v>29.13999938964844</v>
       </c>
       <c r="M57">
-        <v>33.74866664032817</v>
+        <v>48.21308950897048</v>
       </c>
       <c r="N57">
-        <v>56.44382937235348</v>
+        <v>-0.4118029930057832</v>
       </c>
       <c r="O57">
-        <v>132.59</v>
+        <v>65.45</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4018,49 +3973,49 @@
         <v>72</v>
       </c>
       <c r="B58">
+        <v>57</v>
+      </c>
+      <c r="C58">
+        <v>85</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58">
+        <v>8</v>
+      </c>
+      <c r="F58">
+        <v>10</v>
+      </c>
+      <c r="G58">
         <v>56</v>
       </c>
-      <c r="C58">
-        <v>83</v>
-      </c>
-      <c r="D58">
-        <v>4</v>
-      </c>
-      <c r="E58">
-        <v>8</v>
-      </c>
-      <c r="F58">
-        <v>10</v>
-      </c>
-      <c r="G58">
-        <v>55</v>
-      </c>
       <c r="H58">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I58">
-        <v>8.84</v>
+        <v>7.52</v>
       </c>
       <c r="J58">
-        <v>9.390000000000001</v>
+        <v>22.7</v>
       </c>
       <c r="K58">
-        <v>1.39</v>
+        <v>2.23</v>
       </c>
       <c r="L58">
-        <v>12.14000034332275</v>
+        <v>16.92000007629395</v>
       </c>
       <c r="M58">
-        <v>17.13686815027764</v>
+        <v>33.74866664032817</v>
       </c>
       <c r="N58">
-        <v>-22.6523909847771</v>
+        <v>34.16075589623797</v>
       </c>
       <c r="O58">
-        <v>41.16</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="P58" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4071,7 +4026,7 @@
         <v>58</v>
       </c>
       <c r="C59">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="D59">
         <v>4</v>
@@ -4083,34 +4038,34 @@
         <v>10</v>
       </c>
       <c r="G59">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H59">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="I59">
-        <v>14.13</v>
+        <v>8.49</v>
       </c>
       <c r="J59">
-        <v>3.75</v>
+        <v>16.43</v>
       </c>
       <c r="K59">
-        <v>0.91</v>
+        <v>1.98</v>
       </c>
       <c r="L59">
-        <v>12.72000026702881</v>
+        <v>17.07999992370605</v>
       </c>
       <c r="M59">
-        <v>8.762491084160942</v>
+        <v>27.05469460186161</v>
       </c>
       <c r="N59">
-        <v>-70.51886854342071</v>
+        <v>-3.805620179212599</v>
       </c>
       <c r="O59">
-        <v>-31.11</v>
+        <v>58.4</v>
       </c>
       <c r="P59" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4121,46 +4076,46 @@
         <v>59</v>
       </c>
       <c r="C60">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60">
         <v>8</v>
       </c>
       <c r="F60">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G60">
         <v>59</v>
       </c>
       <c r="H60">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I60">
-        <v>8.720000000000001</v>
+        <v>24.16</v>
       </c>
       <c r="J60">
-        <v>47.19</v>
+        <v>5.29</v>
       </c>
       <c r="K60">
-        <v>6.38</v>
+        <v>1.53</v>
       </c>
       <c r="L60">
-        <v>55.43999862670898</v>
+        <v>36.86000061035156</v>
       </c>
       <c r="M60">
-        <v>82.30506971019464</v>
+        <v>13.49474897876948</v>
       </c>
       <c r="N60">
-        <v>-14.88095027248871</v>
+        <v>-85.6483995865307</v>
       </c>
       <c r="O60">
-        <v>48.46</v>
+        <v>-63.39</v>
       </c>
       <c r="P60" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4171,46 +4126,46 @@
         <v>60</v>
       </c>
       <c r="C61">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="D61">
         <v>4</v>
       </c>
       <c r="E61">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F61">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G61">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H61">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="I61">
-        <v>8.44</v>
+        <v>10.8</v>
       </c>
       <c r="J61">
-        <v>16.43</v>
+        <v>11.21</v>
       </c>
       <c r="K61">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="L61">
-        <v>16.3799991607666</v>
+        <v>18.01000022888184</v>
       </c>
       <c r="M61">
-        <v>27.05469460186161</v>
+        <v>20.27626074995091</v>
       </c>
       <c r="N61">
-        <v>0.3052554444151534</v>
+        <v>-37.7568025678144</v>
       </c>
       <c r="O61">
-        <v>65.17</v>
+        <v>12.58</v>
       </c>
       <c r="P61" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4221,46 +4176,46 @@
         <v>61</v>
       </c>
       <c r="C62">
+        <v>30</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62">
+        <v>8</v>
+      </c>
+      <c r="F62">
+        <v>10</v>
+      </c>
+      <c r="G62">
         <v>60</v>
       </c>
-      <c r="D62">
-        <v>4</v>
-      </c>
-      <c r="E62">
-        <v>8</v>
-      </c>
-      <c r="F62">
-        <v>10</v>
-      </c>
-      <c r="G62">
-        <v>61</v>
-      </c>
       <c r="H62">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="I62">
-        <v>24.78</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="J62">
-        <v>5.29</v>
+        <v>26</v>
       </c>
       <c r="K62">
-        <v>1.53</v>
+        <v>3.15</v>
       </c>
       <c r="L62">
-        <v>37.65000152587891</v>
+        <v>30.70000076293945</v>
       </c>
       <c r="M62">
-        <v>13.49474897876948</v>
+        <v>42.92726406376256</v>
       </c>
       <c r="N62">
-        <v>-85.94953576200018</v>
+        <v>-15.3094483587545</v>
       </c>
       <c r="O62">
-        <v>-64.16</v>
+        <v>39.83</v>
       </c>
       <c r="P62" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4271,46 +4226,46 @@
         <v>61</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="D63">
         <v>4</v>
       </c>
       <c r="E63">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F63">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G63">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H63">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="I63">
-        <v>10.56</v>
+        <v>13.85</v>
       </c>
       <c r="J63">
-        <v>11.21</v>
+        <v>17.43</v>
       </c>
       <c r="K63">
-        <v>1.63</v>
+        <v>3.29</v>
       </c>
       <c r="L63">
-        <v>16.89999961853027</v>
+        <v>46.43000030517578</v>
       </c>
       <c r="M63">
-        <v>20.27626074995091</v>
+        <v>35.92013015009829</v>
       </c>
       <c r="N63">
-        <v>-33.66863755601144</v>
+        <v>-62.45961687392668</v>
       </c>
       <c r="O63">
-        <v>19.98</v>
+        <v>-22.64</v>
       </c>
       <c r="P63" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4321,7 +4276,7 @@
         <v>63</v>
       </c>
       <c r="C64">
-        <v>122</v>
+        <v>10</v>
       </c>
       <c r="D64">
         <v>4</v>
@@ -4336,31 +4291,31 @@
         <v>62</v>
       </c>
       <c r="H64">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="I64">
-        <v>13.45</v>
+        <v>11.19</v>
       </c>
       <c r="J64">
-        <v>17.43</v>
+        <v>4.54</v>
       </c>
       <c r="K64">
-        <v>3.29</v>
+        <v>0.63</v>
       </c>
       <c r="L64">
-        <v>43.81999969482422</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="M64">
-        <v>35.92013015009829</v>
+        <v>8.022125653466169</v>
       </c>
       <c r="N64">
-        <v>-60.22364189550933</v>
+        <v>-35.41963208385497</v>
       </c>
       <c r="O64">
-        <v>-18.03</v>
+        <v>14.11</v>
       </c>
       <c r="P64" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4371,46 +4326,46 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E65">
         <v>8</v>
       </c>
       <c r="F65">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G65">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H65">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="I65">
-        <v>9.41</v>
+        <v>8.44</v>
       </c>
       <c r="J65">
-        <v>26</v>
+        <v>40.39</v>
       </c>
       <c r="K65">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="L65">
-        <v>29.45999908447266</v>
+        <v>33.34999847412109</v>
       </c>
       <c r="M65">
-        <v>42.92726406376256</v>
+        <v>59.15051774921332</v>
       </c>
       <c r="N65">
-        <v>-11.74473588594339</v>
+        <v>21.10945081854143</v>
       </c>
       <c r="O65">
-        <v>45.71</v>
+        <v>77.36</v>
       </c>
       <c r="P65" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4421,46 +4376,46 @@
         <v>65</v>
       </c>
       <c r="C66">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E66">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F66">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G66">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H66">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="I66">
-        <v>8.77</v>
+        <v>11.26</v>
       </c>
       <c r="J66">
-        <v>7.61</v>
+        <v>11.68</v>
       </c>
       <c r="K66">
-        <v>0.82</v>
+        <v>1.51</v>
       </c>
       <c r="L66">
-        <v>7.059999942779541</v>
+        <v>17.14999961853027</v>
       </c>
       <c r="M66">
-        <v>11.84924048198871</v>
+        <v>19.92054216129672</v>
       </c>
       <c r="N66">
-        <v>7.790369145582776</v>
+        <v>-31.89504221691081</v>
       </c>
       <c r="O66">
-        <v>67.84</v>
+        <v>16.15</v>
       </c>
       <c r="P66" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4471,7 +4426,7 @@
         <v>66</v>
       </c>
       <c r="C67">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="D67">
         <v>4</v>
@@ -4486,31 +4441,31 @@
         <v>65</v>
       </c>
       <c r="H67">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="I67">
-        <v>11.34</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="J67">
-        <v>4.54</v>
+        <v>32.61</v>
       </c>
       <c r="K67">
-        <v>0.63</v>
+        <v>3.14</v>
       </c>
       <c r="L67">
-        <v>7.090000152587891</v>
+        <v>29.03000068664551</v>
       </c>
       <c r="M67">
-        <v>8.022125653466169</v>
+        <v>47.99892186289188</v>
       </c>
       <c r="N67">
-        <v>-35.96615088445556</v>
+        <v>12.33206761514607</v>
       </c>
       <c r="O67">
-        <v>13.15</v>
+        <v>65.34</v>
       </c>
       <c r="P67" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4521,7 +4476,7 @@
         <v>67</v>
       </c>
       <c r="C68">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -4533,34 +4488,34 @@
         <v>10</v>
       </c>
       <c r="G68">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H68">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I68">
-        <v>7.73</v>
+        <v>13.5</v>
       </c>
       <c r="J68">
-        <v>28.09</v>
+        <v>5.87</v>
       </c>
       <c r="K68">
-        <v>1.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L68">
-        <v>13.90999984741211</v>
+        <v>12.67000007629395</v>
       </c>
       <c r="M68">
-        <v>33.63517132407683</v>
+        <v>11.14228432593604</v>
       </c>
       <c r="N68">
-        <v>101.9410518198245</v>
+        <v>-53.67008709823929</v>
       </c>
       <c r="O68">
-        <v>141.81</v>
+        <v>-12.06</v>
       </c>
       <c r="P68" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4568,10 +4523,10 @@
         <v>83</v>
       </c>
       <c r="B69">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C69">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="D69">
         <v>4</v>
@@ -4583,34 +4538,34 @@
         <v>10</v>
       </c>
       <c r="G69">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H69">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="I69">
-        <v>8.970000000000001</v>
+        <v>12.32</v>
       </c>
       <c r="J69">
-        <v>32.61</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K69">
-        <v>3.14</v>
+        <v>1.29</v>
       </c>
       <c r="L69">
-        <v>28.09000015258789</v>
+        <v>16.18000030517578</v>
       </c>
       <c r="M69">
-        <v>47.99892186289188</v>
+        <v>16.79651749619546</v>
       </c>
       <c r="N69">
-        <v>16.09113500483797</v>
+        <v>-39.92583549648826</v>
       </c>
       <c r="O69">
-        <v>70.88</v>
+        <v>3.81</v>
       </c>
       <c r="P69" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4618,10 +4573,10 @@
         <v>84</v>
       </c>
       <c r="B70">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C70">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="D70">
         <v>4</v>
@@ -4633,34 +4588,34 @@
         <v>10</v>
       </c>
       <c r="G70">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H70">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I70">
-        <v>107.09</v>
+        <v>14.47</v>
       </c>
       <c r="J70">
-        <v>0.54</v>
+        <v>4.14</v>
       </c>
       <c r="K70">
-        <v>0.14</v>
+        <v>0.68</v>
       </c>
       <c r="L70">
-        <v>14.97000026702881</v>
+        <v>10.26000022888184</v>
       </c>
       <c r="M70">
-        <v>1.30422390715705</v>
+        <v>7.958768748996292</v>
       </c>
       <c r="N70">
-        <v>-96.39278563548631</v>
+        <v>-59.6491237071718</v>
       </c>
       <c r="O70">
-        <v>-91.29000000000001</v>
+        <v>-22.43</v>
       </c>
       <c r="P70" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4668,49 +4623,49 @@
         <v>85</v>
       </c>
       <c r="B71">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C71">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F71">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G71">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H71">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="I71">
-        <v>11.42</v>
+        <v>10.38</v>
       </c>
       <c r="J71">
-        <v>11.68</v>
+        <v>7.61</v>
       </c>
       <c r="K71">
-        <v>1.51</v>
+        <v>0.82</v>
       </c>
       <c r="L71">
-        <v>17.18000030517578</v>
+        <v>8.460000038146973</v>
       </c>
       <c r="M71">
-        <v>19.92054216129672</v>
+        <v>11.84924048198871</v>
       </c>
       <c r="N71">
-        <v>-32.01397093991208</v>
+        <v>-10.04728172948273</v>
       </c>
       <c r="O71">
-        <v>15.95</v>
+        <v>40.06</v>
       </c>
       <c r="P71" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4718,10 +4673,10 @@
         <v>86</v>
       </c>
       <c r="B72">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C72">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="D72">
         <v>4</v>
@@ -4733,34 +4688,34 @@
         <v>10</v>
       </c>
       <c r="G72">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H72">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I72">
-        <v>13.18</v>
+        <v>8.18</v>
       </c>
       <c r="J72">
-        <v>5.87</v>
+        <v>19.5</v>
       </c>
       <c r="K72">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="L72">
-        <v>12.22000026702881</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="M72">
-        <v>11.14228432593604</v>
+        <v>22.26628617439379</v>
       </c>
       <c r="N72">
-        <v>-51.9639945030276</v>
+        <v>106.5678057922988</v>
       </c>
       <c r="O72">
-        <v>-8.82</v>
+        <v>135.87</v>
       </c>
       <c r="P72" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4771,46 +4726,46 @@
         <v>72</v>
       </c>
       <c r="C73">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73">
         <v>8</v>
       </c>
       <c r="F73">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G73">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H73">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="I73">
-        <v>9.029999999999999</v>
+        <v>12.47</v>
       </c>
       <c r="J73">
-        <v>40.39</v>
+        <v>22.3</v>
       </c>
       <c r="K73">
-        <v>3.85</v>
+        <v>2.91</v>
       </c>
       <c r="L73">
-        <v>34.06999969482422</v>
+        <v>36.77999877929688</v>
       </c>
       <c r="M73">
-        <v>59.15051774921332</v>
+        <v>38.21115674773534</v>
       </c>
       <c r="N73">
-        <v>18.55004508889353</v>
+        <v>-39.36922039118591</v>
       </c>
       <c r="O73">
-        <v>73.61</v>
+        <v>3.89</v>
       </c>
       <c r="P73" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4821,7 +4776,7 @@
         <v>73</v>
       </c>
       <c r="C74">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="D74">
         <v>4</v>
@@ -4836,31 +4791,31 @@
         <v>72</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="I74">
-        <v>15.3</v>
+        <v>11.37</v>
       </c>
       <c r="J74">
-        <v>4.14</v>
+        <v>8.58</v>
       </c>
       <c r="K74">
-        <v>0.68</v>
+        <v>1.02</v>
       </c>
       <c r="L74">
-        <v>10.26000022888184</v>
+        <v>11.76000022888184</v>
       </c>
       <c r="M74">
-        <v>7.958768748996292</v>
+        <v>14.03249799572407</v>
       </c>
       <c r="N74">
-        <v>-59.6491237071718</v>
+        <v>-27.04081774651629</v>
       </c>
       <c r="O74">
-        <v>-22.43</v>
+        <v>19.32</v>
       </c>
       <c r="P74" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4871,7 +4826,7 @@
         <v>74</v>
       </c>
       <c r="C75">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D75">
         <v>4</v>
@@ -4886,31 +4841,31 @@
         <v>74</v>
       </c>
       <c r="H75">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="I75">
-        <v>10.93</v>
+        <v>14.41</v>
       </c>
       <c r="J75">
-        <v>8.58</v>
+        <v>7.28</v>
       </c>
       <c r="K75">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="L75">
-        <v>11.10000038146973</v>
+        <v>14.72999954223633</v>
       </c>
       <c r="M75">
-        <v>14.03249799572407</v>
+        <v>12.98899534221181</v>
       </c>
       <c r="N75">
-        <v>-22.70270535915115</v>
+        <v>-50.57705209612831</v>
       </c>
       <c r="O75">
-        <v>26.42</v>
+        <v>-11.82</v>
       </c>
       <c r="P75" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4921,7 +4876,7 @@
         <v>75</v>
       </c>
       <c r="C76">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D76">
         <v>4</v>
@@ -4936,31 +4891,31 @@
         <v>75</v>
       </c>
       <c r="H76">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I76">
-        <v>12.49</v>
+        <v>18.68</v>
       </c>
       <c r="J76">
-        <v>22.31</v>
+        <v>5.52</v>
       </c>
       <c r="K76">
-        <v>2.91</v>
+        <v>0.96</v>
       </c>
       <c r="L76">
-        <v>35.7599983215332</v>
+        <v>17.98999977111816</v>
       </c>
       <c r="M76">
-        <v>38.21972331140036</v>
+        <v>10.91934063943423</v>
       </c>
       <c r="N76">
-        <v>-37.61185389495437</v>
+        <v>-69.31628643563398</v>
       </c>
       <c r="O76">
-        <v>6.88</v>
+        <v>-39.3</v>
       </c>
       <c r="P76" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4968,10 +4923,10 @@
         <v>91</v>
       </c>
       <c r="B77">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C77">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="D77">
         <v>4</v>
@@ -4983,34 +4938,34 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H77">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="I77">
-        <v>12.58</v>
+        <v>12.14</v>
       </c>
       <c r="J77">
-        <v>9.720000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="K77">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="L77">
-        <v>16.02000045776367</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="M77">
-        <v>16.79651749619546</v>
+        <v>14.03249799572407</v>
       </c>
       <c r="N77">
-        <v>-39.32584443036355</v>
+        <v>-31.90476396637072</v>
       </c>
       <c r="O77">
-        <v>4.85</v>
+        <v>11.37</v>
       </c>
       <c r="P77" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5018,10 +4973,10 @@
         <v>92</v>
       </c>
       <c r="B78">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C78">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D78">
         <v>4</v>
@@ -5033,34 +4988,34 @@
         <v>10</v>
       </c>
       <c r="G78">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H78">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="I78">
-        <v>8.34</v>
+        <v>25.36</v>
       </c>
       <c r="J78">
-        <v>19.5</v>
+        <v>3.88</v>
       </c>
       <c r="K78">
-        <v>1.13</v>
+        <v>0.71</v>
       </c>
       <c r="L78">
-        <v>9.439999580383301</v>
+        <v>17.47999954223633</v>
       </c>
       <c r="M78">
-        <v>22.26628617439379</v>
+        <v>7.872928298924105</v>
       </c>
       <c r="N78">
-        <v>106.5678057922988</v>
+        <v>-77.80320308004077</v>
       </c>
       <c r="O78">
-        <v>135.87</v>
+        <v>-54.96</v>
       </c>
       <c r="P78" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5068,10 +5023,10 @@
         <v>93</v>
       </c>
       <c r="B79">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C79">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D79">
         <v>4</v>
@@ -5083,34 +5038,34 @@
         <v>10</v>
       </c>
       <c r="G79">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H79">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="I79">
-        <v>14.07</v>
+        <v>10.02</v>
       </c>
       <c r="J79">
-        <v>7.28</v>
+        <v>27.27</v>
       </c>
       <c r="K79">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="L79">
-        <v>14.38000011444092</v>
+        <v>16.67000007629395</v>
       </c>
       <c r="M79">
-        <v>12.98899534221181</v>
+        <v>31.52763073876627</v>
       </c>
       <c r="N79">
-        <v>-49.37413114003275</v>
+        <v>63.58728179479789</v>
       </c>
       <c r="O79">
-        <v>-9.67</v>
+        <v>89.13</v>
       </c>
       <c r="P79" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5118,10 +5073,10 @@
         <v>94</v>
       </c>
       <c r="B80">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C80">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D80">
         <v>4</v>
@@ -5133,34 +5088,34 @@
         <v>10</v>
       </c>
       <c r="G80">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H80">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I80">
-        <v>17.93</v>
+        <v>21.93</v>
       </c>
       <c r="J80">
-        <v>5.52</v>
+        <v>11.08</v>
       </c>
       <c r="K80">
-        <v>0.96</v>
+        <v>1.8</v>
       </c>
       <c r="L80">
-        <v>16.97999954223633</v>
+        <v>39.63999938964844</v>
       </c>
       <c r="M80">
-        <v>10.91934063943423</v>
+        <v>21.18348413269167</v>
       </c>
       <c r="N80">
-        <v>-67.49116520133313</v>
+        <v>-72.04843549292934</v>
       </c>
       <c r="O80">
-        <v>-35.69</v>
+        <v>-46.56</v>
       </c>
       <c r="P80" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5171,7 +5126,7 @@
         <v>80</v>
       </c>
       <c r="C81">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D81">
         <v>4</v>
@@ -5186,31 +5141,31 @@
         <v>80</v>
       </c>
       <c r="H81">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="I81">
-        <v>11.71</v>
+        <v>30.06</v>
       </c>
       <c r="J81">
-        <v>8.58</v>
+        <v>8.17</v>
       </c>
       <c r="K81">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="L81">
-        <v>11.97000026702881</v>
+        <v>43.47999954223633</v>
       </c>
       <c r="M81">
-        <v>14.03249799572407</v>
+        <v>16.2132584633688</v>
       </c>
       <c r="N81">
-        <v>-28.32080360404431</v>
+        <v>-81.20975141210917</v>
       </c>
       <c r="O81">
-        <v>17.23</v>
+        <v>-62.71</v>
       </c>
       <c r="P81" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5221,46 +5176,46 @@
         <v>81</v>
       </c>
       <c r="C82">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D82">
         <v>4</v>
       </c>
       <c r="E82">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F82">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G82">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H82">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I82">
-        <v>24.79</v>
+        <v>11.92</v>
       </c>
       <c r="J82">
-        <v>3.88</v>
+        <v>11.1</v>
       </c>
       <c r="K82">
-        <v>0.71</v>
+        <v>1.09</v>
       </c>
       <c r="L82">
-        <v>17.38999938964844</v>
+        <v>13.86999988555908</v>
       </c>
       <c r="M82">
-        <v>7.872928298924105</v>
+        <v>16.49931816773045</v>
       </c>
       <c r="N82">
-        <v>-77.6883258414051</v>
+        <v>-19.97116011834363</v>
       </c>
       <c r="O82">
-        <v>-54.73</v>
+        <v>18.96</v>
       </c>
       <c r="P82" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5268,49 +5223,49 @@
         <v>97</v>
       </c>
       <c r="B83">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C83">
+        <v>29</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
+      <c r="G83">
         <v>86</v>
       </c>
-      <c r="D83">
-        <v>4</v>
-      </c>
-      <c r="E83">
-        <v>0</v>
-      </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-      <c r="G83">
-        <v>89</v>
-      </c>
       <c r="H83">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="I83">
-        <v>10.83</v>
+        <v>10.03</v>
       </c>
       <c r="J83">
-        <v>4.69</v>
+        <v>5.89</v>
       </c>
       <c r="K83">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="L83">
-        <v>4.639999866485596</v>
+        <v>3.660000085830688</v>
       </c>
       <c r="M83">
-        <v>6.736152462645126</v>
+        <v>6.810561650847894</v>
       </c>
       <c r="N83">
-        <v>1.077589115369437</v>
+        <v>60.92895797468763</v>
       </c>
       <c r="O83">
-        <v>45.18</v>
+        <v>86.08</v>
       </c>
       <c r="P83" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5321,7 +5276,7 @@
         <v>83</v>
       </c>
       <c r="C84">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D84">
         <v>4</v>
@@ -5333,34 +5288,34 @@
         <v>10</v>
       </c>
       <c r="G84">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H84">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="I84">
-        <v>21.88</v>
+        <v>11.32</v>
       </c>
       <c r="J84">
-        <v>11.08</v>
+        <v>20.15</v>
       </c>
       <c r="K84">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="L84">
-        <v>38.68999862670898</v>
+        <v>17.59000015258789</v>
       </c>
       <c r="M84">
-        <v>21.18348413269167</v>
+        <v>26.4234271055062</v>
       </c>
       <c r="N84">
-        <v>-71.36210805561748</v>
+        <v>14.55372271293285</v>
       </c>
       <c r="O84">
-        <v>-45.25</v>
+        <v>50.22</v>
       </c>
       <c r="P84" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5368,49 +5323,49 @@
         <v>99</v>
       </c>
       <c r="B85">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C85">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D85">
         <v>4</v>
       </c>
       <c r="E85">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F85">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G85">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H85">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="I85">
-        <v>9.68</v>
+        <v>17.22</v>
       </c>
       <c r="J85">
-        <v>5.89</v>
+        <v>11.23</v>
       </c>
       <c r="K85">
-        <v>0.35</v>
+        <v>1.39</v>
       </c>
       <c r="L85">
-        <v>3.289999961853027</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="M85">
-        <v>6.810561650847894</v>
+        <v>18.74081775163507</v>
       </c>
       <c r="N85">
-        <v>79.02735769889108</v>
+        <v>-53.26675123134312</v>
       </c>
       <c r="O85">
-        <v>107.01</v>
+        <v>-22.01</v>
       </c>
       <c r="P85" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5433,34 +5388,34 @@
         <v>10</v>
       </c>
       <c r="G86">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H86">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I86">
-        <v>29.72</v>
+        <v>14.26</v>
       </c>
       <c r="J86">
-        <v>8.17</v>
+        <v>9.83</v>
       </c>
       <c r="K86">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="L86">
-        <v>42.22000122070312</v>
+        <v>15.65999984741211</v>
       </c>
       <c r="M86">
-        <v>16.2132584633688</v>
+        <v>15.66857523835527</v>
       </c>
       <c r="N86">
-        <v>-80.64898208483771</v>
+        <v>-37.22860730663127</v>
       </c>
       <c r="O86">
-        <v>-61.6</v>
+        <v>0.05</v>
       </c>
       <c r="P86" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5468,49 +5423,49 @@
         <v>101</v>
       </c>
       <c r="B87">
+        <v>86</v>
+      </c>
+      <c r="C87">
+        <v>74</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+      <c r="E87">
+        <v>8</v>
+      </c>
+      <c r="F87">
+        <v>9</v>
+      </c>
+      <c r="G87">
         <v>85</v>
       </c>
-      <c r="C87">
-        <v>76</v>
-      </c>
-      <c r="D87">
-        <v>4</v>
-      </c>
-      <c r="E87">
-        <v>8</v>
-      </c>
-      <c r="F87">
-        <v>10</v>
-      </c>
-      <c r="G87">
-        <v>83</v>
-      </c>
       <c r="H87">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I87">
-        <v>19.27</v>
+        <v>12.17</v>
       </c>
       <c r="J87">
-        <v>7.79</v>
+        <v>8.74</v>
       </c>
       <c r="K87">
-        <v>1.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L87">
-        <v>22.88999938964844</v>
+        <v>6.840000152587891</v>
       </c>
       <c r="M87">
-        <v>14.50275835832618</v>
+        <v>10.49399828473399</v>
       </c>
       <c r="N87">
-        <v>-65.96767056480186</v>
+        <v>27.7777749272893</v>
       </c>
       <c r="O87">
-        <v>-36.64</v>
+        <v>53.42</v>
       </c>
       <c r="P87" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5521,46 +5476,46 @@
         <v>87</v>
       </c>
       <c r="C88">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="D88">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88">
         <v>8</v>
       </c>
       <c r="F88">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G88">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H88">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="I88">
-        <v>10.38</v>
+        <v>16.44</v>
       </c>
       <c r="J88">
-        <v>27.27</v>
+        <v>2.41</v>
       </c>
       <c r="K88">
-        <v>1.62</v>
+        <v>0.24</v>
       </c>
       <c r="L88">
-        <v>16.77000045776367</v>
+        <v>3.930000066757202</v>
       </c>
       <c r="M88">
-        <v>31.52763073876627</v>
+        <v>3.607492203733779</v>
       </c>
       <c r="N88">
-        <v>62.611802359107</v>
+        <v>-38.67684582538477</v>
       </c>
       <c r="O88">
-        <v>88</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="P88" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5568,49 +5523,49 @@
         <v>103</v>
       </c>
       <c r="B89">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C89">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D89">
         <v>4</v>
       </c>
       <c r="E89">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F89">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G89">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H89">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I89">
-        <v>11.98</v>
+        <v>26.51</v>
       </c>
       <c r="J89">
-        <v>11.1</v>
+        <v>24.57</v>
       </c>
       <c r="K89">
-        <v>1.09</v>
+        <v>2.89</v>
       </c>
       <c r="L89">
-        <v>12.77000045776367</v>
+        <v>75.98999786376953</v>
       </c>
       <c r="M89">
-        <v>16.49931816773045</v>
+        <v>39.97079246149619</v>
       </c>
       <c r="N89">
-        <v>-13.07752856616677</v>
+        <v>-67.66679735397851</v>
       </c>
       <c r="O89">
-        <v>29.2</v>
+        <v>-47.4</v>
       </c>
       <c r="P89" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5618,49 +5573,49 @@
         <v>104</v>
       </c>
       <c r="B90">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C90">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E90">
         <v>8</v>
       </c>
       <c r="F90">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G90">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H90">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="I90">
-        <v>16.93</v>
+        <v>17.71</v>
       </c>
       <c r="J90">
-        <v>11.23</v>
+        <v>23.54</v>
       </c>
       <c r="K90">
-        <v>1.39</v>
+        <v>2.15</v>
       </c>
       <c r="L90">
-        <v>23.42000007629395</v>
+        <v>38.40000152587891</v>
       </c>
       <c r="M90">
-        <v>18.74081775163507</v>
+        <v>33.74533301065497</v>
       </c>
       <c r="N90">
-        <v>-52.04953047217465</v>
+        <v>-38.69791910259251</v>
       </c>
       <c r="O90">
-        <v>-19.98</v>
+        <v>-12.12</v>
       </c>
       <c r="P90" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5671,7 +5626,7 @@
         <v>90</v>
       </c>
       <c r="C91">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D91">
         <v>4</v>
@@ -5683,34 +5638,34 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H91">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I91">
-        <v>13.9</v>
+        <v>16.55</v>
       </c>
       <c r="J91">
-        <v>9.83</v>
+        <v>24.01</v>
       </c>
       <c r="K91">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="L91">
-        <v>15.15999984741211</v>
+        <v>28.70999908447266</v>
       </c>
       <c r="M91">
-        <v>15.66857523835527</v>
+        <v>30.57105248433557</v>
       </c>
       <c r="N91">
-        <v>-35.15831069300418</v>
+        <v>-16.37059991065821</v>
       </c>
       <c r="O91">
-        <v>3.35</v>
+        <v>6.48</v>
       </c>
       <c r="P91" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5721,46 +5676,46 @@
         <v>91</v>
       </c>
       <c r="C92">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D92">
         <v>2</v>
       </c>
       <c r="E92">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G92">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H92">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="I92">
-        <v>11.06</v>
+        <v>13.06</v>
       </c>
       <c r="J92">
-        <v>9.279999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="K92">
-        <v>0.6</v>
+        <v>0.29</v>
       </c>
       <c r="L92">
-        <v>6.559999942779541</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="M92">
-        <v>11.19285486370658</v>
+        <v>6.611921052160257</v>
       </c>
       <c r="N92">
-        <v>41.46341586807949</v>
+        <v>77.24867859024481</v>
       </c>
       <c r="O92">
-        <v>70.62</v>
+        <v>74.92</v>
       </c>
       <c r="P92" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5771,7 +5726,7 @@
         <v>92</v>
       </c>
       <c r="C93">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="D93">
         <v>4</v>
@@ -5783,34 +5738,34 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H93">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="I93">
-        <v>11.76</v>
+        <v>33.9</v>
       </c>
       <c r="J93">
-        <v>20.15</v>
+        <v>5.97</v>
       </c>
       <c r="K93">
-        <v>1.54</v>
+        <v>0.67</v>
       </c>
       <c r="L93">
-        <v>18.04000091552734</v>
+        <v>22.71999931335449</v>
       </c>
       <c r="M93">
-        <v>26.4234271055062</v>
+        <v>9.486714394351713</v>
       </c>
       <c r="N93">
-        <v>11.69622493010265</v>
+        <v>-73.72359075516822</v>
       </c>
       <c r="O93">
-        <v>46.47</v>
+        <v>-58.25</v>
       </c>
       <c r="P93" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5821,46 +5776,46 @@
         <v>93</v>
       </c>
       <c r="C94">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E94">
         <v>8</v>
       </c>
       <c r="F94">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G94">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H94">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="I94">
-        <v>17.62</v>
+        <v>18.57</v>
       </c>
       <c r="J94">
-        <v>2.41</v>
+        <v>21.1</v>
       </c>
       <c r="K94">
-        <v>0.24</v>
+        <v>1.81</v>
       </c>
       <c r="L94">
-        <v>4.210000038146973</v>
+        <v>33.65999984741211</v>
       </c>
       <c r="M94">
-        <v>3.607492203733779</v>
+        <v>29.3137766246521</v>
       </c>
       <c r="N94">
-        <v>-42.75534493674829</v>
+        <v>-37.31431938309341</v>
       </c>
       <c r="O94">
-        <v>-14.31</v>
+        <v>-12.91</v>
       </c>
       <c r="P94" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5871,46 +5826,46 @@
         <v>94</v>
       </c>
       <c r="C95">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="D95">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E95">
         <v>8</v>
       </c>
       <c r="F95">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G95">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H95">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="I95">
-        <v>16.81</v>
+        <v>17.83</v>
       </c>
       <c r="J95">
-        <v>23.54</v>
+        <v>6.88</v>
       </c>
       <c r="K95">
-        <v>2.15</v>
+        <v>0.49</v>
       </c>
       <c r="L95">
-        <v>35.79999923706055</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="M95">
-        <v>33.74533301065497</v>
+        <v>8.709305368397644</v>
       </c>
       <c r="N95">
-        <v>-34.24580865456797</v>
+        <v>-23.21428604119894</v>
       </c>
       <c r="O95">
-        <v>-5.74</v>
+        <v>-2.8</v>
       </c>
       <c r="P95" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5921,46 +5876,46 @@
         <v>95</v>
       </c>
       <c r="C96">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D96">
         <v>2</v>
       </c>
       <c r="E96">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F96">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G96">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H96">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I96">
-        <v>11.92</v>
+        <v>16.18</v>
       </c>
       <c r="J96">
-        <v>6.7</v>
+        <v>51.42</v>
       </c>
       <c r="K96">
-        <v>0.29</v>
+        <v>2.87</v>
       </c>
       <c r="L96">
-        <v>3.299999952316284</v>
+        <v>47.79999923706055</v>
       </c>
       <c r="M96">
-        <v>6.611921052160257</v>
+        <v>57.62331559360326</v>
       </c>
       <c r="N96">
-        <v>103.0303059640119</v>
+        <v>7.573223474306623</v>
       </c>
       <c r="O96">
-        <v>100.36</v>
+        <v>20.55</v>
       </c>
       <c r="P96" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5971,7 +5926,7 @@
         <v>96</v>
       </c>
       <c r="C97">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D97">
         <v>4</v>
@@ -5983,34 +5938,34 @@
         <v>5</v>
       </c>
       <c r="G97">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H97">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I97">
-        <v>26.45</v>
+        <v>28.76</v>
       </c>
       <c r="J97">
-        <v>24.57</v>
+        <v>9.44</v>
       </c>
       <c r="K97">
-        <v>2.89</v>
+        <v>0.89</v>
       </c>
       <c r="L97">
-        <v>76.34999847412109</v>
+        <v>25.81999969482422</v>
       </c>
       <c r="M97">
-        <v>39.97079246149619</v>
+        <v>13.7490363298669</v>
       </c>
       <c r="N97">
-        <v>-67.81925279497155</v>
+        <v>-63.43919399080278</v>
       </c>
       <c r="O97">
-        <v>-47.65</v>
+        <v>-46.75</v>
       </c>
       <c r="P97" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6021,46 +5976,46 @@
         <v>97</v>
       </c>
       <c r="C98">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="D98">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E98">
         <v>8</v>
       </c>
       <c r="F98">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G98">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H98">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="I98">
-        <v>17.11</v>
+        <v>17.09</v>
       </c>
       <c r="J98">
-        <v>24.01</v>
+        <v>51.42</v>
       </c>
       <c r="K98">
-        <v>1.73</v>
+        <v>2.87</v>
       </c>
       <c r="L98">
-        <v>29.54999923706055</v>
+        <v>50.77000045776367</v>
       </c>
       <c r="M98">
-        <v>30.57105248433557</v>
+        <v>57.62331559360326</v>
       </c>
       <c r="N98">
-        <v>-18.74788284296292</v>
+        <v>1.280282718880565</v>
       </c>
       <c r="O98">
-        <v>3.46</v>
+        <v>13.5</v>
       </c>
       <c r="P98" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6071,46 +6026,46 @@
         <v>98</v>
       </c>
       <c r="C99">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="D99">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E99">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F99">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G99">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H99">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="I99">
-        <v>33.83</v>
+        <v>15.09</v>
       </c>
       <c r="J99">
-        <v>5.97</v>
+        <v>19.37</v>
       </c>
       <c r="K99">
-        <v>0.67</v>
+        <v>0.3</v>
       </c>
       <c r="L99">
-        <v>22.68000030517578</v>
+        <v>4.519999980926514</v>
       </c>
       <c r="M99">
-        <v>9.486714394351713</v>
+        <v>11.43448730813935</v>
       </c>
       <c r="N99">
-        <v>-73.67724903144031</v>
+        <v>328.539824817201</v>
       </c>
       <c r="O99">
-        <v>-58.17</v>
+        <v>152.98</v>
       </c>
       <c r="P99" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6121,46 +6076,46 @@
         <v>99</v>
       </c>
       <c r="C100">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="D100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E100">
         <v>8</v>
       </c>
       <c r="F100">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G100">
         <v>97</v>
       </c>
       <c r="H100">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="I100">
-        <v>18.64</v>
+        <v>19.45</v>
       </c>
       <c r="J100">
-        <v>21.1</v>
+        <v>18.93</v>
       </c>
       <c r="K100">
-        <v>1.81</v>
+        <v>1.17</v>
       </c>
       <c r="L100">
-        <v>33.58000183105469</v>
+        <v>23.06999969482422</v>
       </c>
       <c r="M100">
-        <v>29.3137766246521</v>
+        <v>22.32335660244668</v>
       </c>
       <c r="N100">
-        <v>-37.16498258053463</v>
+        <v>-17.94538252964534</v>
       </c>
       <c r="O100">
-        <v>-12.7</v>
+        <v>-3.24</v>
       </c>
       <c r="P100" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6171,46 +6126,46 @@
         <v>100</v>
       </c>
       <c r="C101">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E101">
         <v>8</v>
       </c>
       <c r="F101">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G101">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H101">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="I101">
-        <v>15.65</v>
+        <v>18.15</v>
       </c>
       <c r="J101">
-        <v>51.42</v>
+        <v>24.77</v>
       </c>
       <c r="K101">
-        <v>2.87</v>
+        <v>1.36</v>
       </c>
       <c r="L101">
-        <v>44.54000091552734</v>
+        <v>24.59000015258789</v>
       </c>
       <c r="M101">
-        <v>57.62331559360326</v>
+        <v>27.53110967614636</v>
       </c>
       <c r="N101">
-        <v>15.44678702975551</v>
+        <v>0.7320042549620043</v>
       </c>
       <c r="O101">
-        <v>29.37</v>
+        <v>11.96</v>
       </c>
       <c r="P101" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6218,49 +6173,49 @@
         <v>116</v>
       </c>
       <c r="B102">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C102">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D102">
         <v>4</v>
       </c>
       <c r="E102">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F102">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G102">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H102">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I102">
-        <v>18.26</v>
+        <v>26.18</v>
       </c>
       <c r="J102">
-        <v>6.88</v>
+        <v>6.05</v>
       </c>
       <c r="K102">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
       <c r="L102">
-        <v>8.930000305175781</v>
+        <v>10.01000022888184</v>
       </c>
       <c r="M102">
-        <v>8.709305368397644</v>
+        <v>7.192183256842112</v>
       </c>
       <c r="N102">
-        <v>-22.95632962058929</v>
+        <v>-39.56044094240931</v>
       </c>
       <c r="O102">
-        <v>-2.47</v>
+        <v>-28.15</v>
       </c>
       <c r="P102" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6271,46 +6226,46 @@
         <v>102</v>
       </c>
       <c r="C103">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E103">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F103">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G103">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H103">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I103">
-        <v>16.65</v>
+        <v>18.9</v>
       </c>
       <c r="J103">
-        <v>51.42</v>
+        <v>15</v>
       </c>
       <c r="K103">
-        <v>2.87</v>
+        <v>0.52</v>
       </c>
       <c r="L103">
-        <v>47.4900016784668</v>
+        <v>10.35999965667725</v>
       </c>
       <c r="M103">
-        <v>57.62331559360326</v>
+        <v>13.24764129949177</v>
       </c>
       <c r="N103">
-        <v>8.275422578717585</v>
+        <v>44.78764958580064</v>
       </c>
       <c r="O103">
-        <v>21.34</v>
+        <v>27.87</v>
       </c>
       <c r="P103" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6318,49 +6273,49 @@
         <v>118</v>
       </c>
       <c r="B104">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C104">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D104">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E104">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F104">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G104">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H104">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I104">
-        <v>27.73</v>
+        <v>42.59</v>
       </c>
       <c r="J104">
-        <v>9.44</v>
+        <v>7.21</v>
       </c>
       <c r="K104">
-        <v>0.89</v>
+        <v>0.35</v>
       </c>
       <c r="L104">
-        <v>24.3799991607666</v>
+        <v>14.85000038146973</v>
       </c>
       <c r="M104">
-        <v>13.7490363298669</v>
+        <v>7.535167549563845</v>
       </c>
       <c r="N104">
-        <v>-61.27973615687701</v>
+        <v>-51.4478126950296</v>
       </c>
       <c r="O104">
-        <v>-43.61</v>
+        <v>-49.26</v>
       </c>
       <c r="P104" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6371,46 +6326,43 @@
         <v>104</v>
       </c>
       <c r="C105">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="D105">
         <v>3</v>
       </c>
       <c r="E105">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F105">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G105">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H105">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="I105">
-        <v>14.46</v>
+        <v>0</v>
       </c>
       <c r="J105">
-        <v>19.37</v>
+        <v>0</v>
       </c>
       <c r="K105">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L105">
-        <v>4.320000171661377</v>
+        <v>0</v>
       </c>
       <c r="M105">
-        <v>11.43448730813935</v>
+        <v>0</v>
       </c>
       <c r="N105">
-        <v>348.3796118126247</v>
-      </c>
-      <c r="O105">
-        <v>164.69</v>
-      </c>
-      <c r="P105" t="s">
-        <v>241</v>
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6421,7 +6373,7 @@
         <v>105</v>
       </c>
       <c r="C106">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -6433,34 +6385,34 @@
         <v>4</v>
       </c>
       <c r="G106">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H106">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="I106">
-        <v>15.81</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="J106">
-        <v>15</v>
+        <v>4.87</v>
       </c>
       <c r="K106">
-        <v>0.52</v>
+        <v>0.05</v>
       </c>
       <c r="L106">
-        <v>8.329999923706055</v>
+        <v>4.340000152587891</v>
       </c>
       <c r="M106">
-        <v>13.24764129949177</v>
+        <v>2.340672980149085</v>
       </c>
       <c r="N106">
-        <v>80.07203046079299</v>
+        <v>12.21197762161546</v>
       </c>
       <c r="O106">
-        <v>59.04</v>
+        <v>-46.07</v>
       </c>
       <c r="P106" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6471,46 +6423,46 @@
         <v>105</v>
       </c>
       <c r="C107">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="D107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E107">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F107">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G107">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H107">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="I107">
-        <v>20.52</v>
+        <v>122.06</v>
       </c>
       <c r="J107">
-        <v>18.93</v>
+        <v>14.59</v>
       </c>
       <c r="K107">
-        <v>1.17</v>
+        <v>0.46</v>
       </c>
       <c r="L107">
-        <v>23.94000053405762</v>
+        <v>56.20000076293945</v>
       </c>
       <c r="M107">
-        <v>22.32335660244668</v>
+        <v>12.28847020584743</v>
       </c>
       <c r="N107">
-        <v>-20.92732005970622</v>
+        <v>-74.03914625990321</v>
       </c>
       <c r="O107">
-        <v>-6.75</v>
+        <v>-78.13</v>
       </c>
       <c r="P107" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6521,46 +6473,46 @@
         <v>107</v>
       </c>
       <c r="C108">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="D108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E108">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F108">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G108">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H108">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="I108">
-        <v>17.64</v>
+        <v>104.31</v>
       </c>
       <c r="J108">
-        <v>24.77</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K108">
-        <v>1.36</v>
+        <v>0.12</v>
       </c>
       <c r="L108">
-        <v>23.80999946594238</v>
+        <v>12.22000026702881</v>
       </c>
       <c r="M108">
-        <v>27.53110967614636</v>
+        <v>4.829906831399546</v>
       </c>
       <c r="N108">
-        <v>4.031921695045781</v>
+        <v>-29.29623722421779</v>
       </c>
       <c r="O108">
-        <v>15.63</v>
+        <v>-60.48</v>
       </c>
       <c r="P108" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6568,49 +6520,43 @@
         <v>123</v>
       </c>
       <c r="B109">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C109">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="D109">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E109">
         <v>6</v>
       </c>
       <c r="F109">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G109">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H109">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="I109">
-        <v>25.63</v>
+        <v>-36.22</v>
       </c>
       <c r="J109">
-        <v>6.05</v>
+        <v>3.51</v>
       </c>
       <c r="K109">
-        <v>0.38</v>
+        <v>-1.62</v>
       </c>
       <c r="L109">
-        <v>9.670000076293945</v>
-      </c>
-      <c r="M109">
-        <v>7.192183256842112</v>
+        <v>57.56000137329102</v>
       </c>
       <c r="N109">
-        <v>-37.43536760840772</v>
-      </c>
-      <c r="O109">
-        <v>-25.62</v>
+        <v>-93.90201543388304</v>
       </c>
       <c r="P109" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6618,49 +6564,43 @@
         <v>124</v>
       </c>
       <c r="B110">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C110">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="D110">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E110">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F110">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G110">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H110">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="I110">
-        <v>24.41</v>
+        <v>0.22</v>
       </c>
       <c r="J110">
-        <v>5.92</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="K110">
-        <v>0.32</v>
+        <v>5.68</v>
       </c>
       <c r="L110">
-        <v>7.699999809265137</v>
-      </c>
-      <c r="M110">
-        <v>6.528705844193013</v>
+        <v>1.360000014305115</v>
       </c>
       <c r="N110">
-        <v>-23.11688121242972</v>
-      </c>
-      <c r="O110">
-        <v>-15.21</v>
+        <v>-733.0882286350002</v>
       </c>
       <c r="P110" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6668,13 +6608,13 @@
         <v>125</v>
       </c>
       <c r="B111">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C111">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="D111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E111">
         <v>6</v>
@@ -6683,34 +6623,28 @@
         <v>6</v>
       </c>
       <c r="G111">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H111">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="I111">
-        <v>41.18</v>
+        <v>-7.8</v>
       </c>
       <c r="J111">
-        <v>7.21</v>
+        <v>1.44</v>
       </c>
       <c r="K111">
-        <v>0.35</v>
+        <v>-0.85</v>
       </c>
       <c r="L111">
-        <v>14.19999980926514</v>
-      </c>
-      <c r="M111">
-        <v>7.535167549563845</v>
+        <v>6.519999980926514</v>
       </c>
       <c r="N111">
-        <v>-49.22535143066932</v>
-      </c>
-      <c r="O111">
-        <v>-46.94</v>
+        <v>-77.91411036483821</v>
       </c>
       <c r="P111" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6718,46 +6652,43 @@
         <v>126</v>
       </c>
       <c r="B112">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C112">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="D112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E112">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F112">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G112">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H112">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="I112">
-        <v>0</v>
+        <v>-13.63</v>
       </c>
       <c r="J112">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="M112">
-        <v>0</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="N112">
-        <v>0</v>
-      </c>
-      <c r="P112">
-        <v>0</v>
+        <v>-36.36363836986326</v>
+      </c>
+      <c r="P112" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6765,49 +6696,43 @@
         <v>127</v>
       </c>
       <c r="B113">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C113">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E113">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F113">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G113">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H113">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="I113">
-        <v>78.25</v>
+        <v>-10.6</v>
       </c>
       <c r="J113">
-        <v>4.87</v>
+        <v>0.89</v>
       </c>
       <c r="K113">
-        <v>0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="L113">
-        <v>4.079999923706055</v>
-      </c>
-      <c r="M113">
-        <v>2.340672980149085</v>
+        <v>2.019999980926514</v>
       </c>
       <c r="N113">
-        <v>19.36274733006249</v>
-      </c>
-      <c r="O113">
-        <v>-42.63</v>
+        <v>-55.94059364338293</v>
       </c>
       <c r="P113" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6815,49 +6740,43 @@
         <v>128</v>
       </c>
       <c r="B114">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C114">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D114">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E114">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F114">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G114">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H114">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I114">
-        <v>103.63</v>
+        <v>-4.6</v>
       </c>
       <c r="J114">
-        <v>8.640000000000001</v>
+        <v>10.49</v>
       </c>
       <c r="K114">
-        <v>0.12</v>
+        <v>-1.7</v>
       </c>
       <c r="L114">
-        <v>12.09000015258789</v>
-      </c>
-      <c r="M114">
-        <v>4.829906831399546</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="N114">
-        <v>-28.53598105083076</v>
-      </c>
-      <c r="O114">
-        <v>-60.05</v>
+        <v>32.78480852362706</v>
       </c>
       <c r="P114" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6865,49 +6784,43 @@
         <v>129</v>
       </c>
       <c r="B115">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C115">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E115">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F115">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G115">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H115">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I115">
-        <v>120.18</v>
+        <v>-143.69</v>
       </c>
       <c r="J115">
-        <v>14.59</v>
+        <v>10.06</v>
       </c>
       <c r="K115">
-        <v>0.46</v>
+        <v>-0.11</v>
       </c>
       <c r="L115">
-        <v>54.20000076293945</v>
-      </c>
-      <c r="M115">
-        <v>12.28847020584743</v>
+        <v>16</v>
       </c>
       <c r="N115">
-        <v>-73.08118119072748</v>
-      </c>
-      <c r="O115">
-        <v>-77.33</v>
+        <v>-37.125</v>
       </c>
       <c r="P115" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6915,10 +6828,10 @@
         <v>130</v>
       </c>
       <c r="B116">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C116">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="D116">
         <v>2</v>
@@ -6930,28 +6843,28 @@
         <v>6</v>
       </c>
       <c r="G116">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H116">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="I116">
-        <v>-33.35</v>
+        <v>-110.46</v>
       </c>
       <c r="J116">
-        <v>3.51</v>
+        <v>3.64</v>
       </c>
       <c r="K116">
-        <v>-1.62</v>
+        <v>-0.03</v>
       </c>
       <c r="L116">
-        <v>54.15000152587891</v>
+        <v>3.869999885559082</v>
       </c>
       <c r="N116">
-        <v>-93.51800572282065</v>
+        <v>-5.943149673397341</v>
       </c>
       <c r="P116" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6959,43 +6872,43 @@
         <v>131</v>
       </c>
       <c r="B117">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C117">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="D117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G117">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="H117">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="I117">
-        <v>0.14</v>
+        <v>-52.27</v>
       </c>
       <c r="J117">
-        <v>-8.609999999999999</v>
+        <v>23.88</v>
       </c>
       <c r="K117">
-        <v>5.68</v>
+        <v>-0.28</v>
       </c>
       <c r="L117">
-        <v>0.8100000023841858</v>
+        <v>14.59000015258789</v>
       </c>
       <c r="N117">
-        <v>-1162.962959834196</v>
+        <v>63.67374743148513</v>
       </c>
       <c r="P117" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7003,13 +6916,13 @@
         <v>132</v>
       </c>
       <c r="B118">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C118">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E118">
         <v>6</v>
@@ -7018,28 +6931,28 @@
         <v>6</v>
       </c>
       <c r="G118">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H118">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="I118">
-        <v>-7.07</v>
+        <v>-16.04</v>
       </c>
       <c r="J118">
-        <v>1.44</v>
+        <v>12.08</v>
       </c>
       <c r="K118">
-        <v>-0.85</v>
+        <v>-0.67</v>
       </c>
       <c r="L118">
-        <v>6</v>
+        <v>11.02000045776367</v>
       </c>
       <c r="N118">
-        <v>-76</v>
+        <v>9.618870219642783</v>
       </c>
       <c r="P118" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7047,43 +6960,43 @@
         <v>133</v>
       </c>
       <c r="B119">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C119">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="E119">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F119">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G119">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H119">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="I119">
-        <v>-11.9</v>
+        <v>-41.13</v>
       </c>
       <c r="J119">
-        <v>3.85</v>
+        <v>96.64</v>
       </c>
       <c r="K119">
-        <v>-0.44</v>
+        <v>-0.95</v>
       </c>
       <c r="L119">
-        <v>5.130000114440918</v>
+        <v>39.34999847412109</v>
       </c>
       <c r="N119">
-        <v>-24.95126873073016</v>
+        <v>145.5908608574819</v>
       </c>
       <c r="P119" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7091,398 +7004,43 @@
         <v>134</v>
       </c>
       <c r="B120">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C120">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G120">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="H120">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="I120">
-        <v>-11.17</v>
+        <v>-1.85</v>
       </c>
       <c r="J120">
-        <v>0.89</v>
+        <v>1.76</v>
       </c>
       <c r="K120">
-        <v>-0.19</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L120">
-        <v>2.109999895095825</v>
+        <v>1.279999971389771</v>
       </c>
       <c r="N120">
-        <v>-57.81990311617618</v>
+        <v>37.50000307336456</v>
       </c>
       <c r="P120" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16">
-      <c r="A121" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B121">
-        <v>123</v>
-      </c>
-      <c r="C121">
-        <v>94</v>
-      </c>
-      <c r="D121">
-        <v>0</v>
-      </c>
-      <c r="E121">
-        <v>4</v>
-      </c>
-      <c r="F121">
-        <v>4</v>
-      </c>
-      <c r="G121">
-        <v>123</v>
-      </c>
-      <c r="H121">
-        <v>97</v>
-      </c>
-      <c r="I121">
-        <v>-4.42</v>
-      </c>
-      <c r="J121">
-        <v>10.49</v>
-      </c>
-      <c r="K121">
-        <v>-1.7</v>
-      </c>
-      <c r="L121">
-        <v>7.53000020980835</v>
-      </c>
-      <c r="N121">
-        <v>39.30942506928545</v>
-      </c>
-      <c r="P121" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16">
-      <c r="A122" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B122">
-        <v>123</v>
-      </c>
-      <c r="C122">
-        <v>101</v>
-      </c>
-      <c r="D122">
-        <v>1</v>
-      </c>
-      <c r="E122">
-        <v>4</v>
-      </c>
-      <c r="F122">
-        <v>4</v>
-      </c>
-      <c r="G122">
-        <v>123</v>
-      </c>
-      <c r="H122">
-        <v>104</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>0</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122">
-        <v>0</v>
-      </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
-      <c r="P122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16">
-      <c r="A123" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B123">
-        <v>123</v>
-      </c>
-      <c r="C123">
-        <v>104</v>
-      </c>
-      <c r="D123">
-        <v>3</v>
-      </c>
-      <c r="E123">
-        <v>8</v>
-      </c>
-      <c r="F123">
-        <v>9</v>
-      </c>
-      <c r="G123">
-        <v>115</v>
-      </c>
-      <c r="H123">
-        <v>102</v>
-      </c>
-      <c r="I123">
-        <v>-135.67</v>
-      </c>
-      <c r="J123">
-        <v>10.06</v>
-      </c>
-      <c r="K123">
-        <v>-0.11</v>
-      </c>
-      <c r="L123">
-        <v>14.85999965667725</v>
-      </c>
-      <c r="N123">
-        <v>-32.3014789204278</v>
-      </c>
-      <c r="P123" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16">
-      <c r="A124" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B124">
-        <v>123</v>
-      </c>
-      <c r="C124">
-        <v>106</v>
-      </c>
-      <c r="D124">
-        <v>2</v>
-      </c>
-      <c r="E124">
-        <v>6</v>
-      </c>
-      <c r="F124">
-        <v>6</v>
-      </c>
-      <c r="G124">
-        <v>119</v>
-      </c>
-      <c r="H124">
-        <v>107</v>
-      </c>
-      <c r="I124">
-        <v>-113.89</v>
-      </c>
-      <c r="J124">
-        <v>3.64</v>
-      </c>
-      <c r="K124">
-        <v>-0.03</v>
-      </c>
-      <c r="L124">
-        <v>4</v>
-      </c>
-      <c r="N124">
-        <v>-8.999999999999996</v>
-      </c>
-      <c r="P124" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16">
-      <c r="A125" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B125">
-        <v>123</v>
-      </c>
-      <c r="C125">
-        <v>108</v>
-      </c>
-      <c r="D125">
-        <v>2</v>
-      </c>
-      <c r="E125">
-        <v>8</v>
-      </c>
-      <c r="F125">
-        <v>9</v>
-      </c>
-      <c r="G125">
-        <v>115</v>
-      </c>
-      <c r="H125">
-        <v>105</v>
-      </c>
-      <c r="I125">
-        <v>-50.71</v>
-      </c>
-      <c r="J125">
-        <v>23.88</v>
-      </c>
-      <c r="K125">
-        <v>-0.28</v>
-      </c>
-      <c r="L125">
-        <v>14.18000030517578</v>
-      </c>
-      <c r="N125">
-        <v>68.40620229947147</v>
-      </c>
-      <c r="P125" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16">
-      <c r="A126" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B126">
-        <v>123</v>
-      </c>
-      <c r="C126">
-        <v>110</v>
-      </c>
-      <c r="D126">
-        <v>2</v>
-      </c>
-      <c r="E126">
-        <v>6</v>
-      </c>
-      <c r="F126">
-        <v>6</v>
-      </c>
-      <c r="G126">
-        <v>119</v>
-      </c>
-      <c r="H126">
-        <v>110</v>
-      </c>
-      <c r="I126">
-        <v>-15.79</v>
-      </c>
-      <c r="J126">
-        <v>12.08</v>
-      </c>
-      <c r="K126">
-        <v>-0.67</v>
-      </c>
-      <c r="L126">
-        <v>10.4399995803833</v>
-      </c>
-      <c r="N126">
-        <v>15.7088169112406</v>
-      </c>
-      <c r="P126" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16">
-      <c r="A127" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B127">
-        <v>123</v>
-      </c>
-      <c r="C127">
-        <v>111</v>
-      </c>
-      <c r="D127">
-        <v>1</v>
-      </c>
-      <c r="E127">
-        <v>2</v>
-      </c>
-      <c r="F127">
-        <v>2</v>
-      </c>
-      <c r="G127">
-        <v>125</v>
-      </c>
-      <c r="H127">
-        <v>112</v>
-      </c>
-      <c r="I127">
-        <v>-43.64</v>
-      </c>
-      <c r="J127">
-        <v>96.64</v>
-      </c>
-      <c r="K127">
-        <v>-0.95</v>
-      </c>
-      <c r="L127">
-        <v>41.08000183105469</v>
-      </c>
-      <c r="N127">
-        <v>135.2482855220916</v>
-      </c>
-      <c r="P127" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16">
-      <c r="A128" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B128">
-        <v>123</v>
-      </c>
-      <c r="C128">
-        <v>112</v>
-      </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-      <c r="E128">
-        <v>6</v>
-      </c>
-      <c r="F128">
-        <v>6</v>
-      </c>
-      <c r="G128">
-        <v>119</v>
-      </c>
-      <c r="H128">
-        <v>111</v>
-      </c>
-      <c r="I128">
-        <v>-1.81</v>
-      </c>
-      <c r="J128">
-        <v>1.76</v>
-      </c>
-      <c r="K128">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="L128">
-        <v>1.269999980926514</v>
-      </c>
-      <c r="N128">
-        <v>38.58267924665735</v>
-      </c>
-      <c r="P128" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/DF_RankScoreFM.xlsx
+++ b/DF_RankScoreFM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="239">
   <si>
     <t>FM_Bancos</t>
   </si>
@@ -64,124 +64,130 @@
     <t>TICKER</t>
   </si>
   <si>
-    <t>AMER3</t>
+    <t>MNPR3</t>
+  </si>
+  <si>
+    <t>PPLA11</t>
   </si>
   <si>
     <t>PRIO3</t>
   </si>
   <si>
+    <t>EALT4</t>
+  </si>
+  <si>
     <t>VBBR3</t>
   </si>
   <si>
+    <t>CMIG4</t>
+  </si>
+  <si>
     <t>BBSE3</t>
   </si>
   <si>
-    <t>VULC3</t>
-  </si>
-  <si>
-    <t>MRFG3</t>
-  </si>
-  <si>
-    <t>CMIG4</t>
-  </si>
-  <si>
-    <t>TAEE11</t>
-  </si>
-  <si>
-    <t>JHSF3</t>
-  </si>
-  <si>
-    <t>SAPR11</t>
+    <t>WHRL4</t>
+  </si>
+  <si>
+    <t>CAMB3</t>
+  </si>
+  <si>
+    <t>PETR4</t>
+  </si>
+  <si>
+    <t>SAPR3</t>
+  </si>
+  <si>
+    <t>PETR3</t>
+  </si>
+  <si>
+    <t>EQPA5</t>
+  </si>
+  <si>
+    <t>TAEE3</t>
+  </si>
+  <si>
+    <t>MBRF3</t>
+  </si>
+  <si>
+    <t>TAEE4</t>
+  </si>
+  <si>
+    <t>EQPA7</t>
+  </si>
+  <si>
+    <t>BAZA3</t>
+  </si>
+  <si>
+    <t>DEXP3</t>
   </si>
   <si>
     <t>SBSP3</t>
   </si>
   <si>
-    <t>PETR4</t>
-  </si>
-  <si>
-    <t>PETR3</t>
-  </si>
-  <si>
-    <t>TEND3</t>
-  </si>
-  <si>
-    <t>TTEN3</t>
-  </si>
-  <si>
-    <t>CPFE3</t>
+    <t>ENGI11</t>
   </si>
   <si>
     <t>POMO4</t>
   </si>
   <si>
-    <t>MDNE3</t>
-  </si>
-  <si>
-    <t>PLPL3</t>
-  </si>
-  <si>
-    <t>ENGI11</t>
-  </si>
-  <si>
-    <t>ISAE4</t>
-  </si>
-  <si>
-    <t>CXSE3</t>
-  </si>
-  <si>
-    <t>ECOR3</t>
-  </si>
-  <si>
-    <t>RECV3</t>
-  </si>
-  <si>
-    <t>ITUB3</t>
+    <t>UNIP3</t>
+  </si>
+  <si>
+    <t>BRFS3</t>
+  </si>
+  <si>
+    <t>BRAV3</t>
   </si>
   <si>
     <t>CYRE3</t>
   </si>
   <si>
-    <t>UNIP6</t>
+    <t>CSUD3</t>
+  </si>
+  <si>
+    <t>CGAS5</t>
+  </si>
+  <si>
+    <t>CGRA4</t>
+  </si>
+  <si>
+    <t>CLSC4</t>
+  </si>
+  <si>
+    <t>SUZB3</t>
+  </si>
+  <si>
+    <t>TECN3</t>
+  </si>
+  <si>
+    <t>BMEB4</t>
+  </si>
+  <si>
+    <t>BRAP3</t>
+  </si>
+  <si>
+    <t>OFSA3</t>
   </si>
   <si>
     <t>UGPA3</t>
   </si>
   <si>
-    <t>VIVA3</t>
-  </si>
-  <si>
-    <t>BRAV3</t>
-  </si>
-  <si>
-    <t>CURY3</t>
+    <t>BEES3</t>
   </si>
   <si>
     <t>ITSA4</t>
   </si>
   <si>
+    <t>CEBR3</t>
+  </si>
+  <si>
     <t>ITUB4</t>
   </si>
   <si>
-    <t>SUZB3</t>
-  </si>
-  <si>
-    <t>DIRR3</t>
-  </si>
-  <si>
-    <t>BRFS3</t>
-  </si>
-  <si>
-    <t>EGIE3</t>
-  </si>
-  <si>
-    <t>ODPV3</t>
-  </si>
-  <si>
-    <t>BRAP4</t>
-  </si>
-  <si>
-    <t>PORT3</t>
+    <t>CEBR5</t>
+  </si>
+  <si>
+    <t>ITSA3</t>
   </si>
   <si>
     <t>PSSA3</t>
@@ -190,76 +196,82 @@
     <t>STBP3</t>
   </si>
   <si>
-    <t>IRBR3</t>
+    <t>LPSB3</t>
+  </si>
+  <si>
+    <t>CEBR6</t>
+  </si>
+  <si>
+    <t>KLBN11</t>
+  </si>
+  <si>
+    <t>TASA4</t>
+  </si>
+  <si>
+    <t>BBAS3</t>
+  </si>
+  <si>
+    <t>EUCA4</t>
   </si>
   <si>
     <t>MULT3</t>
   </si>
   <si>
-    <t>SBFG3</t>
-  </si>
-  <si>
-    <t>KLBN11</t>
+    <t>B3SA3</t>
   </si>
   <si>
     <t>BBDC3</t>
   </si>
   <si>
-    <t>CSMG3</t>
-  </si>
-  <si>
-    <t>COGN3</t>
-  </si>
-  <si>
-    <t>CMIN3</t>
-  </si>
-  <si>
-    <t>BRSR6</t>
-  </si>
-  <si>
-    <t>BBAS3</t>
+    <t>BRSR3</t>
+  </si>
+  <si>
+    <t>BLAU3</t>
+  </si>
+  <si>
+    <t>FIQE3</t>
+  </si>
+  <si>
+    <t>WEGE3</t>
   </si>
   <si>
     <t>VALE3</t>
   </si>
   <si>
-    <t>INTB3</t>
-  </si>
-  <si>
-    <t>B3SA3</t>
-  </si>
-  <si>
-    <t>NEOE3</t>
-  </si>
-  <si>
-    <t>EZTC3</t>
+    <t>COCE5</t>
+  </si>
+  <si>
+    <t>ETER3</t>
+  </si>
+  <si>
+    <t>PFRM3</t>
+  </si>
+  <si>
+    <t>BPAC11</t>
+  </si>
+  <si>
+    <t>MTRE3</t>
   </si>
   <si>
     <t>BBDC4</t>
   </si>
   <si>
-    <t>WEGE3</t>
-  </si>
-  <si>
-    <t>CEAB3</t>
-  </si>
-  <si>
-    <t>ALUP11</t>
-  </si>
-  <si>
-    <t>BPAC11</t>
-  </si>
-  <si>
-    <t>GMAT3</t>
-  </si>
-  <si>
-    <t>AZZA3</t>
-  </si>
-  <si>
-    <t>SLCE3</t>
-  </si>
-  <si>
-    <t>SANB11</t>
+    <t>BRSR5</t>
+  </si>
+  <si>
+    <t>ASAI3</t>
+  </si>
+  <si>
+    <t>ALUP4</t>
+  </si>
+  <si>
+    <t>CSED3</t>
+  </si>
+  <si>
+    <t>BMGB4</t>
+  </si>
+  <si>
+    <t>SANB3</t>
   </si>
   <si>
     <t>ABEV3</t>
@@ -268,343 +280,325 @@
     <t>LREN3</t>
   </si>
   <si>
-    <t>ASAI3</t>
-  </si>
-  <si>
-    <t>MOVI3</t>
-  </si>
-  <si>
-    <t>GOAU4</t>
+    <t>BPAC3</t>
+  </si>
+  <si>
+    <t>ROMI3</t>
+  </si>
+  <si>
+    <t>MTSA4</t>
+  </si>
+  <si>
+    <t>ALUP3</t>
+  </si>
+  <si>
+    <t>RADL3</t>
   </si>
   <si>
     <t>EQTL3</t>
   </si>
   <si>
-    <t>CPLE3</t>
-  </si>
-  <si>
     <t>MOTV3</t>
   </si>
   <si>
-    <t>GGPS3</t>
+    <t>SANB4</t>
+  </si>
+  <si>
+    <t>VITT3</t>
+  </si>
+  <si>
+    <t>TKNO4</t>
+  </si>
+  <si>
+    <t>PATI3</t>
+  </si>
+  <si>
+    <t>RDOR3</t>
+  </si>
+  <si>
+    <t>TOTS3</t>
+  </si>
+  <si>
+    <t>CPLE5</t>
   </si>
   <si>
     <t>CPLE6</t>
   </si>
   <si>
-    <t>RADL3</t>
+    <t>GOAU3</t>
+  </si>
+  <si>
+    <t>MATD3</t>
+  </si>
+  <si>
+    <t>RAPT3</t>
+  </si>
+  <si>
+    <t>GGBR3</t>
+  </si>
+  <si>
+    <t>BRST3</t>
+  </si>
+  <si>
+    <t>AFLT3</t>
   </si>
   <si>
     <t>GGBR4</t>
   </si>
   <si>
-    <t>RDOR3</t>
-  </si>
-  <si>
-    <t>TOTS3</t>
-  </si>
-  <si>
-    <t>YDUQ3</t>
-  </si>
-  <si>
-    <t>ANIM3</t>
-  </si>
-  <si>
-    <t>SMTO3</t>
-  </si>
-  <si>
-    <t>IGTI11</t>
-  </si>
-  <si>
-    <t>FLRY3</t>
-  </si>
-  <si>
-    <t>RAPT4</t>
-  </si>
-  <si>
-    <t>VAMO3</t>
+    <t>RENT3</t>
   </si>
   <si>
     <t>EMBR3</t>
   </si>
   <si>
-    <t>RENT3</t>
-  </si>
-  <si>
-    <t>MDIA3</t>
-  </si>
-  <si>
-    <t>CBAV3</t>
-  </si>
-  <si>
     <t>TIMS3</t>
   </si>
   <si>
     <t>VIVT3</t>
   </si>
   <si>
+    <t>SMFT3</t>
+  </si>
+  <si>
+    <t>DMVF3</t>
+  </si>
+  <si>
     <t>NATU3</t>
   </si>
   <si>
+    <t>ALOS3</t>
+  </si>
+  <si>
+    <t>MGLU3</t>
+  </si>
+  <si>
+    <t>LOGN3</t>
+  </si>
+  <si>
     <t>ELET3</t>
   </si>
   <si>
-    <t>SMFT3</t>
-  </si>
-  <si>
     <t>ELET6</t>
   </si>
   <si>
-    <t>USIM5</t>
-  </si>
-  <si>
-    <t>HYPE3</t>
-  </si>
-  <si>
-    <t>ALOS3</t>
-  </si>
-  <si>
-    <t>ALPA4</t>
-  </si>
-  <si>
-    <t>MGLU3</t>
+    <t>EMAE4</t>
+  </si>
+  <si>
+    <t>HBRE3</t>
+  </si>
+  <si>
+    <t>USIM6</t>
   </si>
   <si>
     <t>RAIL3</t>
   </si>
   <si>
-    <t>EMAE3</t>
-  </si>
-  <si>
-    <t>LWSA3</t>
-  </si>
-  <si>
-    <t>ORVR3</t>
-  </si>
-  <si>
-    <t>SRNA3</t>
-  </si>
-  <si>
-    <t>AURA33</t>
-  </si>
-  <si>
-    <t>AZUL4</t>
-  </si>
-  <si>
-    <t>BEEF3</t>
-  </si>
-  <si>
-    <t>SIMH3</t>
-  </si>
-  <si>
-    <t>CVCB3</t>
-  </si>
-  <si>
-    <t>CSNA3</t>
+    <t>LAND3</t>
+  </si>
+  <si>
+    <t>ESPA3</t>
+  </si>
+  <si>
+    <t>AMAR3</t>
+  </si>
+  <si>
+    <t>ALPK3</t>
+  </si>
+  <si>
+    <t>DASA3</t>
+  </si>
+  <si>
+    <t>AALR3</t>
   </si>
   <si>
     <t>ENEV3</t>
   </si>
   <si>
-    <t>PETZ3</t>
-  </si>
-  <si>
-    <t>TUPY3</t>
-  </si>
-  <si>
-    <t>AURE3</t>
+    <t>PTBL3</t>
   </si>
   <si>
     <t>HAPV3</t>
   </si>
   <si>
-    <t>RAIZ4</t>
-  </si>
-  <si>
-    <t>Americanas S.A. operates in the e-commerce business in Brazil. It offers e-commerce digital platform for various digital solutions. The company operates Americanas.com, an online store with various products; Submarino, a digital brand in books, games, technology, and entertainment; Shoptime, an online brand in books, games, technology, and entertainment; Ame, a platform for financial and non-financial products and services; and Puket, an online clothing platform; MinD, an online design and home decoration platform. In addition, it provides imaginarium, a multi-brand e-commerce channels; Lovebrands, an online platform that offers various products and services; Skoob, a virtual library platform, as well as operates a retail chain of fruits and vegetables under Hortifruti Natural da Terra brand. Americanas S.A. was founded in 1999 and is headquartered in Rio de Janeiro, Brazil.</t>
+    <t>SCAR3</t>
+  </si>
+  <si>
+    <t>MEAL3</t>
+  </si>
+  <si>
+    <t>Minupar Participações S.A., through its subsidiaries, engages in the production and slaughtering of poultry primarily in Brazil. It is also involved in the industrialization and commercialization of processed meat products. Minupar Participações S.A. was incorporated in 1984 and is based in Lajeado, Brazil.</t>
+  </si>
+  <si>
+    <t>PPLA Participations Ltd. formerly known as BTG Pactual Participations Ltd. is a private equity firm. The firm also makes equity investments in other financial instruments, including investments in real estate mainly in Brazil as well as investments in other financial instruments in the global market. PPLA Participations Ltd. was founded in March 26, 2010 and it is based in Sao Paulo, Brazil with additional offices in London, United Kingdom and Hong Kong.</t>
   </si>
   <si>
     <t>Prio S.A., together with its subsidiaries, engages in the exploration, development, and production of oil and natural gas properties in Brazil and internationally. It holds a 100% interest in the Polvo Field covering an area of approximately 134 square kilometers located in the southern portion of the Campos Basin, Rio de Janeiro; and the Frade Field that consists of approximately 154 square kilometers located in the northern region of the Campos Basin, Rio de Janeiro. The company also holds interest in the Albacora leste Field and the Wahoo and Itaipu Field located in the Camumu Basin, State of Bahia. In addition, it imports, exports, refines, sells, and distributes oil, natural gas, fuels, and oil by-products; and engages in the generation, sale, and distribution of electric power, as well as holds interests in other companies. The company was formerly known as Petro Rio S.A. and changed its name to Prio S.A. in May 2023. Prio S.A. was incorporated in 2009 and is headquartered in Rio de Janeiro, Brazil.</t>
   </si>
   <si>
+    <t>Electro Aço Altona S.A., a small foundry and mechanical repair shop, produces and supplies steel casting and special alloys. It serves rails, agricultural machinery, oil and gas, power generation, defense, structural components, construction and mining, dredging, marine, industrial equipment sectors. The company was formerly known as Auerbach &amp; Werner and changed its name to Electro Aço Altona S.A. in 1933. Electro Aço Altona S.A. was founded in 1924 and is based in Blumenau, Brazil.</t>
+  </si>
+  <si>
     <t>Vibra Energia S.A. manufactures, processes, distributes, trades in, transports, imports, and exports oil-based products, lubricants, and other fuels. The company also produces, distributes, trades in, and transports various energy forms and chemical products. It operates in Retail and B2B segments. The company markets its oil products, lubricants, compressed natural gas, biofuels, and convenience store products. It also markets oil-based fuels and lubricants and provides associated services to its consumer's market, as well as markets aviation products and services at Brazil's airport facilities. The company was incorporated in 1971 and is based in Rio de Janeiro, Brazil.</t>
   </si>
   <si>
-    <t>BB Seguridade Participações S.A., through its subsidiaries operates in the insurance, pension plans, and bonds, businesses in Brazil. The company operates through two segments Security and Brokerage. The Security segment offers life, rural, special risks and financial, transport, hulls, and housing people insurance products. It also offers pension plans, dental, and capitalization plans. The Brokerage segment engages in the brokerage, management, and promotion of pension plans, capitalization, capitalization, and dental plans. BB Seguridade Participações S.A. was incorporated in 2012 and is headquartered in Brasília, Brazil. BB Seguridade Participações S.A. is a subsidiary of Banco do Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Vulcabras S.A., through its subsidiaries, operates as a footwear company in Brazil and internationally. The company offers sports-oriented clothing, footwear, and accessories; and safety boots for hospital workers, mining companies, steelmakers, agribusiness, civil construction, and other sectors. It offers its products through e-commerce and brand-owned stores. The company markets its products under the Mizuno, Olympikus, UNDER ARMOUR, and Botas Vulcabras brand names. The company was founded in 1952 and is headquartered in Jundiaí, Brazil. Vulcabras S.A. operates as a subsidiary of Gianpega Negócios e Participações S.A.</t>
-  </si>
-  <si>
-    <t>Marfrig Global Foods S.A., through its subsidiaries, operates in the food industry in Brazil and internationally. It operates through Beef  North America; Beef  South America; and Poultry, Pork and Processed Products  BRF segments. The company produces, processes, distributes, and sells animal-based proteins, such as beef, pork, lamb, fish, and poultry; pastas, margarine, pet food, and plant-based proteins; hamburgers; and various ready-to-eat products, including frozen vegetables, lamb, fish, and sauces. It also engages in leather processing; processing and marketing of beef and lamb; trading activities; transportation; transportation leasing; energy generation, trading, and related services; processing and sale of milk derivatives; processing, sale, distribution, and retail of animal feed and nutrition products; road freight; asset management; veterinary services; and real estate activities; as well as produces canned meat and other processed products. In addition, the company provides administrative and marketing services; logistics services; consulting services. It imports, sells, and exports its products to restaurant and supermarket chains, and homes. The company was formerly known as Marfrig Alimentos S.A. and changed its name to Marfrig Global Foods S.A. in January 2014. Marfrig Global Foods S.A. was founded in 1986 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
     <t>Companhia Energética de Minas Gerais - CEMIG, through its subsidiaries, engages in the generation, transmission, distribution, and sale of energy in Brazil. As of December 31, 2024, the company operated 36 hydro plants with a total capacity of 4,449.0 MW, 2 wind farms with a total capacity of 70.8 MW, and 10 photovoltaic power stations with a total capacity of 158.99 MW; 357,044 miles of distribution lines; and 4,754 miles of transmission lines. It is also involved in the acquisition, transportation, and distribution of gas and its sub products and derivatives; sale and trading of energy; construction, implementation, operation and maintenance of electricity transmission; marketing and intermediation of energy-related business; installation, operation, maintenance and rental of solar plants; and distributed generation, account services, cogeneration, energy efficiency, and supply and storage management activities. The company was incorporated in 1952 and is headquartered in Belo Horizonte, Brazil.</t>
   </si>
   <si>
-    <t>Transmissora Aliança de Energia Elétrica S.A., together with its subsidiaries, engages in the implementation, operation, and maintenance of electric power transmission lines in Brazil. It operates approximately a total length of 15,1550 kilometers (km) of transmission lines, which include 14,420 km of transmission lines in operation and 735 km of lines under construction; 110 substations with voltage between 69 and 525kV; and one system operation center located in Rio de Janeiro. The company was founded in 2000 is headquartered in Rio de Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>JHSF Participações S.A., through its subsidiaries, engages in the real estate development business. The company operates through Recurring Income, Real Estate Business, Airport, and Hotels and Restaurants segments. It also engages in construction and operation of shopping malls; purchase and sale of residential and commercial properties, as well as goods; leasing of commercial real estate; operation of hotel, gastronomy, and tourism activities; rental of houses and club; and operation and management of the airfield, as well as rendering of administration services. The company operates through JHSF, Fazenda Boa Vista, Cidade Jardim Mall, Catarina Fashion Outlet, and Fasano brands. The company was founded in 1972 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Companhia de Saneamento do Paraná - SANEPAR provides sanitation services in Brazil. The company engages in water distribution; collection and treatment of sewage and solid waste; study, project, and construction work of facilities; expansion of water distribution; and collection and treatment of sewage networks. It also offers advisory and technical assistance services in its areas of activity. It serves federal, state, municipal agencies, and other entities. The company was founded in 1963 and is headquartered in Curitiba, Brazil.</t>
-  </si>
-  <si>
-    <t>Companhia de Saneamento Básico do Estado de São Paulo - SABESP provides basic and environmental sanitation services in the São Paulo State, Brazil. The company supplies treated water and sewage services on a wholesale basis. As of December 31, 2024, it provided water services through 9.5 million water connections; and sewage services through 8.2 million sewage connections in 375 municipalities of the São Paulo State. The company was founded in 1954 and is headquartered in São Paulo, Brazil.</t>
+    <t>BB Seguridade Participações S.A., through its subsidiaries operates in the insurance, pension plans, and bonds, businesses in Brazil. The company operates through two segments, Security and Brokerage. The Security segment offers products and services related to life insurance, as well as rural, special and financial risk, transport, hull, housing and personal insurance, pension plans, supplementary plans, dental plans, and capitalization plans. The Brokerage segment engages in the brokerage and administration, implementation, promotion, and viability of insurance businesses in the basic, life, and capitalization sectors, as well as open pension plans and dental plans. BB Seguridade Participações S.A. was incorporated in 2012 and is headquartered in Brasília, Brazil. BB Seguridade Participações S.A. is a subsidiary of Banco do Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Whirlpool S.A. manufactures, sells, import, and exports home appliances in Brazil. The company offers refrigerators, freezers, air conditioners, ice makers, stoves, dishwashers, garbage disposals, trash compactors, vacuum cleaners, washing machines, clothes dryers, and microwave ovens. It sells its products under the Brastemp, Consul, KitchenAind, Compra Certa, B.blend, Jenn-Air, KitchenAid, Whirlpool, and Maytag brands. The company was founded in 1957 and is based in São Paulo, Brazil. Whirlpool S.A. operates as a subsidiary of Whirlpool Corporation.</t>
+  </si>
+  <si>
+    <t>Cambuci S.A. manufactures football equipment in Brazil. It sells its products through stores and e-commerce to direct customers and retailers. The company was founded in 1945 and is based in Sao Roque, Brazil.</t>
   </si>
   <si>
     <t>Petróleo Brasileiro S.A. - Petrobras explores, produces, and sells oil and gas in Brazil and internationally. It operates through three segments: Exploration and Production; Refining, Transportation &amp; Marketing; and Gas &amp; Low Carbon Energies. The Exploration and Production segment explores, develops, and produces crude oil, natural gas liquids, and natural gas primarily for supplies to the domestic refineries. The Refining, Transportation and Marketing segment engages in the refining, logistics, transport, acquisition, and export of crude oil; trading of oil products; and production of fertilizers, as well as holding interests in petrochemical companies. The Gas and Low Carbon Energies segment is involved in the logistic and trading of natural gas and electricity; transportation and trading of liquefied natural gas; generation of electricity through thermoelectric power plants; renewable energy business; low carbon business; and natural gas processing business, as well as production of biodiesel and its co-products. The company also engages in prospecting, drilling, refining, processing, trading, and transporting crude oil from producing onshore and offshore oil fields, and shale or other rocks, as well as oil products, natural gas, and other liquid hydrocarbons. In addition, it engages in the research, development, production, transportation, distribution, and trading of energy. The company was incorporated in 1953 and is headquartered in Rio de Janeiro, Brazil.</t>
   </si>
   <si>
-    <t>Construtora Tenda S.A. operates as a construction company in Brazil. The company engages in the construction works, real estate development, real estate purchase and sale, the provision of general construction management services, and the intermediation of the sale of consortium shares. It also holds interests in other companies. Construtora Tenda S.A. was founded in 1969 is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Três Tentos Agroindustrial S/A, together with its subsidiaries, operates in the agribusiness sector in Brazil. It operates in three segments: Agricultural Inputs; Soybean, Corn and Wheat Grains; and Industry. The company markets foliar fertilizers, plant-protection products, and seeds for soybean, corn, and wheat; and processes soybean to produce meal for animal feed and biodiesel. It is also involved in the receipt, standardization, and trading of grain from third parties. In addition, the company provides technical assistance, such as consulting services in administration, crop management, and crop technology; and digital solutions. Further, it is involved in sales promotion; insurance brokerage, supplementary pension plans, and health plans; credit services, such as credit card and financing services to rural producers; and trading of agricultural commodities. The company exports to Saudi Arabia, Australia, Bangladesh, Chile, China, Colombia, South Korea, Denmark, Spain, Guatemala, Netherlands, Virgin Islands, Indonesia, Italy, Japan, Morocco, Singapore, Switzerland, Thailand, Uruguay, Venezuela, and Vietnam. Três Tentos Agroindustrial S/A was founded in 1954 and is headquartered in Santa Bárbara do Sul, Brazil.</t>
-  </si>
-  <si>
-    <t>CPFL Energia S.A., through its subsidiaries, engages in the electric power business in Brazil. It operates through Generation, Distribution, Transmission, Commercialization, and Services segments. The company generates electricity through hydro, wind, biomass, and solar sources; and distributes its products to residential, industrial, and commercial customers under the  CPFL Paulista, CPFL Piratininga, CPFL Santa Cruz, and RGE brands. It also engages in the marketing business; and provides various services, including energy management and consultancy, purchase and trade of electricity, energy infrastructure and services, decarbonization, distributed generation, energy efficiency, maintenance of electrical installations, and renovation of transformer and electrical equipment. The company was founded in 1912 and is headquartered in Campinas, Brazil. CPFL Energia S.A. operates as a subsidiary of State Grid Brazil Power Participações S.A.</t>
-  </si>
-  <si>
-    <t>Marcopolo S.A. engages in manufacture and sale of bus bodies in Brazil, Africa, Argentina, Australia, China, the United Arab Emirates, and Mexico. It operates through Industrial and Financial segments. The company offers buses and micro buses; multiple units with different propulsion, passenger cars, and boxes for people movers, TRAMs, and EMUs; and parts and components. It also provides mobility systems and services; credit solutions for purchase of buses and minibuses; and advance payment services. In addition, the company is involved in wholesale trade of motor vehicle parts and accessories; assembling, import, export, and sale of refrigeration and air conditioning equipment; and the provision of technical services regarding foreign trade, as well as banking activities. The company was founded in 1949 and is headquartered in Caxias Do Sul, Brazil.</t>
-  </si>
-  <si>
-    <t>Moura Dubeux Engenharia S.A. provides real estate development services in Brazil. It engages in the purchase and sale of properties; rental and split of land allotment; real estate construction of properties; and management and administration of own or third parties real properties. The company develops flats, hotels, resorts, and residential buildings; and offers technical construction management and advisory services to the condominiums, as well as engineering services. Moura Dubeux Engenharia S.A. was founded in 1983 and is based in Recife, Brazil.</t>
-  </si>
-  <si>
-    <t>Plano &amp; Plano Desenvolvimento Imobiliário S.A., through its subsidiaries develops, constructs, and sells real estate projects in the São Paulo Metropolitan Region. The company was founded in 1997 and is based in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Energisa S.A., through its subsidiaries, engages in the distribution, transmission, and generation of electricity in Brazil. The company generates electricity through hydraulic, solar, and wind projects. It also provides operating and maintenance services related to electricity distribution, generation, transmission, commission, preparation, and remote and local operations; and offers electrical and mechanical maintenance of plants, substations, transmission lines, and facilities. In addition, the company provides construction, operation, maintenance, and services related to electricity generation, transmission, and distribution; tele-services and personal services for electricity consumers; and aerial surveying services for supporting companies operating high-voltage lines, oil pipelines, and reforestation engineering works. Further, it is involved in the production, marketing, and distribution of natural gas; treatment of industrial organic waste for the production of biofertilizer; development of computer systems and programs, licensing of non-customizable software, intermediation and brokerage of services and business, and business management consulting and provision of insurance brokerage, payment systems optimization, securitization of credits, and financial products and services. The company serves customers in residential, industrial, and commercial markets. It serves approximately 20 million consumers in the Brazilian states. The company was founded in 1905 and is headquartered in Cataguases, Brazil. Energisa S.A. operates as a subsidiary of Gipar S.A.</t>
-  </si>
-  <si>
-    <t>ISA Energía Brasil S.A engages in the electric transmission business in Brazil. As of December 31, 2023, it had a total installed transformation capacity of 85,000 MVA together with transmission lines of 23, 0000 kilometers; 32, 0000 kilometers of circuits; and 137 substations. It operates in the states of Alagoas, Bahia, Espírito Santo, Goiás, Maranhão, Mato Grosso, Mato Grosso do Sul, Minas Gerais, Paraíba, Paraná, Pernambuco, Piauí, Rio Grande do Sul, Rondônia, Santa Catarina, São Paulo, and Tocantins. ISA Energía Brasil S.A was founded in 1999 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Caixa Seguridade Participações S.A. provides various life and non-life insurance products in Brazil. It offers health plans and insurance; dental and assistance insurance; open private pension, premium bonds, and credit letters; capitalization products; and Consortia, basic and life, housing and residential, auto, credit life, and personal and damage insurance products. The company also engages in insurance brokerage business; and provision of intermediation services for assistance services, technical advice in general, and advisory and consultancy services in the insurance field, as well as holds equity interests. The company was incorporated in 2015 and is based in Brasília, Brazil. Caixa Seguridade Participações S.A. is a subsidiary of Caixa Econômica Federal.</t>
-  </si>
-  <si>
-    <t>EcoRodovias Infraestrutura e Logística S.A. operates as an infrastructure company that operates highway concessions in Brazil. It operates Ecopátio Logística Cubatão, an intermodal logistics platform, which is the regulating site for trucks at the Port of Santos. The company is also involved in the port operations and handling and storage of import and export cargo at the Port of Santos. In addition, it offers empty container storage, special export customs clearance, and general warehousing services. The company was founded in 1997 and is based in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Petroreconcavo S.A. engages in the exploration and production of oil and natural gas in Brazil. The company was founded in 1999 and is headquartered in Mata De Sao Joao, Brazil.</t>
+    <t>Companhia de Saneamento do Paraná - SANEPAR provides sanitation services in Brazil. The company engages in water distribution; collection and treatment of sewage and solid waste; study, project, and construction work of new facilities; expansion of water distribution; and collection and treatment of sewage networks. It also offers advisory and technical assistance services in its areas of activity. The company serves federal, state, municipal agencies, and other entities. Companhia de Saneamento do Paraná - SANEPAR was founded in 1963 and is headquartered in Curitiba, Brazil.</t>
+  </si>
+  <si>
+    <t>Transmissora Aliança de Energia Elétrica S.A., together with its subsidiaries, engages in the implementation, operation, and maintenance of electric power transmission lines in Brazil. It operates approximately a total length of 15,123 kilometers (km) of transmission lines, which include 14,388 km of transmission lines in operation and 735 km of lines under construction; 112 substations with voltage between 230 and 525KV; and one system operation center located in Rio de Janeiro. The company was founded in 2000 is headquartered in Rio de Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>Marfrig Global Foods S.A., through its subsidiaries, operates in the food industry in Brazil and internationally. It operates through Beef  North America; Beef  South America; and Poultry, Pork and Processed Products  BRF segments. The company produces, processes, distributes, and sells animal-based proteins, such as beef, pork, lamb, fish, and poultry; pastas, margarine, vegetable, pet food, and plant-based proteins; hamburgers; and various ready-to-eat products, including frozen vegetables, lamb, fish, and sauces. It also engages in leather processing; processing and marketing of beef and lamb; trading activities; transportation; transportation leasing; energy generation, trading, and related services; processing and sale of milk derivatives; processing, sale, distribution, and retail of animal feed and nutritional products; road freight; asset management; veterinary services; and real estate activities; as well as produces canned meat and other processed products. In addition, the company provides administrative and marketing services; logistics services; and consulting services. It imports, sells, and exports its products to restaurant and supermarket chains, and homes. The company sells its products under the Bassi Angus, Bassi, Montana Steakhouse, Montana, GJ, Viva, Pampeano/Palatare, Revolution, and Bona Pet brand names. The company was formerly known as Marfrig Alimentos S.A. and changed its name to Marfrig Global Foods S.A. in January 2014. Marfrig Global Foods S.A. was founded in 1986 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Banco da Amazônia S.A. provides banking products and services in the Amazon region of Brazil. The company offers savings, current, simplified, and salary accounts; credit cards; capitalization products; various personal and business loans; pension plans; investment funds, bank deposit certificates and deposit receipts, and agribusiness letter of credit; insurance products; and direct debit and online financial services. It also provides financing programs for family farming, machines and equipment, rural and biodiversity activities, trucks, green energy, green business and infrastructure, and rural and non-rural investments, as well as science, technology, and innovation activities; development and merchant marine fund; working capital; foreign trade; and legal entity savings, billing, card advance, business check, automatic debit, cellular messaging, and banking domicile services. Banco da Amazônia S.A. was founded in 1942 and is headquartered in Belém, Brazil.</t>
+  </si>
+  <si>
+    <t>Dexxos Participações S.A. engages in the production and sale of thermosetting resins to the reconstituted wood panels industry in Brazil. The company also engages in the production of formaldehyde and hexamine; and resale of methanol and other chemical products. In addition, it manufactures tubes for construction, infrastructure, and automobile markets; and produces steel tubes for petroleum and gas segment. The company was formerly known as GPC Participações S.A. and changed its name to Dexxos Participações S.A. in June 2021. Dexxos Participações S.A. was founded in 1929 and is headquartered in Rio de Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>Companhia de Saneamento Básico do Estado de São Paulo - SABESP provides basic and environmental sanitation services in the São Paulo State, Brazil. The company supplies treated water and sewage services on a wholesale basis. As of December 31, 2024, it provided water services through 9.5 million water connections; and sewage services through 8.2 million sewage connections in the 375 municipalities of the São Paulo State. Companhia de Saneamento Básico do Estado de São Paulo - SABESP was founded in 1954 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Energisa S.A., through its subsidiaries, engages in the generation, transmission, and distribution of electricity in Brazil. The company generates electricity through hydraulic, solar, and wind projects. It also provides operation and maintenance services related to electricity distribution, generation, transmission, commission, preparation, and remote and local operations; and offers electrical and mechanical maintenance of plants, substations, transmission lines, and facilities. In addition, the company offers construction, operation, maintenance, and services related to electricity generation, transmission, and distribution; tele-services and personal services for electricity consumers; and aerial surveying services for supporting companies operating high-voltage lines, oil pipelines, and reforestation engineering works. Further, it is involved in the production, marketing, and distribution of natural gas; treatment of industrial organic waste for the production of biofertilizer; and development of computer systems and programs, licensing of non-customizable software, intermediation and brokerage of services and business, and business management consulting activities, as well as offers insurance brokerage, payment systems optimization, securitization of credits, and financial products and services. The company serves residential, industrial, and commercial markets. It serves approximately 20 million consumers in the Brazilian states. The company was founded in 1905 and is headquartered in Cataguases, Brazil. Energisa S.A. is a subsidiary of Gipar S.A.</t>
+  </si>
+  <si>
+    <t>Marcopolo S.A. engages in manufacture and sale of buses, bus bodies, and components in Brazil, South Africa, Australia, China, Mexico, Argentina, and internationally. The company offers intercity buses, urban buses and microbuses, electric buses, and hybrid buses; and Volare family of microbuses, such as complete buses, with chassis, and bodywork for school transport, executive charter, urban transport, and special projects. It is also involved development and production of new models on rails; production of units with propulsion, passenger cars, as well as the manufacture of boxes for people movers, TRAMs and EMUs; provision of credit solutions for the purchase of buses and minibuses; assembly, marketing, import, and export of refrigeration and air conditioning equipment; seat foam business; banking activities; and plastics solutions business. The company was founded in 1949 and is headquartered in Caxias Do Sul, Brazil.</t>
+  </si>
+  <si>
+    <t>Unipar Carbocloro S.A. produces and sells chlorine and caustic soda in South America. The company offers liquid caustic soda, sodium hypochlorite, dichloroethane, hydrochloric acid, vinyl chloride monomer, and polyvinyl chloride. Its products are used in sanitation, household utilities, civil construction, pulp and paper, mining and steel, health, food, and automobile industries. Unipar Carbocloro S.A. was incorporated in 1969 and is based in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Brava Energia S.A. engages in the exploration and production of oil and natural gas in Brazil. The company was formerly known as 3R Petroleum Óleo e Gás S.A. and changed its name to Brava Energia S.A. in September 2024. The company was founded in 2010 and is headquartered in Rio De Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>Cyrela Brazil Realty S.A. Empreendimentos e Participações engages in the development and construction of residential properties in Brazil. The company also provides real estate services, such as construction management and technical consultancy services. Cyrela Brazil Realty S.A. Empreendimentos e Participações was founded in 1962 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>CSU Digital S.A., a technology company for financial services, provides digital solutions for payments, embedded finance, customer experience, and loyalty and incentive programs in Brazil. The company operates through two segments: CSU Pays and CSU DX. The CSU Pays segment encompasses solutions in digital payments, loyalty and incentives, and embedded finance, including card processing for issuers and acquirers in the credit, debit, digital, and virtual modalities; the offer of digital wallets, instant payments, and cryptocurrencies; and others. The CSU DX segment focuses on the development of digital experience solutions with technological and digital density, directing efforts to projects with added value and complexity. The company also provides development and operational management relationship and customer acquisition programs; electronic transaction services for companies; information technology outsourcing services; and banking correspondent services to financial institutions. In addition, it manages and operates telemarketing and telesales contact centers, and credit analysis; captures electronic transactions as means of payment; and develops credit card administration and issuance activities, as well as payment account management solutions and activities. The company was formerly known as CSU CardSystem S.A. and changed its name to CSU Digital S.A. in August 2022. The company was founded in 1992 and is headquartered in Barueri, Brazil. CSU Digital S.A. is a subsidiary of Greeneville Delaware LLC.</t>
+  </si>
+  <si>
+    <t>Companhia de Gás de São Paulo  COMGÁS engages in distribution of natural gas in Brazil. The company provides natural gas to customers in the industrial, residential, commercial, automotive, thermogeneration, and cogeneration sectors. Its concession area covers 180 municipalities in the São Paulo and Greater Sao Paulo regions. The company was formerly known as Companhia Municipal de Gás (Comgás) and changed its name to Companhia de Gás de São Paulo - COMGÁS in 1974. The company was incorporated in 1872 and is headquartered in São Paulo, Brazil. Companhia de Gás de São Paulo  COMGÁS is a subsidiary of Compass Gas e Energia S.A.</t>
+  </si>
+  <si>
+    <t>Grazziotin S.A. engages in the retail and wholesale business in Brazil. The company's stores offer furniture, convenience store merchandise, home appliances, electronics, housewares, household clothing and accessories, sports articles, and perfumery, as well as cosmetics, foodstuffs, decoration, camping, hygiene, and cleaning products. It is also involved in the financial institutions and insurance brokerage, as well as manages shopping centers. The company provides its products under Grazziotin, Franco Giorgi, Pormenos, Tottal, and GZT brand names. The company was founded in 1950 and is based in Passo Fundo, Brazil. Grazziotin S.A. operates as a subsidiary of V.R. Grazziotin S/A Administração e Participações.</t>
+  </si>
+  <si>
+    <t>Centrais Elétricas de Santa Catarina S.A., through its subsidiaries, engages in the generation, transmission, and sale of electrical energy in Brazil. It primarily owns hydroelectric plants, as well as distributes natural gas through pipes. The company was founded in 1955 and is based in Florianópolis, Brazil.</t>
+  </si>
+  <si>
+    <t>Suzano S.A. manufactures and sells pulp and paper products in Brazil and internationally. It operates in two segments, Pulp, and Paper and Consumer Goods. The company offers coated and uncoated printing and writing papers, paperboards, tissue papers, and market and fluff pulps. It also engages in the research, development, and production of biofuel; operation of port terminals; biotechnology and nanocrystalline pulps research and development activities; power generation and distribution business; road freight transport activities; commercialization of equipment and parts; research and development of lignin; industrialization and commercialization of cellulose, microfiber cellulose, paper, and paperboard products; industrialization, commercialization, and exporting of pulp products; and commercialization of paper and computer materials. In addition, the company is involved in the business office, corporate venture capital, and financial fundraising activities; production of consumer goods through cellulose-based liquids; development and production of cellulose-based fibers, yarns, and textile filaments; restoration, conservation, and preservation of forests; and research of raw materials for the textile industry. The company was formerly known as Suzano Papel e Celulose S.A. and changed its name to Suzano S.A. in April 2019. The company was founded in 1924 and is headquartered in Salvador, Brazil.</t>
+  </si>
+  <si>
+    <t>Technos S.A., together with its subsidiaries, engages in the manufacturing and wholesale distribution of wristwatches. The company also provides technical assistance services for watches. It sells watches through retail stores, as well as websites under the Technos, Mormaii, Michael Kors, Touch, Allora, Fossil, Euro, and Condor brands. Technos S.A. was founded in 1956 and is headquartered in Rio de Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>Banco Mercantil do Brasil S.A., together with its subsidiaries, provides financial services to individuals and corporate clients in Brazil. It operates through Financial, Insurance and Business Intermediation, Marketplace, and Other segments. The company offers current accounts, loans, cards, insurance and investment products, private pension, benefit transfer, special limit, special checks, capital market products, and card receivables. It also provides internet, WhatsApp, Mercantile app, and self-service banking services. In addition, the company engages in real estate, securitization, and technology activities. The company was formerly known as Banco Industrial de Minas Gerais and changed its name to Banco Mercantil do Brasil S.A. in 1974. Banco Mercantil do Brasil S.A. was founded in 1940 and is headquartered in Belo Horizonte, Brazil.</t>
+  </si>
+  <si>
+    <t>Bradespar S.A., through its interest in VALE, operates as a mining company in the production of iron ore and pellets, and nickel in Brazil. The company also produces copper, thermal and metallurgical coal, manganese, platinum group metals, gold, silver, and cobalt, as well as raw materials for the steel industry with applications in the stainless-steel industry, and metal alloys used in the production of various products. In addition, it operates logistics systems, including railways, ports, and terminals, as well as engages in energy generation business. Bradespar S.A. was founded in 1942 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Ouro Fino Saúde Animal Participações S.A., together with its subsidiaries, engages in the development, production, and sale of veterinary drugs, vaccines, and other products for production and companion animals primarily in Brazil. The company operates through three segments: Production Animals; Companion Animals; and International Operations. It manufactures and trades in medicines, including anti-inflammatories, antibiotics, anticoccidials, antimastitics, ectoparasiticides, endectocides, endoparasiticides, hemoparasiticides, inoculants, therapeutics, products for animal reproduction, and vaccines; and performance-enhancing additives, probiotics, and other veterinary products for cattle, swine, poultry, sheep, horses, and goats, as well as manufacturing services. The company also manufactures veterinary solutions for dogs and cats, such as anesthetics, sedatives, anti-inflammatory, antibiotic, antimicrobial, dermatological, ectoparasiticide, endoparasiticide, dermocosmetic, and otological products. In addition, it offers vaccines and other veterinary products for production and companion animals. The company was formerly known as A.H.N.S.P.E. Empreendimentos e Participações S.A. Ouro Fino Saúde Animal Participações S.A. was incorporated in 1987 and is headquartered in Cravinhos, Brazil.</t>
+  </si>
+  <si>
+    <t>Ultrapar Participações S.A., through its subsidiaries, operates in the energy, mobility, and infrastructure business in Brazil. The company distributes liquefied petroleum gas to residential, commercial, and industrial consumers. It also involved in the distribution and marketing of gasoline, ethanol, diesel, fuel oil, kerosene, natural gas for vehicles, and lubricants; and holds AmPm convenience stores and provides Jet Oil lubricant services. In addition, the company operates liquid bulk storage terminals. Further, the company offers digital payments services, combining the abastece aí app and the loyalty program Km de Vantagens. It also exports its products and services to customers in Europe, the United States, Canada, other Latin American countries, Sinagpore, and internationally. Ultrapar Participações S.A. was founded in 1937 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Banestes S.A - Banco do Estado do Espírito Santo S.A. provides various financial products and services to individual and corporate clients in the State of Espírito Santo, Brazil. It operates in the areas of insurance and distribution, intermediation, and administration of third-party resources. The company also offers current and savings accounts, loans, cards, and asset management services. It operates through commercial, rural, industrial, real estate, foreign exchange, leasing, investment, and credit card management credit portfolios. The company was founded in 1935 and is based in Vitória, Brazil.</t>
+  </si>
+  <si>
+    <t>Itaúsa S.A., through its subsidiaries, operates in the financial and industrial markets in Brazil and internationally. The company offers credit products and other financial services to individuals and corporate clients. It also engages in the operation of highway concessions, urban mobility, and airports, as well as the transportation of gas through gas pipelines to distribution companies. In addition, it manufactures and sells bathroom fixtures, fittings, and showers; ceramic tiles, including floor and wall coatings under the Ceusa, Portinari, and Castelatto brands; pine and eucalyptus wood panels primarily used in the manufacture of medium- and high-density wood panels under the Duratex and Durafloor brand; and footwear, apparel, textiles, and related components, as well as leather, resin, and natural and artificial rubber. Further, it provides sanitation services. The company was formerly known as Itaúsa - Investimentos Itaú SA. Itaúsa S.A. was incorporated in 1966 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Companhia Energética de Brasília - CEB, through its subsidiaries, engages in the generation and distribution of electrical energy in Brazil. It operates through Power Generation, Commercialization of Electric Energy, and Others segments. The company produces electricity from hydraulic power plants; distributes piped gas; public lighting services; and provides maintenance and expansion services. It is also involved in the provision of services for studies; engineering projects; execution of implementation, expansion, renovation, or maintenance of overhead and underground electricity transmission and distribution networks; and installation of public lighting systems and electrical building. The company was formerly known as Companhia de Eletricidade de Brasília and changed its name to Companhia Energética de Brasília  CEB in 1992. Companhia Energética de Brasília  CEB was founded in 1968 and is headquartered in Brasília, Brazil.</t>
   </si>
   <si>
     <t>Itaú Unibanco Holding S.A. provides various financial products and services to personal and corporate customers in Brazil and internationally. It operates through three segments: Retail Banking, Wholesale Banking, and Activities with the Market + Corporation. The company offers current account; loans; credit and debit cards; investment and commercial banking services; real estate lending and financing services; economic, financial and brokerage advisory; and leasing and foreign exchange services. The company also provides non-life insurance products covering loss, damage, or liability for objects or people, as well as life insurance products covering death and personal accidents. It serves retail customers, account and non-account holders, individuals and legal entities, high income clients, microenterprises, and small companies, as well as middle-market companies and high net worth institutional clients. The company was formerly known as Itaú Unibanco Banco Múltiplo S.A. and changed its name to Itaú Unibanco Holding S.A. in April 2009. The company was incorporated in 1924 and is headquartered in São Paulo, Brazil. Itaú Unibanco Holding S.A. is a subsidiary of IUPAR - Itaú Unibanco Participações S.A.</t>
   </si>
   <si>
-    <t>Cyrela Brazil Realty S.A. Empreendimentos e Participações develops and constructs residential properties in Brazil. It also provides real estate services, such as construction management and technical consultancy services. The company was founded in 1962 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Unipar Carbocloro S.A. produces and sells chlorine and caustic soda in South America. The company offers liquid caustic soda, sodium hypochlorite, dicloroetano, hydrochloric acid, and polyvinyl chloride. Its products are used in textile, pulp and paper, food, beverage, medicine, and construction industries. Unipar Carbocloro S.A. was incorporated in 1969 and is based in São Paulo, Brazil. Unipar Carbocloro S.A. operates as a subsidiary of Vila Velha S.A. Administração e Participações.</t>
-  </si>
-  <si>
-    <t>Ultrapar Participações S.A., through its subsidiaries, operates in the energy and infrastructure business in Brazil. The company distributes liquefied petroleum gas to residential, commercial, and industrial consumers. In addition, the company is involved in the distribution and marketing of gasoline, ethanol, diesel, fuel oil, kerosene, natural gas for vehicles, and lubricants; and holds AmPm convenience stores and provides Jet Oil lubricant services. Further, it operates liquid bulk storage terminals. Additionally, the company offers digital payments services, combining the abastece aí app and the loyalty program Km de Vantagens. It also exports its products and services to customers in Europe, the United States, Canada, other Latin American countries, Asia, and internationally. The company was founded in 1937 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Vivara Participações S.A. engages in the manufacture and sale of jewelry and other articles in Latin America. It offers jewelry products, including rings, necklaces, alliances and solitaires, earrings, chains, pendants, and bracelets. The company provides various accessories, such as cufflinks, pens, sunglasses, watch and passport holders, notebooks, wallets, bags and backpacks, perfumes, and jewelry cases, pocket knives, travel items, keychains, and watch bands, as well as clocks, gifts, and gift cards. It offers its products through stores and kiosks, as well as through online. Vivara Participações S.A. was founded in 1962 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Brava Energia S.A. engages in the exploration and production of oil and natural gas in Brazil. The company was formerly known as 3R Petroleum Óleo e Gás S.A. and changed its name to Brava Energia S.A. in September 2024. The company was founded in 2010 and is headquartered in Rio De Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Cury Construtora e Incorporadora S.A. operates in real estate businesses. The company provides real estate agency and brokerage services. It also offers financing services. In addition, the company is involved in credit analysis and online brokerage activities. Cury Construtora e Incorporadora S.A. was founded in 1963 and is based in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Itaúsa S.A., through its subsidiaries, operates in the financial and industrial markets in Brazil and internationally. The company offers credit products and other financial services to individuals and corporate clients. It also engages in the operation of highway concessions, urban mobility, and airports, as well as the transportation of gas through gas pipelines to distribution companies. In addition, it manufactures and sells bathroom fixtures, fittings, and showers; ceramic tiles, including floor and wall coatings under the Ceusa, Portinari, and Castelatto brands; pine and eucalyptus wood panels primarily used in the manufacture of medium- and high-density wood panels under the Duratex and Durafloor brand; and footwear, apparel, textiles, and related components, as well as leather, resin, and natural and artificial rubber. Further, it provides sanitation services. The company was formerly known as Itaúsa - Investimentos Itaú SA. Itaúsa S.A. was incorporated in 1966 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Suzano S.A. manufactures and sells pulp and paper products in Brazil and internationally. It operates in two segments, Pulp, and Paper and Consumer Goods. The company offers coated and uncoated printing and writing papers, paperboards, tissue papers, and market and fluff pulps. It also engages in the research, development, and production of biofuel; operation of port terminals; biotechnology and nanocrystalline pulps research and development activities; power generation and distribution business; road freight transport activities; commercialization of equipment and parts; research and development of lignin; industrialization and commercialization of cellulose, microfiber cellulose, paper, and paperboard products; industrialization, commercialization, and exporting of pulp products; and commercialization of paper and computer materials. In addition, the company is involved in the business office, corporate venture capital, and financial fundraising activities; production of consumer goods through cellulose-based liquids; development and production of cellulose-based fibers, yarns, and textile filaments; restoration, conservation, and preservation of forests; and research of raw materials for the textile industry. The company was formerly known as Suzano Papel e Celulose S.A. and changed its name to Suzano S.A. in April 2019. The company was founded in 1924 and is headquartered in Salvador, Brazil.</t>
-  </si>
-  <si>
-    <t>Direcional Engenharia S.A. engages in the development and construction of real estate properties in Brazil. It primarily develops and builds projects for low-income and middle-income families. The company was incorporated in 1981 and is based in Belo Horizonte, Brazil.</t>
-  </si>
-  <si>
-    <t>BRF S.A. raises, produces, and slaughters poultry and pork for processing, production, and sale of fresh meat, processed products, pasta, margarine, pet food, and other products. The company offers frozen whole and cut chicken, frozen pork, and turkey, and halal products for Islamic markets; processed foods, such as marinated, frozen, seasoned whole, and cut chicken, roosters, sausages, ham products, bologna, frankfurters, salamis, bacons, cold meats, and other smoked products; hamburgers, steaks, breaded meat products, kibbeh, and meatballs; and chicken sausages, hot dogs, and chicken bologna. It produces and sells lasagna, macaroni and cheese, pies, ready-to-eat meals, pizzas, and other frozen foods; nuggets, pies, vegetables, and burgers; frozen desserts and cheese bread; margarine, butter, cream cheese, sweet specialties, sandwiches, and pate, as well as soy meal, refined soy flour, animal feed, pet food and hatcheries. The company sells its products under the Sadia, Perdigão, Qualy, Sadia Halal, Chester, BRF Ingredients, Kidelli, Perdix, Borella, Hilal, Balance, Onefoods, Banvit, Deline, Sadia Bio, Sadia Salamitos, Sadia Veg&amp;Tal, Sadia Livre&amp;Lev, Confidence and Hilal, Sadia Hot Pocket, Perdigão Ouro, Chester Perdigão, Perdigão NaBrasa, Claybom, Biofresh, Three Dogs, Three Cats, Guabi Natural, Giran Plus, Balance, PrimoCão, PrimoGato, Faro, Bônos, Apolo, Átila, and Giran Plus brands. It serves supermarkets, wholesalers, retail and wholesale stores, restaurants, and other institutional buyers. The company offers consultancy, administrative, marketing, road freight, and logistics services; generates and commercializes electric energy; distributes nutrients for animals; and veterinary activities, as well as real estate. The company was formerly known as BRF-Brasil Foods S.A. and changed its name to BRF S.A. in April 2013. BRF S.A. was founded in 1934 and is headquartered in São Paulo, Brazil. BRF S.A. is a subsidiary of Marfrig Global Foods S.A.</t>
-  </si>
-  <si>
-    <t>Engie Brasil Energia S.A., together with its subsidiaries, generates, sells, and trades in electrical energy in Brazil. The company operates various plants, including hydroelectric power plants, wind farms, biomass plants, photovoltaic solar plants, and small hydroelectric power plants. It also engages in transportation of natural gas business. Engie Brasil Energia S.A. was founded in 2005 and is headquartered in Florianópolis, Brazil. The company operates as a subsidiary of ENGIE Brasil Participações Ltda.</t>
-  </si>
-  <si>
-    <t>Odontoprev S.A. provides private dental plans in Brazil. It operates through Corporate, Small and Medium-Sized Enterprise (SME), Individual, and Other segments. The company manages and sells dental care plans to corporations and/or individuals. It is also involved in commercial advisory, consulting, and business management services; develops and licenses software programs; retails and wholesales sanitizers, drugs, medicines, pharmaceutical inputs, and related items; provision of warehousing, storage, loading, organization, custody of goods, technical, and administrative programming services, as well as general management of goods and business. In addition, the company engages in collecting, sending, or delivering mail, documents, and objects or goods; integrating technologies to develop dental solutions; and provision of specialized services related to accidents and diseases, besides actuarial, financial, administrative, and commercial and risk management services. Odontoprev S.A. was founded in 1987 and is headquartered in Barueri, Brazil. Odontoprev S.A. is a subsidiary of Bradesco Saúde S.A.</t>
-  </si>
-  <si>
-    <t>Bradespar S.A., through its interest in VALE, operates as a mining company in the production of iron ore and pellets, and nickel in Brazil. The company also produces copper, thermal and metallurgical coal, manganese, platinum group metals, gold, silver, and cobalt, as well as raw materials for the steel industry with applications in the stainless-steel industry, and metal alloys used in the production of various products. In addition, it operates logistics systems, including railways, ports, and terminals, as well as engages in energy generation business. Bradespar S.A. was founded in 1942 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Wilson Sons S.A., through its subsidiaries, provides port and maritime logistics and supply chain solutions primarily in Brazil. The company manages two container terminals, such as Rio Grande and Salvador container terminals. It provides general and bonded warehousing, inventory management, distribution, transport management, and foreign trade solutions. The company also operates 82 tugboats; and offers firefighting and others, as well as offshore maritime support and ocean towage services. In addition, it is involved in the construction, conversion, maintenance, and repair of vessels, marine and offshore structures, as well as shipping agency activities. Further, the company provides logistics services, such as wharf for mooring, cargo handling, storage, water storage/supply, procurement, material inventory management, office, fluid plant, and road scale services; and environmental services, waste management, tank cleaning, and containment barriers to prevent oil spills during docking. It serves shipping owners, importers, exporters, and oil and gas industries, as well as other participants in various sectors. Wilson Sons S.A. was founded in 1837 and is headquartered in Rio De Janeiro, Brazil. As of June 4, 2025, Wilson Sons S.A. operates as a subsidiary of SAS Shipping Agencies Services SÀRL.</t>
-  </si>
-  <si>
-    <t>Porto Seguro S.A. provides a range of insurance products and services in Brazil and Uruguay. It offers auto, health and dental, damage and personal, health, casualty, financial risk, and life insurance; and reinsurance products. The company also provides services related to insurance, protection, and electronic monitoring; telemarketing and call center, telecommunications, and technical insurance brokerage services; vehicle subscription models, cargo management for companies, and other vehicle rental modalities; administrative advisory services to physicians and health care providers; consulting and advisory services in occupational health, labor security, ergonomics, and outpatient medical services; services to obtain credits and financing; assistance, maintenance, repairs, and individualization of consumption measurement; vehicle maintenance, assistance, and repair services; service platform that offers solutions to end consumers through retailers, telecom, utilities and insurers; and assistance services to consumers in the auto, travel, health, concierge and home lines. In addition, the company trades and distributes in auto parts; manages securities portfolios, investment funds, special savings bonds, and other third party funds; retail trades in live animals and pet articles and food; operates oncology, hematology, and radiotherapy centers; grants loans and financing; acquires chattels and properties; distributes investment fund quotas; operates credit cards, electronic payment for opening of toll gates and parking lots, and rental property listing platform; develops technological solutions for the real estate industry; and installs heating, natural gas, and liquefied petroleum gas systems technical. The company was founded in 1945 and is based in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Santos Brasil Participações S.A. provides port container handling and logistics services in Brazil. It offers loading and unloading containers, vehicles and general cargo on and off ships to handling, warehousing, transporting and distributing containers, as well as connects engages in connecting supply chain, integrated, and customized logistics solutions. The company serves shipowners, and import and export clients in various segments, such as chemical, industrial supplies, automotive components, pharmaceutical, food, petrochemicals, agribusiness, auto parts and consumer goods. Santos Brasil Participações S.A. was founded in 1997 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>IRB-Brasil Resseguros S.A. engages in the provision of reinsurance solutions in Brazil and internationally. It offers reinsurance solutions for life and pension, agricultural risks, cargo and marine, casualty, property, oil and gas, financial lines, surety, and housing. The company was incorporated in 1939 and is headquartered in Rio de Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Multiplan Empreendimentos Imobiliários S.A. engages in the planning, development, construction, and sale of real estate projects in Brazil. The company develops residential or commercial properties, including urban shopping malls. It is also involved in the purchase and sale of real estate properties, as well as acquisition and disposal of real estate rights, and its operation through leasing. In addition, the company provides management and administrative services for own or third party shopping malls; consultancy and technical advisory and support services concerning real estate matters; and civil construction, construction works execution, and engineering and related services. Further, it engages in the planning, development, management, promotion, and intermediation of real estate projects; import and export of goods and services related to its activities; generation and sale of electric power; storage of vehicles; and parking, as well as operates theaters; and involved in advertising, agency, and amusement services. Additionally, the company engages in artistic, cultural events, exhibitions, auctions, music festivals, cinematographic, social and promotional events; and charities; and leases sound and light equipment. Multiplan Empreendimentos Imobiliários S.A. was founded in 1974 and is based in Rio de Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Grupo SBF S.A. engages in the retail and wholesale of sports and leisure products in Brazil. The company offers footwear, clothing, equipment, and accessories. It also provides logistics services; and organizing races and sporting events under the Xterra and Uphill brands. In addition, the company engages in the advertising films and audiovisual production businesses. Further, it operates dance platform and sports channel network. The company sells its sports and leisure products through physical stores and e-commerce channels. Grupo SBF S.A. was founded in 1981 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Klabin S.A., together with its subsidiaries, produces and exports packaging paper and sustainable paper packaging solutions in Brazil and internationally. The company engages in the planting of pine and eucalyptus; and forestry management business. It also produces and sells hardwood (eucalyptus), softwood (pine), and fluffed pulp; and paperboard, sackraft, Kraftliner paper, and recycled paper. In addition, the company offers industrial bags, corrugated boxes, and other packaging products. Klabin S.A. was founded in 1899 and is headquartered in São Paulo, Brazil.</t>
+    <t>Porto Seguro S.A. provides a range of insurance products and services in Brazil and Uruguay. It offers auto, health and dental, damage and personal, health, casualty, financial risk, and life insurance; and reinsurance products. The company also provides services related to insurance, protection, and electronic monitoring; telemarketing and call center, telecommunications, and technical insurance brokerage services; vehicle subscription models, cargo management for companies, and other vehicle rental modalities; administrative advisory services to physicians and health care providers; consulting and advisory services in occupational health, labor security, ergonomics, and outpatient medical services; services to obtain credits and financing; assistance, maintenance, repairs, and individualization of consumption measurement; vehicle maintenance, assistance, and repair services; service platform that offers solutions to end consumers through retailers, telecom, utilities and insurers; and assistance services to consumers in the auto, travel, health, concierge and home lines. In addition, the company trades and distributes in auto parts; manages securities portfolios, investment funds, special savings bonds, and other third party funds; retail trades in live animals and pet articles and food; operates oncology, hematology, and radiotherapy centers; grants loans and financing; acquires chattels and properties; distributes investment fund quotas; operates credit cards, electronic payment for opening of toll gates and parking lots, and rental property listing platform; develops technological solutions for the real estate industry; and installs heating, natural gas, and liquefied petroleum gas systems technical. The company was founded in 1945 and is based in São Paulo, Brazil. Porto Seguro S.A. is a subsidiary of Porto Seguro Itaú Unibanco Participações S.A.</t>
+  </si>
+  <si>
+    <t>LPS Brasil - Consultoria de Imóveis S.A. provides real estate brokerage services in Brazil. It operates through Brokerage, Franchises, and Financing Promotion segments. The company provides brokerage services for the sale and purchase of third-party and land subdivision properties; and consulting, technical real estate advisory, franchises, correspondent bank, and other related services. It also engages in promoting and offering financial products and services in the real estate market. The company was founded in 1935 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Klabin S.A., together with its subsidiaries, produces and exports packaging paper and sustainable paper packaging solutions in Brazil and internationally. The company engages in the planting of pine and eucalyptus; and forestry management business. It also produces and sells hardwood (eucalyptus), softwood (pine), and fluffed pulp; and paperboard, sack kraft, Kraftliner paper, corrugated cardboard sheets, and recycled paper. In addition, the company offers industrial bags and corrugated boxes. Klabin S.A. was founded in 1899 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Taurus Armas S.A., together with its subsidiaries, offers firearms and accessories in Brazil and internationally. It operates through Firearms, Helmets, and Other segments. It offers pistols, revolvers, rifles, and suppressors for armed forces; state, federal, civil, and military police; and civilian markets. The company sells its products under the Taurus, Heritage, and Rossi brand names. Taurus Armas S.A. was incorporated in 1939 and is headquartered in São Leopoldo, Brazil. Taurus Armas S.A. is a subsidiary of BYK Participações SA.</t>
+  </si>
+  <si>
+    <t>Banco do Brasil S.A., together with its subsidiaries, provides banking products and services for individuals, companies, and public sectors in Brazil and internationally. The company's Banking segment offers various products and services, including deposits, loans, and other services to retail, wholesale, and public sectors. This segment also engages in the business with micro-entrepreneurs and low-income population undertaken through banking correspondents. Its Investments segment engages in the domestic capital markets; intermediation and distribution of debts in the primary and secondary markets; and provision of equity investments and financial services. The company's Fund Management segment is involved in the purchase, sale, and custody of securities and portfolio management; and management of investment funds and clubs. Its Insurance, Pension and Capitalization segment provides life, property, and automobile insurance products, as well as private pension and capitalization plans. The company's Payments Method segment provides funding, transmission, processing, and settlement services for electronic transactions. Its Other segment engages in the provision of credit recovery and consortium management services. This segment is also involved in developing, manufacturing, selling, leasing, and integrating of digital electronic equipment and systems, peripherals, programs, inputs, and computing supplies. The company was incorporated in 1808 and is headquartered in Brasília, Brazil.</t>
+  </si>
+  <si>
+    <t>Eucatex S.A. Indústria e Comércio produces and sells hardboard, wood, and related materials in Brazil. The company provides laminate and vinyl floors, Eucafix systems, doors, partitions, MDF and MDP panels, T-HDF panels, wood panels, fiberboards, paint and varnishes, wood fiber sheets, lacquers, and other products. It also produces eucalyptus seedlings; and engages in business management consultancy, real estate, forestry, harvesting, forest management, transport, waste collection logistics and recycled material, and electricity activities. The company primarily serves furniture and construction industries. It also exports its products to the United States and Latin America. Eucatex S.A. Indústria e Comércio was incorporated in 1951 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Multiplan Empreendimentos Imobiliários S.A. engages in the planning, development, construction, and sale of real estate projects in Brazil. The company develops residential or commercial properties, including urban shopping malls. It is also involved in the purchase and sale of real estate properties, as well as acquisition and disposal of real estate rights, and its operation through leasing. In addition, the company provides management and administrative services for own or third party shopping malls; consultancy and technical advisory and support services concerning real estate matters; and civil construction, construction works execution, and engineering and related services. Further, it engages in the planning, development, management, promotion, and intermediation of real estate projects; import and export of goods and services related to its activities; generation and sale of electric power; storage of vehicles; and parking, as well as operates shopping mall, and theaters; and involved in advertising, and agency services. Additionally, the company engages in artistic, cultural events, exhibitions, auctions, music festivals, cinematographic, social and promotional events; and charities; and leases sound and light equipment. Multiplan Empreendimentos Imobiliários S.A. was incorporated in 2005 and is based in Rio De Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>B3 S.A. - Brasil, Bolsa, Balcão, a financial market infrastructure company, provides trading services in an exchange and OTC environment. The company engages in the administration of organized securities and bond markets; operation and maintenance of environments or systems for conducting business, including purchases and sales, auctions, and registration of transactions involving securities, bonds, rights, and financial assets; and creation of databases and related activities, including data processing and intelligence. It also provides registration, clearing and settlement services; registrar and central depository; safekeeping services; services for the registration of liens and encumbrances on securities, bonds, financial assets, other types of assets, and other financial instruments, including the registration of instruments constituting collateral; and services associated with the insurance, reinsurance, pension, and capitalization bonds market. In addition, the company offers services related to processed data, including standardization, classification, analysis, quotations, statistics, professional training, conducting studies, publications, information, provision of information. Further, it provides services related to transactions registered and deposited in the markets and systems, and support for credit, financing, and leasing transactions, or transactions registered and deposited in the managed systems. The company was formerly known as BM&amp;FBOVESPA S.A. - Bolsa de Valores, Mercadorias e Futuros and changed its name to B3 S.A. - Brasil, Bolsa, Balcão in June 2017. B3 S.A. - Brasil, Bolsa, Balcão was incorporated in 2007 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
     <t>Banco Bradesco S.A., together with its subsidiaries, provides various banking products and services to individuals, corporates, and businesses in Brazil and internationally. The company operates through two segments, Banking and Insurance. It provides current, savings, click, and salary accounts; real estate credit, vehicle financing, payroll loans, mortgage loans, microcredit, leasing, and personal and installment credit; overdraft and agribusiness loans; debit and business cards; financial and security services; consortium products; car, personal accident, dental, travel, and life insurance; investment products; pension products; foreign currency exchange services; capitalization bonds; and internet banking services. The company was founded in 1943 and is headquartered in Osasco, Brazil.</t>
   </si>
   <si>
-    <t>Companhia de Saneamento de Minas Gerais plans, designs, performs, expands, remodels, manages, and provides water supply and sewage treatment services in Brazil and internationally. It engages in the collection, recycling, treatment, and final disposal of sanitary sewage; drainage and management of urban rainwater; supply of drinking water; and collection, transport, transfer, treatment, and destination of urban, domestic, and industrial waste. The company was formerly known as Companhia Mineira de Água e Esgotos and changed its name to Companhia de Saneamento de Minas Gerais in November 1974. The company was founded in 1963 and is headquartered in Belo Horizonte, Brazil.</t>
-  </si>
-  <si>
-    <t>Cogna Educação S.A. operates as a private educational organization in Brazil and internationally. It operates through three segments: Kroton, Vasta, and Saber. The company provides on campus and distance-learning higher education, and undergraduate and graduate courses; and editing, marketing, and distribution of teaching books, educational materials, and workbooks. It offers basic education, pre-university preparatory courses, and language courses; educational solutions for technical and higher education; and complementary activities, such as education technology development for services to complement management and training. In addition, the company offers administration of kindergarten, elementary and high school activities; advises on and/or enables direct and indirect financing for students; and develops software for adaptive teaching and academic management optimization. The company was incorporated in 2001 and is headquartered in Belo Horizonte, Brazil.</t>
-  </si>
-  <si>
-    <t>CSN Mineração S.A. engages in the iron ore mining business in Brazil. The company operates Casa de Pedra and Engenho mines. It also operates a hydroelectric power plant. The company was founded in 1913 and is based in São Paulo, Brazil. CSN Mineração S.A. operates as a subsidiary of Companhia Siderúrgica Nacional.</t>
-  </si>
-  <si>
     <t>Banco do Estado do Rio Grande do Sul S.A., a multiple-service bank, provides a range of banking products and services primarily in Brazil. The company engages in the retail banking, lending, financing and investment, mortgage loan, development, lease portfolio, and foreign exchange activities. It also provides securities brokerage, payment industry solutions, insurance, and pension plan and saving bonds products, as well as manages sales poll groups. The company was incorporated in 1928 and is headquartered in Porto Alegre, Brazil.</t>
   </si>
   <si>
-    <t>Banco do Brasil S.A., together with its subsidiaries, provides banking products and services for individuals, companies, and public sectors in Brazil and internationally. The company's Banking segment offers various products and services, including deposits, loans, and other services to retail, wholesale, and public sectors. This segment also engages in the business with micro-entrepreneurs and low-income population undertaken through banking correspondents. Its Investments segment engages in the domestic capital markets; intermediation and distribution of debts in the primary and secondary markets; and provision of equity investments and financial services. The company's Fund Management segment is involved in the purchase, sale, and custody of securities and portfolio management; and management of investment funds and clubs. Its Insurance, Pension and Capitalization segment provides life, property, and automobile insurance products, as well as private pension and capitalization plans. The company's Payments Method segment provides funding, transmission, processing, and settlement services for electronic transactions. Its Other segment engages in the provision of credit recovery and consortium management services. This segment is also involved in developing, manufacturing, selling, leasing, and integrating of digital electronic equipment and systems, peripherals, programs, inputs, and computing supplies. The company was incorporated in 1808 and is headquartered in Brasília, Brazil.</t>
-  </si>
-  <si>
-    <t>Vale S.A., together with its subsidiaries, produces iron ore and nickel in Asia, the Americas, Europe, and internationally. It operates through Iron Solutions and Energy Transition Materials segments. The company  extracts, produces, and distributes iron ore, iron ore pellets, briquettes, and other ferrous products; and operates mining complexes, railways, maritime terminals, and ports for the transportation of its products. It also produces nickel, copper, cobalt, and by-products, such as gold, silver, cobalt, platinum group metals, and other precious metals. In addition, the company engages in greenfield mineral exploration; invests in energy businesses through renewable sources; research; trading; and pelletizing plant. It exports its products. The company was formerly known as Companhia Vale do Rio Doce and changed its name to Vale S.A. in May 2009. Vale S.A. was founded in 1942 and is headquartered in Rio De Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Intelbras S.A. - Indústria de Telecomunicação Eletrônica Brasileira engages in the manufacturing, developing, and sale of electronic security equipment and electronic surveillance and monitoring services in Brazil. The company operates through Security, Communication, and Energy segments. It offers electronic safety products and solutions, including automation devices, alarms, storage, cameras, condominium communication, corporate access control, locks, digital video recorders, fire and intercom products, vehicle monitoring, sensors, emergency signaling, video walls, software and application products, and accessories; and networks products and solutions comprise racks, routers, 5G and corporate Wi-Fi products, outdoor radios, optical fiber and passive products, switches, PoE injectors, signal repeaters, USB adapters, software and apps, and cables. The company also provides communication related products and solutions, such as webcams, projectors, wireless mouse and keyboards, cloud solutions, antennas and converters, phone centrals, appliance and conference products, gateways, headsets, radio communicators, smart boxes and controls, smart speakers, software and applications, and phones; and energy related products and solutions that includes electric vehicle chargers, fonts, batteries, UPS, electronic protectors, surge protectors, USB accessories, and illumination presence sensors. In addition, it offers on grid solutions, which includes attachment structures, on grid generators and inverters, solar panels, and string box; and off grid solutions, such as illumination products, mounting structures, outdoor cabinets, solar drive and panels, solar bomb, and off grid generators and inverters. The company was incorporated in 1974 and is headquartered in São José, Brazil.</t>
-  </si>
-  <si>
-    <t>B3 S.A. - Brasil, Bolsa, Balcão, a financial market infrastructure company, provides trading services in an exchange and OTC environment. The company engages in the administration of organized securities and bond markets; operation and maintenance of environments or systems for conducting business, including purchases and sales, auctions, and registration of transactions involving securities, bonds, rights, and financial assets; and creation of databases and related activities, including data processing and intelligence. It also provides registration, clearing and settlement services; registrar and central depository; safekeeping services; services for the registration of liens and encumbrances on securities, bonds, financial assets, other types of assets, and other financial instruments, including the registration of instruments constituting collateral; and services associated with the insurance, reinsurance, pension, and capitalization bonds market. In addition, the company offers services related to processed data, including standardization, classification, analysis, quotations, statistics, professional training, conducting studies, publications, information, provision of information. Further, it provides services related to transactions registered and deposited in the markets and systems, and support for credit, financing, and leasing transactions, or transactions registered and deposited in the managed systems. The company was formerly known as BM&amp;FBOVESPA S.A. - Bolsa de Valores, Mercadorias e Futuros and changed its name to B3 S.A. - Brasil, Bolsa, Balcão in June 2017. B3 S.A. - Brasil, Bolsa, Balcão was incorporated in 2007 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Neoenergia S.A. generates, transmits, distributes, trades in, and commercializes electric energy in Brazil. It operates through Networks, Renewables, Liberalized, and Others. The company provides free energy markets solutions, such as free energy market, power management, management and billing system, renewable energy certificates, and long term contracts; green hydrogen, that includes green ammonia, steel, and methanol; industrial gas solutions; local and remote solar power plant; engineering; and electrified fleet solutions for businesses. It also offers solar electric charge, insurance, and services for residential customers. The company was founded in 1997 and is based in Rio De Janeiro, Brazil. Neoenergia S.A. operates as a subsidiary of Iberdrola Energía, S.A.U.</t>
-  </si>
-  <si>
-    <t>EZTEC Empreendimentos e Participações S.A. engages in the engineering, construction, and real estate development activities in Brazil and internationally. The company develops and sells of real estate properties; manages and leases properties; construction of condominiums; and subdivision of land. It also engages in the provision of services related to construction, supervision, studies, and projects; and execution of civil engineering works and services. EZTEC Empreendimentos e Participações S.A. was founded in 1979 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>WEG S.A. engages in the production and sale of capital goods in Brazil and internationally. The company offers electric motors, generators, and transformers; gear units and geared motors; hydraulic and steam turbines; frequency converters; motor starters and maneuver devices; control and protection of electric circuits for industrial automation; power sockets and switches; and electric traction solutions for heavy vehicles, SUV, locomotives, and sea transportation capital goods. It provides solutions for the generation of renewable and distributed energy through hydro, thermal, biomass, wind, and solar energy power plants; solutions for industry; uninterruptible power supplies and alternators for groups of generators; conventional and movable electric substations; industrial electrical and electronic systems; industrial paint and varnish; and paints for automotive repainting. WEG S.A. was founded in 1961 and is headquartered in Jaraguá do Sul, Brazil. WEG S.A. operates as a subsidiary of WEG Participações e Serviços S.A.</t>
-  </si>
-  <si>
-    <t>C&amp;A Modas S.A. operates as a fashion retailer for women, men, and children in Brazil and internationally. It offers blouses, pants, dresses, skirts, coats, beach and intimate fashion products, T-shirts, Shirts, pants, jackets and coats, shorts, footwear, sandals, perfumes, makeup and skincare products, body and bath products, and accessories, as well as cell phones, smartphones, watches, decoration, pets, jewellery, and other products. The company sells its products through stores, as well as online. The company was founded in 1841 and is based in Barueri, Brazil. C&amp;A Modas S.A. operates as a subsidiary of C&amp;A AG.</t>
-  </si>
-  <si>
-    <t>Alupar Investimento S.A., through its subsidiaries, engages in the transmission, generation, and development of electricity business in Brazil, Colombia, and Peru. The company operates through Transmission and Generation segments. It operates hydroelectric and wind power plant. In addition, the company holds transmission assets. Further, it is involved in solar photovoltaic related business. Alupar Investimento S.A. was founded in 2007 and is headquartered in São Paulo, Brazil. Alupar Investimento S.A. operates as a subsidiary of Guarupart Participações Ltda.</t>
+    <t>Blau Farmacêutica S.A., a pharmaceutical company provides drug products in Brazil, Argentina, Chile, Colombia, Uruguay, Ecuador, Peru, and the United States. Its products cover various areas, such as immunology, hematology, oncology, nephrology, infectology, and anesthesiology. The company offers uterine stimulator, antirheumatic, anaesthetics, antibiotics, feminine health care, biopharmaceuticals, oncologicals, hospital products, antivirals and antiretrovirals, biológicos, acid pump inhibitor, hemoderivatives, antithrombotic, and thrombolytics products. Blau Farmacêutica S.A. was incorporated in 1987 and is headquartered in Cotia, Brazil.</t>
+  </si>
+  <si>
+    <t>Unifique Telecomunicações S.A. provides telecommunications services in Brazil. The company offers data storage, data hosting, and internet services. It also provides SCM multimedia communications services; access to communication networks, portals, content providers, and information services; satellite, cable, and microwave pay-TV; and internet hosting and switched fixed-line telephone services. In addition, the company retail trades computer and mobile phone equipment and supplies; monitors electronic security systems; provides supplementary pension and health plans; and publishes books and retail trades books. Unifique Telecomunicações S.A. was incorporated in 1997 and is headquartered in Timbó, Brazil.</t>
+  </si>
+  <si>
+    <t>WEG S.A. engages in the production and sale of capital goods in Brazil and internationally. The company offers electric motors, generators, and transformers; gear units and geared motors; hydraulic and steam turbines; frequency converters; motor starters and maneuver devices; control and protection of electric circuits for industrial automation; power sockets and switches; and electric traction solutions for heavy vehicles, SUV, locomotives, and sea transportation capital goods. It also provides solutions for the generation of renewable and distributed energy through hydro, thermal, biomass, wind, and solar energy power plants; solutions for industry; uninterruptible power supplies and alternators for groups of generators; conventional and movable electric substations; industrial electrical and electronic systems; industrial paint and varnish; and paints for automotive repainting. WEG S.A. was founded in 1961 and is headquartered in Jaraguá do Sul, Brazil. WEG S.A. is a subsidiary of WEG Participações e Serviços S.A.</t>
+  </si>
+  <si>
+    <t>Vale S.A., together with its subsidiaries, produces iron ore and nickel in Asia, the Americas, Europe, and internationally. It operates through Iron Solutions and Energy Transition Materials segments. The company extracts and produces iron ore, iron ore pellets, briquettes, and other ferrous products; provides logistic related services; and operates mining complexes, railways, maritime terminals, and ports. It also produces nickel, copper, and cobalt, as well as by-products, such as gold, silver, platinum group metals, and other precious metals. In addition, the company engages in greenfield mineral exploration; invests in energy businesses through renewable sources; and operates pelletizing plants and distribution centers to support the delivery of iron ore. The company was formerly known as Companhia Vale do Rio Doce and changed its name to Vale S.A. in May 2009. Vale S.A. was founded in 1942 and is headquartered in Rio De Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>Companhia Energética do Ceará  COELCE engages in the electricity distribution services. It operates in 184 municipalities in the state of Ceará in Brazil. The company is headquartered in Fortaleza, Brazil. Companhia Energética do Ceará  COELCE operates as a subsidiary of Enel Brazil S.A.</t>
+  </si>
+  <si>
+    <t>Eternit S.A., together with its subsidiaries, engages in roofing and construction solutions business in China. The company offers fiber cement tiles, solar roof titles, and other parts. It also provides construction systems, such as cement slabs, cement sheet siding, wall panels, and other accessories. In addition, the company manufactures and markets products made from cement, concrete, plaster, and plastic, as well as other construction materials and related accessories. Eternit S.A. was founded in 1940 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Profarma Distribuidora de Produtos Farmacêuticos S.A., together with its subsidiaries, engages in the distribution of pharmaceutical products in Brazil. It provides pharmaceutical, personal hygiene, and beauty products. The company operates retail stores under the Drogasmil, Farmalife, Drogarias Tamoio and Drogaria Rosário brands. Profarma Distribuidora de Produtos Farmacêuticos S.A. was incorporated in 1961 and is headquartered in Rio De Janeiro, Brazil.</t>
   </si>
   <si>
     <t>Banco BTG Pactual S.A. provides financial products and services related to trading and investment portfolios, credit, financing, leasing, insurance, and foreign exchange in Brazil and internationally. The company also offers personal investment services for a customized investment portfolio; international banking account services, including debit card, transfer, payment and receipt, and customer support services. It also provides wealth management services, such as educational resources, analytics, relationship management, technical advisory, brokerage, marketable securities placement, and research-related services. Banco BTG Pactual S.A. was founded in 1983 and is headquartered in Rio de Janeiro, Brazil. Banco BTG Pactual S.A. operates as a subsidiary of BTG Pactual Holding Financeira Ltda.</t>
   </si>
   <si>
-    <t>Grupo Mateus S.A. operates a supermarket chain in Brazil. The company operates cash and carry, wholesale, furniture, and appliance stores; and slicing and portioning centers, as well as in e-commerce and bakery industry. Grupo Mateus S.A. was founded in 1986 and is headquartered in São Luís, Brazil.</t>
-  </si>
-  <si>
-    <t>Azzas 2154 S.A. designs, develops, manufactures, markets, and sells shoes, handbags, clothing, and accessories for women and men. The company offers its products through franchise stores, company-operated store, and an e-commerce channel under the Arezzo, Schutz, Anacapri, Alexandre Birman, Alme, Vans, AR&amp;CO, TROC, ZZ mall, Baw clothing, Carol Bassi, and Vicenza brands. The company was formerly known as Arezzo Indústria e Comércio S.A. and changed its name to Azzas 2154 S.A. in July 2024. Azzas 2154 S.A. was founded in 1972 and is headquartered in Belo Horizonte, Brazil.</t>
-  </si>
-  <si>
-    <t>SLC Agrícola S.A. produces and sells agricultural products in Brazil and internationally. The company offers soybean, corn, cotton, wheat, seed corn, popcorn, mung bean, and brachiaria crops. In addition, it is involved in the cattle raising and livestock business. The company was founded in 1977 and is headquartered in Porto Alegre, Brazil.</t>
+    <t>Mitre Realty Empreendimentos e Participações S.A., together with its subsidiaries, engages in the development, construction, and sale of residential and commercial real estate properties for middle-class and upper middle-class customers in Brazil. The company was founded in 2005 and is based in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Sendas Distribuidora S.A. engages in the retail and wholesale sale of food products, bazaar items, and other products in Brazil. The company offers grocery, food, perishable, beverage, wrapping, and hygiene products; and parking, air-conditioned, well-lit environments, and butcher services. It serves restaurants, pizzerias, snack bars, schools, small businesses, religious institutions, hospitals, hotels, grocery stores, neighborhood supermarkets, and individuals. The company sells its products through brick-and-mortar stores, as well as telesales. The company was founded in 1974 and is headquartered in Rio De Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>Alupar Investimento S.A., together with its subsidiaries, engages in the transmission, generation, and commercialization of energy in Brazil, Colombia, Peru, and Chile. It operates through Transmission and Generation segments. The company holds a stake in concessions for 42 electricity transmission systems totaling 9,578 km of transmission lines; and operates overhead lines and substations. It is also involved in the generation of renewable energy through hydroelectric plants, wind farms, and photovoltaic power plants, which have an installed capacity of 798.5 MW. The company was incorporated in 2006 and is headquartered in São Paulo, Brazil. Alupar Investimento S.A. is a subsidiary of Guarupart Participações Ltda.</t>
+  </si>
+  <si>
+    <t>Cruzeiro do Sul Educacional S.A. provides education services in Brazil. It offers academic and professional education services, including elementary school, undergraduate, graduate, and extension courses in on-site and distance learning modalities; kindergartens; and medical courses. The company was founded in 1965 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Banco BMG S.A. provides commercial and credit, financing, and investment products and services primarily in Brazil. It operates in Retail Banking and Wholesale Banking segments. The company offers digital accounts; digital account credit card and consigned credit card; payroll and personal loan; insurance products, including lender, life, family life, and FGTS Protected insurance, as well as Bmg Med and Bmg Consortium services. It also provides investment products, such as bank deposit certificates, agribusiness letter of credit, and letters of real estate credit. In addition, the company offers commercial banking; debentures; trade finance; and working capital; and derivatives, such as non-deliverable forward, SWAP, options. The company was formerly known as BMG Financeira S.A.Crédito, Financiamento e Investimento and changed its name to Banco BMG S.A. in April 1989. Banco BMG S.A. was founded in 1930 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
     <t>Banco Santander (Brasil) S.A., together with its subsidiaries, provides various banking products and services to individuals, small and medium enterprises, and corporate customers in Brazil and internationally. It operates in Commercial Banking and Global Wholesale Banking segments. The company offers payroll and real estate loans; home equity financing solutions; a microfinance program; consortiums; agribusiness portfolio, including credit, securities, and other products; and insurance products, such as life and personal accident, vehicle and property coverage, and credit insurance, as well as insurance for travel and banking transactions. It also provides local transaction banking products, which include local loans, commercial financing options, development bank funds, and cash management services; fund and financial advisory services for infrastructure projects, origination, and distribution of fixed income instruments in capital markets; financing for acquisitions; syndicated loans in local and foreign currency; and advisory services for mergers and acquisitions and equity transactions in capital markets; research and brokerage services for corporate, institutional, and individual investors in stocks and listed derivatives; and foreign exchange products, derivatives, and investments to institutional investors, corporate customers, and individuals. In addition, the company offers cash management for corporate customers and SMEs; advance programs for entrepreneurs; and deposits and other bank funding instruments. It provides financial products and services to its customers through multichannel distribution network comprising branches, mini-branches, ATMs, call centers, Internet banking, and mobile banking. The company was incorporated in 1985 and is headquartered in São Paulo, Brazil.</t>
@@ -616,148 +610,127 @@
     <t>Lojas Renner S.A., together with its subsidiaries, operates as a fashion and lifestyle company in Brazil, Argentina, and Uruguay. It operates through Retail and Financial Products segments. The company trades clothes and sports products, shoes, accessories, perfumery, domestic appliances, towels and linen, furniture, and decoration articles, as well as cosmetics. It also involved in the granting of loans to individuals and legal entities, financing of purchases, insurance, and credit and debit transaction services to credit, financing, and investment companies, as well as provides personal loans. It offers its products through stores, as well as digital channels under Renner, Youcom, Camicado, realize, Ashua, Uello, and repasse brand names. Lojas Renner S.A. was incorporated in 1965 and is headquartered in Porto Alegre, Brazil.</t>
   </si>
   <si>
-    <t>Sendas Distribuidora S.A. engages in the retail and wholesale sale of food products, bazaar items, and other products in Brazil. The company offers grocery, food, perishable, beverage, wrapping, and hygiene products; and parking, air-conditioned, well-lit environments, and butcher services. It serves restaurants, pizzerias, snack bars, schools, small businesses, religious institutions, hospitals, hotels, grocery stores, neighborhood supermarkets, and individuals. The company sells its products through brick-and-mortar stores, as well as telesales. The company was founded in 1974 and is headquartered in Rio De Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Movida Participações S.A., through its subsidiaries, provides car rental services in Brazil. It operates in two segments, Rent-a-Car, and Fleet Management and Outsourcing (GTF). The company also offers light vehicle fleet management and outsourcing services; fleet sizing study, including acquisition, customization, and standardization of the customer's fleet, as well as rental, maintenance management, provision of temporary vehicles, replacement vehicles, documentation management, and asset retirement services; and added services, such as corrective and preventive maintenance, insurance, tire replacement, replacement vehicles for maintenance periods, as well as a wide range of vehicle makes and models. In addition, it sells pre-owned cars. The company was formerly known as H.L.C.S.P.E Empreendimentos e Participações S.A. and changed its name to Movida Participações S.A. in December 2014. The company was founded in 2006 and is based in São Paulo, Brazil. Movida Participações S.A. is a subsidiary of Simpar S.A.</t>
-  </si>
-  <si>
-    <t>Metalurgica Gerdau S.A., together with its subsidiaries, produces and supplies long and special steel products in Brazil, Latin America, and North America. The company offers rebars, bars, profiles and drawn products, billets, blocks, plates, wire rod, structural profiles, iron ore, heavy and light structural profiles, stainless steel, as well as square, round, and flat bars. The company was formerly known as METALÚRGICA HUGO GERDAU S.A and changed its name to Metalurgica Gerdau S.A. in June 1965. Metalurgica Gerdau S.A. was founded in 1976 and is headquartered in São Paulo, Brazil. Metalurgica Gerdau S.A. operates as a subsidiary of Indac - Indústria, Administração e Comércio S.A.</t>
-  </si>
-  <si>
-    <t>Equatorial S.A., through its subsidiaries, engages in the electricity generation, distribution, and transmission operations in Brazil. The company generates energy from wind and biomass. It also distributes electric energy in the municipalities of Maranhão and Pará State. In addition, the company distributes electric energy in municipalities of Piauí and Alagoas State. Further, it is involved in telecom related business. Equatorial S.A. was formerly known as Equatorial Energia S.A. and changed its name to Equatorial S.A. in August 2024. Equatorial S.A. was founded in 1958 and is based in Brasília, Brazil.</t>
-  </si>
-  <si>
-    <t>Companhia Paranaense de Energia - COPEL engages in the generation, transformation, distribution, and sale of electricity to industrial, residential, commercial, rural, and other customers in Brazil. The company operates through Power Generation and Transmission, Power Distribution, GAS, Power Sale, and Holding and Services segments. It is also involved in the piped natural gas distribution. The company operates hydroelectric, wind, and thermoelectric plants; and owns and operates transmission and distribution lines. It holds concessions to distribute electricity in municipalities in the State of Paraná and in the municipality of Porto União in the State of Santa Catarina. Companhia Paranaense de Energia  COPEL was founded in 1954 and is headquartered in Curitiba, Brazil.</t>
+    <t>Romi S.A. develops, manufactures, and sells machine tools, plastic processing machines, and cast parts. The company provides machine tools, such as machining and turning centers, vertical turning centers, CNC lathes and vertical CNC lathes, CNC borings, engine lathes, and heavy and extra-heavy-duty CNC lathes; plastic processing machines, including plastic injection, blowing, and molding machines; and casting and machined parts. It also provides presales and aftersales engineering services, technical assistance, and spare parts; and exports its products internationally. Its products and services are used by various industries, such as automotive components manufacturing, consumer goods, agricultural machinery and implements, education, and industrial machinery and equipment. The company was formerly known as Indústrias Romi S.A. Romi S.A. was founded in 1930 and is headquartered in Santa Bárbara d'Oeste, Brazil.</t>
+  </si>
+  <si>
+    <t>METISA Metalúrgica Timboense S.A. manufactures and sells tractor and agricultural implement parts, cutting stone blades, parts for roads, other steel products, railway accessories, hand tools, and washers in Brazil and internationally. It offers agricultural discs for plowing, harrowing, leveling, and planting; cultivator tips, shovels for cane harvesters, extractors, basic knives, and mincers; and drawbars, rotary hoes, brush cutters, peanut blades, and blades for leveling the soil. The company also provides hand tools; post hole diggers; railway accessories, such as sleepers, insulated joints, clamps, emergency joint and joint bars, and tie plates; bars and profiles; and special laminated profiles, as well as mounting and stop brackets, spacers, and toggle supports. In addition, it offers ground engaging tools and undercarriage parts used in earthworks and soil and material handling work, including blades, end bits, scarifier supports and nails, adapter tip castings, grouser bars, and track shoes; stones saw blades used in various types of looms for cutting ornamental stones; and washers used in various mechanical assemblies with high resistance. The company also exports its products. METISA Metalúrgica Timboense S.A. was founded in 1942 and is headquartered in Timbó, Brazil.</t>
+  </si>
+  <si>
+    <t>Raia Drogasil S.A. engages in the retail sale of medicines, perfumes, personal hygiene and beauty products, cosmetics, dermocosmetics, and specialty medicines in Brazil. It sells its products through stores, telesales, and call centers. Raia Drogasil S.A. was founded in 1905 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Equatorial S.A., through its subsidiaries, engages in the electricity generation, distribution, transmission, and commercialization in Brazil. The company generates energy from wind. It also provides telecommunication and sanitation services, as well as engages in photovoltaic installations for residential, commercial, industrial, and agribusiness customers. The company was formerly known as Equatorial Energia S.A. and changed its name to Equatorial S.A. in August 2024. Equatorial S.A. was founded in 1958 and is based in Brasília, Brazil.</t>
   </si>
   <si>
     <t>Motiva Infraestrutura de Mobilidade S.A. provides infrastructure services for highway, rail, and airport concessions in Brazil. It manages and maintains 36 concessions on highways, airports, and rails. The company was formerly known as CCR S.A. and changed its name to Motiva Infraestrutura de Mobilidade S.A. in April 2025. Motiva Infraestrutura de Mobilidade S.A. was incorporated in 1998 and is based in São Paulo, Brazil.</t>
   </si>
   <si>
-    <t>GPS Participações e Empreendimentos S.A., together its subsidiaries, engages in the provision of facilities, security, logistics, utility engineering, industrial service, catering, and infrastructure services in Brazil. It offers security services in the areas of property, firefighting and prevention, personal, monitoring center operations, armed escort, event security, integrated security solution, and civil aviation security (APAC). The company also provides facilities services, including cleaning and conservation, technical and industrial cleaning, cleaning at heights, hospital cleaning and sanitizing, administrative support, specialized services, operational support, caterers and servers, reception desk and gatehouse, building maintenance, firefighters, landscaping and plant maintenance, and indoor waste management services. In addition, it provides electromechanical maintenance, conveyor belts, industrial automation, overhead cranes, electromechanical assembly and shutdowns, scaffolding and lift platforms, industrial cleaning, metallic structures and tubing, building, and refractory industrial maintenance services; industrial refrigeration, compressed air and gases, refrigeration systems automation, steam generation systems, fire suppression systems maintenance, and water and wastewater treatment services; and logistics services. Further, the company operates restaurants under LC Cores and LC Essência brand names; and provides infrastructure services, such as highway maintenance and conservation, and airport and port infrastructure maintenance and conservation, as well as mining, gas pipelines and distribution, railroad, sanitation, and energy project infrastructure and maintenance. Additionally, it engages in installation, operation, and maintenance of utility systems. The company was founded in 1962 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Raia Drogasil S.A. engages in the retail sale of medicines, perfumery, personal care and beauty products, cosmetics, dermocosmetics, and specialty medicines in Brazil. It sells its products through stores, telesales, and call centers in the states of São Paulo, Tocantins, Pernambuco, ParanÃ¡, Rio de Janeiro and Bahia. The company was founded in 1905 and is headquartered in São Paulo, Brazil.</t>
+    <t>Vittia S.A. provides fertilizers in Brazil and internationally. The company operates through four segments: Foliar Fertilizers and Industrial Products; Soil Micronutrients; Soil Conditioners and Organominerals; and Biological Products. It offers biological, organomineral, foliar, bio, and concentrated suspension fertilizers; adjuvants; biological pesticides comprising microbiological and macrobiological control; inoculants; sulfur; acaricides; soil conditioners; vegetable nutrition products consist of chloride, CoMo, phosphite, macro, nitrate, soluble powders, and concentrated suspensions; sulphates; and granulated micronutrients, and salts for agriculture and livestock. The company was formerly known as Vittia Fertilizantes e Biológicos S.A. and changed its name to Vittia S.A. in May 2023. Vittia S.A. was founded in 1971 and is based in São Joaquim da Barra, Brazil.</t>
+  </si>
+  <si>
+    <t>Tekno S.A. Indústria e Comércio manufactures and sells pre-painted materials primarily in Brazil. The company offers pre-painted material for civil construction, home appliances, furniture, metal packaging, refrigeration, automotive, and other industries. It also provides coil coating solutions for painting, lamination, rotogravure, double sheet lamination, protective film lamination, and lubrication to aid printing processes. The company was founded in 1939 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Panatlântica S.A. engages in the production and sale of steel products primarily in Brazil. The company's products include steel coils and sheets, including hot and cold rolled, zinc, galvalume, pre-painted, and pickled coils and sheets, LCG thick plates; steel strips, comprising hot-rolled, cold-rolled, zinc-plated, galvalume, pre-painted and pickled materials; delaminated strips; special profiles, and profiles; and tiles and accessories comprising trapezoidal and corrugated roofing surfaces. It also offers services, including cross section and longitudinal services. The company was formerly known as Acos Laminados Panatlantica S.A. and changed its name to Panatlântica S.A. in April 1987. Panatlântica S.A. was founded in 1952 and is headquartered in Gravataí, Brazil. Panatlântica S.A. operates as a subsidiary of LP Acos Comercio e Participacoes Ltda.</t>
+  </si>
+  <si>
+    <t>Rede D'Or São Luiz S.A. engages in the provision of hospital services in Brazil. The company offers assistance and hospitality concept services; and supplementary services, such as blood bank, dialysis, and outpatient clinics with various specialties. It also provides health insurance and plan, as well as dental plans for small, medium, and large-sized companies; individual plans; individual and group life, travel, credit life, endowment, as well as personal, individual, and group accident insurance products; and pension risk. In addition, the company owns and operates hospitals, and oncology and radiotherapy clinics and laboratories. Further, it is involved in asset management activities. The company was formerly known as Hospital Maternidade São Luiz S.A. Rede D'Or São Luiz S.A. was founded in 1977 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>TOTVS S.A. develops and sells management software, and productivity and collaboration platforms in Brazil and internationally. It offers an ERP platform, which integrates software management, social networks, real-time reporting, and other applications; business intelligence solutions; Fluig platform; and HR solutions, such as recruitment and selection, positions and salaries, electronic point, medicine and work safety, sheet, performance evaluation, and training and development solutions. The company also provides B2B credit, prepayment of receivables, payments via PIX, credit cards, and digital wallets and payment solutions; digital marketing, data intelligence and sales /digital commerce, and customer experience solutions; cloud, CRM, analytics, IPAAS, and electronic signature; and consulting and related services, as well as operates as an investment and equity investment fund. It serves services, manufacturing, agribusiness, logistics, education, construction, healthcare, financial services, retail, legal, distribution, and hospitality industries. TOTVS S.A. was founded in 1983 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Companhia Paranaense de Energia - COPEL engages in the generation, transformation, distribution, and sale of electricity to industrial, residential, commercial, rural, and other customers in Brazil. The company operates hydroelectric, wind, and thermoelectric plants; and owns and operates transmission and distribution lines. It holds concessions to distribute electricity in municipalities in the State of Paraná and in the municipality of Porto União in the State of Santa Catarina. The company was founded in 1954 and is headquartered in Curitiba, Brazil.</t>
+  </si>
+  <si>
+    <t>Metalurgica Gerdau S.A., together with its subsidiaries, produces and supplies long and special steel products in Brazil, Latin America, and North America. The company offers rebars, bars, profiles and drawn products, billets, blocks, plates, wire rod, structural profiles, iron ore, heavy and light structural profiles, stainless steel, as well as square, round, and flat bars. Metalurgica Gerdau S.A.was formerly known as METALÚRGICA HUGO GERDAU S.A and changed its name to Metalurgica Gerdau S.A. in June 1965. Metalurgica Gerdau S.A. was founded in 1976 and is based in São Paulo, Brazil. Metalurgica Gerdau S.A. operates as a subsidiary of Indac - Indústria, Administração e Comércio S.A.</t>
+  </si>
+  <si>
+    <t>Hospital Mater Dei S.A. operates hospitals in Brazil. The company provides healthcare services, such as hospitalizations, surgeries, oncology, medical consultations, exams, and other services. It also engages in data and artificial intelligence business. The company was incorporated in 1973 and is headquartered in Belo Horizonte, Brazil. Hospital Mater Dei S.A. is a subsidiary of JSS Empreendimentos e Administração LTDA.</t>
+  </si>
+  <si>
+    <t>Randoncorp S.A. manufactures and sells trailers and semi-trailers in Latin America and internationally. The company offers trailers and semi-trailers, such as grain truck, tipping truck, tank, sider, refrigerated van, container chassis, sugarcane trailer, low bed trailer, and silo; truck body, including general cargo truck body, beverages distribution, and dry-cargo body. It also provides rail wagons comprising hopper, gondola, flat, sider, tank, and telescopic; and genuine spare parts, such as Fire Extinguisher Box, G-bracket and Hinge, rear signal light, grease, water reservoir, and rigid reflective sticker. In addition, the company offers automatic and manual adjuster, flat and locking and smooth washer, locking bar, suspension bushings, brake chamber, lifting device, balancer, hub, friction disc, hubodometer, return and retention spring, brake shoes, fifth wheel, bearings, hube seal, rala, brake drum, spring support, spring brake, air suspension spring, and aluminum wheel. Randoncorp S.A. was founded in 1949 and is headquartered in Caxias Do Sul, Brazil.</t>
   </si>
   <si>
     <t>Gerdau S.A., together with its subsidiaries, operates as a steel producer company. The company operates through Brazil Business, North America Business, South America Business, and Special Steel Business segments. It provides semi-finished products, including billets, blooms, and slabs; common long-rolled products, such as rebars, wire rods, merchant bars, light shapes, and profiles to the construction and manufacturing industries; drawn products, including barbed and barbless fence wires, galvanized wires, fences, concrete reinforcing wire mesh, nails, and clamps for manufacturing, construction, and agricultural industries; and special steel products used in auto parts, light and heavy vehicles, and agricultural machinery, as well as in the oil and gas, wind energy, machinery and equipment, mining and rail, and other markets. The company also offers flat products, such as hot-rolled steel coils and heavy plates; and resells flat steel products. In addition, it operates mines that produce iron ore located in the Brazilian state of Minas Gerais. The company sells its products through independent distributors, direct sales from the mills, and its retail network. Gerdau S.A. was founded in 1901 and is based in São Paulo, Brazil.</t>
   </si>
   <si>
-    <t>Rede D'Or São Luiz S.A. operates a network of hospitals in Brazil. The company provides services in the medical areas; and diagnosis and treatment on cancer. It operates own hospitals, 75 hospitals, and 61 oncology and radiotherapy treatment clinics, and 11laboratories, having a total of 9,857 operational beds and provides other services, such as blood bank, dialysis, and outpatient clinics of various specialties in the states of Rio de Janeiro, São Paulo, Pernambuco, Maranhão, Bahia, Sergipe, Paraná, Ceará, Minas Gerais, Mato Grosso do Sul, Paraíba and in the Federal District. In addition, it offers health and dental insurance; health and dental plans, and health and wellness solutions; and life insurance, private pension, and asset management solutions. The company was formerly known as Hospital Maternidade São Luiz S.A. Rede D'Or São Luiz S.A. is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>TOTVS S.A. develops and sells management software, and productivity and collaboration platforms in Brazil and internationally. It offers an ERP platform, which integrates software management, social networks, real-time reporting, and other applications; business intelligence solutions; Fluig platform; and HR solutions, such as recruitment and selection, positions and salaries, electronic point, medicine and work safety, sheet, performance evaluation, and training and development solutions. The company also provides B2B credit, prepayment of receivables, payments via PIX, credit cards, and digital wallets and payment solutions; digital marketing, data intelligence and sales /digital commerce, and customer experience solutions; cloud, CRM, analytics, IPAAS, and electronic signature; and consulting and related services, as well as operates as an investment and equity investment fund. It serves services, manufacturing, agribusiness, logistics, education, construction, healthcare, financial services, retail, legal, distribution, and hospitality industries. TOTVS S.A. was founded in 1983 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Yduqs Participações S.A. provides higher education services in Brazil. The company offers face-to-face, semi-face-to-face, and distance education; and masters and doctorate courses. It also operate in two edtechs to prepare the candidates for exams and competitions named HardWork Medicina and Grupo Q, which offers Qconcursos solutions. It serves under stácio, Ibmec, IDOMED, Wyden, and Damásio brand names. The company was formerly known as Estácio Participações S.A. Yduqs Participações S.A. was founded in 1970 and is headquartered in Rio De Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Ânima Holding S.A. operates as an education organization in Brazil. It operates in two segments, Inspirali Medical Education and Ânima Core. The company provides undergraduate courses in medicine; educational services in higher education and professional development courses; professional development services in postgraduate courses; and publishes books and magazine. It also offers consultancy services in technological innovation, technical support, and maintenance; and develops computer programs. The company was founded in 2003 and is based in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>São Martinho S.A., together with its subsidiaries, engages in the production and sale of sugar, ethanol, and other sugarcane byproducts in Brazil. The company operates through Sugar, Ethanol, Electric Power, Real Estate Business, Yeast, and Other Products segment. It offers a range of raw sugar; hydrous ethanol, which is used direct fuel; anhydrous ethanol that is used as a gasoline additive in gasoline-powered vehicles; and industrial ethanol, which is primarily used in the production of paints, cosmetics, and alcoholic beverages. The company also generates electricity from sugarcane bagasse; provides byproducts, including yeast used in animal feed; and SMartLiO, a substitute for soybean oil used in the production of animal nutrition, biofuels, paint manufacturing, and chemical industries, as well as Dried Distillers Grains with Solubles, an animal nutrition for ruminants, pigs, horses, birds, fish, and pets. In addition, it is involved in the cultivation of sugarcane; development of real estate properties; import and export of goods, products, and raw materials; agricultural productions; and investment in other companies. The company was founded in 1914 and is based in São Paulo, Brazil. São Martinho S.A. is a subsidiary of LJN Participações S.A.</t>
-  </si>
-  <si>
-    <t>Iguatemi S.A., together with its subsidiaries, operates shopping centers in Brazil. It also operates commercial towers. The company was formerly known as Jereissati Participações S.A. and changed its name to Iguatemi S.A. in November 2021. The company was founded in 1946 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Fleury S.A., together with its subsidiaries, provides diagnostic imaging, clinical analysis, fertility, and infusions services in Brazil. It operates in two segments, Diagnostic Medicine and Integrated Medicine. The company also provides health management services, such as telemedicine; orthopedic medicine services; laboratory support; toxicological exam; preventive, integrated solutions, and clinical research in oncology; integrated solutions, research, development of processes and services in genomics; and laboratory analysis services. In addition, it operates a health platform, immunobiological drug infusion center, and ophthalmology service centers. Fleury S.A. was founded in 1926 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Randoncorp S.A. manufactures and sells trailers and semi-trailers in Latin America and internationally. The company offers trailers and semi-trailers, such as Bulk Trailer, dumper, tank, dry van, sider, refrigerated van, container chassis, sugarcane trailer, logging trailer, low bed semi-trailer, and silo; truck body, including general cargo truck body, beverages distribution, and dry-cargo body. It also provides rail wagons comprising hopper, gondola, flat, sider, tank, and telescopic; and genuine spare parts, such as Tarpaulin Bow, Tarpaulin, Fire Extinguisher Box, G-bracket and Hinge, fender, rear led light, Led light, grease, water reservoir, and red reflective sticker. In addition, the company offers salck and manual adjustor, landing gear, flat and locking and smooth washer, equalizer, locking bar, suspension bushings, brake chamber, hub, friction disc, camshaft, towing hitch, twist lock, roller fastener, locking grip, hubodometer, brake linings, anchor / return spring, brake shoes, rocker and king pin, fifth wheel, turntable, hub sealing, bearings, brake drum, spring brake, pneumatic spring, spring seat support, and aluminum wheel. Randoncorp S.A. was founded in 1949 and is headquartered in Caxias Do Sul, Brazil.</t>
-  </si>
-  <si>
-    <t>Vamos Locação de Caminhões, Máquinas e Equipamentos S.A., together with its subsidiaries engages in the leasing, reselling, and selling of trucks, machinery, and equipment in Brazil. The company leases tractors, forklift trucks, agricultural machinery and implements, buses, and other vehicles; sells automobile parts and accessories; sells new and used tractors, machines, tires, air tubes, implements, motor vehicles, buses, and micro buses; and provides automobile maintenance and repair, and technical assistance and related services, as well as engages in the logistics and road transportation of cargos. It also offers parts, accessories, lubricants; and fleet management and rendering services, as well as act as a motor vehicle agency. In addition, the company sells fertilizers, herbicides, and seeds; and provides engineering services related to customization of trucks and buses, as well as provision of agricultural activities. Further, the company manufactures and sells truck trailers, truck bodies, wagons, road implements, truck cabs, and industrial machinery and equipment; and provides installation, renovation, repair, and maintenance of equipment and vehicles; information technology services; technical analyses on motor vehicles; forklift operator services; and outsourcing and managing of human resources. Vamos Locação de Caminhões, Máquinas e Equipamentos S.A. was incorporated in 2015 and is headquartered in São Paulo, Brazil. Vamos Locação de Caminhões, Máquinas e Equipamentos S.A. is a subsidiary of SIMPAR S.A.</t>
-  </si>
-  <si>
-    <t>Embraer S.A., together with its subsidiaries, designs, develops, manufactures, and sells aircraft and systems in North America, Latin America, the Asia Pacific, Brazil, Europe, and internationally. It operates through Commercial Aviation; Defense &amp; Security; Executive Aviation; Services &amp; Support; and Other segments. The Commercial Aviation segment develops, produces, and sells commercial jets. Its Defense &amp; Security segment develops and produces military aircraft and radars; and is involved in research and development of software and integrated information systems, communications, border monitoring and surveillance, space systems/satellites, and aircraft modernization services and services support, as well as command, control, communications, computer, intelligence, surveillance, and reconnaissance systems. The Executive Aviation segment develops, produces, and sells executive jets. Its Service &amp; Support segment provides field and technical support, flight operations solutions, aircraft modification, materials management, maintenance solutions, and training programs. The Other segment engages in the supply of structural parts and hydraulic systems; production of agricultural crop-spraying aircraft; development and certification of eVTOLs; creation of a maintenance and service network, and air traffic control system for eVTOLs; development and manufacture of electrical propulsion systems; cybersecurity; and software and technical products. It is also involved in leasing used aircraft; pilot, mechanic, and crew training; engineering services; retail trade, maintenance, and repair of computer products; information technology consulting, data processing, application service providers, and internet hosting; and fabrication of aircraft interiors. The company was formerly known as Embraer-Empresa Brasileira de Aeronáutica S.A. and changed its name to Embraer S.A. in November 2010. Embraer S.A. was incorporated in 1969 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Localiza Rent a Car S.A. engages in car and fleet rental business in Brazil and internationally. The company is also involved in granting franchises; sale of cars; and provision of insurance solution. It serves individuals and legal entities. Localiza Rent a Car S.A. was founded in 1973 and is headquartered in Belo Horizonte, Brazil.</t>
-  </si>
-  <si>
-    <t>M. Dias Branco S.A. Indústria e Comércio de Alimentos engages in the manufacture, distribution, and sale of food products in Brazil. Its products include wheat and rice crackers and cookies, wheat and corn pasta, wheat flour and bran products, cake mixes, margarines and vegetable shortenings, cakes, corn and wheat snacks, toasts, chocolate-iced cookies, peanut butter, cereal bits, spices, and chocolates, as well as healthy foods, seasonings, sauces, and condiments. In addition, the company engages in the wheat milling activities. It offers its products under various brand names, such as Adria, Adorita, Basilar, Bonsabor, Estrela, Delicitos, Isabela, Finna, Fortaleza, Jasmine, Las Acacias, Medalha de Ouro, Pelaggio, Pilar, Piraquê, Predilleto, Puro Sabor, Richester, Salsitos, Vitarella, Zabet, Fit Food, Frontera, Smart, Taste&amp;Co, Jasmine, and Las Acacias brands. The company also exports its products. M. Dias Branco S.A. Indústria e Comércio de Alimentos was founded in 1936 and is headquartered in Eusébio, Brazil.</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira de Alumínio produces and sells aluminum products. The company provides bauxite, hydrate, alumina, molten aluminum, ingots, secondary ingots, slabs, billets, rod, caster rolls, caster sheet and coils, hot-rolled sheet and coils, roofing and siding, foil, coated foil, extruded profiles, surface treatment lines, custom parts, and components and services. It also owns and operates hydroelectric power plants. The company serves e automotive, building and construction, energy, agribusiness, consumer goods, packaging, transportation, and other industries. It operates in Brazil, South America, North America, and Europe. Companhia Brasileira de Alumínio was incorporated in 1941 and is headquartered in São Paulo, Brazil. Companhia Brasileira de Alumínio operates as a subsidiary of Votorantim S.A.</t>
+    <t>Brisanet Serviços de Telecomunicações S.A. provides broadband internet services in Brazil. It offers fiber optic internet, pay TV, music streaming, and fixed and mobile telephony services. The company was founded in 1998 and is based in Pereiro, Brazil. Brisanet Serviços de Telecomunicações S.A. operates as a subsidiary of Brisanet Participações S.A.</t>
+  </si>
+  <si>
+    <t>Localiza Rent a Car S.A. engages in car and fleet rental business in Brazil and internationally. The company is involved in granting franchises; sale of cars; and provision of insurance solutions. It also offers car rentals to app-based drivers through Zarp, a network dedicated to drivers. The company serves individuals and legal entities. Localiza Rent a Car S.A. was founded in 1973 and is headquartered in Belo Horizonte, Brazil.</t>
+  </si>
+  <si>
+    <t>Embraer S.A., together with its subsidiaries, designs, develops, manufactures, and sells aircraft and systems worldwide. It operates through Commercial Aviation; Defense &amp; Security; Executive Aviation; Services &amp; Support; and Other segments. The Commercial Aviation segment develops, produces, and sells commercial jets. Its Defense &amp; Security segment develops and produces military aircraft and radars; and is involved in research and development of software and integrated information systems, communications, border monitoring and surveillance, space systems/satellites, and aircraft modernization services and services support, as well as command, control, communications, computer, intelligence, surveillance, and reconnaissance systems. The Executive Aviation segment develops, produces, and sells executive jets. Its Service &amp; Support segment provides field and technical support, flight operations solutions, aircraft modification, materials management, maintenance solutions, and training programs. The Other segment engages in the supply of structural parts and hydraulic systems; production of agricultural crop-spraying aircraft; development and certification of eVTOLs; creation of a maintenance and service network, and air traffic control system for eVTOLs; development and manufacture of electrical propulsion systems; cybersecurity; and software and technical products. Additionally, the company is involved in leasing of used aircraft; pilot, mechanic, and crew training; engineering services; retail trade, maintenance, and repair of computer products; information technology consulting, data processing, application service providers, and internet hosting; and fabrication of aircraft interiors. The company was formerly known as Embraer-Empresa Brasileira de Aeronáutica S.A. and changed its name to Embraer S.A. in November 2010. Embraer S.A. was incorporated in 1969 and is headquartered in São Paulo, Brazil.</t>
   </si>
   <si>
     <t>TIM S.A., a telecommunications company, provides mobile, fixed, long-distance, data transmission, and broadband services in Brazil. The company offers landline switched telephone services in local, national, and international long-distance modes, as well as personal mobile, multimedia communication, and digital content services. It serves individuals and corporates, as well as small, medium, and large enterprises. The company is based in Rio de Janeiro, Brazil. TIM S.A. is a subsidiary of TIM Brasil Serviços e Participações S.A.</t>
   </si>
   <si>
-    <t>Telefônica Brasil S.A., together with its subsidiaries, operates as a mobile telecommunications company in Brazil. Its fixed line voice services portfolio includes local, domestic long-distance, and international long-distance calls; and mobile portfolio comprises voice and broadband internet access through 3G, 4G, 4.5G, and 5G, as well as value-added, prepaid plans with data sharing features, family plans, voice mail, caller identification, voice minutes in unlimited bundles to mobile and fixed-line phones, and digital services and wireless roaming services. The company also offers data services, including broadband and mobile data services. In addition, it provides pay TV services through IPTV technologies; network services, such as rental of facilities; other services; wholesale services, including interconnection services to users of other network providers; and digital services, such as entertainment, cloud, and security and financial services. Further, the company offers multimedia communication services, which include audio, data, voice and other sounds, images, texts, and other information, as well as sells devices and accessories, such as smartphones, broadband USB modems, and other devices. Additionally, it provides telecommunications solutions and IT support to various industries, such as retail, distribution and digital channel, manufacturing, services, financial institutions, government, etc. It markets and sells its solutions through own stores, dealers, retail and distribution channels, door-to-door sales, and outbound tele sales. The company was formerly known as Telecomunicações de São Paulo S.A. - TELESP and changed its name to Telefônica Brasil S.A. in October 2011. Telefônica Brasil S.A. was incorporated in 1998 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Natura Cosméticos S.A. engages in the development, manufacture, distribution, and marketing of cosmetics, fragrances, and personal hygiene products in Brazil, Peru, Colombia, Chile, Argentina, Uruguay, and Ecuador. It offers its products through retail markets, e-commerce, business-to business, and franchise channels under the Avon and Natura brands. Natura Cosméticos S.A. was founded in 1969 and is headquartered in São Paulo, Brazil.</t>
+    <t>Telefônica Brasil S.A., together with its subsidiaries, operates as a mobile telecommunications company in Brazil. Its fixed line voice services portfolio includes local, domestic long-distance, and international long-distance calls; and mobile portfolio comprises voice and broadband internet access through 3G, 4G, 4.5G, and 5G, as well as value-added, prepaid plans with data sharing features, family plans, voice mail, caller identification, voice minutes in unlimited bundles to mobile and fixed-line phones, and digital services and wireless roaming services. The company also offers data services, including broadband and mobile data services. In addition, it provides pay TV services through IPTV technologies; network services, such as rental of facilities and other services; wholesale services, including interconnection services to users of other network providers; and digital services that include entertainment, cloud, and security and financial services. Further, the company offers multimedia communication services, which include audio, data, voice and other sounds, images, texts, and other information, as well as sells devices and accessories, such as smartphones, broadband USB modems, and other devices. Additionally, it provides telecommunications solutions and IT support to various industries, such as retail, distribution and digital channel, manufacturing, services, financial institutions, government, etc. It markets and sells its solutions through own stores, dealers, retail and distribution channels, door-to-door sales, and outbound tele sales. The company was formerly known as Telecomunicações de São Paulo S.A. - TELESP and changed its name to Telefônica Brasil S.A. in October 2011. Telefônica Brasil S.A. was incorporated in 1998 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Smartfit Escola de Ginástica e Dança S.A. operates a network of Smart Fit gyms in Latin America. The company offers digital fitness services under the Queima Diária brand. It operates through owned and franchised units in Brazil, Mexico, Colombia, Chile, Peru, Argentina, Paraguay, Uruguay, Panama, Costa Rica, Dominican Republic, Ecuador, Guatemala, El Salvador and Honduras under the Smart Fit and Bio Ritmo brands. Smartfit Escola de Ginástica e Dança S.A. was founded in 1996 and is based in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>d1000 Varejo Farma Participações S.A. operates a chain of drugstores in Brazil. It offers pharmaceutical and perfumery products; generic drugs; and hygiene and beauty products. The company was formerly known as Cancun RJ Participações S/A and changed its name to d1000 Varejo Farma Participações S.A. in March 2016. The company was incorporated in 2010 and is based in Rio De Janeiro, Brazil. d1000 Varejo Farma Participações S.A. is a subsidiary of Profarma Distribuidora de Produtos Farmacêuticos S.A.</t>
+  </si>
+  <si>
+    <t>Natura Cosméticos S.A. engages in the development, manufacture, distribution, and marketing of cosmetics, fragrances, and personal hygiene products in Brazil, Peru, Colombia, Chile, Argentina, Uruguay, and Ecuador. It offers its products through retail markets, e-commerce, business-to-business, and franchise channels under the Avon and Natura brands. Natura Cosméticos S.A. was founded in 1969 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Allos S.A. provides planning, development, management, and sales services to third-party shopping centers in Brazil. It provides administration services, including financial, legal, commercial, and operational management for shopping centers and malls; and brokerage and commercial advisory services, as well as engages in the operation of parking lots in shopping centers, leasing of stores and spaces; and management of shopping malls and condominiums. The company was formerly known as Aliansce Shopping Centers S.A. and changed its name to Allos S.A. in October 2023. Allos S.A. is headquartered in Rio De Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>Magazine Luiza S.A. engages in the retail sale of consumer goods. It operates through Retail, Financial Operations, Insurance Operations, and Other Services segments. The company also grants credit and provides extended warranties for its products. In addition, it is involved in the provision of consortium and management services; and e-commerce of perfumes, cosmetics, sports, and fashion products, as well as product delivery management and software development services. Further, the company provides integration, logistics, and technological solutions, as well as resale goods and provision of services in the stores, electronic and food delivery management platform. It serves through physical stores, e-commerce platform, and SuperApp. Magazine Luiza S.A. was founded in 1957 and is headquartered in Franca, Brazil. Magazine Luiza S.A. operates as a subsidiary of LTD Administração e Participação S.A.</t>
+  </si>
+  <si>
+    <t>Log-in Logística Intermodal S.A. engages in the provision of integrated logistics solutions for moving and transporting door-to-door containers and cargo in Brazil, Austria, and internationally. It operates through Integrated Logistics Solutions, Port Terminal, and Road Cargo Transport segments. The company offers cabotage services; coastal shipping and maritime services; warehousing, separation, and cross-dock services; and storage services for containers and general cargo, as well as manages and operates container port terminals. It also provides road freight transport of cargo and parcels; administration, transportation consultancy, storage, and customs clearance services; and river navigation, agency and arm vessels, cargo import and export, and multimodal transport services. In addition, the company is involved in the purchase, sale, rental, administration, construction, and operation of real estate; distribution of material and equipment by air, land, sea, or river; investment activities in securities; maritime trade; and deposit, loading, and unloading of goods. The company was incorporated in 1973 and is headquartered in Rio De Janeiro, Brazil. Log-In Logística Intermodal S.A. is a subsidiary of SAS Shipping Agencies Services SÀRL.</t>
   </si>
   <si>
     <t>Centrais Elétricas Brasileiras S.A. - Eletrobrás, through its subsidiaries, engages in the generation, transmission, and commercialization of electricity in Brazil. The company generates electricity through hydroelectric, thermoelectric, nuclear, wind, and solar plants. It also owns and operates 44 hydroelectric plants with a total capacity of 42,293.5 megawatt (MW); and 66,539.17 kilometers of transmission lines. Centrais Elétricas Brasileiras S.A.  Eletrobrás was incorporated in 1962 and is headquartered in Rio de Janeiro, Brazil.</t>
   </si>
   <si>
-    <t>Smartfit Escola de Ginástica e Dança S.A. operates a network of Smart Fit gyms in Latin America. It offers digital fitness services under the Queima Diária brand. The company operates through owned and franchised units in Brazil, Mexico, Colombia, Chile, Peru, Argentina, Paraguay, Uruguay, Panama, Costa Rica, Dominican Republic, Ecuador, Guatemala, El Salvador and Honduras under the Smart Fit and Bio Ritmo brands. Smartfit Escola de Ginástica e Dança S.A. was founded in 1996 and is based in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Usinas Siderúrgicas de Minas Gerais S.A. processes, manufactures, and markets flat steel products in Brazil and internationally. It operates in two segments, Mining and Logistics, and Steelmaking. The company extracts and process iron ore, such as pellet and sinter feed, and granulated iron ore; provides storage and handling of iron ore and steel products; and road cargo transportation services; and operates highway and railway cargo terminals. It also manufactures and sells steel products; manufactures and installs equipment for various industries; and transforms cold-rolled coils into hot-dip galvanized coils. In addition, the company provides technology transfer services for steel industry; project management and services for civil construction and capital goods industry; road transportation of flat steel; rectification of cylinders and rolling mill rolls; hot-dip galvanizing services; texturing and chrome plating of cylinders; and steel transformation solutions, as well as operates as a distribution center. Further, it offers thick plates, hot strips, cold rolled, electrogalvanized, hot dip galvanized, and synchron. The company serves automotive, construction, distribution, energy, white line, oil and gas, and machines and equipment markets. Usinas Siderúrgicas de Minas Gerais S.A. was founded in 1956 and is headquartered in Belo Horizonte, Brazil.</t>
-  </si>
-  <si>
-    <t>Hypera S.A. operates as a pharmaceutical company in Brazil. It offers prescription products under the Adacne, Addera, apri, AmpliumG, pleased, Celestamine, Celestone, Celestone Soluspan, Cizax, deciprax, Derive C Micro, Micro Drift, Dermotil Fusid, Digedrat, diprogent, Diprosalic, Diprosone, diprospan, Emprol XR, Flow, Garasone, Halobex, Lipanon, Luna, moon, Lydian, macrodantin, MaxSulid, Milgamma, Mioflex  A, Nesina, Novotram, oximax, peridal, Peridal Suspension, PredSim, Pressaliv, Quadriderm, Rizi, Rizi M, Softalm, Tacroz, Tinodin, Umma, and velunid brands. The company also provides sun protection and moisturizing skin care products under the Mantecorp Skincare brands; similar products under the Doralgina, Dropy D, Equilibrisse, balance, Flavonid, Histamin, neofresh, neolefrin, neoquimica Vitamins, Neosorum, and Torsilax brands; and over-the-counter drugs under the Apracur, Benegrip, Buscopan, Coristina D Pro, Engov, Epocler, Estomazil, and Neosaldina brands, as well as similar and generic drugs under the Neo Química brand. In addition, it offers nutritional and vitamin supplement products under the Tamarine, Biotônico Fontoura, and Zero-Cal brands; and generic medicines under the Hydroxyzine, Sodium Diclofenac, Dipyron, Ibuprofen, Losartan Potassium, Mal Dexchlorpheniramine, Naproxene, Paracetamol, Simethicon, Loratadine, Omeprazole, Tadalaphyl, and Desogestrel brands. The company was formerly known as Hypermarcas S.A. and changed its name to Hypera S.A. in February 2018. Hypera S.A. was founded in 1999 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Allos S.A. provides planning, development, administration, and sales services to third-party shopping centers in Brazil. It provides administration services, including financial, legal, commercial, and operational management; brokerage and advisory services; and operation of parking lots in shopping centers; as well as engages in management of shopping malls and condominiums. The company was formerly known as Aliansce Shopping Centers S.A. and changed its name to Allos S.A. in October 2023. Allos S.A. is headquartered in Rio De Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Alpargatas S.A. manufactures and sells footwear and accessories in Brazil and internationally. The company offers its products under the Havaianas, ioasys, and Rothys brands. The company was formerly known as São Paulo Alpargatas S.A. and changed its name to Alpargatas S.A. in 2010. The company was incorporated in 1907 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Magazine Luiza S.A. engages in the retail sale of consumer goods. It operates through Retail, Financial Operations, Insurance Operations, and Other Services segments. The company also grants credit and provides extended warranties for its products. In addition, it is involved in the provision of consortium and management services; and e-commerce of perfumes, cosmetics, sports, and fashion products, as well as product delivery management and software development services. Further, the company provides integration, logistics, and technological solutions, as well as resale goods and provision of services in the stores, electronic and food delivery management platform. It serves through physical stores, e-commerce platform, and SuperApp. The company was founded in 1957 and is headquartered in Franca, Brazil. Magazine Luiza S.A. operates as a subsidiary of LTD Administração e Participação S.A.</t>
-  </si>
-  <si>
-    <t>Rumo S.A., through its subsidiaries, provides rail transportation services. The company operates through North Operations, South Operations, and Container Operations segments. The North Operations segment engages in the railway, highway, and transshipment operations. The South Operations segment comprises of rail and transhipment operations in the area of, Rumo Malha Sul and Rumo Malha Oeste concessions. The Container Operations segment is involved in the container logistics and operations. Rumo S.A. offers logistics services primarily for exporting commodities, including integrated solution for transportation, movement, storage, and shipping from the production centers to the main ports in the south and southeast of Brazil. The company was founded in 2008 and is based in Curitiba, Brazil.</t>
-  </si>
-  <si>
-    <t>Locaweb Serviços de Internet S.A. offers hosting, software licensing, and technical support services in Brazil. It operates through two segments, Be Online and Software as a Service &amp; Solutions (Be Online &amp; SaaS), and Commerce. The Be Online and Software as a Service &amp; Solutions (Be Online &amp; SaaS) segment provides hosting and cloud services; and SaaS solutions, including email and marketing intelligence software and site builder under the Locaweb, Allin, Nextios, Kinghost, Delivery Diretso, Etus, Social Mine, and Connectplug brands. Its Commerce segment offers e-commerce solutions, platform, marketplace integration, and sub-acquiring business services under the Tray, Tray Corp, Yapay, Melhor Envio, Ideris, Samurai, Credisfera, Vindi, Bagy Sul, Bling, PagCerto, Bagy, Octadesk, Squid, and Sintese names. The company provides data center, telecommunications, and intermediation and collection services. Locaweb Serviços de Internet S.A. was founded in 1998 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Orizon Valorização de Resíduos S.A. operates as a waste recovery process company. It engages in disposal of solid waste treatment business; energy, biogas, and carbon credits units business captures and treats gases from the decomposition of waste for the sale or reutilization of methane gas. The company also produces energy from biogas-fueled power plant; and trades in carbon credit. The company's Waste Processing and Industrialization business develops plants for processing materials from the industrial sector, recycling solid urban waste, and the direct burning of waste for energy generation. The company's Environmental Engineering business offers services in the areas of recovery of degraded areas, remediation of contaminated areas, environmental diagnosis and monitoring, waste management, and the cleaning of oil industry tanks. The company was formerly known as Haztec Investimentos e Participações S.A. and changed its name to Orizon Valorização de Resíduos S.A. in August 2020. Orizon Valorização de Resíduos S.A. was founded in 1999 and is based in São Paulo, Brazil. Orizon Valorização de Resíduos S.A. subsidiary of Inovatec Participações S.A.</t>
-  </si>
-  <si>
-    <t>Serena Energia S.A. generates and sells renewable energy. It generates through electricity through wind, water, and solar sources. The company was formerly known as Omega Energia S.A. and changed its name to Serena Energia S.A. in December 2023. The company was founded in 2008 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Aura Minerals Inc., a gold and copper production company, focuses on the development and operation of gold and base metal projects in the Americas. It operates through Minosa Mine, Apoena Mine, the Aranzazu Mine, Corporate, Almas Mine, and Borborema Projects segments. The company primarily explores gold, copper, and silver deposits. The company was formerly known as Aura Gold Inc. and changed its name to Aura Minerals Inc. in July 2007. The company was incorporated in 1946 and is headquartered in Coconut Grove, Florida.</t>
-  </si>
-  <si>
-    <t>Azul S.A., together with its subsidiaries, provides air transportation services in Brazil and internationally. It is also involved in the cargo or mail; passenger charter; development of frequent-flyer programs; intellectual property owner; travel packages; funding: aircraft financing; and provision of maintenance and hangarage services for aircraft, engines, parts and pieces, aircraft acquisition, and lease services. As of December 31, 2023, the company operated approximately 980 daily departures to 160 destinations through a network of 400 non-stop routes; with an operating fleet of 181 aircraft and a passenger contractual fleet of 185 aircraft. The company was incorporated in 2008 and is headquartered in Barueri, Brazil. On May 28, 2025, Azul S.A. along with its affiliates, filed a voluntary petition for reorganization under Chapter 11 in the U.S. Bankruptcy Court for the Southern District of New York.</t>
-  </si>
-  <si>
-    <t>Minerva S.A. produces and sells fresh beef, livestock, and by-products in South America and internationally. The company is also involved in slaughtering, deboning, and processing of cattle, meat, beef, and sheep meat; selling chilled, frozen, and processed meat, as well as beef, pork, and poultry products; exporting and selling live cattle; and breeding and selling live cattle, lambs, pigs, and other live animals. In addition, it trades in and sells electric power; trades in food products and carbon credits; sells third parties' brands primarily Swift products; and prepares products for animals, which include meat/bone meal, blood, and tallow. The company was founded in 1957 and is headquartered in Barretos, Brazil.</t>
-  </si>
-  <si>
-    <t>SIMPAR S.A. provides light vehicle rental, and fleet management and outsourcing services in Brazil. The company provides road logistics; car rental and fleet management sector; rental of trucks, machinery, and equipment; Volkswagen/man truck and bus dealerships; and light and heavy vehicle fleets, including complete service management, customization, maintenance, and fleet operation with driver. It operates car and motorcycle retail business; manages and outsources fleets of light and heavy vehicle to the public sector, municipal passenger transport, and urban cleaning sectors; and offers financial solutions and services. The company was founded in 1956 and is headquartered in São Paulo, Brazil. SIMPAR S.A. is a subsidiary of JSP Holding S.A.</t>
-  </si>
-  <si>
-    <t>CVC Brasil Operadora e Agência de Viagens S.A., together with its subsidiaries, provides tourism services in Brazil and internationally. It offers intermediation, airfare, ground transportation, hotel reservations, tickets and chartered sea cruises, cultural and professional exchange, and other services. The company operates under the Trend Travel and VHC brands in the United States of America; Almundo.com, Avantrip, Biblos, Quiero Viajes, CVC, and Ola brands in Argentina. It provides its tourism services directly to customers through independent service providers. CVC Brasil Operadora e Agência de Viagens S.A. was incorporated in 2009 and is headquartered in Santo André, Brazil.</t>
-  </si>
-  <si>
-    <t>Companhia Siderúrgica Nacional operates as an integrated steel producer in Brazil and Latin America. The company operates through five segments: Steel Industry, Mining, Logistics, Energy, and Cement. The company offers flat steel products, such as hot and cold rolled, galvanized, galvalume, pre-painted, and metal sheets products; coil, sheets, and derivatives; tiles and derivatives, pipes, and profiles; long steel products; food and chemical packaging solutions; and carbochemical products. The company also provides steel cutting services; produces and sells cement; operates railways; and generates electric power from its hydroelectric power plants. In addition, the company explores for iron ore reserves at Casa de Pedra and Engenho mines located in the city of Congonhas; as well as produces tin. Companhia Siderúrgica Nacional was founded in 1941 and is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Eneva S.A., together with its subsidiaries, operates as an integrated power generation company in Brazil. The company generates electricity through natural gas, steam, coal, and solar energy. It also engages in the exploration, development, and production of natural gas through its concessions covering an area of approximately 60,000 square kilometers located in Parnaíba, Amazonas, Solimões, and Paraná Basins. The company was formerly known as MPX Energia S.A. and changed its name to Eneva S.A. in October 2013. The company was incorporated in 2001 and is headquartered in Rio De Janeiro, Brazil.</t>
-  </si>
-  <si>
-    <t>Pet Center Comércio e Participações S.A. operates physical and digital stores that sells products and services for pets in Brazil. The company offers pet food products, such as prescription pet food, super premium, premium, and standard pet food, wet food, snacks, and others; and accessories, hygiene, cleaning products, drugs, and others under the Petz brand. It also operates veterinary centers under the Seres brand. Pet Center Comércio e Participações S.A. was incorporated in 2013 and is based in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Tupy S.A., together with its subsidiaries, engages in the development, manufacture, and sale of cast and compacted graphite iron structural components in North America, South and Central Americas, Europe, Asia, Africa, Oceania, and internationally. The company operates through two segments, Freight Transportation, Infrastructure, Agriculture and Power Generation; and Distribution segments. It offers engine blocks, cylinder heads, and cast and machined products for the manufacturers of engines used in passenger vehicles, commercial vehicles, construction machines, tractors, agricultural machinery, power generators, capital goods in general, and engine assembly for third parties. The company also provides spare parts; malleable iron connections for the construction industry; and cast iron profiles for various use. Tupy S.A. was founded in 1938 and is headquartered in Joinville, Brazil.</t>
-  </si>
-  <si>
-    <t>Auren Energia S.A. engages in the planning, construction, installation, operation, and maintenance of renewable energy generation assets in Brazil. It operates wind, solar, and hydroelectric energy generation systems with a total installed capacity of 3,030 MW. The company was formerly known as VTRM Energia Participações S.A. and changed its name to Auren Energia S.A. in March 2022. Auren Energia S.A. is headquartered in São Paulo, Brazil.</t>
-  </si>
-  <si>
-    <t>Hapvida Participações e Investimentos S.A., together with its subsidiaries, operates in the health sector in Brazil. The company offers health insurance plans through its clinical, outpatient, and hospital networks; and dental plans though a credentialed network. It also provides medical and paramedical, laboratory, diagnostic, imaging, and ultrasound services; health management services; and medical and hospital care services. In addition, the company organizes courses, lectures, seminars, and other events; implements health management tools; and operates hospitals, outpatient units, a children's clinic, clinical and diagnostic centers, preventive and occupational medicine spaces, and an oncology center. Further, it engages in the administration, consultancy, implementation, and commercialization of individual, family, and collective health care systems and plans; and reimbursement of medical, dental, hospital, and healthcare expenses to its beneficiaries. Hapvida Participações e Investimentos S.A. was founded in 1979 and is headquartered in Fortaleza, Brazil.</t>
-  </si>
-  <si>
-    <t>Raízen S.A. operates as an integrated energy company in Brazil, Argentina, Paraguay, rest of Latin America, North America, Asia, Europe, and internationally. It operates in three segments: Marketing and Services, Sugar, and Renewable. The Marketing and Services segment trades in and sells fossil and renewable fuels through a franchised network of service stations under the Shell brand. Its Sugar segment engages in the origination, production, sale, and trading of sugar. The Renewable segment originates, produces, sells, and trades in ethanol; produces and sells bioenergy; resells and trades in electric power; and produces and sells solar energy and biogas. Raízen S.A. company was founded in 2011 and is headquartered in Rio de Janeiro, Brazil.</t>
+    <t>Empresa Metropolitana de Águas e Energia S.A. engages in planning, construction, operation, and maintenance of production systems and sale of electricity in Brazil. The company operates hydraulic system consisting of dikes, dams and reservoirs, and spillways such as Billings and Guarapiranga, in the extreme south of the city of São Paulo, as well as the São Paulo and Pedreira pumping plants and the Pinheiros River channel, in the city of São Paulo. It also engages in assets construction; and offers operation and maintenance services for plant facilities and related structures for companies and public bodies. Empresa Metropolitana de Águas e Energia S.A. was founded in 1899 and is headquartered in Sao Paulo, Brazil. Empresa Metropolitana de Águas e Energia S.A. operates as a subsidiary of Centrais Elétricas Brasileiras S.A. - Eletrobrás.</t>
+  </si>
+  <si>
+    <t>HBR Realty Empreendimentos Imobiliários S.A. engages in the management of commercial and lodging of real estate properties in Brazil. It operates corporate buildings, convenience centers, shopping malls, hotels, and parking lots, as well as provides self-storage units, +Box, built to suit rent agreements, and sells lease back services. The company was founded in 2011 and is headquartered in Mogi das Cruzes, Brazil. HBR Realty Empreendimentos Imobiliários S.A. is a subsidiary of Helio Borenstein S.A. - Administração, Participações e Comércio.</t>
+  </si>
+  <si>
+    <t>Rumo S.A., through its subsidiaries, engages in the rail logistics operation. The company operates through North Operations, South Operations, and Container Operations segments. The North Operations segment is involved in the railway, highway, and transshipment operations. The South Operations segment comprises of rail and transhipment operations in the area of Rumo Malha Sul and Rumo Malha Oeste concessions. The Container Operations segment engages in the rail and road transport, and container logistics and operations. It offers logistics services primarily for exporting commodities, including integrated solution for transportation, movement, storage, and shipment from the production centers to the main ports in the south and southeast of Brazil. The company was incorporated in 1997 and is headquartered in Curitiba, Brazil.</t>
+  </si>
+  <si>
+    <t>Terra Santa Propriedades Agrícolas S.A. operates as a rural real estate company in Brazil. The company engages in leasing of farms for agricultural production located in various municipalities in Mato Grosso. Terra Santa Propriedades Agrícolas S.A. was incorporated in 2021 and is based in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>MPM Corpóreos S.A., together with its subsidiaries, provides laser hair removal services in Brazil, Chile, Argentina, Colombia, and Paraguay. It operates through Laser, International Operations, and Franchising (Royalties) segments. The company offers physiotherapy services in the areas of laser hair removal, and facial and body aesthetics under the Espaçolaser, Cela, and Definit brands. It also franchises its stores. The company was founded in 2004 and is based in São Paulo, Brazil. MPM Corpóreos S.A. is a subsidiary of Grupo Espaçolaser.</t>
+  </si>
+  <si>
+    <t>Marisa Lojas S.A., together with its subsidiaries, engages in the retail of consumer goods in Brazil. The company sells clothing items for men, women, and children; and perfumery, cosmetics, and watches through physical stores and e-commerce. It also engages in the management of non-financial intangible assets, including trademark management; purchase, sale, use, and licensing of trademarks and patents; receipt of royalties; and authorization for reproduction and use of trademarks and patents in processes and products, as well as the retail trade in clothing. Marisa Lojas S.A. was founded in 1948 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Allpark Empreendimentos, Participações e Serviços S.A. engages in the provision of parking services in Brazil. It operates through Leased and Managed Locations, Owned Locations, Public concessions (Otf-Stíeet), Public concessions (On-Street), Long-term Private Contracts, Digital, and Other segments. The company operates parking lots in commercial buildings, shopping malls, hospitals, educational institutions, banks and land; and outside public roads, including airports and underground garages. It is also involved in the investments in parking meters, infrastructure, signage, and initial concessions in the municipalities; and provision of AppZul+ services, as well as technical administration, advisory, and planning services related to vehicle parking. The company was incorporated in 1981 and is based in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Diagnósticos da América S.A., together with its subsidiaries, provides diagnostic and hospital services in Brazil and Argentina. It operates through Hospitals and Oncology; Diagnostics and Care Coordination; and Diagnostics  International Operations segments. The company offers outpatient doctors; medical and outpatient services; diagnostic support assistants for private patients or partner companies; care coordination, remote monitoring, population health management, home medical, and paramedical services; and medical consultations. It is also involved in the development and licensing of computer programs and predictive models using information technology and data science; and brokerage activities. In addition, the company provides oncology, hematology, and infusion centers. The company was formerly known as Laboratório Clínico Delboni Auriemo S.A. and changed its name to Diagnósticos da América S.A. in August 2000. Diagnósticos da América S.A. was founded in 1961 and is headquartered in Barueri, Brazil.</t>
+  </si>
+  <si>
+    <t>Alliança Saúde e Participações S.A. provides diagnostic medicine services in Brazil. It offers imaging diagnosis and graphic methods; nuclear medicine cytology; pathological anatomy; human vaccination and immunization; medical activity; and clinical analysis, as well as other auxiliary diagnostic support services. The company also engages in the import of medical and hospital equipment, diagnostic sets, and related items; provision of consultancy, advice, courses, and lectures in the health area; managing chronic diseases; research and development in the area of diagnostic medicine; preparation, editing, publication, and distribution of newspapers, books, magazines, periodicals, and other written communication vehicles intended for scientific dissemination; and granting and administration of business franchises. The company was formerly known as Centro de Imagem Diagnósticos S.A. and changed its name to Alliança Saúde e Participações S.A. in April 2023. Alliança Saúde e Participações S.A. was founded in 1992 and is headquartered in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>Eneva S.A., together with its subsidiaries, operates as an integrated power generation company in Brazil. It generates electricity through natural gas, steam, coal, and solar energy. The company also engages in the exploration, development, and production of natural gas through its concessions covering an area of approximately 60,000 square kilometers located in Parnaíba, Amazonas, Solimões, and Paraná Basins. The company was formerly known as MPX Energia S.A. and changed its name to Eneva S.A. in October 2013. The company was incorporated in 2001 and is headquartered in Rio De Janeiro, Brazil.</t>
+  </si>
+  <si>
+    <t>PBG S.A. manufactures, exports, and sells ceramic and porcelain products in Brazil and internationally. The company offers flooring, technical and enamelled porcelain, pieces decorated and special, mosaics, products intended for covering internal walls, facades in the field of civil construction materials industry. It sells its products through a network of Portobello Shop retail chain, home centers, Franchise Stores, and civil construction companies. The company was formerly known as Portobello S.A. and changed its name to PBG S.A. in December 2015. PBG S.A. was incorporated in 1977 and is headquartered in Tijucas, Brazil.</t>
+  </si>
+  <si>
+    <t>Hapvida Participações e Investimentos S.A., together with its subsidiaries, operates in the healthcare sector in Brazil. It sells health insurance plans through its own clinical, outpatient, and hospital networks, as well as dental plans through a credentialed network. The company was founded in 1979 and is headquartered in Fortaleza, Brazil.</t>
+  </si>
+  <si>
+    <t>São Carlos Empreendimentos e Participações S.A. engages in the investment and management of real estate in Brazil. The company offers office buildings, shopping, and convenience centers services. It also owns and manages property rentals and condominiums. São Carlos Empreendimentos e Participações S.A. was incorporated in 1989 and is based in São Paulo, Brazil.</t>
+  </si>
+  <si>
+    <t>International Meal Company Alimentação S.A., together with its subsidiaries, operates restaurants, bars, and cafes that offers food and beverages in Brazil, Colombia, and the United States. The company also for airlines; operates food courts at service stations and restaurant chains along highways; sells fuel for vehicles; provides services to franchisees of the KFC and Pizza Hut brands; and subletting stores and spaces for promotional and commercial purposes in its chain stores, as well as provides general services. The company operates its restaurants under the Frango Assado, Viena, Brunella, Margaritaville, KFC, Pizza Hut, Batata Inglesa, and RA Catering brand names. International Meal Company Alimentação S.A. was founded in 1965 and is headquartered in São Paulo, Brazil.</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P120"/>
+  <dimension ref="A1:P122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1176,46 +1149,46 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>8</v>
-      </c>
       <c r="H2">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="I2">
-        <v>0.15</v>
+        <v>0.55</v>
       </c>
       <c r="J2">
-        <v>21.85</v>
+        <v>26.96</v>
       </c>
       <c r="K2">
-        <v>45.44</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="L2">
-        <v>6.829999923706055</v>
+        <v>40</v>
       </c>
       <c r="M2">
-        <v>149.4638417812148</v>
+        <v>210.4179982796148</v>
       </c>
       <c r="N2">
-        <v>219.9121558429518</v>
+        <v>-32.59999999999999</v>
       </c>
       <c r="O2">
-        <v>2088.34</v>
+        <v>426.04</v>
       </c>
       <c r="P2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1226,46 +1199,46 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>3.24</v>
+        <v>0.38</v>
       </c>
       <c r="J3">
-        <v>29.21</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>11.81</v>
+        <v>2.13</v>
       </c>
       <c r="L3">
-        <v>38.27000045776367</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="M3">
-        <v>88.10123296526559</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>-23.67389691505925</v>
+        <v>-100</v>
       </c>
       <c r="O3">
-        <v>130.21</v>
+        <v>-100</v>
       </c>
       <c r="P3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1276,7 +1249,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -1291,31 +1264,31 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="I4">
-        <v>4.9</v>
+        <v>2.98</v>
       </c>
       <c r="J4">
-        <v>18.63</v>
+        <v>29.21</v>
       </c>
       <c r="K4">
-        <v>5.03</v>
+        <v>11.81</v>
       </c>
       <c r="L4">
-        <v>24.56999969482422</v>
+        <v>36.20999908447266</v>
       </c>
       <c r="M4">
-        <v>45.91786417071248</v>
+        <v>88.10123296526559</v>
       </c>
       <c r="N4">
-        <v>-24.17582323403735</v>
+        <v>-19.33167429290091</v>
       </c>
       <c r="O4">
-        <v>86.89</v>
+        <v>143.31</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1326,7 +1299,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1341,31 +1314,31 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>7.2</v>
+        <v>2.87</v>
       </c>
       <c r="J5">
-        <v>5.25</v>
+        <v>14.78</v>
       </c>
       <c r="K5">
-        <v>4.46</v>
+        <v>3.86</v>
       </c>
       <c r="L5">
-        <v>32.04000091552734</v>
+        <v>10.89000034332275</v>
       </c>
       <c r="M5">
-        <v>22.95294098803027</v>
+        <v>35.82796393880065</v>
       </c>
       <c r="N5">
-        <v>-83.61423267795311</v>
+        <v>35.72084053296118</v>
       </c>
       <c r="O5">
-        <v>-28.36</v>
+        <v>229</v>
       </c>
       <c r="P5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1373,10 +1346,10 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -1391,31 +1364,31 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="I6">
-        <v>6.99</v>
+        <v>4.66</v>
       </c>
       <c r="J6">
-        <v>8.550000000000001</v>
+        <v>18.63</v>
       </c>
       <c r="K6">
-        <v>2.91</v>
+        <v>5.03</v>
       </c>
       <c r="L6">
-        <v>20.20000076293945</v>
+        <v>23.31999969482422</v>
       </c>
       <c r="M6">
-        <v>23.66033072465387</v>
+        <v>45.91786417071248</v>
       </c>
       <c r="N6">
-        <v>-57.67326892538283</v>
+        <v>-20.11149123584742</v>
       </c>
       <c r="O6">
-        <v>17.13</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1426,46 +1399,46 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
         <v>6</v>
       </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>95</v>
-      </c>
       <c r="I7">
-        <v>7.58</v>
+        <v>4.77</v>
       </c>
       <c r="J7">
-        <v>3.4</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="K7">
-        <v>3.39</v>
+        <v>2.27</v>
       </c>
       <c r="L7">
-        <v>25.95999908447266</v>
+        <v>10.73999977111816</v>
       </c>
       <c r="M7">
-        <v>16.10388151968338</v>
+        <v>22.54320851165601</v>
       </c>
       <c r="N7">
-        <v>-86.90292711900122</v>
+        <v>-7.355677727690646</v>
       </c>
       <c r="O7">
-        <v>-37.97</v>
+        <v>109.9</v>
       </c>
       <c r="P7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1473,10 +1446,10 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>113</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -1488,34 +1461,34 @@
         <v>10</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="I8">
-        <v>4.82</v>
+        <v>7.18</v>
       </c>
       <c r="J8">
-        <v>9.949999999999999</v>
+        <v>5.25</v>
       </c>
       <c r="K8">
-        <v>2.27</v>
+        <v>4.46</v>
       </c>
       <c r="L8">
-        <v>11.02999973297119</v>
+        <v>32.09999847412109</v>
       </c>
       <c r="M8">
-        <v>22.54320851165601</v>
+        <v>22.95294098803027</v>
       </c>
       <c r="N8">
-        <v>-9.791475603964217</v>
+        <v>-83.64485903563973</v>
       </c>
       <c r="O8">
-        <v>104.38</v>
+        <v>-28.5</v>
       </c>
       <c r="P8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1526,7 +1499,7 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -1538,34 +1511,34 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
-        <v>22.1</v>
+        <v>1.48</v>
       </c>
       <c r="K9">
-        <v>5.2</v>
+        <v>0.62</v>
       </c>
       <c r="L9">
-        <v>34.97000122070312</v>
+        <v>4.71999979019165</v>
       </c>
       <c r="M9">
-        <v>50.84977876058066</v>
+        <v>4.543786966837244</v>
       </c>
       <c r="N9">
-        <v>-36.80297618372331</v>
+        <v>-68.64406640281003</v>
       </c>
       <c r="O9">
-        <v>45.41</v>
+        <v>-3.73</v>
       </c>
       <c r="P9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1576,7 +1549,7 @@
         <v>8</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -1588,34 +1561,34 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>3.28</v>
+        <v>5.77</v>
       </c>
       <c r="J10">
-        <v>8.789999999999999</v>
+        <v>7.28</v>
       </c>
       <c r="K10">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="L10">
-        <v>5.510000228881836</v>
+        <v>9.569999694824219</v>
       </c>
       <c r="M10">
-        <v>18.22805529945528</v>
+        <v>16.43989051058431</v>
       </c>
       <c r="N10">
-        <v>59.52812404481125</v>
+        <v>-23.92894219278532</v>
       </c>
       <c r="O10">
-        <v>230.82</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="P10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1626,46 +1599,46 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>10</v>
       </c>
       <c r="H11">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="I11">
-        <v>4.89</v>
+        <v>4.91</v>
       </c>
       <c r="J11">
-        <v>38.99</v>
+        <v>30.97</v>
       </c>
       <c r="K11">
-        <v>7.48</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>37.02000045776367</v>
+        <v>29.85000038146973</v>
       </c>
       <c r="M11">
-        <v>81.00627753452198</v>
+        <v>64.66026600625766</v>
       </c>
       <c r="N11">
-        <v>5.321446563686338</v>
+        <v>3.752092476439439</v>
       </c>
       <c r="O11">
-        <v>118.82</v>
+        <v>116.62</v>
       </c>
       <c r="P11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1676,7 +1649,7 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -1688,34 +1661,34 @@
         <v>10</v>
       </c>
       <c r="G12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H12">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I12">
-        <v>7.7</v>
+        <v>5.14</v>
       </c>
       <c r="J12">
-        <v>59.17</v>
+        <v>7.8</v>
       </c>
       <c r="K12">
-        <v>16.33</v>
+        <v>1.5</v>
       </c>
       <c r="L12">
-        <v>127.3000030517578</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="M12">
-        <v>147.4467268202316</v>
+        <v>16.22498073958795</v>
       </c>
       <c r="N12">
-        <v>-53.51924699016497</v>
+        <v>6.849312276727537</v>
       </c>
       <c r="O12">
-        <v>15.83</v>
+        <v>122.26</v>
       </c>
       <c r="P12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1723,10 +1696,10 @@
         <v>27</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -1741,10 +1714,10 @@
         <v>12</v>
       </c>
       <c r="H13">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I13">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
       <c r="J13">
         <v>30.97</v>
@@ -1753,16 +1726,16 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>31.3700008392334</v>
+        <v>31.75</v>
       </c>
       <c r="M13">
         <v>64.66026600625766</v>
       </c>
       <c r="N13">
-        <v>-1.275106243328916</v>
+        <v>-2.456692913385827</v>
       </c>
       <c r="O13">
-        <v>106.12</v>
+        <v>103.65</v>
       </c>
       <c r="P13" t="s">
         <v>146</v>
@@ -1776,46 +1749,43 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14">
         <v>8</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>13</v>
       </c>
       <c r="H14">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="I14">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>30.97</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>33.9900016784668</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>64.66026600625766</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>-8.884970665888547</v>
-      </c>
-      <c r="O14">
-        <v>90.23</v>
-      </c>
-      <c r="P14" t="s">
-        <v>146</v>
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1823,49 +1793,49 @@
         <v>29</v>
       </c>
       <c r="B15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H15">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="I15">
-        <v>8.4</v>
+        <v>6.98</v>
       </c>
       <c r="J15">
-        <v>9.619999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="K15">
-        <v>3.16</v>
+        <v>1.73</v>
       </c>
       <c r="L15">
-        <v>26.6299991607666</v>
+        <v>12.09000015258789</v>
       </c>
       <c r="M15">
-        <v>26.15304953537924</v>
+        <v>16.9374511069405</v>
       </c>
       <c r="N15">
-        <v>-63.87532743833903</v>
+        <v>-39.04053013247947</v>
       </c>
       <c r="O15">
-        <v>-1.79</v>
+        <v>40.09</v>
       </c>
       <c r="P15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1873,49 +1843,49 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G16">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H16">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="I16">
-        <v>7.35</v>
+        <v>7.98</v>
       </c>
       <c r="J16">
-        <v>8.98</v>
+        <v>1.97</v>
       </c>
       <c r="K16">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="L16">
-        <v>14.56999969482422</v>
+        <v>15.71000003814697</v>
       </c>
       <c r="M16">
-        <v>19.90020100400999</v>
+        <v>9.344530485797561</v>
       </c>
       <c r="N16">
-        <v>-38.36650522930336</v>
+        <v>-87.46021645310978</v>
       </c>
       <c r="O16">
-        <v>36.58</v>
+        <v>-40.52</v>
       </c>
       <c r="P16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1923,10 +1893,10 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -1941,31 +1911,31 @@
         <v>14</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I17">
-        <v>8.109999999999999</v>
+        <v>7.05</v>
       </c>
       <c r="J17">
-        <v>18.64</v>
+        <v>7.37</v>
       </c>
       <c r="K17">
-        <v>4.69</v>
+        <v>1.73</v>
       </c>
       <c r="L17">
-        <v>38.11999893188477</v>
+        <v>12.14999961853027</v>
       </c>
       <c r="M17">
-        <v>44.3507158905017</v>
+        <v>16.9374511069405</v>
       </c>
       <c r="N17">
-        <v>-51.10178247038482</v>
+        <v>-39.34156188153434</v>
       </c>
       <c r="O17">
-        <v>16.35</v>
+        <v>39.4</v>
       </c>
       <c r="P17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1973,10 +1943,10 @@
         <v>32</v>
       </c>
       <c r="B18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -1988,34 +1958,31 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H18">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="I18">
-        <v>8.94</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>9.609999656677246</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>9.355720175379338</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>-61.8106125794708</v>
-      </c>
-      <c r="O18">
-        <v>-2.65</v>
-      </c>
-      <c r="P18" t="s">
-        <v>150</v>
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2026,7 +1993,7 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="D19">
         <v>4</v>
@@ -2038,34 +2005,34 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="I19">
-        <v>6.81</v>
+        <v>3.59</v>
       </c>
       <c r="J19">
-        <v>19.91</v>
+        <v>125.37</v>
       </c>
       <c r="K19">
-        <v>3.83</v>
+        <v>20.84</v>
       </c>
       <c r="L19">
-        <v>26.36000061035156</v>
+        <v>74.75</v>
       </c>
       <c r="M19">
-        <v>41.42154330780059</v>
+        <v>242.4582293921986</v>
       </c>
       <c r="N19">
-        <v>-24.46889400988348</v>
+        <v>67.71906354515052</v>
       </c>
       <c r="O19">
-        <v>57.14</v>
+        <v>224.36</v>
       </c>
       <c r="P19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2073,10 +2040,10 @@
         <v>34</v>
       </c>
       <c r="B20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -2088,34 +2055,34 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>9.51</v>
+        <v>5.19</v>
       </c>
       <c r="J20">
-        <v>4.47</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K20">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="L20">
-        <v>17.43000030517578</v>
+        <v>7.880000114440918</v>
       </c>
       <c r="M20">
-        <v>13.26673471506836</v>
+        <v>17.75635097648163</v>
       </c>
       <c r="N20">
-        <v>-74.35456155056607</v>
+        <v>17.76649575161091</v>
       </c>
       <c r="O20">
-        <v>-23.89</v>
+        <v>125.33</v>
       </c>
       <c r="P20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2126,7 +2093,7 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -2141,31 +2108,31 @@
         <v>20</v>
       </c>
       <c r="H21">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="I21">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>39.81</v>
+        <v>59.17</v>
       </c>
       <c r="K21">
-        <v>7.46</v>
+        <v>16.33</v>
       </c>
       <c r="L21">
-        <v>49.75</v>
+        <v>130.1000061035156</v>
       </c>
       <c r="M21">
-        <v>81.74416492936973</v>
+        <v>147.4467268202316</v>
       </c>
       <c r="N21">
-        <v>-19.97989949748743</v>
+        <v>-54.51960244112465</v>
       </c>
       <c r="O21">
-        <v>64.31</v>
+        <v>13.33</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2173,49 +2140,49 @@
         <v>36</v>
       </c>
       <c r="B22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22">
+        <v>63</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22">
+        <v>8</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22">
         <v>21</v>
       </c>
-      <c r="D22">
-        <v>4</v>
-      </c>
-      <c r="E22">
-        <v>8</v>
-      </c>
-      <c r="F22">
-        <v>10</v>
-      </c>
-      <c r="G22">
-        <v>20</v>
-      </c>
       <c r="H22">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I22">
-        <v>4.72</v>
+        <v>6.83</v>
       </c>
       <c r="J22">
-        <v>31.27</v>
+        <v>39.81</v>
       </c>
       <c r="K22">
-        <v>4.93</v>
+        <v>7.46</v>
       </c>
       <c r="L22">
-        <v>23.30999946594238</v>
+        <v>50.56999969482422</v>
       </c>
       <c r="M22">
-        <v>58.89503162406825</v>
+        <v>81.74416492936973</v>
       </c>
       <c r="N22">
-        <v>34.14843722192169</v>
+        <v>-21.27743674067194</v>
       </c>
       <c r="O22">
-        <v>152.66</v>
+        <v>61.65</v>
       </c>
       <c r="P22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2223,10 +2190,10 @@
         <v>37</v>
       </c>
       <c r="B23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D23">
         <v>4</v>
@@ -2238,34 +2205,34 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H23">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I23">
-        <v>9.65</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="J23">
-        <v>4.44</v>
+        <v>3.67</v>
       </c>
       <c r="K23">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="L23">
-        <v>13.92000007629395</v>
+        <v>8.729999542236328</v>
       </c>
       <c r="M23">
-        <v>11.99399849924953</v>
+        <v>9.355720175379338</v>
       </c>
       <c r="N23">
-        <v>-68.10344845068346</v>
+        <v>-57.96105163300076</v>
       </c>
       <c r="O23">
-        <v>-13.84</v>
+        <v>7.17</v>
       </c>
       <c r="P23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2273,10 +2240,10 @@
         <v>38</v>
       </c>
       <c r="B24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D24">
         <v>4</v>
@@ -2288,34 +2255,34 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H24">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I24">
-        <v>7.43</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="J24">
-        <v>5.43</v>
+        <v>24.83</v>
       </c>
       <c r="K24">
-        <v>1.08</v>
+        <v>7.03</v>
       </c>
       <c r="L24">
-        <v>8.060000419616699</v>
+        <v>60.38000106811523</v>
       </c>
       <c r="M24">
-        <v>11.48690558853863</v>
+        <v>62.66965174627988</v>
       </c>
       <c r="N24">
-        <v>-32.6302764602309</v>
+        <v>-58.87711235382549</v>
       </c>
       <c r="O24">
-        <v>42.52</v>
+        <v>3.79</v>
       </c>
       <c r="P24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2326,46 +2293,43 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H25">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I25">
-        <v>5.77</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>15.12</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>12.97999954223633</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>27.60521689826037</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>16.48690703570679</v>
-      </c>
-      <c r="O25">
-        <v>112.68</v>
-      </c>
-      <c r="P25" t="s">
-        <v>157</v>
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2373,49 +2337,49 @@
         <v>40</v>
       </c>
       <c r="B26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H26">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="I26">
-        <v>8.380000000000001</v>
+        <v>4.29</v>
       </c>
       <c r="J26">
-        <v>19.34</v>
+        <v>26.37</v>
       </c>
       <c r="K26">
-        <v>3.97</v>
+        <v>3.38</v>
       </c>
       <c r="L26">
-        <v>33.65000152587891</v>
+        <v>14.51000022888184</v>
       </c>
       <c r="M26">
-        <v>41.56375223677477</v>
+        <v>44.78212254907085</v>
       </c>
       <c r="N26">
-        <v>-42.52600557796006</v>
+        <v>81.7367304206591</v>
       </c>
       <c r="O26">
-        <v>23.52</v>
+        <v>208.63</v>
       </c>
       <c r="P26" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2423,10 +2387,10 @@
         <v>41</v>
       </c>
       <c r="B27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C27">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D27">
         <v>4</v>
@@ -2438,13 +2402,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H27">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I27">
-        <v>6.94</v>
+        <v>6.79</v>
       </c>
       <c r="J27">
         <v>25.48</v>
@@ -2453,19 +2417,19 @@
         <v>4.39</v>
       </c>
       <c r="L27">
-        <v>30.84000015258789</v>
+        <v>29.77000045776367</v>
       </c>
       <c r="M27">
         <v>50.16758913880554</v>
       </c>
       <c r="N27">
-        <v>-17.38002634911827</v>
+        <v>-14.41048166542734</v>
       </c>
       <c r="O27">
-        <v>62.67</v>
+        <v>68.52</v>
       </c>
       <c r="P27" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2476,7 +2440,7 @@
         <v>27</v>
       </c>
       <c r="C28">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -2488,34 +2452,34 @@
         <v>10</v>
       </c>
       <c r="G28">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H28">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="I28">
-        <v>10.27</v>
+        <v>7.9</v>
       </c>
       <c r="J28">
-        <v>24.83</v>
+        <v>11.8</v>
       </c>
       <c r="K28">
-        <v>7.03</v>
+        <v>2.22</v>
       </c>
       <c r="L28">
-        <v>70.66999816894531</v>
+        <v>17.29000091552734</v>
       </c>
       <c r="M28">
-        <v>62.66965174627988</v>
+        <v>24.27776760742223</v>
       </c>
       <c r="N28">
-        <v>-64.86486395451598</v>
+        <v>-31.75246168204091</v>
       </c>
       <c r="O28">
-        <v>-11.32</v>
+        <v>40.42</v>
       </c>
       <c r="P28" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2523,10 +2487,10 @@
         <v>43</v>
       </c>
       <c r="B29">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -2538,34 +2502,34 @@
         <v>10</v>
       </c>
       <c r="G29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H29">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I29">
-        <v>7.97</v>
+        <v>10.51</v>
       </c>
       <c r="J29">
-        <v>14.4</v>
+        <v>12.95</v>
       </c>
       <c r="K29">
-        <v>2.61</v>
+        <v>12.09</v>
       </c>
       <c r="L29">
-        <v>20.98999977111816</v>
+        <v>126.5</v>
       </c>
       <c r="M29">
-        <v>29.07988995852632</v>
+        <v>59.35253785643879</v>
       </c>
       <c r="N29">
-        <v>-31.39590206278076</v>
+        <v>-89.76284584980237</v>
       </c>
       <c r="O29">
-        <v>38.54</v>
+        <v>-53.08</v>
       </c>
       <c r="P29" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2576,7 +2540,7 @@
         <v>29</v>
       </c>
       <c r="C30">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -2591,31 +2555,31 @@
         <v>28</v>
       </c>
       <c r="H30">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I30">
-        <v>10.08</v>
+        <v>5.28</v>
       </c>
       <c r="J30">
-        <v>11.7</v>
+        <v>46.11</v>
       </c>
       <c r="K30">
-        <v>2.85</v>
+        <v>5.72</v>
       </c>
       <c r="L30">
-        <v>28.86000061035156</v>
+        <v>30.59000015258789</v>
       </c>
       <c r="M30">
-        <v>27.39092002835976</v>
+        <v>77.03477786039237</v>
       </c>
       <c r="N30">
-        <v>-59.45946031683928</v>
+        <v>50.73553373650157</v>
       </c>
       <c r="O30">
-        <v>-5.09</v>
+        <v>151.83</v>
       </c>
       <c r="P30" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2623,49 +2587,49 @@
         <v>45</v>
       </c>
       <c r="B31">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C31">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H31">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="I31">
-        <v>5.36</v>
+        <v>6.59</v>
       </c>
       <c r="J31">
-        <v>26.39</v>
+        <v>100.5</v>
       </c>
       <c r="K31">
-        <v>3.38</v>
+        <v>15.75</v>
       </c>
       <c r="L31">
-        <v>18.39999961853027</v>
+        <v>102</v>
       </c>
       <c r="M31">
-        <v>44.799101553491</v>
+        <v>188.7185404246228</v>
       </c>
       <c r="N31">
-        <v>43.4239160169501</v>
+        <v>-1.470588235294112</v>
       </c>
       <c r="O31">
-        <v>143.47</v>
+        <v>85.02</v>
       </c>
       <c r="P31" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2676,46 +2640,46 @@
         <v>31</v>
       </c>
       <c r="C32">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G32">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H32">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="I32">
-        <v>12.45</v>
+        <v>7.71</v>
       </c>
       <c r="J32">
-        <v>4.56</v>
+        <v>34.12</v>
       </c>
       <c r="K32">
-        <v>2.69</v>
+        <v>6.19</v>
       </c>
       <c r="L32">
-        <v>33.52999877929688</v>
+        <v>48.22000122070312</v>
       </c>
       <c r="M32">
-        <v>16.6130671460751</v>
+        <v>68.93520871078871</v>
       </c>
       <c r="N32">
-        <v>-86.40023809718843</v>
+        <v>-29.24098063823634</v>
       </c>
       <c r="O32">
-        <v>-50.45</v>
+        <v>42.96</v>
       </c>
       <c r="P32" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2723,10 +2687,10 @@
         <v>47</v>
       </c>
       <c r="B33">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -2738,34 +2702,34 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H33">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I33">
-        <v>7.78</v>
+        <v>6.5</v>
       </c>
       <c r="J33">
-        <v>8.15</v>
+        <v>6.76</v>
       </c>
       <c r="K33">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="L33">
-        <v>11.14999961853027</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="M33">
-        <v>16.0797621251062</v>
+        <v>12.39439389401515</v>
       </c>
       <c r="N33">
-        <v>-26.90582709567586</v>
+        <v>2.735563501231231</v>
       </c>
       <c r="O33">
-        <v>44.21</v>
+        <v>88.36</v>
       </c>
       <c r="P33" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2773,49 +2737,49 @@
         <v>48</v>
       </c>
       <c r="B34">
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>113</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>8</v>
+      </c>
+      <c r="F34">
+        <v>9</v>
+      </c>
+      <c r="G34">
         <v>32</v>
       </c>
-      <c r="C34">
-        <v>115</v>
-      </c>
-      <c r="D34">
-        <v>4</v>
-      </c>
-      <c r="E34">
-        <v>8</v>
-      </c>
-      <c r="F34">
-        <v>10</v>
-      </c>
-      <c r="G34">
-        <v>31</v>
-      </c>
       <c r="H34">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="I34">
-        <v>9.380000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="J34">
-        <v>19.34</v>
+        <v>19.74</v>
       </c>
       <c r="K34">
-        <v>3.97</v>
+        <v>5.37</v>
       </c>
       <c r="L34">
-        <v>37.93999862670898</v>
+        <v>54.20000076293945</v>
       </c>
       <c r="M34">
-        <v>41.56375223677477</v>
+        <v>48.83733715099545</v>
       </c>
       <c r="N34">
-        <v>-49.02477411692621</v>
+        <v>-63.57933630602881</v>
       </c>
       <c r="O34">
-        <v>9.550000000000001</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="P34" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2826,46 +2790,46 @@
         <v>34</v>
       </c>
       <c r="C35">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G35">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H35">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="I35">
-        <v>8.15</v>
+        <v>5.8</v>
       </c>
       <c r="J35">
-        <v>34.12</v>
+        <v>22.31</v>
       </c>
       <c r="K35">
-        <v>6.19</v>
+        <v>2.75</v>
       </c>
       <c r="L35">
-        <v>50.54000091552734</v>
+        <v>16.07999992370605</v>
       </c>
       <c r="M35">
-        <v>68.93520871078871</v>
+        <v>37.15415521849474</v>
       </c>
       <c r="N35">
-        <v>-32.48911875362204</v>
+        <v>38.74378175281781</v>
       </c>
       <c r="O35">
-        <v>36.4</v>
+        <v>131.06</v>
       </c>
       <c r="P35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2873,49 +2837,49 @@
         <v>50</v>
       </c>
       <c r="B36">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C36">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H36">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="I36">
-        <v>11.73</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J36">
-        <v>4.23</v>
+        <v>12.19</v>
       </c>
       <c r="K36">
-        <v>1.33</v>
+        <v>2.43</v>
       </c>
       <c r="L36">
-        <v>15.48999977111816</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="M36">
-        <v>11.25089996400288</v>
+        <v>25.81643371962905</v>
       </c>
       <c r="N36">
-        <v>-72.69205898965193</v>
+        <v>-42.50000206929325</v>
       </c>
       <c r="O36">
-        <v>-27.37</v>
+        <v>21.78</v>
       </c>
       <c r="P36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2926,46 +2890,46 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G37">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H37">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="I37">
-        <v>9.85</v>
+        <v>7.97</v>
       </c>
       <c r="J37">
-        <v>10.01</v>
+        <v>14.4</v>
       </c>
       <c r="K37">
-        <v>2.13</v>
+        <v>2.61</v>
       </c>
       <c r="L37">
-        <v>21.06999969482422</v>
+        <v>20.39999961853027</v>
       </c>
       <c r="M37">
-        <v>21.9027224335241</v>
+        <v>29.07988995852632</v>
       </c>
       <c r="N37">
-        <v>-52.49169366405388</v>
+        <v>-29.41176338591788</v>
       </c>
       <c r="O37">
-        <v>3.95</v>
+        <v>42.55</v>
       </c>
       <c r="P37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2973,49 +2937,49 @@
         <v>52</v>
       </c>
       <c r="B38">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C38">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="D38">
         <v>4</v>
       </c>
       <c r="E38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G38">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H38">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="I38">
-        <v>11.03</v>
+        <v>7.5</v>
       </c>
       <c r="J38">
-        <v>15.09</v>
+        <v>6.8</v>
       </c>
       <c r="K38">
-        <v>3.69</v>
+        <v>1.07</v>
       </c>
       <c r="L38">
-        <v>40.90999984741211</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="M38">
-        <v>35.39558235147432</v>
+        <v>12.79492086728167</v>
       </c>
       <c r="N38">
-        <v>-63.11415288124338</v>
+        <v>-13.92405167200533</v>
       </c>
       <c r="O38">
-        <v>-13.48</v>
+        <v>61.96</v>
       </c>
       <c r="P38" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3026,7 +2990,7 @@
         <v>38</v>
       </c>
       <c r="C39">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -3041,31 +3005,31 @@
         <v>36</v>
       </c>
       <c r="H39">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I39">
-        <v>12.69</v>
+        <v>7.97</v>
       </c>
       <c r="J39">
-        <v>2.37</v>
+        <v>8.15</v>
       </c>
       <c r="K39">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="L39">
-        <v>13.32999992370605</v>
+        <v>11.23999977111816</v>
       </c>
       <c r="M39">
-        <v>7.518277728309855</v>
+        <v>16.0797621251062</v>
       </c>
       <c r="N39">
-        <v>-82.22055503702445</v>
+        <v>-27.49110172633721</v>
       </c>
       <c r="O39">
-        <v>-43.6</v>
+        <v>43.06</v>
       </c>
       <c r="P39" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3076,46 +3040,46 @@
         <v>39</v>
       </c>
       <c r="C40">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40">
         <v>8</v>
       </c>
       <c r="F40">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>37</v>
+      </c>
+      <c r="H40">
         <v>9</v>
       </c>
-      <c r="G40">
-        <v>39</v>
-      </c>
-      <c r="H40">
-        <v>13</v>
-      </c>
       <c r="I40">
-        <v>6.14</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="J40">
-        <v>22.31</v>
+        <v>14.93</v>
       </c>
       <c r="K40">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="L40">
-        <v>16.89999961853027</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="M40">
-        <v>37.15415521849474</v>
+        <v>30.28325032092823</v>
       </c>
       <c r="N40">
-        <v>32.01183729932067</v>
+        <v>-31.82648283077019</v>
       </c>
       <c r="O40">
-        <v>119.85</v>
+        <v>38.28</v>
       </c>
       <c r="P40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3123,10 +3087,10 @@
         <v>55</v>
       </c>
       <c r="B41">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C41">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -3138,34 +3102,34 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H41">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="I41">
-        <v>11.59</v>
+        <v>9.59</v>
       </c>
       <c r="J41">
-        <v>5.87</v>
+        <v>19.34</v>
       </c>
       <c r="K41">
-        <v>1.57</v>
+        <v>3.97</v>
       </c>
       <c r="L41">
-        <v>18.14999961853027</v>
+        <v>38.11000061035156</v>
       </c>
       <c r="M41">
-        <v>14.39992187478807</v>
+        <v>41.56375223677477</v>
       </c>
       <c r="N41">
-        <v>-67.65840152411346</v>
+        <v>-49.25216559889846</v>
       </c>
       <c r="O41">
-        <v>-20.66</v>
+        <v>9.06</v>
       </c>
       <c r="P41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3173,49 +3137,49 @@
         <v>56</v>
       </c>
       <c r="B42">
+        <v>41</v>
+      </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42">
+        <v>8</v>
+      </c>
+      <c r="F42">
+        <v>10</v>
+      </c>
+      <c r="G42">
         <v>40</v>
       </c>
-      <c r="C42">
-        <v>21</v>
-      </c>
-      <c r="D42">
-        <v>4</v>
-      </c>
-      <c r="E42">
-        <v>8</v>
-      </c>
-      <c r="F42">
-        <v>10</v>
-      </c>
-      <c r="G42">
-        <v>39</v>
-      </c>
       <c r="H42">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I42">
-        <v>10.36</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J42">
-        <v>22.4</v>
+        <v>14.93</v>
       </c>
       <c r="K42">
-        <v>4.83</v>
+        <v>2.73</v>
       </c>
       <c r="L42">
-        <v>50.22000122070312</v>
+        <v>21.90999984741211</v>
       </c>
       <c r="M42">
-        <v>49.33882852277706</v>
+        <v>30.28325032092823</v>
       </c>
       <c r="N42">
-        <v>-55.39625755571343</v>
+        <v>-31.85759879517548</v>
       </c>
       <c r="O42">
-        <v>-1.75</v>
+        <v>38.22</v>
       </c>
       <c r="P42" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3226,7 +3190,7 @@
         <v>42</v>
       </c>
       <c r="C43">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -3238,34 +3202,34 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H43">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I43">
-        <v>15.23</v>
+        <v>7.98</v>
       </c>
       <c r="J43">
-        <v>0.93</v>
+        <v>8.15</v>
       </c>
       <c r="K43">
-        <v>0.9399999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="L43">
-        <v>14.36999988555908</v>
+        <v>11.25</v>
       </c>
       <c r="M43">
-        <v>4.435031003273822</v>
+        <v>16.0797621251062</v>
       </c>
       <c r="N43">
-        <v>-93.52818366453441</v>
+        <v>-27.55555555555556</v>
       </c>
       <c r="O43">
-        <v>-69.14</v>
+        <v>42.93</v>
       </c>
       <c r="P43" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3276,46 +3240,46 @@
         <v>43</v>
       </c>
       <c r="C44">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="D44">
         <v>4</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G44">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H44">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="I44">
-        <v>6.13</v>
+        <v>9.75</v>
       </c>
       <c r="J44">
-        <v>63.63</v>
+        <v>22.4</v>
       </c>
       <c r="K44">
-        <v>7.52</v>
+        <v>4.83</v>
       </c>
       <c r="L44">
-        <v>46.38999938964844</v>
+        <v>47.22000122070312</v>
       </c>
       <c r="M44">
-        <v>103.7602814182768</v>
+        <v>49.33882852277706</v>
       </c>
       <c r="N44">
-        <v>37.16318352484939</v>
+        <v>-52.56247475449249</v>
       </c>
       <c r="O44">
-        <v>123.67</v>
+        <v>4.49</v>
       </c>
       <c r="P44" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3326,7 +3290,7 @@
         <v>44</v>
       </c>
       <c r="C45">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -3341,31 +3305,28 @@
         <v>43</v>
       </c>
       <c r="H45">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="I45">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="J45">
-        <v>11.51</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="L45">
-        <v>28.68000030517578</v>
+        <v>0</v>
       </c>
       <c r="M45">
-        <v>25.4956319788312</v>
+        <v>0</v>
       </c>
       <c r="N45">
-        <v>-59.8675039137889</v>
-      </c>
-      <c r="O45">
-        <v>-11.1</v>
-      </c>
-      <c r="P45" t="s">
-        <v>176</v>
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3376,7 +3337,7 @@
         <v>45</v>
       </c>
       <c r="C46">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -3388,34 +3349,34 @@
         <v>10</v>
       </c>
       <c r="G46">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H46">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="I46">
-        <v>7.71</v>
+        <v>6.49</v>
       </c>
       <c r="J46">
-        <v>11.9</v>
+        <v>1.64</v>
       </c>
       <c r="K46">
-        <v>1.57</v>
+        <v>0.19</v>
       </c>
       <c r="L46">
-        <v>12.48999977111816</v>
+        <v>1.25</v>
       </c>
       <c r="M46">
-        <v>20.50286565336661</v>
+        <v>2.647829299633947</v>
       </c>
       <c r="N46">
-        <v>-4.723777277262064</v>
+        <v>31.19999999999998</v>
       </c>
       <c r="O46">
-        <v>64.15000000000001</v>
+        <v>111.83</v>
       </c>
       <c r="P46" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3426,7 +3387,7 @@
         <v>45</v>
       </c>
       <c r="C47">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -3438,34 +3399,34 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H47">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="I47">
-        <v>11</v>
+        <v>8.98</v>
       </c>
       <c r="J47">
-        <v>8.25</v>
+        <v>14.93</v>
       </c>
       <c r="K47">
-        <v>1.69</v>
+        <v>2.73</v>
       </c>
       <c r="L47">
-        <v>18.54999923706055</v>
+        <v>23.79999923706055</v>
       </c>
       <c r="M47">
-        <v>17.71175457147033</v>
+        <v>30.28325032092823</v>
       </c>
       <c r="N47">
-        <v>-55.52560463982368</v>
+        <v>-37.26890555209971</v>
       </c>
       <c r="O47">
-        <v>-4.52</v>
+        <v>27.24</v>
       </c>
       <c r="P47" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3476,7 +3437,7 @@
         <v>47</v>
       </c>
       <c r="C48">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="D48">
         <v>4</v>
@@ -3488,34 +3449,34 @@
         <v>10</v>
       </c>
       <c r="G48">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H48">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="I48">
-        <v>7.27</v>
+        <v>10.32</v>
       </c>
       <c r="J48">
-        <v>16.43</v>
+        <v>8.25</v>
       </c>
       <c r="K48">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="L48">
-        <v>14.68000030517578</v>
+        <v>17.61000061035156</v>
       </c>
       <c r="M48">
-        <v>27.05469460186161</v>
+        <v>17.71175457147033</v>
       </c>
       <c r="N48">
-        <v>11.92097859975667</v>
+        <v>-53.15162002237263</v>
       </c>
       <c r="O48">
-        <v>84.3</v>
+        <v>0.58</v>
       </c>
       <c r="P48" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3523,10 +3484,10 @@
         <v>63</v>
       </c>
       <c r="B49">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C49">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D49">
         <v>4</v>
@@ -3538,34 +3499,34 @@
         <v>10</v>
       </c>
       <c r="G49">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H49">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="I49">
-        <v>9.109999999999999</v>
+        <v>5.33</v>
       </c>
       <c r="J49">
-        <v>22.15</v>
+        <v>9.15</v>
       </c>
       <c r="K49">
-        <v>3.57</v>
+        <v>0.85</v>
       </c>
       <c r="L49">
-        <v>32.65999984741211</v>
+        <v>4.519999980926514</v>
       </c>
       <c r="M49">
-        <v>42.1805494274316</v>
+        <v>13.22852032541811</v>
       </c>
       <c r="N49">
-        <v>-32.18003642533665</v>
+        <v>102.4336291728131</v>
       </c>
       <c r="O49">
-        <v>29.15</v>
+        <v>192.67</v>
       </c>
       <c r="P49" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3576,46 +3537,46 @@
         <v>49</v>
       </c>
       <c r="C50">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G50">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H50">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="I50">
-        <v>4.92</v>
+        <v>6.29</v>
       </c>
       <c r="J50">
-        <v>6.7</v>
+        <v>31.76</v>
       </c>
       <c r="K50">
-        <v>0.59</v>
+        <v>3.27</v>
       </c>
       <c r="L50">
-        <v>3.039999961853027</v>
+        <v>20.69000053405762</v>
       </c>
       <c r="M50">
-        <v>9.430933145770888</v>
+        <v>48.33985932954295</v>
       </c>
       <c r="N50">
-        <v>120.3947396076948</v>
+        <v>53.50410430255987</v>
       </c>
       <c r="O50">
-        <v>210.23</v>
+        <v>133.64</v>
       </c>
       <c r="P50" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3626,46 +3587,46 @@
         <v>50</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G51">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I51">
-        <v>12.62</v>
+        <v>6.02</v>
       </c>
       <c r="J51">
-        <v>1.68</v>
+        <v>29.45</v>
       </c>
       <c r="K51">
-        <v>0.4</v>
+        <v>2.79</v>
       </c>
       <c r="L51">
-        <v>5.110000133514404</v>
+        <v>16.88999938964844</v>
       </c>
       <c r="M51">
-        <v>3.888444419044716</v>
+        <v>42.99678767070861</v>
       </c>
       <c r="N51">
-        <v>-67.12328853023767</v>
+        <v>74.36353501616672</v>
       </c>
       <c r="O51">
-        <v>-23.91</v>
+        <v>154.57</v>
       </c>
       <c r="P51" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3673,49 +3634,49 @@
         <v>66</v>
       </c>
       <c r="B52">
+        <v>51</v>
+      </c>
+      <c r="C52">
+        <v>51</v>
+      </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52">
+        <v>8</v>
+      </c>
+      <c r="F52">
+        <v>10</v>
+      </c>
+      <c r="G52">
         <v>50</v>
       </c>
-      <c r="C52">
-        <v>115</v>
-      </c>
-      <c r="D52">
-        <v>4</v>
-      </c>
-      <c r="E52">
-        <v>8</v>
-      </c>
-      <c r="F52">
-        <v>10</v>
-      </c>
-      <c r="G52">
-        <v>48</v>
-      </c>
       <c r="H52">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="I52">
-        <v>5.19</v>
+        <v>10.98</v>
       </c>
       <c r="J52">
-        <v>26.49</v>
+        <v>11.51</v>
       </c>
       <c r="K52">
-        <v>2.27</v>
+        <v>2.51</v>
       </c>
       <c r="L52">
-        <v>11.56999969482422</v>
+        <v>27.54000091552734</v>
       </c>
       <c r="M52">
-        <v>36.78283227267851</v>
+        <v>25.4956319788312</v>
       </c>
       <c r="N52">
-        <v>128.9541979145442</v>
+        <v>-58.20624685052012</v>
       </c>
       <c r="O52">
-        <v>217.92</v>
+        <v>-7.42</v>
       </c>
       <c r="P52" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3726,7 +3687,7 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="D53">
         <v>4</v>
@@ -3741,31 +3702,31 @@
         <v>51</v>
       </c>
       <c r="H53">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="I53">
-        <v>6.82</v>
+        <v>13.72</v>
       </c>
       <c r="J53">
-        <v>31.76</v>
+        <v>3.75</v>
       </c>
       <c r="K53">
-        <v>3.27</v>
+        <v>0.91</v>
       </c>
       <c r="L53">
-        <v>22.09000015258789</v>
+        <v>12.44999980926514</v>
       </c>
       <c r="M53">
-        <v>48.33985932954295</v>
+        <v>8.762491084160942</v>
       </c>
       <c r="N53">
-        <v>43.77546301772772</v>
+        <v>-69.87951761084128</v>
       </c>
       <c r="O53">
-        <v>118.83</v>
+        <v>-29.62</v>
       </c>
       <c r="P53" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3773,49 +3734,49 @@
         <v>68</v>
       </c>
       <c r="B54">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C54">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54">
         <v>8</v>
       </c>
       <c r="F54">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G54">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H54">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="I54">
-        <v>8.93</v>
+        <v>7.72</v>
       </c>
       <c r="J54">
-        <v>47.19</v>
+        <v>16.43</v>
       </c>
       <c r="K54">
-        <v>6.38</v>
+        <v>1.98</v>
       </c>
       <c r="L54">
-        <v>57.29999923706055</v>
+        <v>15.22999954223633</v>
       </c>
       <c r="M54">
-        <v>82.30506971019464</v>
+        <v>27.05469460186161</v>
       </c>
       <c r="N54">
-        <v>-17.64397796103563</v>
+        <v>7.87918905995888</v>
       </c>
       <c r="O54">
-        <v>43.64</v>
+        <v>77.64</v>
       </c>
       <c r="P54" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3826,7 +3787,7 @@
         <v>54</v>
       </c>
       <c r="C55">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="D55">
         <v>4</v>
@@ -3838,34 +3799,34 @@
         <v>10</v>
       </c>
       <c r="G55">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H55">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="I55">
-        <v>9.220000000000001</v>
+        <v>6.11</v>
       </c>
       <c r="J55">
-        <v>9.390000000000001</v>
+        <v>26.49</v>
       </c>
       <c r="K55">
-        <v>1.39</v>
+        <v>2.27</v>
       </c>
       <c r="L55">
-        <v>13.10000038146973</v>
+        <v>13.93000030517578</v>
       </c>
       <c r="M55">
-        <v>17.13686815027764</v>
+        <v>36.78283227267851</v>
       </c>
       <c r="N55">
-        <v>-28.32061277431421</v>
+        <v>90.16510710453802</v>
       </c>
       <c r="O55">
-        <v>30.82</v>
+        <v>164.05</v>
       </c>
       <c r="P55" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3873,10 +3834,10 @@
         <v>70</v>
       </c>
       <c r="B56">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C56">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -3888,34 +3849,34 @@
         <v>10</v>
       </c>
       <c r="G56">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H56">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="I56">
-        <v>14.22</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="J56">
-        <v>3.75</v>
+        <v>12.63</v>
       </c>
       <c r="K56">
-        <v>0.91</v>
+        <v>1.58</v>
       </c>
       <c r="L56">
-        <v>13.42000007629395</v>
+        <v>12.5</v>
       </c>
       <c r="M56">
-        <v>8.762491084160942</v>
+        <v>21.18953751264997</v>
       </c>
       <c r="N56">
-        <v>-72.0566320515581</v>
+        <v>1.039999999999996</v>
       </c>
       <c r="O56">
-        <v>-34.71</v>
+        <v>69.52</v>
       </c>
       <c r="P56" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3926,7 +3887,7 @@
         <v>56</v>
       </c>
       <c r="C57">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -3938,34 +3899,34 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H57">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="I57">
-        <v>8.140000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="J57">
-        <v>29.02</v>
+        <v>3.5</v>
       </c>
       <c r="K57">
-        <v>3.56</v>
+        <v>0.49</v>
       </c>
       <c r="L57">
-        <v>29.13999938964844</v>
+        <v>4.5</v>
       </c>
       <c r="M57">
-        <v>48.21308950897048</v>
+        <v>6.211883772254597</v>
       </c>
       <c r="N57">
-        <v>-0.4118029930057832</v>
+        <v>-22.22222222222222</v>
       </c>
       <c r="O57">
-        <v>65.45</v>
+        <v>38.04</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3976,7 +3937,7 @@
         <v>57</v>
       </c>
       <c r="C58">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="D58">
         <v>4</v>
@@ -3988,34 +3949,34 @@
         <v>10</v>
       </c>
       <c r="G58">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H58">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="I58">
-        <v>7.52</v>
+        <v>25.99</v>
       </c>
       <c r="J58">
-        <v>22.7</v>
+        <v>5.29</v>
       </c>
       <c r="K58">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="L58">
-        <v>16.92000007629395</v>
+        <v>40.02000045776367</v>
       </c>
       <c r="M58">
-        <v>33.74866664032817</v>
+        <v>13.49474897876948</v>
       </c>
       <c r="N58">
-        <v>34.16075589623797</v>
+        <v>-86.78160934659917</v>
       </c>
       <c r="O58">
-        <v>99.45999999999999</v>
+        <v>-66.28</v>
       </c>
       <c r="P58" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4026,46 +3987,46 @@
         <v>58</v>
       </c>
       <c r="C59">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E59">
         <v>8</v>
       </c>
       <c r="F59">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G59">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H59">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="I59">
-        <v>8.49</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="J59">
-        <v>16.43</v>
+        <v>47.19</v>
       </c>
       <c r="K59">
-        <v>1.98</v>
+        <v>6.38</v>
       </c>
       <c r="L59">
-        <v>17.07999992370605</v>
+        <v>61.88000106811523</v>
       </c>
       <c r="M59">
-        <v>27.05469460186161</v>
+        <v>82.30506971019464</v>
       </c>
       <c r="N59">
-        <v>-3.805620179212599</v>
+        <v>-23.73949711465748</v>
       </c>
       <c r="O59">
-        <v>58.4</v>
+        <v>33.01</v>
       </c>
       <c r="P59" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4073,10 +4034,10 @@
         <v>74</v>
       </c>
       <c r="B60">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C60">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D60">
         <v>4</v>
@@ -4088,34 +4049,34 @@
         <v>10</v>
       </c>
       <c r="G60">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H60">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="I60">
-        <v>24.16</v>
+        <v>6.49</v>
       </c>
       <c r="J60">
-        <v>5.29</v>
+        <v>60.78</v>
       </c>
       <c r="K60">
-        <v>1.53</v>
+        <v>4.5</v>
       </c>
       <c r="L60">
-        <v>36.86000061035156</v>
+        <v>29.20000076293945</v>
       </c>
       <c r="M60">
-        <v>13.49474897876948</v>
+        <v>78.44727528729089</v>
       </c>
       <c r="N60">
-        <v>-85.6483995865307</v>
+        <v>108.1506794929327</v>
       </c>
       <c r="O60">
-        <v>-63.39</v>
+        <v>168.66</v>
       </c>
       <c r="P60" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4126,46 +4087,46 @@
         <v>60</v>
       </c>
       <c r="C61">
+        <v>113</v>
+      </c>
+      <c r="D61">
         <v>3</v>
       </c>
-      <c r="D61">
-        <v>4</v>
-      </c>
       <c r="E61">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F61">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G61">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H61">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="I61">
-        <v>10.8</v>
+        <v>5.77</v>
       </c>
       <c r="J61">
-        <v>11.21</v>
+        <v>13.38</v>
       </c>
       <c r="K61">
-        <v>1.63</v>
+        <v>0.76</v>
       </c>
       <c r="L61">
-        <v>18.01000022888184</v>
+        <v>4.300000190734863</v>
       </c>
       <c r="M61">
-        <v>20.27626074995091</v>
+        <v>15.12607021007109</v>
       </c>
       <c r="N61">
-        <v>-37.7568025678144</v>
+        <v>211.1627768954443</v>
       </c>
       <c r="O61">
-        <v>12.58</v>
+        <v>251.77</v>
       </c>
       <c r="P61" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4176,7 +4137,7 @@
         <v>61</v>
       </c>
       <c r="C62">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -4191,31 +4152,31 @@
         <v>60</v>
       </c>
       <c r="H62">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I62">
-        <v>9.710000000000001</v>
+        <v>7.42</v>
       </c>
       <c r="J62">
-        <v>26</v>
+        <v>10.79</v>
       </c>
       <c r="K62">
-        <v>3.15</v>
+        <v>0.95</v>
       </c>
       <c r="L62">
-        <v>30.70000076293945</v>
+        <v>6.840000152587891</v>
       </c>
       <c r="M62">
-        <v>42.92726406376256</v>
+        <v>15.18671294256924</v>
       </c>
       <c r="N62">
-        <v>-15.3094483587545</v>
+        <v>57.74853449261459</v>
       </c>
       <c r="O62">
-        <v>39.83</v>
+        <v>122.03</v>
       </c>
       <c r="P62" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4223,10 +4184,10 @@
         <v>77</v>
       </c>
       <c r="B63">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C63">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D63">
         <v>4</v>
@@ -4238,13 +4199,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H63">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I63">
-        <v>13.85</v>
+        <v>14.29</v>
       </c>
       <c r="J63">
         <v>17.43</v>
@@ -4253,19 +4214,19 @@
         <v>3.29</v>
       </c>
       <c r="L63">
-        <v>46.43000030517578</v>
+        <v>47.29999923706055</v>
       </c>
       <c r="M63">
         <v>35.92013015009829</v>
       </c>
       <c r="N63">
-        <v>-62.45961687392668</v>
+        <v>-63.15010511386387</v>
       </c>
       <c r="O63">
-        <v>-22.64</v>
+        <v>-24.06</v>
       </c>
       <c r="P63" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4276,7 +4237,7 @@
         <v>63</v>
       </c>
       <c r="C64">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="D64">
         <v>4</v>
@@ -4288,34 +4249,34 @@
         <v>10</v>
       </c>
       <c r="G64">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H64">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="I64">
-        <v>11.19</v>
+        <v>6.48</v>
       </c>
       <c r="J64">
-        <v>4.54</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="K64">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="L64">
-        <v>7.03000020980835</v>
+        <v>3.549999952316284</v>
       </c>
       <c r="M64">
-        <v>8.022125653466169</v>
+        <v>10.67553277359027</v>
       </c>
       <c r="N64">
-        <v>-35.41963208385497</v>
+        <v>164.2253556617597</v>
       </c>
       <c r="O64">
-        <v>14.11</v>
+        <v>200.72</v>
       </c>
       <c r="P64" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4326,46 +4287,46 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F65">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G65">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H65">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="I65">
-        <v>8.44</v>
+        <v>9.06</v>
       </c>
       <c r="J65">
-        <v>40.39</v>
+        <v>16.43</v>
       </c>
       <c r="K65">
-        <v>3.85</v>
+        <v>1.98</v>
       </c>
       <c r="L65">
-        <v>33.34999847412109</v>
+        <v>17.79000091552734</v>
       </c>
       <c r="M65">
-        <v>59.15051774921332</v>
+        <v>27.05469460186161</v>
       </c>
       <c r="N65">
-        <v>21.10945081854143</v>
+        <v>-7.644748991217409</v>
       </c>
       <c r="O65">
-        <v>77.36</v>
+        <v>52.08</v>
       </c>
       <c r="P65" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4376,46 +4337,43 @@
         <v>65</v>
       </c>
       <c r="C66">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E66">
         <v>8</v>
       </c>
       <c r="F66">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G66">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H66">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="I66">
-        <v>11.26</v>
+        <v>0</v>
       </c>
       <c r="J66">
-        <v>11.68</v>
+        <v>0</v>
       </c>
       <c r="K66">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="L66">
-        <v>17.14999961853027</v>
+        <v>0</v>
       </c>
       <c r="M66">
-        <v>19.92054216129672</v>
+        <v>0</v>
       </c>
       <c r="N66">
-        <v>-31.89504221691081</v>
-      </c>
-      <c r="O66">
-        <v>16.15</v>
-      </c>
-      <c r="P66" t="s">
-        <v>196</v>
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4423,49 +4381,49 @@
         <v>81</v>
       </c>
       <c r="B67">
+        <v>67</v>
+      </c>
+      <c r="C67">
+        <v>8</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+      <c r="E67">
+        <v>8</v>
+      </c>
+      <c r="F67">
+        <v>10</v>
+      </c>
+      <c r="G67">
         <v>66</v>
       </c>
-      <c r="C67">
-        <v>115</v>
-      </c>
-      <c r="D67">
-        <v>4</v>
-      </c>
-      <c r="E67">
-        <v>8</v>
-      </c>
-      <c r="F67">
-        <v>10</v>
-      </c>
-      <c r="G67">
-        <v>65</v>
-      </c>
       <c r="H67">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="I67">
-        <v>9.140000000000001</v>
+        <v>12.43</v>
       </c>
       <c r="J67">
-        <v>32.61</v>
+        <v>4.14</v>
       </c>
       <c r="K67">
-        <v>3.14</v>
+        <v>0.68</v>
       </c>
       <c r="L67">
-        <v>29.03000068664551</v>
+        <v>7.869999885559082</v>
       </c>
       <c r="M67">
-        <v>47.99892186289188</v>
+        <v>7.958768748996292</v>
       </c>
       <c r="N67">
-        <v>12.33206761514607</v>
+        <v>-47.39517077253559</v>
       </c>
       <c r="O67">
-        <v>65.34</v>
+        <v>1.13</v>
       </c>
       <c r="P67" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4476,7 +4434,7 @@
         <v>67</v>
       </c>
       <c r="C68">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -4488,34 +4446,34 @@
         <v>10</v>
       </c>
       <c r="G68">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H68">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I68">
-        <v>13.5</v>
+        <v>9.65</v>
       </c>
       <c r="J68">
-        <v>5.87</v>
+        <v>8.67</v>
       </c>
       <c r="K68">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="L68">
-        <v>12.67000007629395</v>
+        <v>10.14000034332275</v>
       </c>
       <c r="M68">
-        <v>11.14228432593604</v>
+        <v>14.31183950441033</v>
       </c>
       <c r="N68">
-        <v>-53.67008709823929</v>
+        <v>-14.49704431509963</v>
       </c>
       <c r="O68">
-        <v>-12.06</v>
+        <v>41.14</v>
       </c>
       <c r="P68" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4523,49 +4481,49 @@
         <v>83</v>
       </c>
       <c r="B69">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C69">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E69">
         <v>8</v>
       </c>
       <c r="F69">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G69">
         <v>68</v>
       </c>
       <c r="H69">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="I69">
-        <v>12.32</v>
+        <v>10.37</v>
       </c>
       <c r="J69">
-        <v>9.720000000000001</v>
+        <v>4.23</v>
       </c>
       <c r="K69">
-        <v>1.29</v>
+        <v>0.55</v>
       </c>
       <c r="L69">
-        <v>16.18000030517578</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="M69">
-        <v>16.79651749619546</v>
+        <v>7.235070835866088</v>
       </c>
       <c r="N69">
-        <v>-39.92583549648826</v>
+        <v>-26.17801071693589</v>
       </c>
       <c r="O69">
-        <v>3.81</v>
+        <v>26.27</v>
       </c>
       <c r="P69" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4573,49 +4531,49 @@
         <v>84</v>
       </c>
       <c r="B70">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>113</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E70">
         <v>8</v>
       </c>
       <c r="F70">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G70">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="I70">
-        <v>14.47</v>
+        <v>7.66</v>
       </c>
       <c r="J70">
-        <v>4.14</v>
+        <v>7.67</v>
       </c>
       <c r="K70">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="L70">
-        <v>10.26000022888184</v>
+        <v>3.930000066757202</v>
       </c>
       <c r="M70">
-        <v>7.958768748996292</v>
+        <v>9.473067085163073</v>
       </c>
       <c r="N70">
-        <v>-59.6491237071718</v>
+        <v>95.16539108684594</v>
       </c>
       <c r="O70">
-        <v>-22.43</v>
+        <v>141.04</v>
       </c>
       <c r="P70" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4626,46 +4584,46 @@
         <v>70</v>
       </c>
       <c r="C71">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="D71">
         <v>4</v>
       </c>
       <c r="E71">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F71">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G71">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H71">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="I71">
-        <v>10.38</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="J71">
-        <v>7.61</v>
+        <v>16.31</v>
       </c>
       <c r="K71">
-        <v>0.82</v>
+        <v>1.57</v>
       </c>
       <c r="L71">
-        <v>8.460000038146973</v>
+        <v>13.5</v>
       </c>
       <c r="M71">
-        <v>11.84924048198871</v>
+        <v>24.00314041953677</v>
       </c>
       <c r="N71">
-        <v>-10.04728172948273</v>
+        <v>20.8148148148148</v>
       </c>
       <c r="O71">
-        <v>40.06</v>
+        <v>77.8</v>
       </c>
       <c r="P71" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4673,10 +4631,10 @@
         <v>86</v>
       </c>
       <c r="B72">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C72">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D72">
         <v>4</v>
@@ -4688,34 +4646,34 @@
         <v>10</v>
       </c>
       <c r="G72">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H72">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I72">
-        <v>8.18</v>
+        <v>13.07</v>
       </c>
       <c r="J72">
-        <v>19.5</v>
+        <v>5.87</v>
       </c>
       <c r="K72">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L72">
-        <v>9.439999580383301</v>
+        <v>12.06999969482422</v>
       </c>
       <c r="M72">
-        <v>22.26628617439379</v>
+        <v>11.14228432593604</v>
       </c>
       <c r="N72">
-        <v>106.5678057922988</v>
+        <v>-51.36702445388514</v>
       </c>
       <c r="O72">
-        <v>135.87</v>
+        <v>-7.69</v>
       </c>
       <c r="P72" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4726,46 +4684,46 @@
         <v>72</v>
       </c>
       <c r="C73">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D73">
         <v>4</v>
       </c>
       <c r="E73">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F73">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G73">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H73">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I73">
-        <v>12.47</v>
+        <v>11.08</v>
       </c>
       <c r="J73">
-        <v>22.3</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K73">
-        <v>2.91</v>
+        <v>1.29</v>
       </c>
       <c r="L73">
-        <v>36.77999877929688</v>
+        <v>14.47000026702881</v>
       </c>
       <c r="M73">
-        <v>38.21115674773534</v>
+        <v>16.79651749619546</v>
       </c>
       <c r="N73">
-        <v>-39.36922039118591</v>
+        <v>-32.82653890374908</v>
       </c>
       <c r="O73">
-        <v>3.89</v>
+        <v>16.08</v>
       </c>
       <c r="P73" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4773,10 +4731,10 @@
         <v>88</v>
       </c>
       <c r="B74">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C74">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="D74">
         <v>4</v>
@@ -4788,34 +4746,34 @@
         <v>10</v>
       </c>
       <c r="G74">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H74">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="I74">
-        <v>11.37</v>
+        <v>24.11</v>
       </c>
       <c r="J74">
-        <v>8.58</v>
+        <v>5.81</v>
       </c>
       <c r="K74">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="L74">
-        <v>11.76000022888184</v>
+        <v>27.07999992370605</v>
       </c>
       <c r="M74">
-        <v>14.03249799572407</v>
+        <v>11.99155953160389</v>
       </c>
       <c r="N74">
-        <v>-27.04081774651629</v>
+        <v>-78.54505163822442</v>
       </c>
       <c r="O74">
-        <v>19.32</v>
+        <v>-55.72</v>
       </c>
       <c r="P74" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4826,46 +4784,46 @@
         <v>74</v>
       </c>
       <c r="C75">
+        <v>97</v>
+      </c>
+      <c r="D75">
+        <v>4</v>
+      </c>
+      <c r="E75">
+        <v>8</v>
+      </c>
+      <c r="F75">
+        <v>10</v>
+      </c>
+      <c r="G75">
         <v>73</v>
       </c>
-      <c r="D75">
-        <v>4</v>
-      </c>
-      <c r="E75">
-        <v>8</v>
-      </c>
-      <c r="F75">
-        <v>10</v>
-      </c>
-      <c r="G75">
-        <v>74</v>
-      </c>
       <c r="H75">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="I75">
-        <v>14.41</v>
+        <v>7.99</v>
       </c>
       <c r="J75">
-        <v>7.28</v>
+        <v>13.11</v>
       </c>
       <c r="K75">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="L75">
-        <v>14.72999954223633</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="M75">
-        <v>12.98899534221181</v>
+        <v>17.00222044322447</v>
       </c>
       <c r="N75">
-        <v>-50.57705209612831</v>
+        <v>61.45320424591785</v>
       </c>
       <c r="O75">
-        <v>-11.82</v>
+        <v>109.39</v>
       </c>
       <c r="P75" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4876,7 +4834,7 @@
         <v>75</v>
       </c>
       <c r="C76">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="D76">
         <v>4</v>
@@ -4888,34 +4846,34 @@
         <v>10</v>
       </c>
       <c r="G76">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H76">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="I76">
-        <v>18.68</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="J76">
-        <v>5.52</v>
+        <v>53.43</v>
       </c>
       <c r="K76">
-        <v>0.96</v>
+        <v>4.88</v>
       </c>
       <c r="L76">
-        <v>17.98999977111816</v>
+        <v>42.02000045776367</v>
       </c>
       <c r="M76">
-        <v>10.91934063943423</v>
+        <v>76.59382481636493</v>
       </c>
       <c r="N76">
-        <v>-69.31628643563398</v>
+        <v>27.15373493083388</v>
       </c>
       <c r="O76">
-        <v>-39.3</v>
+        <v>82.28</v>
       </c>
       <c r="P76" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4926,7 +4884,7 @@
         <v>76</v>
       </c>
       <c r="C77">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="D77">
         <v>4</v>
@@ -4941,31 +4899,31 @@
         <v>76</v>
       </c>
       <c r="H77">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="I77">
-        <v>12.14</v>
+        <v>10.67</v>
       </c>
       <c r="J77">
-        <v>8.58</v>
+        <v>8.67</v>
       </c>
       <c r="K77">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="L77">
-        <v>12.60000038146973</v>
+        <v>11.25</v>
       </c>
       <c r="M77">
-        <v>14.03249799572407</v>
+        <v>14.31183950441033</v>
       </c>
       <c r="N77">
-        <v>-31.90476396637072</v>
+        <v>-22.93333333333334</v>
       </c>
       <c r="O77">
-        <v>11.37</v>
+        <v>27.22</v>
       </c>
       <c r="P77" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4973,7 +4931,7 @@
         <v>92</v>
       </c>
       <c r="B78">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C78">
         <v>55</v>
@@ -4988,13 +4946,13 @@
         <v>10</v>
       </c>
       <c r="G78">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H78">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I78">
-        <v>25.36</v>
+        <v>27.57</v>
       </c>
       <c r="J78">
         <v>3.88</v>
@@ -5003,19 +4961,19 @@
         <v>0.71</v>
       </c>
       <c r="L78">
-        <v>17.47999954223633</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="M78">
         <v>7.872928298924105</v>
       </c>
       <c r="N78">
-        <v>-77.80320308004077</v>
+        <v>-80.05141466424487</v>
       </c>
       <c r="O78">
-        <v>-54.96</v>
+        <v>-59.52</v>
       </c>
       <c r="P78" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5026,7 +4984,7 @@
         <v>78</v>
       </c>
       <c r="C79">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D79">
         <v>4</v>
@@ -5041,31 +4999,31 @@
         <v>78</v>
       </c>
       <c r="H79">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I79">
-        <v>10.02</v>
+        <v>12.51</v>
       </c>
       <c r="J79">
-        <v>27.27</v>
+        <v>22.3</v>
       </c>
       <c r="K79">
-        <v>1.62</v>
+        <v>2.91</v>
       </c>
       <c r="L79">
-        <v>16.67000007629395</v>
+        <v>36.56999969482422</v>
       </c>
       <c r="M79">
-        <v>31.52763073876627</v>
+        <v>38.21115674773534</v>
       </c>
       <c r="N79">
-        <v>63.58728179479789</v>
+        <v>-39.02105500111301</v>
       </c>
       <c r="O79">
-        <v>89.13</v>
+        <v>4.49</v>
       </c>
       <c r="P79" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5073,10 +5031,10 @@
         <v>94</v>
       </c>
       <c r="B80">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C80">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D80">
         <v>4</v>
@@ -5088,34 +5046,34 @@
         <v>10</v>
       </c>
       <c r="G80">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H80">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I80">
-        <v>21.93</v>
+        <v>14.64</v>
       </c>
       <c r="J80">
-        <v>11.08</v>
+        <v>7.28</v>
       </c>
       <c r="K80">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="L80">
-        <v>39.63999938964844</v>
+        <v>15.25</v>
       </c>
       <c r="M80">
-        <v>21.18348413269167</v>
+        <v>12.98899534221181</v>
       </c>
       <c r="N80">
-        <v>-72.04843549292934</v>
+        <v>-52.26229508196722</v>
       </c>
       <c r="O80">
-        <v>-46.56</v>
+        <v>-14.83</v>
       </c>
       <c r="P80" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5123,10 +5081,10 @@
         <v>95</v>
       </c>
       <c r="B81">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C81">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="D81">
         <v>4</v>
@@ -5138,34 +5096,34 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H81">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="I81">
-        <v>30.06</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J81">
-        <v>8.17</v>
+        <v>16.31</v>
       </c>
       <c r="K81">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="L81">
-        <v>43.47999954223633</v>
+        <v>14.96000003814697</v>
       </c>
       <c r="M81">
-        <v>16.2132584633688</v>
+        <v>24.00314041953677</v>
       </c>
       <c r="N81">
-        <v>-81.20975141210917</v>
+        <v>9.024063893119116</v>
       </c>
       <c r="O81">
-        <v>-62.71</v>
+        <v>60.45</v>
       </c>
       <c r="P81" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5176,46 +5134,46 @@
         <v>81</v>
       </c>
       <c r="C82">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E82">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G82">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H82">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="I82">
-        <v>11.92</v>
+        <v>10.42</v>
       </c>
       <c r="J82">
-        <v>11.1</v>
+        <v>4</v>
       </c>
       <c r="K82">
-        <v>1.09</v>
+        <v>0.45</v>
       </c>
       <c r="L82">
-        <v>13.86999988555908</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="M82">
-        <v>16.49931816773045</v>
+        <v>6.363961030678928</v>
       </c>
       <c r="N82">
-        <v>-19.97116011834363</v>
+        <v>-14.89361356749894</v>
       </c>
       <c r="O82">
-        <v>18.96</v>
+        <v>35.4</v>
       </c>
       <c r="P82" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5223,49 +5181,49 @@
         <v>97</v>
       </c>
       <c r="B83">
+        <v>82</v>
+      </c>
+      <c r="C83">
+        <v>89</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83">
+        <v>8</v>
+      </c>
+      <c r="F83">
+        <v>10</v>
+      </c>
+      <c r="G83">
         <v>81</v>
       </c>
-      <c r="C83">
-        <v>29</v>
-      </c>
-      <c r="D83">
-        <v>4</v>
-      </c>
-      <c r="E83">
-        <v>2</v>
-      </c>
-      <c r="F83">
-        <v>3</v>
-      </c>
-      <c r="G83">
-        <v>86</v>
-      </c>
       <c r="H83">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="I83">
-        <v>10.03</v>
+        <v>13.6</v>
       </c>
       <c r="J83">
-        <v>5.89</v>
+        <v>111.44</v>
       </c>
       <c r="K83">
-        <v>0.35</v>
+        <v>14.38</v>
       </c>
       <c r="L83">
-        <v>3.660000085830688</v>
+        <v>197.8999938964844</v>
       </c>
       <c r="M83">
-        <v>6.810561650847894</v>
+        <v>189.8852600914563</v>
       </c>
       <c r="N83">
-        <v>60.92895797468763</v>
+        <v>-43.68872994594888</v>
       </c>
       <c r="O83">
-        <v>86.08</v>
+        <v>-4.05</v>
       </c>
       <c r="P83" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5276,7 +5234,7 @@
         <v>83</v>
       </c>
       <c r="C84">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D84">
         <v>4</v>
@@ -5288,34 +5246,34 @@
         <v>10</v>
       </c>
       <c r="G84">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H84">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="I84">
-        <v>11.32</v>
+        <v>10.58</v>
       </c>
       <c r="J84">
-        <v>20.15</v>
+        <v>32.34</v>
       </c>
       <c r="K84">
-        <v>1.54</v>
+        <v>3.37</v>
       </c>
       <c r="L84">
-        <v>17.59000015258789</v>
+        <v>35.65000152587891</v>
       </c>
       <c r="M84">
-        <v>26.4234271055062</v>
+        <v>49.51949616060325</v>
       </c>
       <c r="N84">
-        <v>14.55372271293285</v>
+        <v>-9.28471636523247</v>
       </c>
       <c r="O84">
-        <v>50.22</v>
+        <v>38.9</v>
       </c>
       <c r="P84" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5326,7 +5284,7 @@
         <v>84</v>
       </c>
       <c r="C85">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D85">
         <v>4</v>
@@ -5338,34 +5296,34 @@
         <v>10</v>
       </c>
       <c r="G85">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H85">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I85">
-        <v>17.22</v>
+        <v>23.04</v>
       </c>
       <c r="J85">
-        <v>11.23</v>
+        <v>11.08</v>
       </c>
       <c r="K85">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="L85">
-        <v>24.03000068664551</v>
+        <v>42.11000061035156</v>
       </c>
       <c r="M85">
-        <v>18.74081775163507</v>
+        <v>21.18348413269167</v>
       </c>
       <c r="N85">
-        <v>-53.26675123134312</v>
+        <v>-73.6879604858607</v>
       </c>
       <c r="O85">
-        <v>-22.01</v>
+        <v>-49.69</v>
       </c>
       <c r="P85" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5373,10 +5331,10 @@
         <v>100</v>
       </c>
       <c r="B86">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C86">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D86">
         <v>4</v>
@@ -5391,31 +5349,31 @@
         <v>84</v>
       </c>
       <c r="H86">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="I86">
-        <v>14.26</v>
+        <v>29.15</v>
       </c>
       <c r="J86">
-        <v>9.83</v>
+        <v>8.17</v>
       </c>
       <c r="K86">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="L86">
-        <v>15.65999984741211</v>
+        <v>41.5</v>
       </c>
       <c r="M86">
-        <v>15.66857523835527</v>
+        <v>16.2132584633688</v>
       </c>
       <c r="N86">
-        <v>-37.22860730663127</v>
+        <v>-80.31325301204819</v>
       </c>
       <c r="O86">
-        <v>0.05</v>
+        <v>-60.93</v>
       </c>
       <c r="P86" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5426,46 +5384,43 @@
         <v>86</v>
       </c>
       <c r="C87">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E87">
         <v>8</v>
       </c>
       <c r="F87">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G87">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H87">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I87">
-        <v>12.17</v>
+        <v>0</v>
       </c>
       <c r="J87">
-        <v>8.74</v>
+        <v>0</v>
       </c>
       <c r="K87">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="L87">
-        <v>6.840000152587891</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>10.49399828473399</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>27.7777749272893</v>
-      </c>
-      <c r="O87">
-        <v>53.42</v>
-      </c>
-      <c r="P87" t="s">
-        <v>216</v>
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5476,46 +5431,46 @@
         <v>87</v>
       </c>
       <c r="C88">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="D88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88">
         <v>8</v>
       </c>
       <c r="F88">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G88">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H88">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="I88">
-        <v>16.44</v>
+        <v>13</v>
       </c>
       <c r="J88">
-        <v>2.41</v>
+        <v>8.58</v>
       </c>
       <c r="K88">
-        <v>0.24</v>
+        <v>1.02</v>
       </c>
       <c r="L88">
-        <v>3.930000066757202</v>
+        <v>13.48999977111816</v>
       </c>
       <c r="M88">
-        <v>3.607492203733779</v>
+        <v>14.03249799572407</v>
       </c>
       <c r="N88">
-        <v>-38.67684582538477</v>
+        <v>-36.39733027742803</v>
       </c>
       <c r="O88">
-        <v>-8.210000000000001</v>
+        <v>4.02</v>
       </c>
       <c r="P88" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5526,46 +5481,46 @@
         <v>88</v>
       </c>
       <c r="C89">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="D89">
         <v>4</v>
       </c>
       <c r="E89">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F89">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G89">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H89">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="I89">
-        <v>26.51</v>
+        <v>9.32</v>
       </c>
       <c r="J89">
-        <v>24.57</v>
+        <v>19.5</v>
       </c>
       <c r="K89">
-        <v>2.89</v>
+        <v>1.13</v>
       </c>
       <c r="L89">
-        <v>75.98999786376953</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="M89">
-        <v>39.97079246149619</v>
+        <v>22.26628617439379</v>
       </c>
       <c r="N89">
-        <v>-67.66679735397851</v>
+        <v>93.06929963860466</v>
       </c>
       <c r="O89">
-        <v>-47.4</v>
+        <v>120.46</v>
       </c>
       <c r="P89" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5573,49 +5528,49 @@
         <v>104</v>
       </c>
       <c r="B90">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C90">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E90">
         <v>8</v>
       </c>
       <c r="F90">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G90">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H90">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="I90">
-        <v>17.71</v>
+        <v>10.95</v>
       </c>
       <c r="J90">
-        <v>23.54</v>
+        <v>4.35</v>
       </c>
       <c r="K90">
-        <v>2.15</v>
+        <v>0.39</v>
       </c>
       <c r="L90">
-        <v>38.40000152587891</v>
+        <v>4.190000057220459</v>
       </c>
       <c r="M90">
-        <v>33.74533301065497</v>
+        <v>6.178288597985691</v>
       </c>
       <c r="N90">
-        <v>-38.69791910259251</v>
+        <v>3.818614333997905</v>
       </c>
       <c r="O90">
-        <v>-12.12</v>
+        <v>47.45</v>
       </c>
       <c r="P90" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5626,46 +5581,46 @@
         <v>90</v>
       </c>
       <c r="C91">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="D91">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E91">
         <v>8</v>
       </c>
       <c r="F91">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G91">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H91">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="I91">
-        <v>16.55</v>
+        <v>10.2</v>
       </c>
       <c r="J91">
-        <v>24.01</v>
+        <v>8.74</v>
       </c>
       <c r="K91">
-        <v>1.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L91">
-        <v>28.70999908447266</v>
+        <v>5.630000114440918</v>
       </c>
       <c r="M91">
-        <v>30.57105248433557</v>
+        <v>10.49399828473399</v>
       </c>
       <c r="N91">
-        <v>-16.37059991065821</v>
+        <v>55.23978370057134</v>
       </c>
       <c r="O91">
-        <v>6.48</v>
+        <v>86.39</v>
       </c>
       <c r="P91" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5673,49 +5628,49 @@
         <v>106</v>
       </c>
       <c r="B92">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C92">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E92">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F92">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G92">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H92">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I92">
-        <v>13.06</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="J92">
-        <v>6.7</v>
+        <v>27.27</v>
       </c>
       <c r="K92">
-        <v>0.29</v>
+        <v>1.62</v>
       </c>
       <c r="L92">
-        <v>3.779999971389771</v>
+        <v>15.22000026702881</v>
       </c>
       <c r="M92">
-        <v>6.611921052160257</v>
+        <v>31.52763073876627</v>
       </c>
       <c r="N92">
-        <v>77.24867859024481</v>
+        <v>79.17213877502478</v>
       </c>
       <c r="O92">
-        <v>74.92</v>
+        <v>107.15</v>
       </c>
       <c r="P92" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5726,7 +5681,7 @@
         <v>92</v>
       </c>
       <c r="C93">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="D93">
         <v>4</v>
@@ -5738,34 +5693,34 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H93">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="I93">
-        <v>33.9</v>
+        <v>10.84</v>
       </c>
       <c r="J93">
-        <v>5.97</v>
+        <v>3.56</v>
       </c>
       <c r="K93">
-        <v>0.67</v>
+        <v>0.26</v>
       </c>
       <c r="L93">
-        <v>22.71999931335449</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="M93">
-        <v>9.486714394351713</v>
+        <v>4.563551248753541</v>
       </c>
       <c r="N93">
-        <v>-73.72359075516822</v>
+        <v>26.69039403889057</v>
       </c>
       <c r="O93">
-        <v>-58.25</v>
+        <v>62.4</v>
       </c>
       <c r="P93" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5776,7 +5731,7 @@
         <v>93</v>
       </c>
       <c r="C94">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D94">
         <v>4</v>
@@ -5788,34 +5743,31 @@
         <v>10</v>
       </c>
       <c r="G94">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H94">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="I94">
-        <v>18.57</v>
+        <v>0</v>
       </c>
       <c r="J94">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="K94">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="L94">
-        <v>33.65999984741211</v>
+        <v>0</v>
       </c>
       <c r="M94">
-        <v>29.3137766246521</v>
+        <v>0</v>
       </c>
       <c r="N94">
-        <v>-37.31431938309341</v>
-      </c>
-      <c r="O94">
-        <v>-12.91</v>
-      </c>
-      <c r="P94" t="s">
-        <v>223</v>
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5826,7 +5778,7 @@
         <v>94</v>
       </c>
       <c r="C95">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D95">
         <v>4</v>
@@ -5838,34 +5790,34 @@
         <v>10</v>
       </c>
       <c r="G95">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H95">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="I95">
-        <v>17.83</v>
+        <v>11.3</v>
       </c>
       <c r="J95">
-        <v>6.88</v>
+        <v>27.27</v>
       </c>
       <c r="K95">
-        <v>0.49</v>
+        <v>1.62</v>
       </c>
       <c r="L95">
-        <v>8.960000038146973</v>
+        <v>18</v>
       </c>
       <c r="M95">
-        <v>8.709305368397644</v>
+        <v>31.52763073876627</v>
       </c>
       <c r="N95">
-        <v>-23.21428604119894</v>
+        <v>51.49999999999999</v>
       </c>
       <c r="O95">
-        <v>-2.8</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="P95" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5876,10 +5828,10 @@
         <v>95</v>
       </c>
       <c r="C96">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96">
         <v>8</v>
@@ -5888,34 +5840,34 @@
         <v>9</v>
       </c>
       <c r="G96">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H96">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I96">
-        <v>16.18</v>
+        <v>17.35</v>
       </c>
       <c r="J96">
-        <v>51.42</v>
+        <v>23.54</v>
       </c>
       <c r="K96">
-        <v>2.87</v>
+        <v>2.15</v>
       </c>
       <c r="L96">
-        <v>47.79999923706055</v>
+        <v>37.79000091552734</v>
       </c>
       <c r="M96">
-        <v>57.62331559360326</v>
+        <v>33.74533301065497</v>
       </c>
       <c r="N96">
-        <v>7.573223474306623</v>
+        <v>-37.70838997167696</v>
       </c>
       <c r="O96">
-        <v>20.55</v>
+        <v>-10.7</v>
       </c>
       <c r="P96" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5926,46 +5878,46 @@
         <v>96</v>
       </c>
       <c r="C97">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D97">
         <v>4</v>
       </c>
       <c r="E97">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F97">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G97">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H97">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I97">
-        <v>28.76</v>
+        <v>28.59</v>
       </c>
       <c r="J97">
-        <v>9.44</v>
+        <v>24.57</v>
       </c>
       <c r="K97">
-        <v>0.89</v>
+        <v>2.89</v>
       </c>
       <c r="L97">
-        <v>25.81999969482422</v>
+        <v>84.73999786376953</v>
       </c>
       <c r="M97">
-        <v>13.7490363298669</v>
+        <v>39.97079246149619</v>
       </c>
       <c r="N97">
-        <v>-63.43919399080278</v>
+        <v>-71.00542763819814</v>
       </c>
       <c r="O97">
-        <v>-46.75</v>
+        <v>-52.83</v>
       </c>
       <c r="P97" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5976,46 +5928,46 @@
         <v>97</v>
       </c>
       <c r="C98">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="D98">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E98">
         <v>8</v>
       </c>
       <c r="F98">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G98">
         <v>96</v>
       </c>
       <c r="H98">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="I98">
-        <v>17.09</v>
+        <v>35.05</v>
       </c>
       <c r="J98">
-        <v>51.42</v>
+        <v>5.97</v>
       </c>
       <c r="K98">
-        <v>2.87</v>
+        <v>0.67</v>
       </c>
       <c r="L98">
-        <v>50.77000045776367</v>
+        <v>23.71999931335449</v>
       </c>
       <c r="M98">
-        <v>57.62331559360326</v>
+        <v>9.486714394351713</v>
       </c>
       <c r="N98">
-        <v>1.280282718880565</v>
+        <v>-74.83136520733854</v>
       </c>
       <c r="O98">
-        <v>13.5</v>
+        <v>-60.01</v>
       </c>
       <c r="P98" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6026,46 +5978,46 @@
         <v>98</v>
       </c>
       <c r="C99">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E99">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F99">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G99">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H99">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I99">
-        <v>15.09</v>
+        <v>18.27</v>
       </c>
       <c r="J99">
-        <v>19.37</v>
+        <v>21.1</v>
       </c>
       <c r="K99">
-        <v>0.3</v>
+        <v>1.81</v>
       </c>
       <c r="L99">
-        <v>4.519999980926514</v>
+        <v>33.13000106811523</v>
       </c>
       <c r="M99">
-        <v>11.43448730813935</v>
+        <v>29.3137766246521</v>
       </c>
       <c r="N99">
-        <v>328.539824817201</v>
+        <v>-36.31150220424554</v>
       </c>
       <c r="O99">
-        <v>152.98</v>
+        <v>-11.52</v>
       </c>
       <c r="P99" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6076,46 +6028,46 @@
         <v>99</v>
       </c>
       <c r="C100">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="D100">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E100">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G100">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H100">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="I100">
-        <v>19.45</v>
+        <v>28.34</v>
       </c>
       <c r="J100">
-        <v>18.93</v>
+        <v>9.44</v>
       </c>
       <c r="K100">
-        <v>1.17</v>
+        <v>0.89</v>
       </c>
       <c r="L100">
-        <v>23.06999969482422</v>
+        <v>25.52000045776367</v>
       </c>
       <c r="M100">
-        <v>22.32335660244668</v>
+        <v>13.7490363298669</v>
       </c>
       <c r="N100">
-        <v>-17.94538252964534</v>
+        <v>-63.00940505223161</v>
       </c>
       <c r="O100">
-        <v>-3.24</v>
+        <v>-46.12</v>
       </c>
       <c r="P100" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6126,7 +6078,7 @@
         <v>100</v>
       </c>
       <c r="C101">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -6138,34 +6090,34 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H101">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="I101">
-        <v>18.15</v>
+        <v>12.24</v>
       </c>
       <c r="J101">
-        <v>24.77</v>
+        <v>17.83</v>
       </c>
       <c r="K101">
-        <v>1.36</v>
+        <v>0.38</v>
       </c>
       <c r="L101">
-        <v>24.59000015258789</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="M101">
-        <v>27.53110967614636</v>
+        <v>12.34692269352975</v>
       </c>
       <c r="N101">
-        <v>0.7320042549620043</v>
+        <v>276.1603557165132</v>
       </c>
       <c r="O101">
-        <v>11.96</v>
+        <v>160.48</v>
       </c>
       <c r="P101" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6173,49 +6125,49 @@
         <v>116</v>
       </c>
       <c r="B102">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C102">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D102">
         <v>4</v>
       </c>
       <c r="E102">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F102">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G102">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H102">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="I102">
-        <v>26.18</v>
+        <v>17.7</v>
       </c>
       <c r="J102">
-        <v>6.05</v>
+        <v>6.88</v>
       </c>
       <c r="K102">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="L102">
-        <v>10.01000022888184</v>
+        <v>8.510000228881836</v>
       </c>
       <c r="M102">
-        <v>7.192183256842112</v>
+        <v>8.709305368397644</v>
       </c>
       <c r="N102">
-        <v>-39.56044094240931</v>
+        <v>-19.15393871964688</v>
       </c>
       <c r="O102">
-        <v>-28.15</v>
+        <v>2.34</v>
       </c>
       <c r="P102" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6226,46 +6178,46 @@
         <v>102</v>
       </c>
       <c r="C103">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="D103">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E103">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F103">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G103">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H103">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="I103">
-        <v>18.9</v>
+        <v>16.74</v>
       </c>
       <c r="J103">
-        <v>15</v>
+        <v>26.67</v>
       </c>
       <c r="K103">
-        <v>0.52</v>
+        <v>1.46</v>
       </c>
       <c r="L103">
-        <v>10.35999965667725</v>
+        <v>24.29999923706055</v>
       </c>
       <c r="M103">
-        <v>13.24764129949177</v>
+        <v>29.59914694716725</v>
       </c>
       <c r="N103">
-        <v>44.78764958580064</v>
+        <v>9.753089865636323</v>
       </c>
       <c r="O103">
-        <v>27.87</v>
+        <v>21.81</v>
       </c>
       <c r="P103" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6276,46 +6228,46 @@
         <v>103</v>
       </c>
       <c r="C104">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E104">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F104">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G104">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H104">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="I104">
-        <v>42.59</v>
+        <v>16.18</v>
       </c>
       <c r="J104">
-        <v>7.21</v>
+        <v>15</v>
       </c>
       <c r="K104">
-        <v>0.35</v>
+        <v>0.52</v>
       </c>
       <c r="L104">
-        <v>14.85000038146973</v>
+        <v>8.340000152587891</v>
       </c>
       <c r="M104">
-        <v>7.535167549563845</v>
+        <v>13.24764129949177</v>
       </c>
       <c r="N104">
-        <v>-51.4478126950296</v>
+        <v>79.85611181728241</v>
       </c>
       <c r="O104">
-        <v>-49.26</v>
+        <v>58.84</v>
       </c>
       <c r="P104" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6326,7 +6278,7 @@
         <v>104</v>
       </c>
       <c r="C105">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="D105">
         <v>3</v>
@@ -6338,31 +6290,34 @@
         <v>9</v>
       </c>
       <c r="G105">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H105">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="I105">
-        <v>0</v>
+        <v>32.95</v>
       </c>
       <c r="J105">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="K105">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="L105">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M105">
-        <v>0</v>
+        <v>13.49374855257056</v>
       </c>
       <c r="N105">
-        <v>0</v>
-      </c>
-      <c r="P105">
-        <v>0</v>
+        <v>-63.88888888888889</v>
+      </c>
+      <c r="O105">
+        <v>-50.02</v>
+      </c>
+      <c r="P105" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6373,46 +6328,46 @@
         <v>105</v>
       </c>
       <c r="C106">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="D106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F106">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G106">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H106">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="I106">
-        <v>79.56999999999999</v>
+        <v>19.13</v>
       </c>
       <c r="J106">
-        <v>4.87</v>
+        <v>51.42</v>
       </c>
       <c r="K106">
-        <v>0.05</v>
+        <v>2.87</v>
       </c>
       <c r="L106">
-        <v>4.340000152587891</v>
+        <v>54.11000061035156</v>
       </c>
       <c r="M106">
-        <v>2.340672980149085</v>
+        <v>57.62331559360326</v>
       </c>
       <c r="N106">
-        <v>12.21197762161546</v>
+        <v>-4.97135571984626</v>
       </c>
       <c r="O106">
-        <v>-46.07</v>
+        <v>6.49</v>
       </c>
       <c r="P106" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6420,49 +6375,49 @@
         <v>121</v>
       </c>
       <c r="B107">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C107">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="D107">
         <v>2</v>
       </c>
       <c r="E107">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F107">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G107">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H107">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="I107">
-        <v>122.06</v>
+        <v>20.23</v>
       </c>
       <c r="J107">
-        <v>14.59</v>
+        <v>51.42</v>
       </c>
       <c r="K107">
-        <v>0.46</v>
+        <v>2.87</v>
       </c>
       <c r="L107">
-        <v>56.20000076293945</v>
+        <v>57.22999954223633</v>
       </c>
       <c r="M107">
-        <v>12.28847020584743</v>
+        <v>57.62331559360326</v>
       </c>
       <c r="N107">
-        <v>-74.03914625990321</v>
+        <v>-10.15201745362323</v>
       </c>
       <c r="O107">
-        <v>-78.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P107" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6473,46 +6428,46 @@
         <v>107</v>
       </c>
       <c r="C108">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E108">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F108">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G108">
         <v>106</v>
       </c>
       <c r="H108">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="I108">
-        <v>104.31</v>
+        <v>20.21</v>
       </c>
       <c r="J108">
-        <v>8.640000000000001</v>
+        <v>34.18</v>
       </c>
       <c r="K108">
-        <v>0.12</v>
+        <v>1.81</v>
       </c>
       <c r="L108">
-        <v>12.22000026702881</v>
+        <v>39.15000152587891</v>
       </c>
       <c r="M108">
-        <v>4.829906831399546</v>
+        <v>37.30925488400968</v>
       </c>
       <c r="N108">
-        <v>-29.29623722421779</v>
+        <v>-12.69476713198502</v>
       </c>
       <c r="O108">
-        <v>-60.48</v>
+        <v>-4.7</v>
       </c>
       <c r="P108" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6520,43 +6475,49 @@
         <v>123</v>
       </c>
       <c r="B109">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C109">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="D109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F109">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G109">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H109">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="I109">
-        <v>-36.22</v>
+        <v>20.06</v>
       </c>
       <c r="J109">
-        <v>3.51</v>
+        <v>19.45</v>
       </c>
       <c r="K109">
-        <v>-1.62</v>
+        <v>0.21</v>
       </c>
       <c r="L109">
-        <v>57.56000137329102</v>
+        <v>4.260000228881836</v>
+      </c>
+      <c r="M109">
+        <v>9.58651396494054</v>
       </c>
       <c r="N109">
-        <v>-93.90201543388304</v>
+        <v>356.5727454222516</v>
+      </c>
+      <c r="O109">
+        <v>125.04</v>
       </c>
       <c r="P109" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6564,43 +6525,46 @@
         <v>124</v>
       </c>
       <c r="B110">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C110">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="D110">
         <v>3</v>
       </c>
       <c r="E110">
+        <v>8</v>
+      </c>
+      <c r="F110">
+        <v>9</v>
+      </c>
+      <c r="G110">
+        <v>109</v>
+      </c>
+      <c r="H110">
+        <v>82</v>
+      </c>
+      <c r="I110">
         <v>0</v>
       </c>
-      <c r="F110">
+      <c r="J110">
         <v>0</v>
       </c>
-      <c r="G110">
-        <v>118</v>
-      </c>
-      <c r="H110">
-        <v>32</v>
-      </c>
-      <c r="I110">
-        <v>0.22</v>
-      </c>
-      <c r="J110">
-        <v>-8.609999999999999</v>
-      </c>
       <c r="K110">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="L110">
-        <v>1.360000014305115</v>
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
       </c>
       <c r="N110">
-        <v>-733.0882286350002</v>
-      </c>
-      <c r="P110" t="s">
-        <v>237</v>
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6608,13 +6572,13 @@
         <v>125</v>
       </c>
       <c r="B111">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C111">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="D111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E111">
         <v>6</v>
@@ -6623,28 +6587,34 @@
         <v>6</v>
       </c>
       <c r="G111">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H111">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="I111">
-        <v>-7.8</v>
+        <v>44.95</v>
       </c>
       <c r="J111">
-        <v>1.44</v>
+        <v>7.21</v>
       </c>
       <c r="K111">
-        <v>-0.85</v>
+        <v>0.35</v>
       </c>
       <c r="L111">
-        <v>6.519999980926514</v>
+        <v>15.36999988555908</v>
+      </c>
+      <c r="M111">
+        <v>7.535167549563845</v>
       </c>
       <c r="N111">
-        <v>-77.91411036483821</v>
+        <v>-53.09043556484232</v>
+      </c>
+      <c r="O111">
+        <v>-50.97</v>
       </c>
       <c r="P111" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6652,43 +6622,49 @@
         <v>126</v>
       </c>
       <c r="B112">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C112">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F112">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G112">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H112">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="I112">
-        <v>-13.63</v>
+        <v>44.47</v>
       </c>
       <c r="J112">
-        <v>3.85</v>
+        <v>7.61</v>
       </c>
       <c r="K112">
-        <v>-0.44</v>
+        <v>0.17</v>
       </c>
       <c r="L112">
-        <v>6.050000190734863</v>
+        <v>7.349999904632568</v>
+      </c>
+      <c r="M112">
+        <v>5.395206205512445</v>
       </c>
       <c r="N112">
-        <v>-36.36363836986326</v>
+        <v>3.537416309401031</v>
+      </c>
+      <c r="O112">
+        <v>-26.6</v>
       </c>
       <c r="P112" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6696,43 +6672,49 @@
         <v>127</v>
       </c>
       <c r="B113">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C113">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G113">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H113">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="I113">
-        <v>-10.6</v>
+        <v>39.84</v>
       </c>
       <c r="J113">
-        <v>0.89</v>
+        <v>2.41</v>
       </c>
       <c r="K113">
-        <v>-0.19</v>
+        <v>0.03</v>
       </c>
       <c r="L113">
-        <v>2.019999980926514</v>
+        <v>1.080000042915344</v>
+      </c>
+      <c r="M113">
+        <v>1.275441100168879</v>
       </c>
       <c r="N113">
-        <v>-55.94059364338293</v>
+        <v>123.1481392810378</v>
+      </c>
+      <c r="O113">
+        <v>18.1</v>
       </c>
       <c r="P113" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6740,43 +6722,43 @@
         <v>128</v>
       </c>
       <c r="B114">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C114">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D114">
+        <v>2</v>
+      </c>
+      <c r="E114">
         <v>0</v>
       </c>
-      <c r="E114">
-        <v>4</v>
-      </c>
       <c r="F114">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G114">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H114">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="I114">
-        <v>-4.6</v>
+        <v>-10.36</v>
       </c>
       <c r="J114">
-        <v>10.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K114">
-        <v>-1.7</v>
+        <v>-0.12</v>
       </c>
       <c r="L114">
-        <v>7.900000095367432</v>
+        <v>1.210000038146973</v>
       </c>
       <c r="N114">
-        <v>32.78480852362706</v>
+        <v>-53.71900972353691</v>
       </c>
       <c r="P114" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6784,43 +6766,43 @@
         <v>129</v>
       </c>
       <c r="B115">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C115">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="D115">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E115">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F115">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="H115">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="I115">
-        <v>-143.69</v>
+        <v>-233.33</v>
       </c>
       <c r="J115">
-        <v>10.06</v>
+        <v>1.6</v>
       </c>
       <c r="K115">
-        <v>-0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="L115">
-        <v>16</v>
+        <v>3.619999885559082</v>
       </c>
       <c r="N115">
-        <v>-37.125</v>
+        <v>-55.80110357509329</v>
       </c>
       <c r="P115" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6828,43 +6810,43 @@
         <v>130</v>
       </c>
       <c r="B116">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C116">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="D116">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E116">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F116">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G116">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H116">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="I116">
-        <v>-110.46</v>
+        <v>-1.47</v>
       </c>
       <c r="J116">
-        <v>3.64</v>
+        <v>6.07</v>
       </c>
       <c r="K116">
-        <v>-0.03</v>
+        <v>-0.97</v>
       </c>
       <c r="L116">
-        <v>3.869999885559082</v>
+        <v>1.409999966621399</v>
       </c>
       <c r="N116">
-        <v>-5.943149673397341</v>
+        <v>330.4964640917516</v>
       </c>
       <c r="P116" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6872,43 +6854,43 @@
         <v>131</v>
       </c>
       <c r="B117">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C117">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="D117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F117">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="H117">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I117">
-        <v>-52.27</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="J117">
-        <v>23.88</v>
+        <v>6.95</v>
       </c>
       <c r="K117">
-        <v>-0.28</v>
+        <v>-0.57</v>
       </c>
       <c r="L117">
-        <v>14.59000015258789</v>
+        <v>5.599999904632568</v>
       </c>
       <c r="N117">
-        <v>63.67374743148513</v>
+        <v>24.10714497067494</v>
       </c>
       <c r="P117" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6916,43 +6898,43 @@
         <v>132</v>
       </c>
       <c r="B118">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C118">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E118">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F118">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G118">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H118">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I118">
-        <v>-16.04</v>
+        <v>-149.46</v>
       </c>
       <c r="J118">
-        <v>12.08</v>
+        <v>10.06</v>
       </c>
       <c r="K118">
-        <v>-0.67</v>
+        <v>-0.11</v>
       </c>
       <c r="L118">
-        <v>11.02000045776367</v>
+        <v>16.60000038146973</v>
       </c>
       <c r="N118">
-        <v>9.618870219642783</v>
+        <v>-39.39759175409543</v>
       </c>
       <c r="P118" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6960,43 +6942,43 @@
         <v>133</v>
       </c>
       <c r="B119">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C119">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="E119">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F119">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G119">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H119">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I119">
-        <v>-41.13</v>
+        <v>-3.59</v>
       </c>
       <c r="J119">
-        <v>96.64</v>
+        <v>1.76</v>
       </c>
       <c r="K119">
-        <v>-0.95</v>
+        <v>-1.04</v>
       </c>
       <c r="L119">
-        <v>39.34999847412109</v>
+        <v>3.759999990463257</v>
       </c>
       <c r="N119">
-        <v>145.5908608574819</v>
+        <v>-53.19148924297852</v>
       </c>
       <c r="P119" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7004,43 +6986,131 @@
         <v>134</v>
       </c>
       <c r="B120">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C120">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120">
+        <v>2</v>
+      </c>
+      <c r="F120">
+        <v>2</v>
+      </c>
+      <c r="G120">
+        <v>116</v>
+      </c>
+      <c r="H120">
+        <v>102</v>
+      </c>
+      <c r="I120">
+        <v>-34.58</v>
+      </c>
+      <c r="J120">
+        <v>96.64</v>
+      </c>
+      <c r="K120">
+        <v>-0.95</v>
+      </c>
+      <c r="L120">
+        <v>32.36000061035156</v>
+      </c>
+      <c r="N120">
+        <v>198.6402910298032</v>
+      </c>
+      <c r="P120" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
+      <c r="A121" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B121">
+        <v>122</v>
+      </c>
+      <c r="C121">
+        <v>102</v>
+      </c>
+      <c r="D121">
         <v>0</v>
       </c>
-      <c r="E120">
+      <c r="E121">
         <v>6</v>
       </c>
-      <c r="F120">
+      <c r="F121">
         <v>6</v>
       </c>
-      <c r="G120">
-        <v>112</v>
-      </c>
-      <c r="H120">
-        <v>104</v>
-      </c>
-      <c r="I120">
-        <v>-1.85</v>
-      </c>
-      <c r="J120">
-        <v>1.76</v>
-      </c>
-      <c r="K120">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="L120">
-        <v>1.279999971389771</v>
-      </c>
-      <c r="N120">
-        <v>37.50000307336456</v>
-      </c>
-      <c r="P120" t="s">
-        <v>247</v>
+      <c r="G121">
+        <v>114</v>
+      </c>
+      <c r="H121">
+        <v>101</v>
+      </c>
+      <c r="I121">
+        <v>-24.56</v>
+      </c>
+      <c r="J121">
+        <v>26.48</v>
+      </c>
+      <c r="K121">
+        <v>-0.86</v>
+      </c>
+      <c r="L121">
+        <v>21.04000091552734</v>
+      </c>
+      <c r="N121">
+        <v>25.85550783155139</v>
+      </c>
+      <c r="P121" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
+      <c r="A122" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B122">
+        <v>122</v>
+      </c>
+      <c r="C122">
+        <v>103</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>2</v>
+      </c>
+      <c r="F122">
+        <v>2</v>
+      </c>
+      <c r="G122">
+        <v>116</v>
+      </c>
+      <c r="H122">
+        <v>103</v>
+      </c>
+      <c r="I122">
+        <v>-2.68</v>
+      </c>
+      <c r="J122">
+        <v>3.27</v>
+      </c>
+      <c r="K122">
+        <v>-0.46</v>
+      </c>
+      <c r="L122">
+        <v>1.240000009536743</v>
+      </c>
+      <c r="N122">
+        <v>163.7096753911843</v>
+      </c>
+      <c r="P122" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
